--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="375" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="998" uniqueCount="49">
   <si>
     <t>Subject</t>
   </si>
@@ -149,6 +149,21 @@
   </si>
   <si>
     <t>Standing</t>
+  </si>
+  <si>
+    <t>test5</t>
+  </si>
+  <si>
+    <t>test6</t>
+  </si>
+  <si>
+    <t>test7</t>
+  </si>
+  <si>
+    <t>test8</t>
+  </si>
+  <si>
+    <t>test9</t>
   </si>
 </sst>
 </file>
@@ -197,17 +212,17 @@
   <dimension ref="A1:K89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="true"/>
-    <col min="2" max="2" width="9.88671875" customWidth="true"/>
+    <col min="1" max="1" width="7.21875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
     <col min="3" max="3" width="5.33203125" customWidth="true"/>
-    <col min="4" max="4" width="14.5546875" customWidth="true"/>
-    <col min="5" max="5" width="13.5546875" customWidth="true"/>
+    <col min="4" max="4" width="12.5546875" customWidth="true"/>
+    <col min="5" max="5" width="12.5546875" customWidth="true"/>
     <col min="6" max="6" width="12.5546875" customWidth="true"/>
-    <col min="7" max="7" width="14.5546875" customWidth="true"/>
+    <col min="7" max="7" width="12.5546875" customWidth="true"/>
     <col min="8" max="8" width="6" customWidth="true"/>
-    <col min="9" max="9" width="7" customWidth="true"/>
-    <col min="10" max="10" width="6" customWidth="true"/>
-    <col min="11" max="11" width="5" customWidth="true"/>
+    <col min="9" max="9" width="6" customWidth="true"/>
+    <col min="10" max="10" width="5" customWidth="true"/>
+    <col min="11" max="11" width="6" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -256,28 +271,28 @@
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>0.92626920147720249</v>
+        <v>0.80866814635637485</v>
       </c>
       <c r="E2" s="0">
-        <v>0.90766766838818802</v>
+        <v>0.74834807537670878</v>
       </c>
       <c r="F2" s="0">
-        <v>0.95169811320754716</v>
+        <v>0.95133333333333336</v>
       </c>
       <c r="G2" s="0">
-        <v>0.86753121667641298</v>
+        <v>0.6167521466028929</v>
       </c>
       <c r="H2" s="0">
-        <v>25220</v>
+        <v>21405</v>
       </c>
       <c r="I2" s="0">
-        <v>39240</v>
+        <v>39440</v>
       </c>
       <c r="J2" s="0">
-        <v>1280</v>
+        <v>1095</v>
       </c>
       <c r="K2" s="0">
-        <v>3851</v>
+        <v>13301</v>
       </c>
     </row>
     <row r="3">
@@ -291,19 +306,19 @@
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>0.93517839950568316</v>
+        <v>0.85830863491979104</v>
       </c>
       <c r="E3" s="0">
-        <v>0.91829526724746879</v>
+        <v>0.82337933433839727</v>
       </c>
       <c r="F3" s="0">
-        <v>0.96940726577437863</v>
+        <v>0.96881091617933723</v>
       </c>
       <c r="G3" s="0">
-        <v>0.87230308661092182</v>
+        <v>0.71591138255884301</v>
       </c>
       <c r="H3" s="0">
-        <v>25350</v>
+        <v>24850</v>
       </c>
       <c r="I3" s="0">
         <v>39730</v>
@@ -312,7 +327,7 @@
         <v>800</v>
       </c>
       <c r="K3" s="0">
-        <v>3711</v>
+        <v>9861</v>
       </c>
     </row>
     <row r="4">
@@ -396,25 +411,25 @@
         <v>8</v>
       </c>
       <c r="D6" s="0">
-        <v>0.78753407915765727</v>
+        <v>0.78784745072232143</v>
       </c>
       <c r="E6" s="0">
-        <v>0.73349056603773588</v>
+        <v>0.7339882121807465</v>
       </c>
       <c r="F6" s="0">
-        <v>0.73754940711462447</v>
+        <v>0.73833992094861656</v>
       </c>
       <c r="G6" s="0">
-        <v>0.72947615324472248</v>
+        <v>0.72968750000000004</v>
       </c>
       <c r="H6" s="0">
-        <v>9330</v>
+        <v>9340</v>
       </c>
       <c r="I6" s="0">
         <v>15801</v>
       </c>
       <c r="J6" s="0">
-        <v>3320</v>
+        <v>3310</v>
       </c>
       <c r="K6" s="0">
         <v>3460</v>
@@ -457,72 +472,72 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <v>0.97560061387441033</v>
+        <v>0.82189900189232312</v>
       </c>
       <c r="E8" s="0">
-        <v>0</v>
+        <v>0.78571428571428581</v>
       </c>
       <c r="F8" s="0">
-        <v>0</v>
+        <v>0.90256410256410258</v>
       </c>
       <c r="G8" s="0">
-        <v>1</v>
+        <v>0.69565217391304346</v>
       </c>
       <c r="H8" s="0">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="I8" s="0">
-        <v>413841</v>
+        <v>13351</v>
       </c>
       <c r="J8" s="0">
-        <v>10350</v>
+        <v>950</v>
       </c>
       <c r="K8" s="0">
-        <v>0</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <v>0.99233835701370376</v>
+        <v>0.82189900189232312</v>
       </c>
       <c r="E9" s="0">
-        <v>0</v>
+        <v>0.78666666666666663</v>
       </c>
       <c r="F9" s="0">
-        <v>0</v>
+        <v>0.89847715736040612</v>
       </c>
       <c r="G9" s="0">
-        <v>1</v>
+        <v>0.69960474308300391</v>
       </c>
       <c r="H9" s="0">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="I9" s="0">
-        <v>420941</v>
+        <v>13301</v>
       </c>
       <c r="J9" s="0">
-        <v>3250</v>
+        <v>1000</v>
       </c>
       <c r="K9" s="0">
-        <v>0</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="10">
@@ -530,34 +545,34 @@
         <v>1</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="0">
-        <v>0.99200915522501365</v>
+        <v>0.82577077494129236</v>
       </c>
       <c r="E10" s="0">
-        <v>0</v>
+        <v>0.708860759493671</v>
       </c>
       <c r="F10" s="0">
-        <v>0</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="G10" s="0">
-        <v>1</v>
+        <v>0.67469879518072284</v>
       </c>
       <c r="H10" s="0">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="I10" s="0">
-        <v>347601</v>
+        <v>8101</v>
       </c>
       <c r="J10" s="0">
-        <v>2800</v>
+        <v>950</v>
       </c>
       <c r="K10" s="0">
-        <v>0</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="11">
@@ -565,244 +580,244 @@
         <v>1</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="0">
-        <v>0.99315070447858311</v>
+        <v>0.9090977956215438</v>
       </c>
       <c r="E11" s="0">
-        <v>0</v>
+        <v>0.84615384615384603</v>
       </c>
       <c r="F11" s="0">
-        <v>0</v>
+        <v>0.90410958904109584</v>
       </c>
       <c r="G11" s="0">
-        <v>1</v>
+        <v>0.79518072289156627</v>
       </c>
       <c r="H11" s="0">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="I11" s="0">
-        <v>348001</v>
+        <v>8701</v>
       </c>
       <c r="J11" s="0">
-        <v>2400</v>
+        <v>350</v>
       </c>
       <c r="K11" s="0">
-        <v>0</v>
+        <v>850</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="0">
-        <v>0.83194675540765395</v>
+        <v>0.5808504191495808</v>
       </c>
       <c r="E12" s="0">
-        <v>0.90826521344232514</v>
+        <v>0.27826086956521745</v>
       </c>
       <c r="F12" s="0">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="0">
-        <v>0.83194675540765395</v>
+        <v>0.19277108433734941</v>
       </c>
       <c r="H12" s="0">
-        <v>5500</v>
+        <v>800</v>
       </c>
       <c r="I12" s="0">
-        <v>0</v>
+        <v>4951</v>
       </c>
       <c r="J12" s="0">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K12" s="0">
-        <v>1111</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <v>0.82438360308576619</v>
+        <v>0.78790021209978789</v>
       </c>
       <c r="E13" s="0">
-        <v>0.90373932509742139</v>
+        <v>0.73749999999999993</v>
       </c>
       <c r="F13" s="0">
-        <v>1</v>
+        <v>0.76623376623376627</v>
       </c>
       <c r="G13" s="0">
-        <v>0.82438360308576619</v>
+        <v>0.71084337349397586</v>
       </c>
       <c r="H13" s="0">
-        <v>5450</v>
+        <v>2950</v>
       </c>
       <c r="I13" s="0">
-        <v>0</v>
+        <v>4851</v>
       </c>
       <c r="J13" s="0">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K13" s="0">
-        <v>1161</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>0.93938898872733212</v>
+        <v>0.78023588015529999</v>
       </c>
       <c r="E14" s="0">
-        <v>0.96874736753432733</v>
+        <v>0.62500000000000011</v>
       </c>
       <c r="F14" s="0">
-        <v>1</v>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G14" s="0">
-        <v>0.93938898872733212</v>
+        <v>0.60240963855421692</v>
       </c>
       <c r="H14" s="0">
-        <v>5750</v>
+        <v>2500</v>
       </c>
       <c r="I14" s="0">
-        <v>0</v>
+        <v>8151</v>
       </c>
       <c r="J14" s="0">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="K14" s="0">
-        <v>371</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="0">
-        <v>0.94755758862930894</v>
+        <v>0.87180426342392503</v>
       </c>
       <c r="E15" s="0">
-        <v>0.97307272879791962</v>
+        <v>0.7712418300653594</v>
       </c>
       <c r="F15" s="0">
-        <v>1</v>
+        <v>0.84285714285714286</v>
       </c>
       <c r="G15" s="0">
-        <v>0.94755758862930894</v>
+        <v>0.71084337349397586</v>
       </c>
       <c r="H15" s="0">
-        <v>5800</v>
+        <v>2950</v>
       </c>
       <c r="I15" s="0">
-        <v>0</v>
+        <v>8951</v>
       </c>
       <c r="J15" s="0">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="K15" s="0">
-        <v>321</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="0">
-        <v>0.89708041102593383</v>
+        <v>0.75231630125676541</v>
       </c>
       <c r="E16" s="0">
-        <v>0.94574843091737604</v>
+        <v>0.7065217391304347</v>
       </c>
       <c r="F16" s="0">
-        <v>1</v>
+        <v>0.64356435643564358</v>
       </c>
       <c r="G16" s="0">
-        <v>0.89708041102593383</v>
+        <v>0.7831325301204819</v>
       </c>
       <c r="H16" s="0">
-        <v>5500</v>
+        <v>3250</v>
       </c>
       <c r="I16" s="0">
-        <v>0</v>
+        <v>4951</v>
       </c>
       <c r="J16" s="0">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="K16" s="0">
-        <v>631</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="0">
-        <v>0.78290654053172404</v>
+        <v>0.85140264790297193</v>
       </c>
       <c r="E17" s="0">
-        <v>0.87823620894703147</v>
+        <v>0.7841291190316072</v>
       </c>
       <c r="F17" s="0">
-        <v>1</v>
+        <v>0.85735294117647054</v>
       </c>
       <c r="G17" s="0">
-        <v>0.78290654053172404</v>
+        <v>0.72242874845105332</v>
       </c>
       <c r="H17" s="0">
-        <v>4800</v>
+        <v>2915</v>
       </c>
       <c r="I17" s="0">
-        <v>0</v>
+        <v>6281</v>
       </c>
       <c r="J17" s="0">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="K17" s="0">
-        <v>1331</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="18">
@@ -3338,7 +3353,7 @@
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="13.88671875" customWidth="true"/>
     <col min="4" max="4" width="13.88671875" customWidth="true"/>
-    <col min="5" max="5" width="12.5546875" customWidth="true"/>
+    <col min="5" max="5" width="11.5546875" customWidth="true"/>
     <col min="6" max="6" width="12.5546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3367,19 +3382,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="0">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C2" s="0">
-        <v>0.75331737173246127</v>
+        <v>0.8628186691189097</v>
       </c>
       <c r="D2" s="0">
-        <v>0.88231086236728806</v>
+        <v>0.88626402390431447</v>
       </c>
       <c r="E2" s="0">
-        <v>0.75146397333616166</v>
+        <v>0.75520517800038978</v>
       </c>
       <c r="F2" s="0">
-        <v>0.69074720545812085</v>
+        <v>0.8136431892026792</v>
       </c>
     </row>
     <row r="3">
@@ -3387,19 +3402,19 @@
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C3" s="0">
-        <v>0.7142714410383465</v>
+        <v>0.78609871070904369</v>
       </c>
       <c r="D3" s="0">
-        <v>0.87889065521766474</v>
+        <v>0.76422004231926133</v>
       </c>
       <c r="E3" s="0">
-        <v>0.72029369071359561</v>
+        <v>0.64528677151570457</v>
       </c>
       <c r="F3" s="0">
-        <v>0.65835519672934961</v>
+        <v>0.6884624016777845</v>
       </c>
     </row>
   </sheetData>
@@ -3411,7 +3426,7 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" customWidth="true"/>
+    <col min="1" max="1" width="7" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="13.88671875" customWidth="true"/>
     <col min="4" max="4" width="13.88671875" customWidth="true"/>
@@ -3441,162 +3456,162 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B2" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="0">
-        <v>0.98827470764792769</v>
+        <v>0.833488390638083</v>
       </c>
       <c r="D2" s="0">
-        <v>0</v>
+        <v>0.9600721247563353</v>
       </c>
       <c r="E2" s="0">
-        <v>1</v>
+        <v>0.66633176458086796</v>
       </c>
       <c r="F2" s="0">
-        <v>0</v>
+        <v>0.78586370485755297</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B3" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>0.99588409614751394</v>
+        <v>0.91414504619129278</v>
       </c>
       <c r="D3" s="0">
-        <v>0.5</v>
+        <v>0.97994124286283357</v>
       </c>
       <c r="E3" s="0">
-        <v>1</v>
+        <v>0.83130656672381487</v>
       </c>
       <c r="F3" s="0">
-        <v>0.5</v>
+        <v>0.89914734476009639</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B4" s="0">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>0.81580522885452411</v>
+        <v>0.84644793331453105</v>
       </c>
       <c r="D4" s="0">
-        <v>1</v>
+        <v>0.80633471143216262</v>
       </c>
       <c r="E4" s="0">
-        <v>0.81580522885452411</v>
+        <v>0.810546875</v>
       </c>
       <c r="F4" s="0">
-        <v>0.88964494178875875</v>
+        <v>0.8083867559936615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="0">
-        <v>0.97932641708013835</v>
+        <v>0.82189900189232312</v>
       </c>
       <c r="D5" s="0">
-        <v>0.5</v>
+        <v>0.90052062996225435</v>
       </c>
       <c r="E5" s="0">
-        <v>1</v>
+        <v>0.69762845849802368</v>
       </c>
       <c r="F5" s="0">
-        <v>0.5</v>
+        <v>0.78619047619047622</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B6" s="0">
         <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>0.80181965588685711</v>
+        <v>0.86743428528141808</v>
       </c>
       <c r="D6" s="0">
-        <v>0</v>
+        <v>0.82538812785388127</v>
       </c>
       <c r="E6" s="0">
-        <v>1</v>
+        <v>0.73493975903614461</v>
       </c>
       <c r="F6" s="0">
-        <v>0</v>
+        <v>0.77750730282375846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B7" s="0">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C7" s="0">
-        <v>0.62848314839494712</v>
+        <v>0.68437531562468434</v>
       </c>
       <c r="D7" s="0">
-        <v>1</v>
+        <v>0.63311688311688319</v>
       </c>
       <c r="E7" s="0">
-        <v>0.62848314839494712</v>
+        <v>0.45180722891566261</v>
       </c>
       <c r="F7" s="0">
-        <v>0.69010871416593056</v>
+        <v>0.50788043478260869</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B8" s="0">
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>0.93072380049144288</v>
+        <v>0.82602007178961245</v>
       </c>
       <c r="D8" s="0">
-        <v>0.96055268949096284</v>
+        <v>0.74610389610389616</v>
       </c>
       <c r="E8" s="0">
-        <v>0.86991715164366745</v>
+        <v>0.65662650602409633</v>
       </c>
       <c r="F8" s="0">
-        <v>0.91298146781782841</v>
+        <v>0.6981209150326797</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>0.91414504619129278</v>
+        <v>0.80185947457986861</v>
       </c>
       <c r="D9" s="0">
-        <v>0.97994124286283357</v>
+        <v>0.75045864880605706</v>
       </c>
       <c r="E9" s="0">
-        <v>0.83130656672381487</v>
+        <v>0.75278063928576766</v>
       </c>
       <c r="F9" s="0">
-        <v>0.89914734476009639</v>
+        <v>0.74532542908102095</v>
       </c>
     </row>
     <row r="10">
@@ -3628,7 +3643,7 @@
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="true"/>
+    <col min="1" max="1" width="7.21875" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="13.88671875" customWidth="true"/>
     <col min="4" max="4" width="13.88671875" customWidth="true"/>
@@ -3661,19 +3676,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="0">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C2" s="0">
-        <v>0.91405679705874698</v>
+        <v>0.82477582656133741</v>
       </c>
       <c r="D2" s="0">
-        <v>0.63432324241919436</v>
+        <v>0.76763241878070521</v>
       </c>
       <c r="E2" s="0">
-        <v>0.91764473613971853</v>
+        <v>0.73998467343662133</v>
       </c>
       <c r="F2" s="0">
-        <v>0.60562252395053118</v>
+        <v>0.75061103336912061</v>
       </c>
     </row>
     <row r="3">
@@ -3684,16 +3699,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="0">
-        <v>0.91787322120280057</v>
+        <v>0.82426840792556022</v>
       </c>
       <c r="D3" s="0">
-        <v>0.58809878647075942</v>
+        <v>0.85980780171043758</v>
       </c>
       <c r="E3" s="0">
-        <v>0.93026427839201897</v>
+        <v>0.67640275555090279</v>
       </c>
       <c r="F3" s="0">
-        <v>0.55723976653198215</v>
+        <v>0.75131785268289852</v>
       </c>
     </row>
     <row r="4">

--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="998" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3169" uniqueCount="49">
   <si>
     <t>Subject</t>
   </si>
@@ -222,7 +222,7 @@
     <col min="8" max="8" width="6" customWidth="true"/>
     <col min="9" max="9" width="6" customWidth="true"/>
     <col min="10" max="10" width="5" customWidth="true"/>
-    <col min="11" max="11" width="6" customWidth="true"/>
+    <col min="11" max="11" width="5" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -271,28 +271,28 @@
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>0.80866814635637485</v>
+        <v>0.95912841879995459</v>
       </c>
       <c r="E2" s="0">
-        <v>0.74834807537670878</v>
+        <v>0.94395411395922724</v>
       </c>
       <c r="F2" s="0">
-        <v>0.95133333333333336</v>
+        <v>0.90920770877944324</v>
       </c>
       <c r="G2" s="0">
-        <v>0.6167521466028929</v>
+        <v>0.9814617909481762</v>
       </c>
       <c r="H2" s="0">
-        <v>21405</v>
+        <v>21230</v>
       </c>
       <c r="I2" s="0">
-        <v>39440</v>
+        <v>37930</v>
       </c>
       <c r="J2" s="0">
-        <v>1095</v>
+        <v>2120</v>
       </c>
       <c r="K2" s="0">
-        <v>13301</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
@@ -306,28 +306,28 @@
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>0.85830863491979104</v>
+        <v>0.95703776787916606</v>
       </c>
       <c r="E3" s="0">
-        <v>0.82337933433839727</v>
+        <v>0.94863031522700847</v>
       </c>
       <c r="F3" s="0">
-        <v>0.96881091617933723</v>
+        <v>0.93470085470085473</v>
       </c>
       <c r="G3" s="0">
-        <v>0.71591138255884301</v>
+        <v>0.96298122644500017</v>
       </c>
       <c r="H3" s="0">
-        <v>24850</v>
+        <v>27340</v>
       </c>
       <c r="I3" s="0">
-        <v>39730</v>
+        <v>38620</v>
       </c>
       <c r="J3" s="0">
-        <v>800</v>
+        <v>1910</v>
       </c>
       <c r="K3" s="0">
-        <v>9861</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="4">
@@ -341,28 +341,28 @@
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>0.93120171119839201</v>
+        <v>0.93153530819313313</v>
       </c>
       <c r="E4" s="0">
-        <v>0.92100527196121196</v>
+        <v>0.92578070016689784</v>
       </c>
       <c r="F4" s="0">
-        <v>0.98194130925507905</v>
+        <v>0.93387423935091274</v>
       </c>
       <c r="G4" s="0">
-        <v>0.86719030341692915</v>
+        <v>0.91782624297276827</v>
       </c>
       <c r="H4" s="0">
-        <v>21750</v>
+        <v>23020</v>
       </c>
       <c r="I4" s="0">
-        <v>28750</v>
+        <v>27200</v>
       </c>
       <c r="J4" s="0">
-        <v>400</v>
+        <v>1630</v>
       </c>
       <c r="K4" s="0">
-        <v>3331</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="5">
@@ -376,28 +376,28 @@
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>0.89708838118419354</v>
+        <v>0.90389332546430345</v>
       </c>
       <c r="E5" s="0">
-        <v>0.87728941755898071</v>
+        <v>0.89393661842828342</v>
       </c>
       <c r="F5" s="0">
-        <v>0.9779411764705882</v>
+        <v>0.91309771309771315</v>
       </c>
       <c r="G5" s="0">
-        <v>0.79542283003070058</v>
+        <v>0.87556317531198913</v>
       </c>
       <c r="H5" s="0">
-        <v>19950</v>
+        <v>21960</v>
       </c>
       <c r="I5" s="0">
-        <v>28700</v>
+        <v>27050</v>
       </c>
       <c r="J5" s="0">
-        <v>450</v>
+        <v>2090</v>
       </c>
       <c r="K5" s="0">
-        <v>5131</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="6">
@@ -411,28 +411,28 @@
         <v>8</v>
       </c>
       <c r="D6" s="0">
-        <v>0.78784745072232143</v>
+        <v>0.79988080675010198</v>
       </c>
       <c r="E6" s="0">
-        <v>0.7339882121807465</v>
+        <v>0.78387533875338755</v>
       </c>
       <c r="F6" s="0">
-        <v>0.73833992094861656</v>
+        <v>0.6907462686567164</v>
       </c>
       <c r="G6" s="0">
-        <v>0.72968750000000004</v>
+        <v>0.90602975724353951</v>
       </c>
       <c r="H6" s="0">
-        <v>9340</v>
+        <v>11570</v>
       </c>
       <c r="I6" s="0">
-        <v>15801</v>
+        <v>13931</v>
       </c>
       <c r="J6" s="0">
-        <v>3310</v>
+        <v>5180</v>
       </c>
       <c r="K6" s="0">
-        <v>3460</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
@@ -446,28 +446,28 @@
         <v>9</v>
       </c>
       <c r="D7" s="0">
-        <v>0.90504841590674068</v>
+        <v>0.87026417222901198</v>
       </c>
       <c r="E7" s="0">
-        <v>0.88278529980657638</v>
+        <v>0.85966101694915253</v>
       </c>
       <c r="F7" s="0">
-        <v>0.8743295019157088</v>
+        <v>0.75928143712574847</v>
       </c>
       <c r="G7" s="0">
-        <v>0.89140624999999996</v>
+        <v>0.99062499999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>11410</v>
+        <v>12680</v>
       </c>
       <c r="I7" s="0">
-        <v>17471</v>
+        <v>15091</v>
       </c>
       <c r="J7" s="0">
-        <v>1640</v>
+        <v>4020</v>
       </c>
       <c r="K7" s="0">
-        <v>1390</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -481,28 +481,28 @@
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <v>0.82189900189232312</v>
+        <v>0.87224982256919803</v>
       </c>
       <c r="E8" s="0">
-        <v>0.78571428571428581</v>
+        <v>0.86330935251798557</v>
       </c>
       <c r="F8" s="0">
-        <v>0.90256410256410258</v>
+        <v>0.8605577689243028</v>
       </c>
       <c r="G8" s="0">
-        <v>0.69565217391304346</v>
+        <v>0.8660785886126704</v>
       </c>
       <c r="H8" s="0">
-        <v>8800</v>
+        <v>10800</v>
       </c>
       <c r="I8" s="0">
-        <v>13351</v>
+        <v>12551</v>
       </c>
       <c r="J8" s="0">
-        <v>950</v>
+        <v>1750</v>
       </c>
       <c r="K8" s="0">
-        <v>3850</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="9">
@@ -516,28 +516,28 @@
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <v>0.82189900189232312</v>
+        <v>0.90265189660960055</v>
       </c>
       <c r="E9" s="0">
-        <v>0.78666666666666663</v>
+        <v>0.89646965489884956</v>
       </c>
       <c r="F9" s="0">
-        <v>0.89847715736040612</v>
+        <v>0.88976377952755903</v>
       </c>
       <c r="G9" s="0">
-        <v>0.69960474308300391</v>
+        <v>0.90327737809752195</v>
       </c>
       <c r="H9" s="0">
-        <v>8850</v>
+        <v>11300</v>
       </c>
       <c r="I9" s="0">
-        <v>13301</v>
+        <v>12901</v>
       </c>
       <c r="J9" s="0">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="K9" s="0">
-        <v>3800</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="10">
@@ -551,28 +551,28 @@
         <v>8</v>
       </c>
       <c r="D10" s="0">
-        <v>0.82577077494129236</v>
+        <v>0.80683281569578058</v>
       </c>
       <c r="E10" s="0">
-        <v>0.708860759493671</v>
+        <v>0.73575129533678763</v>
       </c>
       <c r="F10" s="0">
-        <v>0.7466666666666667</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="G10" s="0">
-        <v>0.67469879518072284</v>
+        <v>0.85542168674698793</v>
       </c>
       <c r="H10" s="0">
-        <v>2800</v>
+        <v>3550</v>
       </c>
       <c r="I10" s="0">
-        <v>8101</v>
+        <v>7101</v>
       </c>
       <c r="J10" s="0">
-        <v>950</v>
+        <v>1950</v>
       </c>
       <c r="K10" s="0">
-        <v>1350</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -586,28 +586,28 @@
         <v>9</v>
       </c>
       <c r="D11" s="0">
-        <v>0.9090977956215438</v>
+        <v>0.88258465267782749</v>
       </c>
       <c r="E11" s="0">
-        <v>0.84615384615384603</v>
+        <v>0.82285714285714295</v>
       </c>
       <c r="F11" s="0">
-        <v>0.90410958904109584</v>
+        <v>0.78260869565217395</v>
       </c>
       <c r="G11" s="0">
-        <v>0.79518072289156627</v>
+        <v>0.86746987951807231</v>
       </c>
       <c r="H11" s="0">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="I11" s="0">
-        <v>8701</v>
+        <v>8051</v>
       </c>
       <c r="J11" s="0">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="K11" s="0">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12">
@@ -621,28 +621,28 @@
         <v>8</v>
       </c>
       <c r="D12" s="0">
-        <v>0.5808504191495808</v>
+        <v>0.60607005508782874</v>
       </c>
       <c r="E12" s="0">
-        <v>0.27826086956521745</v>
+        <v>0.44671532846715328</v>
       </c>
       <c r="F12" s="0">
-        <v>0.5</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="G12" s="0">
-        <v>0.19277108433734941</v>
+        <v>0.36867469879518072</v>
       </c>
       <c r="H12" s="0">
-        <v>800</v>
+        <v>1530</v>
       </c>
       <c r="I12" s="0">
-        <v>4951</v>
+        <v>4301</v>
       </c>
       <c r="J12" s="0">
-        <v>800</v>
+        <v>1170</v>
       </c>
       <c r="K12" s="0">
-        <v>3350</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="13">
@@ -656,28 +656,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <v>0.78790021209978789</v>
+        <v>0.73831585378271047</v>
       </c>
       <c r="E13" s="0">
-        <v>0.73749999999999993</v>
+        <v>0.70289017341040461</v>
       </c>
       <c r="F13" s="0">
-        <v>0.76623376623376627</v>
+        <v>0.67555555555555558</v>
       </c>
       <c r="G13" s="0">
-        <v>0.71084337349397586</v>
+        <v>0.73253012048192767</v>
       </c>
       <c r="H13" s="0">
-        <v>2950</v>
+        <v>3040</v>
       </c>
       <c r="I13" s="0">
-        <v>4851</v>
+        <v>4211</v>
       </c>
       <c r="J13" s="0">
-        <v>900</v>
+        <v>1460</v>
       </c>
       <c r="K13" s="0">
-        <v>1200</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="14">
@@ -691,28 +691,28 @@
         <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>0.78023588015529999</v>
+        <v>0.81661761376499886</v>
       </c>
       <c r="E14" s="0">
-        <v>0.62500000000000011</v>
+        <v>0.75279755849440488</v>
       </c>
       <c r="F14" s="0">
-        <v>0.64935064935064934</v>
+        <v>0.61157024793388426</v>
       </c>
       <c r="G14" s="0">
-        <v>0.60240963855421692</v>
+        <v>0.97883597883597884</v>
       </c>
       <c r="H14" s="0">
-        <v>2500</v>
+        <v>3700</v>
       </c>
       <c r="I14" s="0">
-        <v>8151</v>
+        <v>7121</v>
       </c>
       <c r="J14" s="0">
-        <v>1350</v>
+        <v>2350</v>
       </c>
       <c r="K14" s="0">
-        <v>1650</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -726,28 +726,28 @@
         <v>9</v>
       </c>
       <c r="D15" s="0">
-        <v>0.87180426342392503</v>
+        <v>0.91753184596126947</v>
       </c>
       <c r="E15" s="0">
-        <v>0.7712418300653594</v>
+        <v>0.8752783964365255</v>
       </c>
       <c r="F15" s="0">
-        <v>0.84285714285714286</v>
+        <v>0.80204081632653057</v>
       </c>
       <c r="G15" s="0">
-        <v>0.71084337349397586</v>
+        <v>0.96323529411764708</v>
       </c>
       <c r="H15" s="0">
-        <v>2950</v>
+        <v>3930</v>
       </c>
       <c r="I15" s="0">
-        <v>8951</v>
+        <v>8531</v>
       </c>
       <c r="J15" s="0">
-        <v>550</v>
+        <v>970</v>
       </c>
       <c r="K15" s="0">
-        <v>1200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -761,28 +761,28 @@
         <v>8</v>
       </c>
       <c r="D16" s="0">
-        <v>0.75231630125676541</v>
+        <v>0.7110356847995597</v>
       </c>
       <c r="E16" s="0">
-        <v>0.7065217391304347</v>
+        <v>0.7069767441860465</v>
       </c>
       <c r="F16" s="0">
-        <v>0.64356435643564358</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="G16" s="0">
-        <v>0.7831325301204819</v>
+        <v>0.91566265060240959</v>
       </c>
       <c r="H16" s="0">
-        <v>3250</v>
+        <v>3800</v>
       </c>
       <c r="I16" s="0">
-        <v>4951</v>
+        <v>3951</v>
       </c>
       <c r="J16" s="0">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="K16" s="0">
-        <v>900</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17">
@@ -796,28 +796,28 @@
         <v>9</v>
       </c>
       <c r="D17" s="0">
-        <v>0.85140264790297193</v>
+        <v>0.73057118907915219</v>
       </c>
       <c r="E17" s="0">
-        <v>0.7841291190316072</v>
+        <v>0.73867595818815335</v>
       </c>
       <c r="F17" s="0">
-        <v>0.85735294117647054</v>
+        <v>0.594392523364486</v>
       </c>
       <c r="G17" s="0">
-        <v>0.72242874845105332</v>
+        <v>0.97546012269938653</v>
       </c>
       <c r="H17" s="0">
-        <v>2915</v>
+        <v>3180</v>
       </c>
       <c r="I17" s="0">
-        <v>6281</v>
+        <v>2921</v>
       </c>
       <c r="J17" s="0">
-        <v>485</v>
+        <v>2170</v>
       </c>
       <c r="K17" s="0">
-        <v>1120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -3353,7 +3353,7 @@
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="13.88671875" customWidth="true"/>
     <col min="4" max="4" width="13.88671875" customWidth="true"/>
-    <col min="5" max="5" width="11.5546875" customWidth="true"/>
+    <col min="5" max="5" width="12.5546875" customWidth="true"/>
     <col min="6" max="6" width="12.5546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3385,16 +3385,16 @@
         <v>8</v>
       </c>
       <c r="C2" s="0">
-        <v>0.8628186691189097</v>
+        <v>0.86285633796038019</v>
       </c>
       <c r="D2" s="0">
-        <v>0.88626402390431447</v>
+        <v>0.79393017191882764</v>
       </c>
       <c r="E2" s="0">
-        <v>0.75520517800038978</v>
+        <v>0.90889277458394302</v>
       </c>
       <c r="F2" s="0">
-        <v>0.8136431892026792</v>
+        <v>0.84229990954944001</v>
       </c>
     </row>
     <row r="3">
@@ -3405,16 +3405,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="0">
-        <v>0.78609871070904369</v>
+        <v>0.81291881570756941</v>
       </c>
       <c r="D3" s="0">
-        <v>0.76422004231926133</v>
+        <v>0.72422937769050599</v>
       </c>
       <c r="E3" s="0">
-        <v>0.64528677151570457</v>
+        <v>0.84874892434471394</v>
       </c>
       <c r="F3" s="0">
-        <v>0.6884624016777845</v>
+        <v>0.76989505398523628</v>
       </c>
     </row>
   </sheetData>
@@ -3462,16 +3462,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="0">
-        <v>0.833488390638083</v>
+        <v>0.95808309333956032</v>
       </c>
       <c r="D2" s="0">
-        <v>0.9600721247563353</v>
+        <v>0.92195428174014893</v>
       </c>
       <c r="E2" s="0">
-        <v>0.66633176458086796</v>
+        <v>0.97222150869658819</v>
       </c>
       <c r="F2" s="0">
-        <v>0.78586370485755297</v>
+        <v>0.94629221459311785</v>
       </c>
     </row>
     <row r="3">
@@ -3482,16 +3482,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>0.91414504619129278</v>
+        <v>0.91771431682871829</v>
       </c>
       <c r="D3" s="0">
-        <v>0.97994124286283357</v>
+        <v>0.92348597622431294</v>
       </c>
       <c r="E3" s="0">
-        <v>0.83130656672381487</v>
+        <v>0.8966947091423787</v>
       </c>
       <c r="F3" s="0">
-        <v>0.89914734476009639</v>
+        <v>0.90985865929759058</v>
       </c>
     </row>
     <row r="4">
@@ -3502,16 +3502,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>0.84644793331453105</v>
+        <v>0.83507248948955692</v>
       </c>
       <c r="D4" s="0">
-        <v>0.80633471143216262</v>
+        <v>0.72501385289123244</v>
       </c>
       <c r="E4" s="0">
-        <v>0.810546875</v>
+        <v>0.94832737862176975</v>
       </c>
       <c r="F4" s="0">
-        <v>0.8083867559936615</v>
+        <v>0.82176817785126999</v>
       </c>
     </row>
     <row r="5">
@@ -3522,16 +3522,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="0">
-        <v>0.82189900189232312</v>
+        <v>0.88745085958939929</v>
       </c>
       <c r="D5" s="0">
-        <v>0.90052062996225435</v>
+        <v>0.87516077422593086</v>
       </c>
       <c r="E5" s="0">
-        <v>0.69762845849802368</v>
+        <v>0.88467798335509618</v>
       </c>
       <c r="F5" s="0">
-        <v>0.78619047619047622</v>
+        <v>0.87988950370841756</v>
       </c>
     </row>
     <row r="6">
@@ -3542,16 +3542,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>0.86743428528141808</v>
+        <v>0.84470873418680403</v>
       </c>
       <c r="D6" s="0">
-        <v>0.82538812785388127</v>
+        <v>0.71403162055335967</v>
       </c>
       <c r="E6" s="0">
-        <v>0.73493975903614461</v>
+        <v>0.86144578313253017</v>
       </c>
       <c r="F6" s="0">
-        <v>0.77750730282375846</v>
+        <v>0.77930421909696523</v>
       </c>
     </row>
     <row r="7">
@@ -3562,16 +3562,16 @@
         <v>2</v>
       </c>
       <c r="C7" s="0">
-        <v>0.68437531562468434</v>
+        <v>0.67219295443526961</v>
       </c>
       <c r="D7" s="0">
-        <v>0.63311688311688319</v>
+        <v>0.62111111111111117</v>
       </c>
       <c r="E7" s="0">
-        <v>0.45180722891566261</v>
+        <v>0.55060240963855422</v>
       </c>
       <c r="F7" s="0">
-        <v>0.50788043478260869</v>
+        <v>0.57480275093877897</v>
       </c>
     </row>
     <row r="8">
@@ -3582,16 +3582,16 @@
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>0.82602007178961245</v>
+        <v>0.86707472986313416</v>
       </c>
       <c r="D8" s="0">
-        <v>0.74610389610389616</v>
+        <v>0.70680553213020736</v>
       </c>
       <c r="E8" s="0">
-        <v>0.65662650602409633</v>
+        <v>0.9710356364768129</v>
       </c>
       <c r="F8" s="0">
-        <v>0.6981209150326797</v>
+        <v>0.81403797746546513</v>
       </c>
     </row>
     <row r="9">
@@ -3602,16 +3602,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>0.80185947457986861</v>
+        <v>0.72080343693935589</v>
       </c>
       <c r="D9" s="0">
-        <v>0.75045864880605706</v>
+        <v>0.58507504956103085</v>
       </c>
       <c r="E9" s="0">
-        <v>0.75278063928576766</v>
+        <v>0.94556138665089806</v>
       </c>
       <c r="F9" s="0">
-        <v>0.74532542908102095</v>
+        <v>0.72282635118709992</v>
       </c>
     </row>
     <row r="10">
@@ -3679,16 +3679,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="0">
-        <v>0.82477582656133741</v>
+        <v>0.80765021876401555</v>
       </c>
       <c r="D2" s="0">
-        <v>0.76763241878070521</v>
+        <v>0.67229814486082373</v>
       </c>
       <c r="E2" s="0">
-        <v>0.73998467343662133</v>
+        <v>0.95497480058316031</v>
       </c>
       <c r="F2" s="0">
-        <v>0.75061103336912061</v>
+        <v>0.78621083550127846</v>
       </c>
     </row>
     <row r="3">
@@ -3699,16 +3699,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="0">
-        <v>0.82426840792556022</v>
+        <v>0.85602999167595029</v>
       </c>
       <c r="D3" s="0">
-        <v>0.85980780171043758</v>
+        <v>0.81114875277097265</v>
       </c>
       <c r="E3" s="0">
-        <v>0.67640275555090279</v>
+        <v>0.83312847879302954</v>
       </c>
       <c r="F3" s="0">
-        <v>0.75131785268289852</v>
+        <v>0.81802946952697408</v>
       </c>
     </row>
     <row r="4">

--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3169" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3272" uniqueCount="51">
   <si>
     <t>Subject</t>
   </si>
@@ -164,6 +164,12 @@
   </si>
   <si>
     <t>test9</t>
+  </si>
+  <si>
+    <t>test10</t>
+  </si>
+  <si>
+    <t>test11</t>
   </si>
 </sst>
 </file>
@@ -262,212 +268,212 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>0.95912841879995459</v>
+        <v>0.75926146989773591</v>
       </c>
       <c r="E2" s="0">
-        <v>0.94395411395922724</v>
+        <v>0.71925754060324831</v>
       </c>
       <c r="F2" s="0">
-        <v>0.90920770877944324</v>
+        <v>0.82887700534759357</v>
       </c>
       <c r="G2" s="0">
-        <v>0.9814617909481762</v>
+        <v>0.63524590163934425</v>
       </c>
       <c r="H2" s="0">
-        <v>21230</v>
+        <v>7750</v>
       </c>
       <c r="I2" s="0">
-        <v>37930</v>
+        <v>11331</v>
       </c>
       <c r="J2" s="0">
-        <v>2120</v>
+        <v>1600</v>
       </c>
       <c r="K2" s="0">
-        <v>401</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>0.95703776787916606</v>
+        <v>0.80900083562134417</v>
       </c>
       <c r="E3" s="0">
-        <v>0.94863031522700847</v>
+        <v>0.80165289256198347</v>
       </c>
       <c r="F3" s="0">
-        <v>0.93470085470085473</v>
+        <v>0.80833333333333335</v>
       </c>
       <c r="G3" s="0">
-        <v>0.96298122644500017</v>
+        <v>0.79508196721311475</v>
       </c>
       <c r="H3" s="0">
-        <v>27340</v>
+        <v>9700</v>
       </c>
       <c r="I3" s="0">
-        <v>38620</v>
+        <v>10631</v>
       </c>
       <c r="J3" s="0">
-        <v>1910</v>
+        <v>2300</v>
       </c>
       <c r="K3" s="0">
-        <v>1051</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>0.93153530819313313</v>
+        <v>0.93687107241138534</v>
       </c>
       <c r="E4" s="0">
-        <v>0.92578070016689784</v>
+        <v>0.93963948632692329</v>
       </c>
       <c r="F4" s="0">
-        <v>0.93387423935091274</v>
+        <v>0.98194254445964435</v>
       </c>
       <c r="G4" s="0">
-        <v>0.91782624297276827</v>
+        <v>0.90083080243969782</v>
       </c>
       <c r="H4" s="0">
-        <v>23020</v>
+        <v>35890</v>
       </c>
       <c r="I4" s="0">
-        <v>27200</v>
+        <v>32540</v>
       </c>
       <c r="J4" s="0">
-        <v>1630</v>
+        <v>660</v>
       </c>
       <c r="K4" s="0">
-        <v>2061</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>0.90389332546430345</v>
+        <v>0.95565738839558889</v>
       </c>
       <c r="E5" s="0">
-        <v>0.89393661842828342</v>
+        <v>0.95900227555600259</v>
       </c>
       <c r="F5" s="0">
-        <v>0.91309771309771315</v>
+        <v>0.97295918367346934</v>
       </c>
       <c r="G5" s="0">
-        <v>0.87556317531198913</v>
+        <v>0.94544012295183555</v>
       </c>
       <c r="H5" s="0">
-        <v>21960</v>
+        <v>38140</v>
       </c>
       <c r="I5" s="0">
-        <v>27050</v>
+        <v>32140</v>
       </c>
       <c r="J5" s="0">
-        <v>2090</v>
+        <v>1060</v>
       </c>
       <c r="K5" s="0">
-        <v>3121</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="0">
-        <v>0.79988080675010198</v>
+        <v>0.8316985781683176</v>
       </c>
       <c r="E6" s="0">
-        <v>0.78387533875338755</v>
+        <v>0.7065939345976654</v>
       </c>
       <c r="F6" s="0">
-        <v>0.6907462686567164</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="G6" s="0">
-        <v>0.90602975724353951</v>
+        <v>0.57787434700198792</v>
       </c>
       <c r="H6" s="0">
-        <v>11570</v>
+        <v>12500</v>
       </c>
       <c r="I6" s="0">
-        <v>13931</v>
+        <v>38800</v>
       </c>
       <c r="J6" s="0">
-        <v>5180</v>
+        <v>1250</v>
       </c>
       <c r="K6" s="0">
-        <v>1200</v>
+        <v>9131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="0">
-        <v>0.87026417222901198</v>
+        <v>0.9341129699220847</v>
       </c>
       <c r="E7" s="0">
-        <v>0.85966101694915253</v>
+        <v>0.91794510399161555</v>
       </c>
       <c r="F7" s="0">
-        <v>0.75928143712574847</v>
+        <v>0.9424860853432282</v>
       </c>
       <c r="G7" s="0">
-        <v>0.99062499999999998</v>
+        <v>0.89464971293719842</v>
       </c>
       <c r="H7" s="0">
-        <v>12680</v>
+        <v>25400</v>
       </c>
       <c r="I7" s="0">
-        <v>15091</v>
+        <v>38980</v>
       </c>
       <c r="J7" s="0">
-        <v>4020</v>
+        <v>1550</v>
       </c>
       <c r="K7" s="0">
-        <v>120</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="8">
@@ -475,34 +481,34 @@
         <v>1</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <v>0.87224982256919803</v>
+        <v>0.93431767171820224</v>
       </c>
       <c r="E8" s="0">
-        <v>0.86330935251798557</v>
+        <v>0.92726114911361723</v>
       </c>
       <c r="F8" s="0">
-        <v>0.8605577689243028</v>
+        <v>0.95635593220338988</v>
       </c>
       <c r="G8" s="0">
-        <v>0.8660785886126704</v>
+        <v>0.89988437462621107</v>
       </c>
       <c r="H8" s="0">
-        <v>10800</v>
+        <v>22570</v>
       </c>
       <c r="I8" s="0">
-        <v>12551</v>
+        <v>27800</v>
       </c>
       <c r="J8" s="0">
-        <v>1750</v>
+        <v>1030</v>
       </c>
       <c r="K8" s="0">
-        <v>1670</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="9">
@@ -510,104 +516,104 @@
         <v>1</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <v>0.90265189660960055</v>
+        <v>0.90112686966304567</v>
       </c>
       <c r="E9" s="0">
-        <v>0.89646965489884956</v>
+        <v>0.88709167877677386</v>
       </c>
       <c r="F9" s="0">
-        <v>0.88976377952755903</v>
+        <v>0.94017857142857142</v>
       </c>
       <c r="G9" s="0">
-        <v>0.90327737809752195</v>
+        <v>0.83967943861887484</v>
       </c>
       <c r="H9" s="0">
-        <v>11300</v>
+        <v>21060</v>
       </c>
       <c r="I9" s="0">
-        <v>12901</v>
+        <v>27800</v>
       </c>
       <c r="J9" s="0">
-        <v>1400</v>
+        <v>1340</v>
       </c>
       <c r="K9" s="0">
-        <v>1210</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="0">
-        <v>0.80683281569578058</v>
+        <v>0.78921614754869673</v>
       </c>
       <c r="E10" s="0">
-        <v>0.73575129533678763</v>
+        <v>0.75129533678756477</v>
       </c>
       <c r="F10" s="0">
-        <v>0.6454545454545455</v>
+        <v>0.71228070175438596</v>
       </c>
       <c r="G10" s="0">
-        <v>0.85542168674698793</v>
+        <v>0.79483163664839462</v>
       </c>
       <c r="H10" s="0">
-        <v>3550</v>
+        <v>10150</v>
       </c>
       <c r="I10" s="0">
-        <v>7101</v>
+        <v>15011</v>
       </c>
       <c r="J10" s="0">
-        <v>1950</v>
+        <v>4100</v>
       </c>
       <c r="K10" s="0">
-        <v>600</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="0">
-        <v>0.88258465267782749</v>
+        <v>0.88123217699225975</v>
       </c>
       <c r="E11" s="0">
-        <v>0.82285714285714295</v>
+        <v>0.86243194192377493</v>
       </c>
       <c r="F11" s="0">
-        <v>0.78260869565217395</v>
+        <v>0.80542372881355928</v>
       </c>
       <c r="G11" s="0">
-        <v>0.86746987951807231</v>
+        <v>0.92812499999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>3600</v>
+        <v>11880</v>
       </c>
       <c r="I11" s="0">
-        <v>8051</v>
+        <v>16241</v>
       </c>
       <c r="J11" s="0">
-        <v>1000</v>
+        <v>2870</v>
       </c>
       <c r="K11" s="0">
-        <v>550</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12">
@@ -615,34 +621,34 @@
         <v>1</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="0">
-        <v>0.60607005508782874</v>
+        <v>0.85992305106271716</v>
       </c>
       <c r="E12" s="0">
-        <v>0.44671532846715328</v>
+        <v>0.84289903644742348</v>
       </c>
       <c r="F12" s="0">
-        <v>0.56666666666666665</v>
+        <v>0.88245614035087716</v>
       </c>
       <c r="G12" s="0">
-        <v>0.36867469879518072</v>
+        <v>0.80673616680032079</v>
       </c>
       <c r="H12" s="0">
-        <v>1530</v>
+        <v>10060</v>
       </c>
       <c r="I12" s="0">
-        <v>4301</v>
+        <v>12961</v>
       </c>
       <c r="J12" s="0">
-        <v>1170</v>
+        <v>1340</v>
       </c>
       <c r="K12" s="0">
-        <v>2620</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="13">
@@ -650,314 +656,314 @@
         <v>1</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <v>0.73831585378271047</v>
+        <v>0.87094849129088803</v>
       </c>
       <c r="E13" s="0">
-        <v>0.70289017341040461</v>
+        <v>0.85619285120532007</v>
       </c>
       <c r="F13" s="0">
-        <v>0.67555555555555558</v>
+        <v>0.89177489177489178</v>
       </c>
       <c r="G13" s="0">
-        <v>0.73253012048192767</v>
+        <v>0.82334132693844919</v>
       </c>
       <c r="H13" s="0">
-        <v>3040</v>
+        <v>10300</v>
       </c>
       <c r="I13" s="0">
-        <v>4211</v>
+        <v>13051</v>
       </c>
       <c r="J13" s="0">
-        <v>1460</v>
+        <v>1250</v>
       </c>
       <c r="K13" s="0">
-        <v>1110</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>0.81661761376499886</v>
+        <v>0.80304522384667831</v>
       </c>
       <c r="E14" s="0">
-        <v>0.75279755849440488</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="F14" s="0">
-        <v>0.61157024793388426</v>
+        <v>0.66315789473684206</v>
       </c>
       <c r="G14" s="0">
-        <v>0.97883597883597884</v>
+        <v>0.75903614457831325</v>
       </c>
       <c r="H14" s="0">
-        <v>3700</v>
+        <v>3150</v>
       </c>
       <c r="I14" s="0">
-        <v>7121</v>
+        <v>7451</v>
       </c>
       <c r="J14" s="0">
-        <v>2350</v>
+        <v>1600</v>
       </c>
       <c r="K14" s="0">
-        <v>80</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="0">
-        <v>0.91753184596126947</v>
+        <v>0.88637224452692975</v>
       </c>
       <c r="E15" s="0">
-        <v>0.8752783964365255</v>
+        <v>0.82352941176470607</v>
       </c>
       <c r="F15" s="0">
-        <v>0.80204081632653057</v>
+        <v>0.8045977011494253</v>
       </c>
       <c r="G15" s="0">
-        <v>0.96323529411764708</v>
+        <v>0.84337349397590367</v>
       </c>
       <c r="H15" s="0">
-        <v>3930</v>
+        <v>3500</v>
       </c>
       <c r="I15" s="0">
-        <v>8531</v>
+        <v>8201</v>
       </c>
       <c r="J15" s="0">
-        <v>970</v>
+        <v>850</v>
       </c>
       <c r="K15" s="0">
-        <v>150</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="0">
-        <v>0.7110356847995597</v>
+        <v>0.55306101236877658</v>
       </c>
       <c r="E16" s="0">
-        <v>0.7069767441860465</v>
+        <v>0.28333333333333333</v>
       </c>
       <c r="F16" s="0">
-        <v>0.5757575757575758</v>
+        <v>0.45945945945945948</v>
       </c>
       <c r="G16" s="0">
-        <v>0.91566265060240959</v>
+        <v>0.20481927710843373</v>
       </c>
       <c r="H16" s="0">
-        <v>3800</v>
+        <v>850</v>
       </c>
       <c r="I16" s="0">
-        <v>3951</v>
+        <v>4471</v>
       </c>
       <c r="J16" s="0">
-        <v>2800</v>
+        <v>1000</v>
       </c>
       <c r="K16" s="0">
-        <v>350</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="0">
-        <v>0.73057118907915219</v>
+        <v>0.70776906628652891</v>
       </c>
       <c r="E17" s="0">
-        <v>0.73867595818815335</v>
+        <v>0.65212121212121221</v>
       </c>
       <c r="F17" s="0">
-        <v>0.594392523364486</v>
+        <v>0.65609756097560978</v>
       </c>
       <c r="G17" s="0">
-        <v>0.97546012269938653</v>
+        <v>0.64819277108433737</v>
       </c>
       <c r="H17" s="0">
-        <v>3180</v>
+        <v>2690</v>
       </c>
       <c r="I17" s="0">
-        <v>2921</v>
+        <v>4261</v>
       </c>
       <c r="J17" s="0">
-        <v>2170</v>
+        <v>1410</v>
       </c>
       <c r="K17" s="0">
-        <v>80</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="0">
-        <v>0.91922666350373616</v>
+        <v>0.79775111312353786</v>
       </c>
       <c r="E18" s="0">
-        <v>0.95791360237315371</v>
+        <v>0.6912442396313363</v>
       </c>
       <c r="F18" s="0">
-        <v>1</v>
+        <v>0.61224489795918369</v>
       </c>
       <c r="G18" s="0">
-        <v>0.91922666350373616</v>
+        <v>0.79365079365079361</v>
       </c>
       <c r="H18" s="0">
-        <v>7750</v>
+        <v>3000</v>
       </c>
       <c r="I18" s="0">
-        <v>0</v>
+        <v>7571</v>
       </c>
       <c r="J18" s="0">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="K18" s="0">
-        <v>681</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="0">
-        <v>0.40327363302099395</v>
+        <v>0.89617848464766958</v>
       </c>
       <c r="E19" s="0">
-        <v>0.57476122052235656</v>
+        <v>0.82656826568265673</v>
       </c>
       <c r="F19" s="0">
-        <v>1</v>
+        <v>0.82962962962962961</v>
       </c>
       <c r="G19" s="0">
-        <v>0.40327363302099395</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="H19" s="0">
-        <v>3400</v>
+        <v>3360</v>
       </c>
       <c r="I19" s="0">
-        <v>0</v>
+        <v>8811</v>
       </c>
       <c r="J19" s="0">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="K19" s="0">
-        <v>5031</v>
+        <v>720</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="0">
-        <v>0.71755243652420753</v>
+        <v>0.71562241996147147</v>
       </c>
       <c r="E20" s="0">
-        <v>0.83555229088238003</v>
+        <v>0.68686868686868674</v>
       </c>
       <c r="F20" s="0">
-        <v>1</v>
+        <v>0.59130434782608698</v>
       </c>
       <c r="G20" s="0">
-        <v>0.71755243652420753</v>
+        <v>0.81927710843373491</v>
       </c>
       <c r="H20" s="0">
-        <v>4550</v>
+        <v>3400</v>
       </c>
       <c r="I20" s="0">
-        <v>0</v>
+        <v>4401</v>
       </c>
       <c r="J20" s="0">
-        <v>0</v>
+        <v>2350</v>
       </c>
       <c r="K20" s="0">
-        <v>1791</v>
+        <v>750</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="0">
-        <v>0.96199337643904748</v>
+        <v>0.81199856304634177</v>
       </c>
       <c r="E21" s="0">
-        <v>0.98062856683546329</v>
+        <v>0.70979667282809611</v>
       </c>
       <c r="F21" s="0">
-        <v>1</v>
+        <v>0.89302325581395348</v>
       </c>
       <c r="G21" s="0">
-        <v>0.96199337643904748</v>
+        <v>0.58895705521472397</v>
       </c>
       <c r="H21" s="0">
-        <v>6100</v>
+        <v>1920</v>
       </c>
       <c r="I21" s="0">
-        <v>0</v>
+        <v>4861</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="K21" s="0">
-        <v>241</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="22">
@@ -3382,19 +3388,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="0">
-        <v>0.86285633796038019</v>
+        <v>0.86543970903926815</v>
       </c>
       <c r="D2" s="0">
-        <v>0.79393017191882764</v>
+        <v>0.85445039419356728</v>
       </c>
       <c r="E2" s="0">
-        <v>0.90889277458394302</v>
+        <v>0.81303703006991435</v>
       </c>
       <c r="F2" s="0">
-        <v>0.84229990954944001</v>
+        <v>0.82963323064121419</v>
       </c>
     </row>
     <row r="3">
@@ -3402,19 +3408,19 @@
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0">
-        <v>0.81291881570756941</v>
+        <v>0.79807677601075189</v>
       </c>
       <c r="D3" s="0">
-        <v>0.72422937769050599</v>
+        <v>0.7597169833188373</v>
       </c>
       <c r="E3" s="0">
-        <v>0.84874892434471394</v>
+        <v>0.71921865529272322</v>
       </c>
       <c r="F3" s="0">
-        <v>0.76989505398523628</v>
+        <v>0.72562579122491244</v>
       </c>
     </row>
   </sheetData>
@@ -3423,7 +3429,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="true"/>
@@ -3462,176 +3468,196 @@
         <v>2</v>
       </c>
       <c r="C2" s="0">
-        <v>0.95808309333956032</v>
+        <v>0.8829057740452011</v>
       </c>
       <c r="D2" s="0">
-        <v>0.92195428174014893</v>
+        <v>0.92578849721706868</v>
       </c>
       <c r="E2" s="0">
-        <v>0.97222150869658819</v>
+        <v>0.73626202996959322</v>
       </c>
       <c r="F2" s="0">
-        <v>0.94629221459311785</v>
+        <v>0.81226951929464053</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B3" s="0">
         <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>0.91771431682871829</v>
+        <v>0.78413115275954004</v>
       </c>
       <c r="D3" s="0">
-        <v>0.92348597622431294</v>
+        <v>0.81860516934046346</v>
       </c>
       <c r="E3" s="0">
-        <v>0.8966947091423787</v>
+        <v>0.7151639344262295</v>
       </c>
       <c r="F3" s="0">
-        <v>0.90985865929759058</v>
+        <v>0.76045521658261594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B4" s="0">
         <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>0.83507248948955692</v>
+        <v>0.94626423040348717</v>
       </c>
       <c r="D4" s="0">
-        <v>0.72501385289123244</v>
+        <v>0.9774508640665569</v>
       </c>
       <c r="E4" s="0">
-        <v>0.94832737862176975</v>
+        <v>0.92313546269576663</v>
       </c>
       <c r="F4" s="0">
-        <v>0.82176817785126999</v>
+        <v>0.94932088094146294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B5" s="0">
         <v>2</v>
       </c>
       <c r="C5" s="0">
-        <v>0.88745085958939929</v>
+        <v>0.91772227069062395</v>
       </c>
       <c r="D5" s="0">
-        <v>0.87516077422593086</v>
+        <v>0.94826725181598071</v>
       </c>
       <c r="E5" s="0">
-        <v>0.88467798335509618</v>
+        <v>0.86978190662254296</v>
       </c>
       <c r="F5" s="0">
-        <v>0.87988950370841756</v>
+        <v>0.90717641394519555</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B6" s="0">
         <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>0.84470873418680403</v>
+        <v>0.83522416227047824</v>
       </c>
       <c r="D6" s="0">
-        <v>0.71403162055335967</v>
+        <v>0.75885221528397262</v>
       </c>
       <c r="E6" s="0">
-        <v>0.86144578313253017</v>
+        <v>0.8614783183241973</v>
       </c>
       <c r="F6" s="0">
-        <v>0.77930421909696523</v>
+        <v>0.80686363935566985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" s="0">
         <v>2</v>
       </c>
       <c r="C7" s="0">
-        <v>0.67219295443526961</v>
+        <v>0.86543577117680259</v>
       </c>
       <c r="D7" s="0">
-        <v>0.62111111111111117</v>
+        <v>0.88711551606288452</v>
       </c>
       <c r="E7" s="0">
-        <v>0.55060240963855422</v>
+        <v>0.81503874686938493</v>
       </c>
       <c r="F7" s="0">
-        <v>0.57480275093877897</v>
+        <v>0.84954594382637172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B8" s="0">
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>0.86707472986313416</v>
+        <v>0.84470873418680403</v>
       </c>
       <c r="D8" s="0">
-        <v>0.70680553213020736</v>
+        <v>0.73387779794313368</v>
       </c>
       <c r="E8" s="0">
-        <v>0.9710356364768129</v>
+        <v>0.8012048192771084</v>
       </c>
       <c r="F8" s="0">
-        <v>0.81403797746546513</v>
+        <v>0.76569729015201593</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>0.72080343693935589</v>
+        <v>0.63041503932765275</v>
       </c>
       <c r="D9" s="0">
-        <v>0.58507504956103085</v>
+        <v>0.55777851021753466</v>
       </c>
       <c r="E9" s="0">
-        <v>0.94556138665089806</v>
+        <v>0.42650602409638555</v>
       </c>
       <c r="F9" s="0">
-        <v>0.72282635118709992</v>
+        <v>0.46772727272727277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B10" s="0">
         <v>2</v>
       </c>
       <c r="C10" s="0">
-        <v>0.84629124753219898</v>
+        <v>0.84696479888560372</v>
       </c>
       <c r="D10" s="0">
-        <v>0.80593945451516658</v>
+        <v>0.7209372637944067</v>
       </c>
       <c r="E10" s="0">
-        <v>0.81044120162236122</v>
+        <v>0.80859010270774978</v>
       </c>
       <c r="F10" s="0">
-        <v>0.80813793292215608</v>
+        <v>0.75890625265699652</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.76381049150390656</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0.74216380182002029</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0.7041170818242295</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0.69833267984839142</v>
       </c>
     </row>
   </sheetData>
@@ -3647,7 +3673,7 @@
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="13.88671875" customWidth="true"/>
     <col min="4" max="4" width="13.88671875" customWidth="true"/>
-    <col min="5" max="5" width="12.5546875" customWidth="true"/>
+    <col min="5" max="5" width="11.44140625" customWidth="true"/>
     <col min="6" max="6" width="12.5546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3676,19 +3702,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="0">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" s="0">
-        <v>0.80765021876401555</v>
+        <v>0.83527896716460304</v>
       </c>
       <c r="D2" s="0">
-        <v>0.67229814486082373</v>
+        <v>0.80360186286108404</v>
       </c>
       <c r="E2" s="0">
-        <v>0.95497480058316031</v>
+        <v>0.80249697999563452</v>
       </c>
       <c r="F2" s="0">
-        <v>0.78621083550127846</v>
+        <v>0.79477573387702738</v>
       </c>
     </row>
     <row r="3">
@@ -3699,16 +3725,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="0">
-        <v>0.85602999167595029</v>
+        <v>0.82823751788541689</v>
       </c>
       <c r="D3" s="0">
-        <v>0.81114875277097265</v>
+        <v>0.81056551465132043</v>
       </c>
       <c r="E3" s="0">
-        <v>0.83312847879302954</v>
+        <v>0.72975870536700294</v>
       </c>
       <c r="F3" s="0">
-        <v>0.81802946952697408</v>
+        <v>0.76048328798909925</v>
       </c>
     </row>
     <row r="4">

--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3272" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="5766" uniqueCount="55">
   <si>
     <t>Subject</t>
   </si>
@@ -170,6 +170,18 @@
   </si>
   <si>
     <t>test11</t>
+  </si>
+  <si>
+    <t>sum_TP</t>
+  </si>
+  <si>
+    <t>sum_FP</t>
+  </si>
+  <si>
+    <t>sum_TN</t>
+  </si>
+  <si>
+    <t>sum_FN</t>
   </si>
 </sst>
 </file>
@@ -215,19 +227,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.21875" customWidth="true"/>
-    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="1" max="1" width="9.33203125" customWidth="true"/>
+    <col min="2" max="2" width="9.88671875" customWidth="true"/>
     <col min="3" max="3" width="5.33203125" customWidth="true"/>
-    <col min="4" max="4" width="12.5546875" customWidth="true"/>
-    <col min="5" max="5" width="12.5546875" customWidth="true"/>
+    <col min="4" max="4" width="14.5546875" customWidth="true"/>
+    <col min="5" max="5" width="13.5546875" customWidth="true"/>
     <col min="6" max="6" width="12.5546875" customWidth="true"/>
-    <col min="7" max="7" width="12.5546875" customWidth="true"/>
+    <col min="7" max="7" width="14.5546875" customWidth="true"/>
     <col min="8" max="8" width="6" customWidth="true"/>
-    <col min="9" max="9" width="6" customWidth="true"/>
-    <col min="10" max="10" width="5" customWidth="true"/>
+    <col min="9" max="9" width="7" customWidth="true"/>
+    <col min="10" max="10" width="6" customWidth="true"/>
     <col min="11" max="11" width="5" customWidth="true"/>
   </cols>
   <sheetData>
@@ -277,28 +289,28 @@
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>0.75926146989773591</v>
+        <v>0.84680275357128643</v>
       </c>
       <c r="E2" s="0">
-        <v>0.71925754060324831</v>
+        <v>0.85048543689320399</v>
       </c>
       <c r="F2" s="0">
-        <v>0.82887700534759357</v>
+        <v>0.80811808118081185</v>
       </c>
       <c r="G2" s="0">
-        <v>0.63524590163934425</v>
+        <v>0.89754098360655743</v>
       </c>
       <c r="H2" s="0">
-        <v>7750</v>
+        <v>10950</v>
       </c>
       <c r="I2" s="0">
-        <v>11331</v>
+        <v>10331</v>
       </c>
       <c r="J2" s="0">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="K2" s="0">
-        <v>4450</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="3">
@@ -312,28 +324,28 @@
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>0.80900083562134417</v>
+        <v>0.85277147745811943</v>
       </c>
       <c r="E3" s="0">
-        <v>0.80165289256198347</v>
+        <v>0.85603112840466933</v>
       </c>
       <c r="F3" s="0">
-        <v>0.80833333333333335</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="G3" s="0">
-        <v>0.79508196721311475</v>
+        <v>0.90163934426229508</v>
       </c>
       <c r="H3" s="0">
-        <v>9700</v>
+        <v>11000</v>
       </c>
       <c r="I3" s="0">
-        <v>10631</v>
+        <v>10431</v>
       </c>
       <c r="J3" s="0">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="K3" s="0">
-        <v>2500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="4">
@@ -347,28 +359,28 @@
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>0.93687107241138534</v>
+        <v>0.97999753563067316</v>
       </c>
       <c r="E4" s="0">
-        <v>0.93963948632692329</v>
+        <v>0.98172402146583104</v>
       </c>
       <c r="F4" s="0">
-        <v>0.98194254445964435</v>
+        <v>0.97855361596009971</v>
       </c>
       <c r="G4" s="0">
-        <v>0.90083080243969782</v>
+        <v>0.98491503727316076</v>
       </c>
       <c r="H4" s="0">
-        <v>35890</v>
+        <v>39240</v>
       </c>
       <c r="I4" s="0">
-        <v>32540</v>
+        <v>32340</v>
       </c>
       <c r="J4" s="0">
-        <v>660</v>
+        <v>860</v>
       </c>
       <c r="K4" s="0">
-        <v>3951</v>
+        <v>601</v>
       </c>
     </row>
     <row r="5">
@@ -382,28 +394,28 @@
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>0.95565738839558889</v>
+        <v>0.97877374525774741</v>
       </c>
       <c r="E5" s="0">
-        <v>0.95900227555600259</v>
+        <v>0.98083275008902149</v>
       </c>
       <c r="F5" s="0">
-        <v>0.97295918367346934</v>
+        <v>0.97177615571776155</v>
       </c>
       <c r="G5" s="0">
-        <v>0.94544012295183555</v>
+        <v>0.99005974071044345</v>
       </c>
       <c r="H5" s="0">
-        <v>38140</v>
+        <v>39940</v>
       </c>
       <c r="I5" s="0">
-        <v>32140</v>
+        <v>32040</v>
       </c>
       <c r="J5" s="0">
-        <v>1060</v>
+        <v>1160</v>
       </c>
       <c r="K5" s="0">
-        <v>2201</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6">
@@ -417,28 +429,28 @@
         <v>8</v>
       </c>
       <c r="D6" s="0">
-        <v>0.8316985781683176</v>
+        <v>0.96480277557108352</v>
       </c>
       <c r="E6" s="0">
-        <v>0.7065939345976654</v>
+        <v>0.95157368784992524</v>
       </c>
       <c r="F6" s="0">
-        <v>0.90909090909090906</v>
+        <v>0.91939655172413792</v>
       </c>
       <c r="G6" s="0">
-        <v>0.57787434700198792</v>
+        <v>0.98608478572419211</v>
       </c>
       <c r="H6" s="0">
-        <v>12500</v>
+        <v>21330</v>
       </c>
       <c r="I6" s="0">
-        <v>38800</v>
+        <v>38180</v>
       </c>
       <c r="J6" s="0">
-        <v>1250</v>
+        <v>1870</v>
       </c>
       <c r="K6" s="0">
-        <v>9131</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7">
@@ -452,28 +464,28 @@
         <v>9</v>
       </c>
       <c r="D7" s="0">
-        <v>0.9341129699220847</v>
+        <v>0.95921417274850918</v>
       </c>
       <c r="E7" s="0">
-        <v>0.91794510399161555</v>
+        <v>0.95161040436556443</v>
       </c>
       <c r="F7" s="0">
-        <v>0.9424860853432282</v>
+        <v>0.9306397306397306</v>
       </c>
       <c r="G7" s="0">
-        <v>0.89464971293719842</v>
+        <v>0.97354795533795924</v>
       </c>
       <c r="H7" s="0">
-        <v>25400</v>
+        <v>27640</v>
       </c>
       <c r="I7" s="0">
-        <v>38980</v>
+        <v>38470</v>
       </c>
       <c r="J7" s="0">
-        <v>1550</v>
+        <v>2060</v>
       </c>
       <c r="K7" s="0">
-        <v>2991</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8">
@@ -487,28 +499,28 @@
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <v>0.93431767171820224</v>
+        <v>0.94915694385190408</v>
       </c>
       <c r="E8" s="0">
-        <v>0.92726114911361723</v>
+        <v>0.94537773260795921</v>
       </c>
       <c r="F8" s="0">
-        <v>0.95635593220338988</v>
+        <v>0.94501992031872506</v>
       </c>
       <c r="G8" s="0">
-        <v>0.89988437462621107</v>
+        <v>0.94573581595630163</v>
       </c>
       <c r="H8" s="0">
-        <v>22570</v>
+        <v>23720</v>
       </c>
       <c r="I8" s="0">
-        <v>27800</v>
+        <v>27450</v>
       </c>
       <c r="J8" s="0">
-        <v>1030</v>
+        <v>1380</v>
       </c>
       <c r="K8" s="0">
-        <v>2511</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="9">
@@ -522,28 +534,28 @@
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <v>0.90112686966304567</v>
+        <v>0.93524649121189207</v>
       </c>
       <c r="E9" s="0">
-        <v>0.88709167877677386</v>
+        <v>0.93079182353984746</v>
       </c>
       <c r="F9" s="0">
-        <v>0.94017857142857142</v>
+        <v>0.92046783625730999</v>
       </c>
       <c r="G9" s="0">
-        <v>0.83967943861887484</v>
+        <v>0.94135002591603201</v>
       </c>
       <c r="H9" s="0">
-        <v>21060</v>
+        <v>23610</v>
       </c>
       <c r="I9" s="0">
-        <v>27800</v>
+        <v>27100</v>
       </c>
       <c r="J9" s="0">
-        <v>1340</v>
+        <v>2040</v>
       </c>
       <c r="K9" s="0">
-        <v>4021</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="10">
@@ -557,28 +569,28 @@
         <v>8</v>
       </c>
       <c r="D10" s="0">
-        <v>0.78921614754869673</v>
+        <v>0.78419748439509429</v>
       </c>
       <c r="E10" s="0">
-        <v>0.75129533678756477</v>
+        <v>0.77604166666666663</v>
       </c>
       <c r="F10" s="0">
-        <v>0.71228070175438596</v>
+        <v>0.66406685236768803</v>
       </c>
       <c r="G10" s="0">
-        <v>0.79483163664839462</v>
+        <v>0.93343774471417384</v>
       </c>
       <c r="H10" s="0">
-        <v>10150</v>
+        <v>11920</v>
       </c>
       <c r="I10" s="0">
-        <v>15011</v>
+        <v>13081</v>
       </c>
       <c r="J10" s="0">
-        <v>4100</v>
+        <v>6030</v>
       </c>
       <c r="K10" s="0">
-        <v>2620</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11">
@@ -592,28 +604,28 @@
         <v>9</v>
       </c>
       <c r="D11" s="0">
-        <v>0.88123217699225975</v>
+        <v>0.86713045658236976</v>
       </c>
       <c r="E11" s="0">
-        <v>0.86243194192377493</v>
+        <v>0.85771812080536913</v>
       </c>
       <c r="F11" s="0">
-        <v>0.80542372881355928</v>
+        <v>0.75176470588235289</v>
       </c>
       <c r="G11" s="0">
-        <v>0.92812499999999998</v>
+        <v>0.99843749999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>11880</v>
+        <v>12780</v>
       </c>
       <c r="I11" s="0">
-        <v>16241</v>
+        <v>14891</v>
       </c>
       <c r="J11" s="0">
-        <v>2870</v>
+        <v>4220</v>
       </c>
       <c r="K11" s="0">
-        <v>920</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -627,28 +639,28 @@
         <v>8</v>
       </c>
       <c r="D12" s="0">
-        <v>0.85992305106271716</v>
+        <v>0.87785290052668929</v>
       </c>
       <c r="E12" s="0">
-        <v>0.84289903644742348</v>
+        <v>0.87408548324990376</v>
       </c>
       <c r="F12" s="0">
-        <v>0.88245614035087716</v>
+        <v>0.84074074074074079</v>
       </c>
       <c r="G12" s="0">
-        <v>0.80673616680032079</v>
+        <v>0.91018444266238974</v>
       </c>
       <c r="H12" s="0">
-        <v>10060</v>
+        <v>11350</v>
       </c>
       <c r="I12" s="0">
-        <v>12961</v>
+        <v>12151</v>
       </c>
       <c r="J12" s="0">
-        <v>1340</v>
+        <v>2150</v>
       </c>
       <c r="K12" s="0">
-        <v>2410</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13">
@@ -662,28 +674,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <v>0.87094849129088803</v>
+        <v>0.90227891537055682</v>
       </c>
       <c r="E13" s="0">
-        <v>0.85619285120532007</v>
+        <v>0.89829192546583847</v>
       </c>
       <c r="F13" s="0">
-        <v>0.89177489177489178</v>
+        <v>0.8732075471698113</v>
       </c>
       <c r="G13" s="0">
-        <v>0.82334132693844919</v>
+        <v>0.92486011191047157</v>
       </c>
       <c r="H13" s="0">
-        <v>10300</v>
+        <v>11570</v>
       </c>
       <c r="I13" s="0">
-        <v>13051</v>
+        <v>12621</v>
       </c>
       <c r="J13" s="0">
-        <v>1250</v>
+        <v>1680</v>
       </c>
       <c r="K13" s="0">
-        <v>2210</v>
+        <v>940</v>
       </c>
     </row>
     <row r="14">
@@ -697,28 +709,28 @@
         <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>0.80304522384667831</v>
+        <v>0.78789485645026891</v>
       </c>
       <c r="E14" s="0">
-        <v>0.7078651685393258</v>
+        <v>0.73076923076923073</v>
       </c>
       <c r="F14" s="0">
-        <v>0.66315789473684206</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="G14" s="0">
-        <v>0.75903614457831325</v>
+        <v>0.91566265060240959</v>
       </c>
       <c r="H14" s="0">
-        <v>3150</v>
+        <v>3800</v>
       </c>
       <c r="I14" s="0">
-        <v>7451</v>
+        <v>6601</v>
       </c>
       <c r="J14" s="0">
-        <v>1600</v>
+        <v>2450</v>
       </c>
       <c r="K14" s="0">
-        <v>1000</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15">
@@ -732,28 +744,28 @@
         <v>9</v>
       </c>
       <c r="D15" s="0">
-        <v>0.88637224452692975</v>
+        <v>0.89773502007423678</v>
       </c>
       <c r="E15" s="0">
-        <v>0.82352941176470607</v>
+        <v>0.8540540540540541</v>
       </c>
       <c r="F15" s="0">
-        <v>0.8045977011494253</v>
+        <v>0.77450980392156865</v>
       </c>
       <c r="G15" s="0">
-        <v>0.84337349397590367</v>
+        <v>0.95180722891566261</v>
       </c>
       <c r="H15" s="0">
-        <v>3500</v>
+        <v>3950</v>
       </c>
       <c r="I15" s="0">
-        <v>8201</v>
+        <v>7901</v>
       </c>
       <c r="J15" s="0">
-        <v>850</v>
+        <v>1150</v>
       </c>
       <c r="K15" s="0">
-        <v>650</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
@@ -767,28 +779,28 @@
         <v>8</v>
       </c>
       <c r="D16" s="0">
-        <v>0.55306101236877658</v>
+        <v>0.6580397048123896</v>
       </c>
       <c r="E16" s="0">
-        <v>0.28333333333333333</v>
+        <v>0.58089171974522291</v>
       </c>
       <c r="F16" s="0">
-        <v>0.45945945945945948</v>
+        <v>0.61621621621621625</v>
       </c>
       <c r="G16" s="0">
-        <v>0.20481927710843373</v>
+        <v>0.54939759036144575</v>
       </c>
       <c r="H16" s="0">
-        <v>850</v>
+        <v>2280</v>
       </c>
       <c r="I16" s="0">
-        <v>4471</v>
+        <v>4051</v>
       </c>
       <c r="J16" s="0">
-        <v>1000</v>
+        <v>1420</v>
       </c>
       <c r="K16" s="0">
-        <v>3300</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="17">
@@ -802,28 +814,28 @@
         <v>9</v>
       </c>
       <c r="D17" s="0">
-        <v>0.70776906628652891</v>
+        <v>0.75868037878016492</v>
       </c>
       <c r="E17" s="0">
-        <v>0.65212121212121221</v>
+        <v>0.74652406417112305</v>
       </c>
       <c r="F17" s="0">
-        <v>0.65609756097560978</v>
+        <v>0.6711538461538461</v>
       </c>
       <c r="G17" s="0">
-        <v>0.64819277108433737</v>
+        <v>0.84096385542168672</v>
       </c>
       <c r="H17" s="0">
-        <v>2690</v>
+        <v>3490</v>
       </c>
       <c r="I17" s="0">
-        <v>4261</v>
+        <v>3961</v>
       </c>
       <c r="J17" s="0">
-        <v>1410</v>
+        <v>1710</v>
       </c>
       <c r="K17" s="0">
-        <v>1460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="18">
@@ -837,28 +849,28 @@
         <v>8</v>
       </c>
       <c r="D18" s="0">
-        <v>0.79775111312353786</v>
+        <v>0.82039091389329111</v>
       </c>
       <c r="E18" s="0">
-        <v>0.6912442396313363</v>
+        <v>0.75156576200417524</v>
       </c>
       <c r="F18" s="0">
-        <v>0.61224489795918369</v>
+        <v>0.62068965517241381</v>
       </c>
       <c r="G18" s="0">
-        <v>0.79365079365079361</v>
+        <v>0.95238095238095233</v>
       </c>
       <c r="H18" s="0">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="I18" s="0">
-        <v>7571</v>
+        <v>7271</v>
       </c>
       <c r="J18" s="0">
-        <v>1900</v>
+        <v>2200</v>
       </c>
       <c r="K18" s="0">
-        <v>780</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -875,25 +887,25 @@
         <v>0.89617848464766958</v>
       </c>
       <c r="E19" s="0">
-        <v>0.82656826568265673</v>
+        <v>0.84723726977248115</v>
       </c>
       <c r="F19" s="0">
-        <v>0.82962962962962961</v>
+        <v>0.75922330097087376</v>
       </c>
       <c r="G19" s="0">
-        <v>0.82352941176470584</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="H19" s="0">
-        <v>3360</v>
+        <v>3910</v>
       </c>
       <c r="I19" s="0">
-        <v>8811</v>
+        <v>8261</v>
       </c>
       <c r="J19" s="0">
-        <v>690</v>
+        <v>1240</v>
       </c>
       <c r="K19" s="0">
-        <v>720</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20">
@@ -907,28 +919,28 @@
         <v>8</v>
       </c>
       <c r="D20" s="0">
-        <v>0.71562241996147147</v>
+        <v>0.74314283093294198</v>
       </c>
       <c r="E20" s="0">
-        <v>0.68686868686868674</v>
+        <v>0.73831775700934565</v>
       </c>
       <c r="F20" s="0">
-        <v>0.59130434782608698</v>
+        <v>0.60305343511450382</v>
       </c>
       <c r="G20" s="0">
-        <v>0.81927710843373491</v>
+        <v>0.95180722891566261</v>
       </c>
       <c r="H20" s="0">
-        <v>3400</v>
+        <v>3950</v>
       </c>
       <c r="I20" s="0">
-        <v>4401</v>
+        <v>4151</v>
       </c>
       <c r="J20" s="0">
-        <v>2350</v>
+        <v>2600</v>
       </c>
       <c r="K20" s="0">
-        <v>750</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
@@ -942,98 +954,98 @@
         <v>9</v>
       </c>
       <c r="D21" s="0">
-        <v>0.81199856304634177</v>
+        <v>0.89821578254101309</v>
       </c>
       <c r="E21" s="0">
-        <v>0.70979667282809611</v>
+        <v>0.8804500703234881</v>
       </c>
       <c r="F21" s="0">
-        <v>0.89302325581395348</v>
+        <v>0.81298701298701304</v>
       </c>
       <c r="G21" s="0">
-        <v>0.58895705521472397</v>
+        <v>0.96012269938650308</v>
       </c>
       <c r="H21" s="0">
-        <v>1920</v>
+        <v>3130</v>
       </c>
       <c r="I21" s="0">
-        <v>4861</v>
+        <v>4371</v>
       </c>
       <c r="J21" s="0">
-        <v>230</v>
+        <v>720</v>
       </c>
       <c r="K21" s="0">
-        <v>1340</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="0">
-        <v>0.58927892535800275</v>
+        <v>0.92698422434598393</v>
       </c>
       <c r="E22" s="0">
-        <v>0.74156765808149261</v>
+        <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="0">
-        <v>0.58927892535800275</v>
+        <v>1</v>
       </c>
       <c r="H22" s="0">
-        <v>4650</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>0</v>
+        <v>392931</v>
       </c>
       <c r="J22" s="0">
-        <v>0</v>
+        <v>30950</v>
       </c>
       <c r="K22" s="0">
-        <v>3241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="0">
-        <v>0.88075022177163853</v>
+        <v>0.97760178808462284</v>
       </c>
       <c r="E23" s="0">
-        <v>0.93659456909911731</v>
+        <v>0</v>
       </c>
       <c r="F23" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="0">
-        <v>0.88075022177163853</v>
+        <v>1</v>
       </c>
       <c r="H23" s="0">
-        <v>6950</v>
+        <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>0</v>
+        <v>414641</v>
       </c>
       <c r="J23" s="0">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="K23" s="0">
-        <v>941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1041,13 +1053,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="0">
-        <v>0.63516800288262321</v>
+        <v>0.9655774279339886</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1062,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>7051</v>
+        <v>338011</v>
       </c>
       <c r="J24" s="0">
-        <v>4050</v>
+        <v>12050</v>
       </c>
       <c r="K24" s="0">
         <v>0</v>
@@ -1076,13 +1088,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="0">
-        <v>0.9684713088910909</v>
+        <v>0.97174101064421936</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1097,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>10751</v>
+        <v>340431</v>
       </c>
       <c r="J25" s="0">
-        <v>350</v>
+        <v>9900</v>
       </c>
       <c r="K25" s="0">
         <v>0</v>
@@ -1108,28 +1120,28 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="0">
-        <v>0.99009900990099009</v>
+        <v>0.9891120993712621</v>
       </c>
       <c r="E26" s="0">
-        <v>0.99502487562189057</v>
+        <v>0.99452625086731938</v>
       </c>
       <c r="F26" s="0">
         <v>1</v>
       </c>
       <c r="G26" s="0">
-        <v>0.99009900990099009</v>
+        <v>0.9891120993712621</v>
       </c>
       <c r="H26" s="0">
-        <v>7100</v>
+        <v>6450</v>
       </c>
       <c r="I26" s="0">
         <v>0</v>
@@ -1143,28 +1155,28 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="0">
-        <v>0.96918142518477202</v>
+        <v>0.98587175904362678</v>
       </c>
       <c r="E27" s="0">
-        <v>0.98434955031513349</v>
+        <v>0.99288562270346337</v>
       </c>
       <c r="F27" s="0">
         <v>1</v>
       </c>
       <c r="G27" s="0">
-        <v>0.96918142518477202</v>
+        <v>0.98587175904362678</v>
       </c>
       <c r="H27" s="0">
-        <v>6950</v>
+        <v>6350</v>
       </c>
       <c r="I27" s="0">
         <v>0</v>
@@ -1173,33 +1185,33 @@
         <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>221</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="0">
-        <v>0.91591400585167282</v>
+        <v>0.99326875718272867</v>
       </c>
       <c r="E28" s="0">
-        <v>0.95611181196467698</v>
+        <v>0.99662301293138955</v>
       </c>
       <c r="F28" s="0">
         <v>1</v>
       </c>
       <c r="G28" s="0">
-        <v>0.91591400585167282</v>
+        <v>0.99326875718272867</v>
       </c>
       <c r="H28" s="0">
-        <v>7200</v>
+        <v>6050</v>
       </c>
       <c r="I28" s="0">
         <v>0</v>
@@ -1208,33 +1220,33 @@
         <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>661</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="0">
-        <v>0.95407708942882585</v>
+        <v>0.99157164105106599</v>
       </c>
       <c r="E29" s="0">
-        <v>0.97649892585118148</v>
+        <v>0.99576798605924821</v>
       </c>
       <c r="F29" s="0">
         <v>1</v>
       </c>
       <c r="G29" s="0">
-        <v>0.95407708942882585</v>
+        <v>0.99157164105106599</v>
       </c>
       <c r="H29" s="0">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="I29" s="0">
         <v>0</v>
@@ -1243,33 +1255,33 @@
         <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>361</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="0">
-        <v>0.92958571219440789</v>
+        <v>0.98667982239763197</v>
       </c>
       <c r="E30" s="0">
-        <v>0.96350807981185049</v>
+        <v>0.99329525701514776</v>
       </c>
       <c r="F30" s="0">
         <v>1</v>
       </c>
       <c r="G30" s="0">
-        <v>0.92958571219440789</v>
+        <v>0.98667982239763197</v>
       </c>
       <c r="H30" s="0">
-        <v>6350</v>
+        <v>6000</v>
       </c>
       <c r="I30" s="0">
         <v>0</v>
@@ -1278,33 +1290,33 @@
         <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>481</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="0">
-        <v>0.98814229249011853</v>
+        <v>0.90647998563992105</v>
       </c>
       <c r="E31" s="0">
-        <v>0.9940357852882703</v>
+        <v>0.95094623858393745</v>
       </c>
       <c r="F31" s="0">
         <v>1</v>
       </c>
       <c r="G31" s="0">
-        <v>0.98814229249011853</v>
+        <v>0.90647998563992105</v>
       </c>
       <c r="H31" s="0">
-        <v>6750</v>
+        <v>5050</v>
       </c>
       <c r="I31" s="0">
         <v>0</v>
@@ -1313,33 +1325,33 @@
         <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>81</v>
+        <v>521</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="0">
-        <v>0.74590062877573671</v>
+        <v>0.97944958538637183</v>
       </c>
       <c r="E32" s="0">
-        <v>0.85445943083115605</v>
+        <v>0.98961811668993993</v>
       </c>
       <c r="F32" s="0">
         <v>1</v>
       </c>
       <c r="G32" s="0">
-        <v>0.74590062877573671</v>
+        <v>0.97944958538637183</v>
       </c>
       <c r="H32" s="0">
-        <v>6050</v>
+        <v>8150</v>
       </c>
       <c r="I32" s="0">
         <v>0</v>
@@ -1348,33 +1360,33 @@
         <v>0</v>
       </c>
       <c r="K32" s="0">
-        <v>2061</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="0">
-        <v>0.99247934903217849</v>
+        <v>0.85121688046996768</v>
       </c>
       <c r="E33" s="0">
-        <v>0.99622548109646669</v>
+        <v>0.91962955767113541</v>
       </c>
       <c r="F33" s="0">
         <v>1</v>
       </c>
       <c r="G33" s="0">
-        <v>0.99247934903217849</v>
+        <v>0.85121688046996768</v>
       </c>
       <c r="H33" s="0">
-        <v>8050</v>
+        <v>7100</v>
       </c>
       <c r="I33" s="0">
         <v>0</v>
@@ -1383,33 +1395,33 @@
         <v>0</v>
       </c>
       <c r="K33" s="0">
-        <v>61</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="0">
-        <v>0.12709710218607015</v>
+        <v>0.9302701828183142</v>
       </c>
       <c r="E34" s="0">
-        <v>0.22552999548940009</v>
+        <v>0.96387561813762468</v>
       </c>
       <c r="F34" s="0">
         <v>1</v>
       </c>
       <c r="G34" s="0">
-        <v>0.12709710218607015</v>
+        <v>0.9302701828183142</v>
       </c>
       <c r="H34" s="0">
-        <v>750</v>
+        <v>5750</v>
       </c>
       <c r="I34" s="0">
         <v>0</v>
@@ -1418,33 +1430,33 @@
         <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>5151</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="0">
-        <v>0.53380782918149461</v>
+        <v>0.99348275313940548</v>
       </c>
       <c r="E35" s="0">
-        <v>0.69605568445475641</v>
+        <v>0.99673072322781275</v>
       </c>
       <c r="F35" s="0">
         <v>1</v>
       </c>
       <c r="G35" s="0">
-        <v>0.53380782918149461</v>
+        <v>0.99348275313940548</v>
       </c>
       <c r="H35" s="0">
-        <v>3150</v>
+        <v>6250</v>
       </c>
       <c r="I35" s="0">
         <v>0</v>
@@ -1453,33 +1465,33 @@
         <v>0</v>
       </c>
       <c r="K35" s="0">
-        <v>2751</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="0">
-        <v>0.034656038814763472</v>
+        <v>0.94547338427664807</v>
       </c>
       <c r="E36" s="0">
-        <v>0.0669904538603249</v>
+        <v>0.9719725717329073</v>
       </c>
       <c r="F36" s="0">
         <v>1</v>
       </c>
       <c r="G36" s="0">
-        <v>0.034656038814763472</v>
+        <v>0.94547338427664807</v>
       </c>
       <c r="H36" s="0">
-        <v>200</v>
+        <v>7300</v>
       </c>
       <c r="I36" s="0">
         <v>0</v>
@@ -1488,33 +1500,33 @@
         <v>0</v>
       </c>
       <c r="K36" s="0">
-        <v>5571</v>
+        <v>421</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="0">
-        <v>0.18194420377750822</v>
+        <v>0.98064350724266125</v>
       </c>
       <c r="E37" s="0">
-        <v>0.30787274593168151</v>
+        <v>0.99022716976247493</v>
       </c>
       <c r="F37" s="0">
         <v>1</v>
       </c>
       <c r="G37" s="0">
-        <v>0.18194420377750822</v>
+        <v>0.98064350724266125</v>
       </c>
       <c r="H37" s="0">
-        <v>1050</v>
+        <v>7650</v>
       </c>
       <c r="I37" s="0">
         <v>0</v>
@@ -1523,82 +1535,82 @@
         <v>0</v>
       </c>
       <c r="K37" s="0">
-        <v>4721</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="0">
-        <v>0.35124979578500243</v>
+        <v>0.27484010449509055</v>
       </c>
       <c r="E38" s="0">
-        <v>0.51988876798452421</v>
+        <v>0</v>
       </c>
       <c r="F38" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="0">
-        <v>0.35124979578500243</v>
+        <v>1</v>
       </c>
       <c r="H38" s="0">
-        <v>2150</v>
+        <v>0</v>
       </c>
       <c r="I38" s="0">
-        <v>0</v>
+        <v>3051</v>
       </c>
       <c r="J38" s="0">
-        <v>0</v>
+        <v>8050</v>
       </c>
       <c r="K38" s="0">
-        <v>3971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="0">
-        <v>0.049011599411860805</v>
+        <v>0.75227456985857133</v>
       </c>
       <c r="E39" s="0">
-        <v>0.093443388880236733</v>
+        <v>0</v>
       </c>
       <c r="F39" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="0">
-        <v>0.049011599411860805</v>
+        <v>1</v>
       </c>
       <c r="H39" s="0">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I39" s="0">
-        <v>0</v>
+        <v>8351</v>
       </c>
       <c r="J39" s="0">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="K39" s="0">
-        <v>5821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>41</v>
@@ -1607,19 +1619,19 @@
         <v>8</v>
       </c>
       <c r="D40" s="0">
-        <v>0.037446171129002059</v>
+        <v>0.99985716326239105</v>
       </c>
       <c r="E40" s="0">
-        <v>0.072189135535101964</v>
+        <v>0.9999285765302478</v>
       </c>
       <c r="F40" s="0">
         <v>1</v>
       </c>
       <c r="G40" s="0">
-        <v>0.037446171129002059</v>
+        <v>0.99985716326239105</v>
       </c>
       <c r="H40" s="0">
-        <v>200</v>
+        <v>7000</v>
       </c>
       <c r="I40" s="0">
         <v>0</v>
@@ -1628,12 +1640,12 @@
         <v>0</v>
       </c>
       <c r="K40" s="0">
-        <v>5141</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>41</v>
@@ -1642,19 +1654,19 @@
         <v>9</v>
       </c>
       <c r="D41" s="0">
-        <v>0.0093615427822505148</v>
+        <v>0.99400672416313407</v>
       </c>
       <c r="E41" s="0">
-        <v>0.018549434242255611</v>
+        <v>0.99699435525254743</v>
       </c>
       <c r="F41" s="0">
         <v>1</v>
       </c>
       <c r="G41" s="0">
-        <v>0.0093615427822505148</v>
+        <v>0.99400672416313407</v>
       </c>
       <c r="H41" s="0">
-        <v>50</v>
+        <v>6800</v>
       </c>
       <c r="I41" s="0">
         <v>0</v>
@@ -1663,12 +1675,12 @@
         <v>0</v>
       </c>
       <c r="K41" s="0">
-        <v>5291</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>41</v>
@@ -1677,19 +1689,19 @@
         <v>8</v>
       </c>
       <c r="D42" s="0">
-        <v>0.52568934735171591</v>
+        <v>0.99074436188241433</v>
       </c>
       <c r="E42" s="0">
-        <v>0.68911714991548556</v>
+        <v>0.99535066465850308</v>
       </c>
       <c r="F42" s="0">
         <v>1</v>
       </c>
       <c r="G42" s="0">
-        <v>0.52568934735171591</v>
+        <v>0.99074436188241433</v>
       </c>
       <c r="H42" s="0">
-        <v>2650</v>
+        <v>7600</v>
       </c>
       <c r="I42" s="0">
         <v>0</v>
@@ -1698,12 +1710,12 @@
         <v>0</v>
       </c>
       <c r="K42" s="0">
-        <v>2391</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>41</v>
@@ -1712,19 +1724,19 @@
         <v>9</v>
       </c>
       <c r="D43" s="0">
-        <v>0.66455068438801823</v>
+        <v>0.99850563782094826</v>
       </c>
       <c r="E43" s="0">
-        <v>0.79847455607198192</v>
+        <v>0.99925226021344571</v>
       </c>
       <c r="F43" s="0">
         <v>1</v>
       </c>
       <c r="G43" s="0">
-        <v>0.66455068438801823</v>
+        <v>0.99850563782094826</v>
       </c>
       <c r="H43" s="0">
-        <v>3350</v>
+        <v>7350</v>
       </c>
       <c r="I43" s="0">
         <v>0</v>
@@ -1733,12 +1745,12 @@
         <v>0</v>
       </c>
       <c r="K43" s="0">
-        <v>1691</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>41</v>
@@ -1747,19 +1759,19 @@
         <v>8</v>
       </c>
       <c r="D44" s="0">
-        <v>0.04725004725004725</v>
+        <v>0.99510345916916754</v>
       </c>
       <c r="E44" s="0">
-        <v>0.090236419418877459</v>
+        <v>0.99754572084553883</v>
       </c>
       <c r="F44" s="0">
         <v>1</v>
       </c>
       <c r="G44" s="0">
-        <v>0.04725004725004725</v>
+        <v>0.99510345916916754</v>
       </c>
       <c r="H44" s="0">
-        <v>250</v>
+        <v>6300</v>
       </c>
       <c r="I44" s="0">
         <v>0</v>
@@ -1768,12 +1780,12 @@
         <v>0</v>
       </c>
       <c r="K44" s="0">
-        <v>5041</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>41</v>
@@ -1782,19 +1794,19 @@
         <v>9</v>
       </c>
       <c r="D45" s="0">
-        <v>0.17955017955017955</v>
+        <v>0.99546186502708245</v>
       </c>
       <c r="E45" s="0">
-        <v>0.30443839128344818</v>
+        <v>0.9977257721370405</v>
       </c>
       <c r="F45" s="0">
         <v>1</v>
       </c>
       <c r="G45" s="0">
-        <v>0.17955017955017955</v>
+        <v>0.99546186502708245</v>
       </c>
       <c r="H45" s="0">
-        <v>950</v>
+        <v>6800</v>
       </c>
       <c r="I45" s="0">
         <v>0</v>
@@ -1803,12 +1815,12 @@
         <v>0</v>
       </c>
       <c r="K45" s="0">
-        <v>4341</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>41</v>
@@ -1817,19 +1829,19 @@
         <v>8</v>
       </c>
       <c r="D46" s="0">
-        <v>0.98988748041589514</v>
+        <v>0.98076678130174499</v>
       </c>
       <c r="E46" s="0">
-        <v>0.99491804452079313</v>
+        <v>0.99029001350395462</v>
       </c>
       <c r="F46" s="0">
         <v>1</v>
       </c>
       <c r="G46" s="0">
-        <v>0.98988748041589514</v>
+        <v>0.98076678130174499</v>
       </c>
       <c r="H46" s="0">
-        <v>6950</v>
+        <v>7700</v>
       </c>
       <c r="I46" s="0">
         <v>0</v>
@@ -1838,12 +1850,12 @@
         <v>0</v>
       </c>
       <c r="K46" s="0">
-        <v>71</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>41</v>
@@ -1852,19 +1864,19 @@
         <v>9</v>
       </c>
       <c r="D47" s="0">
-        <v>0.94715852442671988</v>
+        <v>0.99596406717875274</v>
       </c>
       <c r="E47" s="0">
-        <v>0.97286226318484392</v>
+        <v>0.99797795316678628</v>
       </c>
       <c r="F47" s="0">
         <v>1</v>
       </c>
       <c r="G47" s="0">
-        <v>0.94715852442671988</v>
+        <v>0.99596406717875274</v>
       </c>
       <c r="H47" s="0">
-        <v>6650</v>
+        <v>7650</v>
       </c>
       <c r="I47" s="0">
         <v>0</v>
@@ -1873,12 +1885,12 @@
         <v>0</v>
       </c>
       <c r="K47" s="0">
-        <v>371</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>41</v>
@@ -1887,19 +1899,19 @@
         <v>8</v>
       </c>
       <c r="D48" s="0">
-        <v>0.77649026400668975</v>
+        <v>0.45681779003620065</v>
       </c>
       <c r="E48" s="0">
-        <v>0.87418465469706141</v>
+        <v>0.62714471660158555</v>
       </c>
       <c r="F48" s="0">
         <v>1</v>
       </c>
       <c r="G48" s="0">
-        <v>0.77649026400668975</v>
+        <v>0.45681779003620065</v>
       </c>
       <c r="H48" s="0">
-        <v>6500</v>
+        <v>2650</v>
       </c>
       <c r="I48" s="0">
         <v>0</v>
@@ -1908,12 +1920,12 @@
         <v>0</v>
       </c>
       <c r="K48" s="0">
-        <v>1871</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>41</v>
@@ -1922,19 +1934,19 @@
         <v>9</v>
       </c>
       <c r="D49" s="0">
-        <v>0.65105722135945521</v>
+        <v>0.69815549043268399</v>
       </c>
       <c r="E49" s="0">
-        <v>0.78865494537298308</v>
+        <v>0.82225154806618606</v>
       </c>
       <c r="F49" s="0">
         <v>1</v>
       </c>
       <c r="G49" s="0">
-        <v>0.65105722135945521</v>
+        <v>0.69815549043268399</v>
       </c>
       <c r="H49" s="0">
-        <v>5450</v>
+        <v>4050</v>
       </c>
       <c r="I49" s="0">
         <v>0</v>
@@ -1943,12 +1955,12 @@
         <v>0</v>
       </c>
       <c r="K49" s="0">
-        <v>2921</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>41</v>
@@ -1957,19 +1969,19 @@
         <v>8</v>
       </c>
       <c r="D50" s="0">
-        <v>0.86914198303434853</v>
+        <v>0.27047192687931354</v>
       </c>
       <c r="E50" s="0">
-        <v>0.92999032810058779</v>
+        <v>0.4257818235207752</v>
       </c>
       <c r="F50" s="0">
         <v>1</v>
       </c>
       <c r="G50" s="0">
-        <v>0.86914198303434853</v>
+        <v>0.27047192687931354</v>
       </c>
       <c r="H50" s="0">
-        <v>6250</v>
+        <v>1450</v>
       </c>
       <c r="I50" s="0">
         <v>0</v>
@@ -1978,12 +1990,12 @@
         <v>0</v>
       </c>
       <c r="K50" s="0">
-        <v>941</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>41</v>
@@ -1992,19 +2004,19 @@
         <v>9</v>
       </c>
       <c r="D51" s="0">
-        <v>0.9525796134056459</v>
+        <v>0.19262520638414971</v>
       </c>
       <c r="E51" s="0">
-        <v>0.97571398048572033</v>
+        <v>0.32302722658052607</v>
       </c>
       <c r="F51" s="0">
         <v>1</v>
       </c>
       <c r="G51" s="0">
-        <v>0.9525796134056459</v>
+        <v>0.19262520638414971</v>
       </c>
       <c r="H51" s="0">
-        <v>6850</v>
+        <v>1050</v>
       </c>
       <c r="I51" s="0">
         <v>0</v>
@@ -2013,12 +2025,12 @@
         <v>0</v>
       </c>
       <c r="K51" s="0">
-        <v>341</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>41</v>
@@ -2027,19 +2039,19 @@
         <v>8</v>
       </c>
       <c r="D52" s="0">
-        <v>0.89522128357079811</v>
+        <v>0.62385626351688572</v>
       </c>
       <c r="E52" s="0">
-        <v>0.94471425720178293</v>
+        <v>0.7683638971416864</v>
       </c>
       <c r="F52" s="0">
         <v>1</v>
       </c>
       <c r="G52" s="0">
-        <v>0.89522128357079811</v>
+        <v>0.62385626351688572</v>
       </c>
       <c r="H52" s="0">
-        <v>7100</v>
+        <v>3750</v>
       </c>
       <c r="I52" s="0">
         <v>0</v>
@@ -2048,12 +2060,12 @@
         <v>0</v>
       </c>
       <c r="K52" s="0">
-        <v>831</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>41</v>
@@ -2062,19 +2074,19 @@
         <v>9</v>
       </c>
       <c r="D53" s="0">
-        <v>0.89522128357079811</v>
+        <v>0.41179377367814196</v>
       </c>
       <c r="E53" s="0">
-        <v>0.94471425720178293</v>
+        <v>0.58336250145840629</v>
       </c>
       <c r="F53" s="0">
         <v>1</v>
       </c>
       <c r="G53" s="0">
-        <v>0.89522128357079811</v>
+        <v>0.41179377367814196</v>
       </c>
       <c r="H53" s="0">
-        <v>7100</v>
+        <v>2500</v>
       </c>
       <c r="I53" s="0">
         <v>0</v>
@@ -2083,12 +2095,12 @@
         <v>0</v>
       </c>
       <c r="K53" s="0">
-        <v>831</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>41</v>
@@ -2097,19 +2109,19 @@
         <v>8</v>
       </c>
       <c r="D54" s="0">
-        <v>0.37872412051843124</v>
+        <v>0.29744770677413163</v>
       </c>
       <c r="E54" s="0">
-        <v>0.54938346966182394</v>
+        <v>0.45851205442981802</v>
       </c>
       <c r="F54" s="0">
         <v>1</v>
       </c>
       <c r="G54" s="0">
-        <v>0.37872412051843124</v>
+        <v>0.29744770677413163</v>
       </c>
       <c r="H54" s="0">
-        <v>2250</v>
+        <v>1550</v>
       </c>
       <c r="I54" s="0">
         <v>0</v>
@@ -2118,12 +2130,12 @@
         <v>0</v>
       </c>
       <c r="K54" s="0">
-        <v>3691</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>41</v>
@@ -2132,19 +2144,19 @@
         <v>9</v>
       </c>
       <c r="D55" s="0">
-        <v>0.67328732536610003</v>
+        <v>0.46657779470577032</v>
       </c>
       <c r="E55" s="0">
-        <v>0.80474801327834222</v>
+        <v>0.63628100246721209</v>
       </c>
       <c r="F55" s="0">
         <v>1</v>
       </c>
       <c r="G55" s="0">
-        <v>0.67328732536610003</v>
+        <v>0.46657779470577032</v>
       </c>
       <c r="H55" s="0">
-        <v>4000</v>
+        <v>2450</v>
       </c>
       <c r="I55" s="0">
         <v>0</v>
@@ -2153,12 +2165,12 @@
         <v>0</v>
       </c>
       <c r="K55" s="0">
-        <v>1941</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>41</v>
@@ -2167,19 +2179,19 @@
         <v>8</v>
       </c>
       <c r="D56" s="0">
-        <v>0.91894872266127547</v>
+        <v>0.79647872563403899</v>
       </c>
       <c r="E56" s="0">
-        <v>0.95776266641126317</v>
+        <v>0.88671100221677746</v>
       </c>
       <c r="F56" s="0">
         <v>1</v>
       </c>
       <c r="G56" s="0">
-        <v>0.91894872266127547</v>
+        <v>0.79647872563403899</v>
       </c>
       <c r="H56" s="0">
-        <v>5000</v>
+        <v>3800</v>
       </c>
       <c r="I56" s="0">
         <v>0</v>
@@ -2188,12 +2200,12 @@
         <v>0</v>
       </c>
       <c r="K56" s="0">
-        <v>441</v>
+        <v>971</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>41</v>
@@ -2202,19 +2214,19 @@
         <v>9</v>
       </c>
       <c r="D57" s="0">
-        <v>0.90056974820805002</v>
+        <v>0.88641517212945786</v>
       </c>
       <c r="E57" s="0">
-        <v>0.947683976404603</v>
+        <v>0.93978800131133211</v>
       </c>
       <c r="F57" s="0">
         <v>1</v>
       </c>
       <c r="G57" s="0">
-        <v>0.90056974820805002</v>
+        <v>0.88641517212945786</v>
       </c>
       <c r="H57" s="0">
-        <v>4900</v>
+        <v>4300</v>
       </c>
       <c r="I57" s="0">
         <v>0</v>
@@ -2223,12 +2235,12 @@
         <v>0</v>
       </c>
       <c r="K57" s="0">
-        <v>541</v>
+        <v>551</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>41</v>
@@ -2237,19 +2249,19 @@
         <v>8</v>
       </c>
       <c r="D58" s="0">
-        <v>0.73397488174849124</v>
+        <v>0.25188916876574308</v>
       </c>
       <c r="E58" s="0">
-        <v>0.84658075439751668</v>
+        <v>0.4024144869215292</v>
       </c>
       <c r="F58" s="0">
         <v>1</v>
       </c>
       <c r="G58" s="0">
-        <v>0.73397488174849124</v>
+        <v>0.25188916876574308</v>
       </c>
       <c r="H58" s="0">
-        <v>4500</v>
+        <v>1300</v>
       </c>
       <c r="I58" s="0">
         <v>0</v>
@@ -2258,12 +2270,12 @@
         <v>0</v>
       </c>
       <c r="K58" s="0">
-        <v>1631</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>41</v>
@@ -2272,19 +2284,19 @@
         <v>9</v>
       </c>
       <c r="D59" s="0">
-        <v>0.88892513456206168</v>
+        <v>0.43298563274945878</v>
       </c>
       <c r="E59" s="0">
-        <v>0.94119678784215532</v>
+        <v>0.60431259442384289</v>
       </c>
       <c r="F59" s="0">
         <v>1</v>
       </c>
       <c r="G59" s="0">
-        <v>0.88892513456206168</v>
+        <v>0.43298563274945878</v>
       </c>
       <c r="H59" s="0">
-        <v>5450</v>
+        <v>2200</v>
       </c>
       <c r="I59" s="0">
         <v>0</v>
@@ -2293,12 +2305,12 @@
         <v>0</v>
       </c>
       <c r="K59" s="0">
-        <v>681</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>41</v>
@@ -2307,19 +2319,19 @@
         <v>8</v>
       </c>
       <c r="D60" s="0">
-        <v>0.9089320048942493</v>
+        <v>0.99396259755558825</v>
       </c>
       <c r="E60" s="0">
-        <v>0.95229374599395666</v>
+        <v>0.99697215862934785</v>
       </c>
       <c r="F60" s="0">
         <v>1</v>
       </c>
       <c r="G60" s="0">
-        <v>0.9089320048942493</v>
+        <v>0.99396259755558825</v>
       </c>
       <c r="H60" s="0">
-        <v>5200</v>
+        <v>6750</v>
       </c>
       <c r="I60" s="0">
         <v>0</v>
@@ -2328,12 +2340,12 @@
         <v>0</v>
       </c>
       <c r="K60" s="0">
-        <v>521</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>41</v>
@@ -2342,19 +2354,19 @@
         <v>9</v>
       </c>
       <c r="D61" s="0">
-        <v>0.88271281244537669</v>
+        <v>0.99413531683593193</v>
       </c>
       <c r="E61" s="0">
-        <v>0.9377030916349457</v>
+        <v>0.9970590345025464</v>
       </c>
       <c r="F61" s="0">
         <v>1</v>
       </c>
       <c r="G61" s="0">
-        <v>0.88271281244537669</v>
+        <v>0.99413531683593193</v>
       </c>
       <c r="H61" s="0">
-        <v>5050</v>
+        <v>6950</v>
       </c>
       <c r="I61" s="0">
         <v>0</v>
@@ -2363,12 +2375,12 @@
         <v>0</v>
       </c>
       <c r="K61" s="0">
-        <v>671</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>41</v>
@@ -2377,19 +2389,19 @@
         <v>8</v>
       </c>
       <c r="D62" s="0">
-        <v>0</v>
+        <v>0.99746100834240115</v>
       </c>
       <c r="E62" s="0">
-        <v>0</v>
+        <v>0.99872889050299618</v>
       </c>
       <c r="F62" s="0">
         <v>1</v>
       </c>
       <c r="G62" s="0">
-        <v>0</v>
+        <v>0.99746100834240115</v>
       </c>
       <c r="H62" s="0">
-        <v>0</v>
+        <v>8250</v>
       </c>
       <c r="I62" s="0">
         <v>0</v>
@@ -2398,12 +2410,12 @@
         <v>0</v>
       </c>
       <c r="K62" s="0">
-        <v>6641</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>41</v>
@@ -2412,19 +2424,19 @@
         <v>9</v>
       </c>
       <c r="D63" s="0">
-        <v>0.80560156602921251</v>
+        <v>0.91008372770294865</v>
       </c>
       <c r="E63" s="0">
-        <v>0.89233591860562089</v>
+        <v>0.95292548122736798</v>
       </c>
       <c r="F63" s="0">
         <v>1</v>
       </c>
       <c r="G63" s="0">
-        <v>0.80560156602921251</v>
+        <v>0.91008372770294865</v>
       </c>
       <c r="H63" s="0">
-        <v>5350</v>
+        <v>7500</v>
       </c>
       <c r="I63" s="0">
         <v>0</v>
@@ -2433,12 +2445,12 @@
         <v>0</v>
       </c>
       <c r="K63" s="0">
-        <v>1291</v>
+        <v>741</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>41</v>
@@ -2447,19 +2459,19 @@
         <v>8</v>
       </c>
       <c r="D64" s="0">
-        <v>0.78031212484993995</v>
+        <v>0.98725668673855205</v>
       </c>
       <c r="E64" s="0">
-        <v>0.87660148347943356</v>
+        <v>0.99358748502572047</v>
       </c>
       <c r="F64" s="0">
         <v>1</v>
       </c>
       <c r="G64" s="0">
-        <v>0.78031212484993995</v>
+        <v>0.98725668673855205</v>
       </c>
       <c r="H64" s="0">
-        <v>4550</v>
+        <v>7050</v>
       </c>
       <c r="I64" s="0">
         <v>0</v>
@@ -2468,12 +2480,12 @@
         <v>0</v>
       </c>
       <c r="K64" s="0">
-        <v>1281</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>41</v>
@@ -2482,19 +2494,19 @@
         <v>9</v>
       </c>
       <c r="D65" s="0">
-        <v>0.24009603841536614</v>
+        <v>0.99009900990099009</v>
       </c>
       <c r="E65" s="0">
-        <v>0.38722168441432719</v>
+        <v>0.99502487562189057</v>
       </c>
       <c r="F65" s="0">
         <v>1</v>
       </c>
       <c r="G65" s="0">
-        <v>0.24009603841536614</v>
+        <v>0.99009900990099009</v>
       </c>
       <c r="H65" s="0">
-        <v>1400</v>
+        <v>7100</v>
       </c>
       <c r="I65" s="0">
         <v>0</v>
@@ -2503,12 +2515,12 @@
         <v>0</v>
       </c>
       <c r="K65" s="0">
-        <v>4431</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>41</v>
@@ -2517,19 +2529,19 @@
         <v>8</v>
       </c>
       <c r="D66" s="0">
-        <v>0.9702266330913939</v>
+        <v>0.98154691794267768</v>
       </c>
       <c r="E66" s="0">
-        <v>0.98488835425907828</v>
+        <v>0.99068753715078262</v>
       </c>
       <c r="F66" s="0">
         <v>1</v>
       </c>
       <c r="G66" s="0">
-        <v>0.9702266330913939</v>
+        <v>0.98154691794267768</v>
       </c>
       <c r="H66" s="0">
-        <v>6550</v>
+        <v>7500</v>
       </c>
       <c r="I66" s="0">
         <v>0</v>
@@ -2538,12 +2550,12 @@
         <v>0</v>
       </c>
       <c r="K66" s="0">
-        <v>201</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>41</v>
@@ -2552,19 +2564,19 @@
         <v>9</v>
       </c>
       <c r="D67" s="0">
-        <v>0.9702266330913939</v>
+        <v>0.99466909374593682</v>
       </c>
       <c r="E67" s="0">
-        <v>0.98488835425907828</v>
+        <v>0.99732742324489931</v>
       </c>
       <c r="F67" s="0">
         <v>1</v>
       </c>
       <c r="G67" s="0">
-        <v>0.9702266330913939</v>
+        <v>0.99466909374593682</v>
       </c>
       <c r="H67" s="0">
-        <v>6550</v>
+        <v>7650</v>
       </c>
       <c r="I67" s="0">
         <v>0</v>
@@ -2573,12 +2585,12 @@
         <v>0</v>
       </c>
       <c r="K67" s="0">
-        <v>201</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>41</v>
@@ -2587,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="D68" s="0">
-        <v>0.98903074986513217</v>
+        <v>0.95546835011090259</v>
       </c>
       <c r="E68" s="0">
-        <v>0.99448512792695054</v>
+        <v>0.97722711805252593</v>
       </c>
       <c r="F68" s="0">
         <v>1</v>
       </c>
       <c r="G68" s="0">
-        <v>0.98903074986513217</v>
+        <v>0.95546835011090259</v>
       </c>
       <c r="H68" s="0">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I68" s="0">
         <v>0</v>
@@ -2608,12 +2620,12 @@
         <v>0</v>
       </c>
       <c r="K68" s="0">
-        <v>61</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>41</v>
@@ -2622,19 +2634,19 @@
         <v>9</v>
       </c>
       <c r="D69" s="0">
-        <v>0.98903074986513217</v>
+        <v>0.99444543988532519</v>
       </c>
       <c r="E69" s="0">
-        <v>0.99448512792695054</v>
+        <v>0.99721498517653395</v>
       </c>
       <c r="F69" s="0">
         <v>1</v>
       </c>
       <c r="G69" s="0">
-        <v>0.98903074986513217</v>
+        <v>0.99444543988532519</v>
       </c>
       <c r="H69" s="0">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="I69" s="0">
         <v>0</v>
@@ -2643,12 +2655,12 @@
         <v>0</v>
       </c>
       <c r="K69" s="0">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>41</v>
@@ -2657,19 +2669,19 @@
         <v>8</v>
       </c>
       <c r="D70" s="0">
-        <v>0.0090236419418877455</v>
+        <v>0.98818058515791518</v>
       </c>
       <c r="E70" s="0">
-        <v>0.017885888034340908</v>
+        <v>0.99405516031575869</v>
       </c>
       <c r="F70" s="0">
         <v>1</v>
       </c>
       <c r="G70" s="0">
-        <v>0.0090236419418877455</v>
+        <v>0.98818058515791518</v>
       </c>
       <c r="H70" s="0">
-        <v>50</v>
+        <v>5100</v>
       </c>
       <c r="I70" s="0">
         <v>0</v>
@@ -2678,12 +2690,12 @@
         <v>0</v>
       </c>
       <c r="K70" s="0">
-        <v>5491</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>41</v>
@@ -2692,19 +2704,19 @@
         <v>9</v>
       </c>
       <c r="D71" s="0">
-        <v>0.0090236419418877455</v>
+        <v>0.98405825624876997</v>
       </c>
       <c r="E71" s="0">
-        <v>0.017885888034340908</v>
+        <v>0.99196508282908447</v>
       </c>
       <c r="F71" s="0">
         <v>1</v>
       </c>
       <c r="G71" s="0">
-        <v>0.0090236419418877455</v>
+        <v>0.98405825624876997</v>
       </c>
       <c r="H71" s="0">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="I71" s="0">
         <v>0</v>
@@ -2713,12 +2725,12 @@
         <v>0</v>
       </c>
       <c r="K71" s="0">
-        <v>5491</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>41</v>
@@ -2727,19 +2739,19 @@
         <v>8</v>
       </c>
       <c r="D72" s="0">
-        <v>0.017633574325515784</v>
+        <v>0.99818511796733211</v>
       </c>
       <c r="E72" s="0">
-        <v>0.034656038814763472</v>
+        <v>0.99909173478655766</v>
       </c>
       <c r="F72" s="0">
         <v>1</v>
       </c>
       <c r="G72" s="0">
-        <v>0.017633574325515784</v>
+        <v>0.99818511796733211</v>
       </c>
       <c r="H72" s="0">
-        <v>100</v>
+        <v>6050</v>
       </c>
       <c r="I72" s="0">
         <v>0</v>
@@ -2748,12 +2760,12 @@
         <v>0</v>
       </c>
       <c r="K72" s="0">
-        <v>5571</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>41</v>
@@ -2762,19 +2774,19 @@
         <v>9</v>
       </c>
       <c r="D73" s="0">
-        <v>0.052900722976547347</v>
+        <v>0.99315640126856952</v>
       </c>
       <c r="E73" s="0">
-        <v>0.10048568079048736</v>
+        <v>0.99656645172096148</v>
       </c>
       <c r="F73" s="0">
         <v>1</v>
       </c>
       <c r="G73" s="0">
-        <v>0.052900722976547347</v>
+        <v>0.99315640126856952</v>
       </c>
       <c r="H73" s="0">
-        <v>300</v>
+        <v>5950</v>
       </c>
       <c r="I73" s="0">
         <v>0</v>
@@ -2783,173 +2795,173 @@
         <v>0</v>
       </c>
       <c r="K73" s="0">
-        <v>5371</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C74" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="0">
-        <v>1</v>
+        <v>0.98296199213630409</v>
       </c>
       <c r="E74" s="0">
-        <v>1</v>
+        <v>0.99140779907468601</v>
       </c>
       <c r="F74" s="0">
         <v>1</v>
       </c>
       <c r="G74" s="0">
-        <v>1</v>
+        <v>0.98296199213630409</v>
       </c>
       <c r="H74" s="0">
-        <v>0</v>
+        <v>5250</v>
       </c>
       <c r="I74" s="0">
-        <v>6771</v>
+        <v>0</v>
       </c>
       <c r="J74" s="0">
         <v>0</v>
       </c>
       <c r="K74" s="0">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="0">
-        <v>1</v>
+        <v>0.98494703586693921</v>
       </c>
       <c r="E75" s="0">
-        <v>1</v>
+        <v>0.99241644040820143</v>
       </c>
       <c r="F75" s="0">
         <v>1</v>
       </c>
       <c r="G75" s="0">
-        <v>1</v>
+        <v>0.98494703586693921</v>
       </c>
       <c r="H75" s="0">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I75" s="0">
-        <v>6771</v>
+        <v>0</v>
       </c>
       <c r="J75" s="0">
         <v>0</v>
       </c>
       <c r="K75" s="0">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="0">
-        <v>0.98902425639337066</v>
+        <v>0.77205320287417822</v>
       </c>
       <c r="E76" s="0">
-        <v>0</v>
+        <v>0.87136571477870761</v>
       </c>
       <c r="F76" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" s="0">
-        <v>1</v>
+        <v>0.77205320287417822</v>
       </c>
       <c r="H76" s="0">
-        <v>0</v>
+        <v>5050</v>
       </c>
       <c r="I76" s="0">
-        <v>9011</v>
+        <v>0</v>
       </c>
       <c r="J76" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K76" s="0">
-        <v>0</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="0">
-        <v>0.99451212819668533</v>
+        <v>0.99070263679317172</v>
       </c>
       <c r="E77" s="0">
-        <v>0</v>
+        <v>0.9953296072276242</v>
       </c>
       <c r="F77" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="0">
-        <v>1</v>
+        <v>0.99070263679317172</v>
       </c>
       <c r="H77" s="0">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="I77" s="0">
-        <v>9061</v>
+        <v>0</v>
       </c>
       <c r="J77" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K77" s="0">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C78" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="0">
-        <v>0.98822845516640023</v>
+        <v>0.99412989964021969</v>
       </c>
       <c r="E78" s="0">
-        <v>0.99407938016226882</v>
+        <v>0.99705630994207584</v>
       </c>
       <c r="F78" s="0">
         <v>1</v>
       </c>
       <c r="G78" s="0">
-        <v>0.98822845516640023</v>
+        <v>0.99412989964021969</v>
       </c>
       <c r="H78" s="0">
-        <v>6800</v>
+        <v>5250</v>
       </c>
       <c r="I78" s="0">
         <v>0</v>
@@ -2958,33 +2970,33 @@
         <v>0</v>
       </c>
       <c r="K78" s="0">
-        <v>81</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C79" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="0">
-        <v>0.94463014096788256</v>
+        <v>0.96489615879433932</v>
       </c>
       <c r="E79" s="0">
-        <v>0.97152679171960243</v>
+        <v>0.98213450565896543</v>
       </c>
       <c r="F79" s="0">
         <v>1</v>
       </c>
       <c r="G79" s="0">
-        <v>0.94463014096788256</v>
+        <v>0.96489615879433932</v>
       </c>
       <c r="H79" s="0">
-        <v>6500</v>
+        <v>5250</v>
       </c>
       <c r="I79" s="0">
         <v>0</v>
@@ -2993,33 +3005,33 @@
         <v>0</v>
       </c>
       <c r="K79" s="0">
-        <v>381</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="0">
-        <v>0.72529465095194923</v>
+        <v>0.98787606645711723</v>
       </c>
       <c r="E80" s="0">
-        <v>0.84077771939043622</v>
+        <v>0.99390106166704317</v>
       </c>
       <c r="F80" s="0">
         <v>1</v>
       </c>
       <c r="G80" s="0">
-        <v>0.72529465095194923</v>
+        <v>0.98787606645711723</v>
       </c>
       <c r="H80" s="0">
-        <v>5600</v>
+        <v>6600</v>
       </c>
       <c r="I80" s="0">
         <v>0</v>
@@ -3028,33 +3040,33 @@
         <v>0</v>
       </c>
       <c r="K80" s="0">
-        <v>2121</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C81" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="0">
-        <v>0.69939127056080819</v>
+        <v>0.99238919564244144</v>
       </c>
       <c r="E81" s="0">
-        <v>0.8231079948174681</v>
+        <v>0.99618006141862026</v>
       </c>
       <c r="F81" s="0">
         <v>1</v>
       </c>
       <c r="G81" s="0">
-        <v>0.69939127056080819</v>
+        <v>0.99238919564244144</v>
       </c>
       <c r="H81" s="0">
-        <v>5400</v>
+        <v>6650</v>
       </c>
       <c r="I81" s="0">
         <v>0</v>
@@ -3063,152 +3075,152 @@
         <v>0</v>
       </c>
       <c r="K81" s="0">
-        <v>2321</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C82" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="0">
-        <v>0.96241166741843331</v>
+        <v>0.99434409779237365</v>
       </c>
       <c r="E82" s="0">
-        <v>0</v>
+        <v>0.99716402890860856</v>
       </c>
       <c r="F82" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="0">
-        <v>1</v>
+        <v>0.99434409779237365</v>
       </c>
       <c r="H82" s="0">
-        <v>0</v>
+        <v>5450</v>
       </c>
       <c r="I82" s="0">
-        <v>6401</v>
+        <v>0</v>
       </c>
       <c r="J82" s="0">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="K82" s="0">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C83" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="0">
-        <v>0.95489400090211995</v>
+        <v>0.99429202725096666</v>
       </c>
       <c r="E83" s="0">
-        <v>0</v>
+        <v>0.99713784507432379</v>
       </c>
       <c r="F83" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="0">
-        <v>1</v>
+        <v>0.99429202725096666</v>
       </c>
       <c r="H83" s="0">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="I83" s="0">
-        <v>6351</v>
+        <v>0</v>
       </c>
       <c r="J83" s="0">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K83" s="0">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C84" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="0">
-        <v>1</v>
+        <v>0.010264832683227263</v>
       </c>
       <c r="E84" s="0">
-        <v>1</v>
+        <v>0.020321072952651897</v>
       </c>
       <c r="F84" s="0">
         <v>1</v>
       </c>
       <c r="G84" s="0">
-        <v>1</v>
+        <v>0.010264832683227263</v>
       </c>
       <c r="H84" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I84" s="0">
-        <v>5381</v>
+        <v>0</v>
       </c>
       <c r="J84" s="0">
         <v>0</v>
       </c>
       <c r="K84" s="0">
-        <v>0</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C85" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="0">
-        <v>1</v>
+        <v>0.0098212531919072872</v>
       </c>
       <c r="E85" s="0">
-        <v>1</v>
+        <v>0.019451468585878234</v>
       </c>
       <c r="F85" s="0">
         <v>1</v>
       </c>
       <c r="G85" s="0">
-        <v>1</v>
+        <v>0.0098212531919072872</v>
       </c>
       <c r="H85" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I85" s="0">
-        <v>5381</v>
+        <v>0</v>
       </c>
       <c r="J85" s="0">
         <v>0</v>
       </c>
       <c r="K85" s="0">
-        <v>0</v>
+        <v>5041</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>41</v>
@@ -3217,19 +3229,19 @@
         <v>8</v>
       </c>
       <c r="D86" s="0">
-        <v>0.76371210367970377</v>
+        <v>0.0090073860565663844</v>
       </c>
       <c r="E86" s="0">
-        <v>0.86602808030442191</v>
+        <v>0.017853954650955184</v>
       </c>
       <c r="F86" s="0">
         <v>1</v>
       </c>
       <c r="G86" s="0">
-        <v>0.76371210367970377</v>
+        <v>0.0090073860565663844</v>
       </c>
       <c r="H86" s="0">
-        <v>3300</v>
+        <v>50</v>
       </c>
       <c r="I86" s="0">
         <v>0</v>
@@ -3238,12 +3250,12 @@
         <v>0</v>
       </c>
       <c r="K86" s="0">
-        <v>1021</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>41</v>
@@ -3252,19 +3264,19 @@
         <v>9</v>
       </c>
       <c r="D87" s="0">
-        <v>0.69428373061791249</v>
+        <v>0.0095038965976050188</v>
       </c>
       <c r="E87" s="0">
-        <v>0.81956016937576837</v>
+        <v>0.018828845791752966</v>
       </c>
       <c r="F87" s="0">
         <v>1</v>
       </c>
       <c r="G87" s="0">
-        <v>0.69428373061791249</v>
+        <v>0.0095038965976050188</v>
       </c>
       <c r="H87" s="0">
-        <v>3000</v>
+        <v>50</v>
       </c>
       <c r="I87" s="0">
         <v>0</v>
@@ -3273,77 +3285,567 @@
         <v>0</v>
       </c>
       <c r="K87" s="0">
-        <v>1321</v>
+        <v>5211</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C88" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="0">
-        <v>0.91458000355176705</v>
+        <v>1</v>
       </c>
       <c r="E88" s="0">
-        <v>0.95538447268342452</v>
+        <v>1</v>
       </c>
       <c r="F88" s="0">
         <v>1</v>
       </c>
       <c r="G88" s="0">
-        <v>0.91458000355176705</v>
+        <v>1</v>
       </c>
       <c r="H88" s="0">
-        <v>5150</v>
+        <v>0</v>
       </c>
       <c r="I88" s="0">
-        <v>0</v>
+        <v>6721</v>
       </c>
       <c r="J88" s="0">
         <v>0</v>
       </c>
       <c r="K88" s="0">
-        <v>481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C89" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="0">
-        <v>0.9856153436334576</v>
+        <v>1</v>
       </c>
       <c r="E89" s="0">
-        <v>0.99275556748054739</v>
+        <v>1</v>
       </c>
       <c r="F89" s="0">
         <v>1</v>
       </c>
       <c r="G89" s="0">
-        <v>0.9856153436334576</v>
+        <v>1</v>
       </c>
       <c r="H89" s="0">
-        <v>5550</v>
+        <v>0</v>
       </c>
       <c r="I89" s="0">
-        <v>0</v>
+        <v>6501</v>
       </c>
       <c r="J89" s="0">
         <v>0</v>
       </c>
       <c r="K89" s="0">
-        <v>81</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="0">
+        <v>1</v>
+      </c>
+      <c r="E90" s="0">
+        <v>1</v>
+      </c>
+      <c r="F90" s="0">
+        <v>1</v>
+      </c>
+      <c r="G90" s="0">
+        <v>1</v>
+      </c>
+      <c r="H90" s="0">
+        <v>0</v>
+      </c>
+      <c r="I90" s="0">
+        <v>8991</v>
+      </c>
+      <c r="J90" s="0">
+        <v>0</v>
+      </c>
+      <c r="K90" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="0">
+        <v>0.98353638459005599</v>
+      </c>
+      <c r="E91" s="0">
+        <v>0</v>
+      </c>
+      <c r="F91" s="0">
+        <v>0</v>
+      </c>
+      <c r="G91" s="0">
+        <v>1</v>
+      </c>
+      <c r="H91" s="0">
+        <v>0</v>
+      </c>
+      <c r="I91" s="0">
+        <v>8961</v>
+      </c>
+      <c r="J91" s="0">
+        <v>150</v>
+      </c>
+      <c r="K91" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="0">
+        <v>0.99680413940039569</v>
+      </c>
+      <c r="E92" s="0">
+        <v>0.99839951223229939</v>
+      </c>
+      <c r="F92" s="0">
+        <v>1</v>
+      </c>
+      <c r="G92" s="0">
+        <v>0.99680413940039569</v>
+      </c>
+      <c r="H92" s="0">
+        <v>6550</v>
+      </c>
+      <c r="I92" s="0">
+        <v>0</v>
+      </c>
+      <c r="J92" s="0">
+        <v>0</v>
+      </c>
+      <c r="K92" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="0">
+        <v>0.99373184528359582</v>
+      </c>
+      <c r="E93" s="0">
+        <v>0.99685606931983739</v>
+      </c>
+      <c r="F93" s="0">
+        <v>1</v>
+      </c>
+      <c r="G93" s="0">
+        <v>0.99373184528359582</v>
+      </c>
+      <c r="H93" s="0">
+        <v>6500</v>
+      </c>
+      <c r="I93" s="0">
+        <v>0</v>
+      </c>
+      <c r="J93" s="0">
+        <v>0</v>
+      </c>
+      <c r="K93" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="0">
+        <v>0.99810703837549475</v>
+      </c>
+      <c r="E94" s="0">
+        <v>0.99905262251313409</v>
+      </c>
+      <c r="F94" s="0">
+        <v>1</v>
+      </c>
+      <c r="G94" s="0">
+        <v>0.99810703837549475</v>
+      </c>
+      <c r="H94" s="0">
+        <v>5800</v>
+      </c>
+      <c r="I94" s="0">
+        <v>0</v>
+      </c>
+      <c r="J94" s="0">
+        <v>0</v>
+      </c>
+      <c r="K94" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="0">
+        <v>0.97652750403153554</v>
+      </c>
+      <c r="E95" s="0">
+        <v>0.98812437675641374</v>
+      </c>
+      <c r="F95" s="0">
+        <v>1</v>
+      </c>
+      <c r="G95" s="0">
+        <v>0.97652750403153554</v>
+      </c>
+      <c r="H95" s="0">
+        <v>5450</v>
+      </c>
+      <c r="I95" s="0">
+        <v>0</v>
+      </c>
+      <c r="J95" s="0">
+        <v>0</v>
+      </c>
+      <c r="K95" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="0">
+        <v>0.85608241175579458</v>
+      </c>
+      <c r="E96" s="0">
+        <v>0</v>
+      </c>
+      <c r="F96" s="0">
+        <v>0</v>
+      </c>
+      <c r="G96" s="0">
+        <v>1</v>
+      </c>
+      <c r="H96" s="0">
+        <v>0</v>
+      </c>
+      <c r="I96" s="0">
+        <v>5651</v>
+      </c>
+      <c r="J96" s="0">
+        <v>950</v>
+      </c>
+      <c r="K96" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="0">
+        <v>0.84735154938177382</v>
+      </c>
+      <c r="E97" s="0">
+        <v>0</v>
+      </c>
+      <c r="F97" s="0">
+        <v>0</v>
+      </c>
+      <c r="G97" s="0">
+        <v>1</v>
+      </c>
+      <c r="H97" s="0">
+        <v>0</v>
+      </c>
+      <c r="I97" s="0">
+        <v>5551</v>
+      </c>
+      <c r="J97" s="0">
+        <v>1000</v>
+      </c>
+      <c r="K97" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="0">
+        <v>1</v>
+      </c>
+      <c r="E98" s="0">
+        <v>1</v>
+      </c>
+      <c r="F98" s="0">
+        <v>1</v>
+      </c>
+      <c r="G98" s="0">
+        <v>1</v>
+      </c>
+      <c r="H98" s="0">
+        <v>0</v>
+      </c>
+      <c r="I98" s="0">
+        <v>5351</v>
+      </c>
+      <c r="J98" s="0">
+        <v>0</v>
+      </c>
+      <c r="K98" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="0">
+        <v>0.98120654012403685</v>
+      </c>
+      <c r="E99" s="0">
+        <v>0</v>
+      </c>
+      <c r="F99" s="0">
+        <v>0</v>
+      </c>
+      <c r="G99" s="0">
+        <v>1</v>
+      </c>
+      <c r="H99" s="0">
+        <v>0</v>
+      </c>
+      <c r="I99" s="0">
+        <v>5221</v>
+      </c>
+      <c r="J99" s="0">
+        <v>100</v>
+      </c>
+      <c r="K99" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="0">
+        <v>0.98117210289047996</v>
+      </c>
+      <c r="E100" s="0">
+        <v>0.99049658680230213</v>
+      </c>
+      <c r="F100" s="0">
+        <v>1</v>
+      </c>
+      <c r="G100" s="0">
+        <v>0.98117210289047996</v>
+      </c>
+      <c r="H100" s="0">
+        <v>3700</v>
+      </c>
+      <c r="I100" s="0">
+        <v>0</v>
+      </c>
+      <c r="J100" s="0">
+        <v>0</v>
+      </c>
+      <c r="K100" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="0">
+        <v>0.99275870123802845</v>
+      </c>
+      <c r="E101" s="0">
+        <v>0.99636619388113945</v>
+      </c>
+      <c r="F101" s="0">
+        <v>1</v>
+      </c>
+      <c r="G101" s="0">
+        <v>0.99275870123802845</v>
+      </c>
+      <c r="H101" s="0">
+        <v>4250</v>
+      </c>
+      <c r="I101" s="0">
+        <v>0</v>
+      </c>
+      <c r="J101" s="0">
+        <v>0</v>
+      </c>
+      <c r="K101" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="0">
+        <v>0.98155859607376561</v>
+      </c>
+      <c r="E102" s="0">
+        <v>0.99069348543980784</v>
+      </c>
+      <c r="F102" s="0">
+        <v>1</v>
+      </c>
+      <c r="G102" s="0">
+        <v>0.98155859607376561</v>
+      </c>
+      <c r="H102" s="0">
+        <v>1650</v>
+      </c>
+      <c r="I102" s="0">
+        <v>0</v>
+      </c>
+      <c r="J102" s="0">
+        <v>0</v>
+      </c>
+      <c r="K102" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="0">
+        <v>0.99942889777270127</v>
+      </c>
+      <c r="E103" s="0">
+        <v>0.99971436732362184</v>
+      </c>
+      <c r="F103" s="0">
+        <v>1</v>
+      </c>
+      <c r="G103" s="0">
+        <v>0.99942889777270127</v>
+      </c>
+      <c r="H103" s="0">
+        <v>1750</v>
+      </c>
+      <c r="I103" s="0">
+        <v>0</v>
+      </c>
+      <c r="J103" s="0">
+        <v>0</v>
+      </c>
+      <c r="K103" s="0">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3352,15 +3854,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
-    <col min="3" max="3" width="13.88671875" customWidth="true"/>
-    <col min="4" max="4" width="13.88671875" customWidth="true"/>
-    <col min="5" max="5" width="12.5546875" customWidth="true"/>
-    <col min="6" max="6" width="12.5546875" customWidth="true"/>
+    <col min="3" max="3" width="7.33203125" customWidth="true"/>
+    <col min="4" max="4" width="7.21875" customWidth="true"/>
+    <col min="5" max="5" width="7.6640625" customWidth="true"/>
+    <col min="6" max="6" width="7.5546875" customWidth="true"/>
+    <col min="7" max="7" width="12.5546875" customWidth="true"/>
+    <col min="8" max="8" width="12.5546875" customWidth="true"/>
+    <col min="9" max="9" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="12.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3371,16 +3877,28 @@
         <v>18</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
@@ -3388,19 +3906,31 @@
         <v>9</v>
       </c>
       <c r="B2" s="0">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="C2" s="0">
-        <v>0.86543970903926815</v>
+        <v>317420</v>
       </c>
       <c r="D2" s="0">
-        <v>0.85445039419356728</v>
+        <v>41880</v>
       </c>
       <c r="E2" s="0">
-        <v>0.81303703006991435</v>
+        <v>949704</v>
       </c>
       <c r="F2" s="0">
-        <v>0.82963323064121419</v>
+        <v>36027</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.88344002226551632</v>
+      </c>
+      <c r="H2" s="0">
+        <v>0.89806958327556885</v>
+      </c>
+      <c r="I2" s="0">
+        <v>0.94207791493281567</v>
+      </c>
+      <c r="J2" s="0">
+        <v>0.89069473459726944</v>
       </c>
     </row>
     <row r="3">
@@ -3408,19 +3938,31 @@
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="C3" s="0">
-        <v>0.79807677601075189</v>
+        <v>306640</v>
       </c>
       <c r="D3" s="0">
-        <v>0.7597169833188373</v>
+        <v>75560</v>
       </c>
       <c r="E3" s="0">
-        <v>0.71921865529272322</v>
+        <v>916314</v>
       </c>
       <c r="F3" s="0">
-        <v>0.72562579122491244</v>
+        <v>40177</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.80230245944531664</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0.88415504430290326</v>
+      </c>
+      <c r="I3" s="0">
+        <v>0.9135446492132987</v>
+      </c>
+      <c r="J3" s="0">
+        <v>0.84124238529417006</v>
       </c>
     </row>
   </sheetData>
@@ -3429,15 +3971,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="true"/>
+    <col min="1" max="1" width="9.88671875" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
-    <col min="3" max="3" width="13.88671875" customWidth="true"/>
-    <col min="4" max="4" width="13.88671875" customWidth="true"/>
-    <col min="5" max="5" width="12.5546875" customWidth="true"/>
-    <col min="6" max="6" width="12.5546875" customWidth="true"/>
+    <col min="3" max="3" width="7.33203125" customWidth="true"/>
+    <col min="4" max="4" width="7.21875" customWidth="true"/>
+    <col min="5" max="5" width="8" customWidth="true"/>
+    <col min="6" max="6" width="7.5546875" customWidth="true"/>
+    <col min="7" max="7" width="12.5546875" customWidth="true"/>
+    <col min="8" max="8" width="12.5546875" customWidth="true"/>
+    <col min="9" max="9" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="12.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3448,216 +3994,540 @@
         <v>18</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="0">
         <v>4</v>
       </c>
-      <c r="B2" s="0">
-        <v>2</v>
-      </c>
       <c r="C2" s="0">
-        <v>0.8829057740452011</v>
+        <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>0.92578849721706868</v>
+        <v>62400</v>
       </c>
       <c r="E2" s="0">
-        <v>0.73626202996959322</v>
+        <v>1486014</v>
       </c>
       <c r="F2" s="0">
-        <v>0.81226951929464053</v>
+        <v>0</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0</v>
+      </c>
+      <c r="H2" s="0">
+        <v>0</v>
+      </c>
+      <c r="I2" s="0">
+        <v>0.95970070020033404</v>
+      </c>
+      <c r="J2" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B3" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="0">
-        <v>0.78413115275954004</v>
+        <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>0.81860516934046346</v>
+        <v>150</v>
       </c>
       <c r="E3" s="0">
-        <v>0.7151639344262295</v>
+        <v>31174</v>
       </c>
       <c r="F3" s="0">
-        <v>0.76045521658261594</v>
+        <v>0</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0">
+        <v>0.99521133954795049</v>
+      </c>
+      <c r="J3" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B4" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C4" s="0">
-        <v>0.94626423040348717</v>
+        <v>102400</v>
       </c>
       <c r="D4" s="0">
-        <v>0.9774508640665569</v>
+        <v>0</v>
       </c>
       <c r="E4" s="0">
-        <v>0.92313546269576663</v>
+        <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>0.94932088094146294</v>
+        <v>3516</v>
+      </c>
+      <c r="G4" s="0">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0">
+        <v>0.96680388232184</v>
+      </c>
+      <c r="I4" s="0">
+        <v>0.96680388232184</v>
+      </c>
+      <c r="J4" s="0">
+        <v>0.98312179573340497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B5" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>0.91772227069062395</v>
+        <v>0</v>
       </c>
       <c r="D5" s="0">
-        <v>0.94826725181598071</v>
+        <v>2050</v>
       </c>
       <c r="E5" s="0">
-        <v>0.86978190662254296</v>
+        <v>21774</v>
       </c>
       <c r="F5" s="0">
-        <v>0.90717641394519555</v>
+        <v>0</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0">
+        <v>0.91395231699126933</v>
+      </c>
+      <c r="J5" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B6" s="0">
         <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>0.83522416227047824</v>
+        <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>0.75885221528397262</v>
+        <v>10800</v>
       </c>
       <c r="E6" s="0">
-        <v>0.8614783183241973</v>
+        <v>11402</v>
       </c>
       <c r="F6" s="0">
-        <v>0.80686363935566985</v>
+        <v>0</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0">
+        <v>0.51355733717683094</v>
+      </c>
+      <c r="J6" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B7" s="0">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="C7" s="0">
-        <v>0.86543577117680259</v>
+        <v>248500</v>
       </c>
       <c r="D7" s="0">
-        <v>0.88711551606288452</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>0.81503874686938493</v>
+        <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>0.84954594382637172</v>
+        <v>58662</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0">
+        <v>0.80901934484083315</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0.80901934484083315</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0.89442862747497576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="B8" s="0">
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>0.84470873418680403</v>
+        <v>48970</v>
       </c>
       <c r="D8" s="0">
-        <v>0.73387779794313368</v>
+        <v>3930</v>
       </c>
       <c r="E8" s="0">
-        <v>0.8012048192771084</v>
+        <v>76650</v>
       </c>
       <c r="F8" s="0">
-        <v>0.76569729015201593</v>
+        <v>1052</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.92570888468809076</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0.97896925352844744</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0.96185357038942743</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0.95159441130176248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>0.63041503932765275</v>
+        <v>21950</v>
       </c>
       <c r="D9" s="0">
-        <v>0.55777851021753466</v>
+        <v>5100</v>
       </c>
       <c r="E9" s="0">
-        <v>0.42650602409638555</v>
+        <v>20762</v>
       </c>
       <c r="F9" s="0">
-        <v>0.46772727272727277</v>
+        <v>2450</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.81146025878003691</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0.89959016393442626</v>
+      </c>
+      <c r="I9" s="0">
+        <v>0.84978711551470298</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0.85325558794946554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10" s="0">
         <v>2</v>
       </c>
       <c r="C10" s="0">
-        <v>0.84696479888560372</v>
+        <v>79180</v>
       </c>
       <c r="D10" s="0">
-        <v>0.7209372637944067</v>
+        <v>2020</v>
       </c>
       <c r="E10" s="0">
-        <v>0.80859010270774978</v>
+        <v>64380</v>
       </c>
       <c r="F10" s="0">
-        <v>0.75890625265699652</v>
+        <v>1002</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.97512315270935956</v>
+      </c>
+      <c r="H10" s="0">
+        <v>0.98750342969743832</v>
+      </c>
+      <c r="I10" s="0">
+        <v>0.97938355323300263</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0.9812742437198696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="B11" s="0">
         <v>2</v>
       </c>
       <c r="C11" s="0">
-        <v>0.76381049150390656</v>
+        <v>47330</v>
       </c>
       <c r="D11" s="0">
-        <v>0.74216380182002029</v>
+        <v>3420</v>
       </c>
       <c r="E11" s="0">
-        <v>0.7041170818242295</v>
+        <v>54550</v>
       </c>
       <c r="F11" s="0">
-        <v>0.69833267984839142</v>
+        <v>2832</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.93261083743842366</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0.94354292093616687</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0.94218177782710022</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0.93804502933248768</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="0">
+        <v>2</v>
+      </c>
+      <c r="C12" s="0">
+        <v>24700</v>
+      </c>
+      <c r="D12" s="0">
+        <v>10250</v>
+      </c>
+      <c r="E12" s="0">
+        <v>27972</v>
+      </c>
+      <c r="F12" s="0">
+        <v>870</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0.70672389127324753</v>
+      </c>
+      <c r="H12" s="0">
+        <v>0.96597575283535397</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0.82568347128166542</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0.81625908790482482</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="0">
+        <v>2</v>
+      </c>
+      <c r="C13" s="0">
+        <v>22920</v>
+      </c>
+      <c r="D13" s="0">
+        <v>3830</v>
+      </c>
+      <c r="E13" s="0">
+        <v>24772</v>
+      </c>
+      <c r="F13" s="0">
+        <v>2060</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0.856822429906542</v>
+      </c>
+      <c r="H13" s="0">
+        <v>0.91753402722177746</v>
+      </c>
+      <c r="I13" s="0">
+        <v>0.89007502519502824</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0.88613957084863704</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="0">
+        <v>2</v>
+      </c>
+      <c r="C14" s="0">
+        <v>7750</v>
+      </c>
+      <c r="D14" s="0">
+        <v>3600</v>
+      </c>
+      <c r="E14" s="0">
+        <v>14502</v>
+      </c>
+      <c r="F14" s="0">
+        <v>550</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.68281938325991187</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0.9337349397590361</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0.84281493826225284</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0.78880407124681939</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="0">
+        <v>2</v>
+      </c>
+      <c r="C15" s="0">
+        <v>5770</v>
+      </c>
+      <c r="D15" s="0">
+        <v>3130</v>
+      </c>
+      <c r="E15" s="0">
+        <v>8012</v>
+      </c>
+      <c r="F15" s="0">
+        <v>2530</v>
+      </c>
+      <c r="G15" s="0">
+        <v>0.64831460674157304</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0.69518072289156629</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0.70887768748071189</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0.67093023255813955</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="0">
+        <v>2</v>
+      </c>
+      <c r="C16" s="0">
+        <v>7510</v>
+      </c>
+      <c r="D16" s="0">
+        <v>3440</v>
+      </c>
+      <c r="E16" s="0">
+        <v>15532</v>
+      </c>
+      <c r="F16" s="0">
+        <v>350</v>
+      </c>
+      <c r="G16" s="0">
+        <v>0.68584474885844748</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0.95547073791348602</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0.85875074537865237</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0.79851143009037751</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="0">
+        <v>2</v>
+      </c>
+      <c r="C17" s="0">
+        <v>7080</v>
+      </c>
+      <c r="D17" s="0">
+        <v>3320</v>
+      </c>
+      <c r="E17" s="0">
+        <v>8522</v>
+      </c>
+      <c r="F17" s="0">
+        <v>330</v>
+      </c>
+      <c r="G17" s="0">
+        <v>0.68076923076923079</v>
+      </c>
+      <c r="H17" s="0">
+        <v>0.95546558704453444</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0.81040930812383127</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0.7950589556428973</v>
       </c>
     </row>
   </sheetData>
@@ -3666,15 +4536,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.21875" customWidth="true"/>
+    <col min="1" max="1" width="9.33203125" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
-    <col min="3" max="3" width="13.88671875" customWidth="true"/>
-    <col min="4" max="4" width="13.88671875" customWidth="true"/>
-    <col min="5" max="5" width="11.44140625" customWidth="true"/>
-    <col min="6" max="6" width="12.5546875" customWidth="true"/>
+    <col min="3" max="3" width="7.33203125" customWidth="true"/>
+    <col min="4" max="4" width="7.21875" customWidth="true"/>
+    <col min="5" max="5" width="7.6640625" customWidth="true"/>
+    <col min="6" max="6" width="7.5546875" customWidth="true"/>
+    <col min="7" max="7" width="12.5546875" customWidth="true"/>
+    <col min="8" max="8" width="12.5546875" customWidth="true"/>
+    <col min="9" max="9" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="12.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3685,16 +4559,28 @@
         <v>18</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
@@ -3702,19 +4588,31 @@
         <v>2</v>
       </c>
       <c r="B2" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C2" s="0">
-        <v>0.83527896716460304</v>
+        <v>161420</v>
       </c>
       <c r="D2" s="0">
-        <v>0.80360186286108404</v>
+        <v>66530</v>
       </c>
       <c r="E2" s="0">
-        <v>0.80249697999563452</v>
+        <v>969164</v>
       </c>
       <c r="F2" s="0">
-        <v>0.79477573387702738</v>
+        <v>5166</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.70813774950647068</v>
+      </c>
+      <c r="H2" s="0">
+        <v>0.96898899067148503</v>
+      </c>
+      <c r="I2" s="0">
+        <v>0.94036663672355858</v>
+      </c>
+      <c r="J2" s="0">
+        <v>0.81827767301336263</v>
       </c>
     </row>
     <row r="3">
@@ -3722,19 +4620,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3" s="0">
-        <v>0.82823751788541689</v>
+        <v>136140</v>
       </c>
       <c r="D3" s="0">
-        <v>0.81056551465132043</v>
+        <v>50660</v>
       </c>
       <c r="E3" s="0">
-        <v>0.72975870536700294</v>
+        <v>868330</v>
       </c>
       <c r="F3" s="0">
-        <v>0.76048328798909925</v>
+        <v>9056</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.7288008565310492</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0.93762913578886475</v>
+      </c>
+      <c r="I3" s="0">
+        <v>0.94388574929570579</v>
+      </c>
+      <c r="J3" s="0">
+        <v>0.82013036301642195</v>
       </c>
     </row>
     <row r="4">
@@ -3745,16 +4655,28 @@
         <v>4</v>
       </c>
       <c r="C4" s="0">
-        <v>0.95731788259156525</v>
+        <v>28750</v>
       </c>
       <c r="D4" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="0">
-        <v>0.95731788259156525</v>
+        <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>0.9779962909382206</v>
+        <v>124</v>
+      </c>
+      <c r="G4" s="0">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0">
+        <v>0.99570547897762696</v>
+      </c>
+      <c r="I4" s="0">
+        <v>0.99570547897762696</v>
+      </c>
+      <c r="J4" s="0">
+        <v>0.99784811883937252</v>
       </c>
     </row>
     <row r="5">
@@ -3765,16 +4687,28 @@
         <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>0.91402699562311041</v>
+        <v>28450</v>
       </c>
       <c r="D5" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>0.91402699562311041</v>
+        <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>0.9520571942569358</v>
+        <v>244</v>
+      </c>
+      <c r="G5" s="0">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0">
+        <v>0.99149648010036939</v>
+      </c>
+      <c r="I5" s="0">
+        <v>0.99149648010036939</v>
+      </c>
+      <c r="J5" s="0">
+        <v>0.995730085398292</v>
       </c>
     </row>
     <row r="6">
@@ -3785,16 +4719,28 @@
         <v>4</v>
       </c>
       <c r="C6" s="0">
-        <v>0.2193762934899591</v>
+        <v>9200</v>
       </c>
       <c r="D6" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>0.2193762934899591</v>
+        <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>0.32411221993404071</v>
+        <v>13214</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0">
+        <v>0.41045774962077275</v>
+      </c>
+      <c r="I6" s="0">
+        <v>0.41045774962077275</v>
+      </c>
+      <c r="J6" s="0">
+        <v>0.58202062377427732</v>
       </c>
     </row>
     <row r="7">
@@ -3805,16 +4751,28 @@
         <v>4</v>
       </c>
       <c r="C7" s="0">
-        <v>0.11176727727702895</v>
+        <v>10250</v>
       </c>
       <c r="D7" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>0.11176727727702895</v>
+        <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>0.17601768166052964</v>
+        <v>12294</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0">
+        <v>0.45466643009226404</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0.45466643009226404</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0.62511435018600969</v>
       </c>
     </row>
     <row r="8">
@@ -3825,16 +4783,28 @@
         <v>4</v>
       </c>
       <c r="C8" s="0">
-        <v>0.35426006463499021</v>
+        <v>11600</v>
       </c>
       <c r="D8" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>0.35426006463499021</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>0.47056662917244829</v>
+        <v>8264</v>
+      </c>
+      <c r="G8" s="0">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0.58397100281917036</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0.58397100281917036</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0.73735062293414699</v>
       </c>
     </row>
     <row r="9">
@@ -3845,16 +4815,28 @@
         <v>4</v>
       </c>
       <c r="C9" s="0">
-        <v>0.84114837255218999</v>
+        <v>29450</v>
       </c>
       <c r="D9" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0">
-        <v>0.84114837255218999</v>
+        <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>0.90765497694392039</v>
+        <v>844</v>
+      </c>
+      <c r="G9" s="0">
+        <v>1</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0.97213969762989372</v>
+      </c>
+      <c r="I9" s="0">
+        <v>0.97213969762989372</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0.98587305838243167</v>
       </c>
     </row>
     <row r="10">
@@ -3865,16 +4847,28 @@
         <v>4</v>
       </c>
       <c r="C10" s="0">
-        <v>0.90304104089539772</v>
+        <v>29300</v>
       </c>
       <c r="D10" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0">
-        <v>0.90304104089539772</v>
+        <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>0.94878320574746844</v>
+        <v>344</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0">
+        <v>0.98839562812036164</v>
+      </c>
+      <c r="I10" s="0">
+        <v>0.98839562812036164</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0.99416395222584153</v>
       </c>
     </row>
     <row r="11">
@@ -3885,16 +4879,28 @@
         <v>4</v>
       </c>
       <c r="C11" s="0">
-        <v>0.71788247918846426</v>
+        <v>21250</v>
       </c>
       <c r="D11" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="0">
-        <v>0.71788247918846426</v>
+        <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>0.81489453143900814</v>
+        <v>434</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0.97998524257517061</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0.97998524257517061</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0.98989146131271244</v>
       </c>
     </row>
     <row r="12">
@@ -3905,16 +4911,28 @@
         <v>4</v>
       </c>
       <c r="C12" s="0">
-        <v>0.85363620841254462</v>
+        <v>22550</v>
       </c>
       <c r="D12" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0">
-        <v>0.85363620841254462</v>
+        <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>0.91944359496714356</v>
+        <v>224</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0">
+        <v>0.99016422235883028</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0.99016422235883028</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0.99505780601888627</v>
       </c>
     </row>
     <row r="13">
@@ -3925,16 +4943,28 @@
         <v>4</v>
       </c>
       <c r="C13" s="0">
-        <v>0.45650243232362964</v>
+        <v>22050</v>
       </c>
       <c r="D13" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0">
-        <v>0.45650243232362964</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>0.5390397716248454</v>
+        <v>1774</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1</v>
+      </c>
+      <c r="H13" s="0">
+        <v>0.92553727333781066</v>
+      </c>
+      <c r="I13" s="0">
+        <v>0.92553727333781066</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0.96132885730479145</v>
       </c>
     </row>
     <row r="14">
@@ -3945,16 +4975,28 @@
         <v>8</v>
       </c>
       <c r="C14" s="0">
-        <v>0.93272396272038927</v>
+        <v>48950</v>
       </c>
       <c r="D14" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0">
-        <v>0.93272396272038927</v>
+        <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>0.96407144990550653</v>
+        <v>448</v>
+      </c>
+      <c r="G14" s="0">
+        <v>1</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0.9909308069152597</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0.9909308069152597</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0.99544474722414289</v>
       </c>
     </row>
     <row r="15">
@@ -3965,16 +5007,28 @@
         <v>4</v>
       </c>
       <c r="C15" s="0">
-        <v>0.75062181202059697</v>
+        <v>26300</v>
       </c>
       <c r="D15" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0">
-        <v>0.75062181202059697</v>
+        <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>0.83916486568997939</v>
+        <v>2014</v>
+      </c>
+      <c r="G15" s="0">
+        <v>1</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0.9288691106872925</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0.9288691106872925</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0.96312300875233459</v>
       </c>
     </row>
     <row r="16">
@@ -3985,16 +5039,28 @@
         <v>4</v>
       </c>
       <c r="C16" s="0">
-        <v>0.78739374002322404</v>
+        <v>26950</v>
       </c>
       <c r="D16" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0">
-        <v>0.78739374002322404</v>
+        <v>0</v>
       </c>
       <c r="F16" s="0">
-        <v>0.87358577122461334</v>
+        <v>1044</v>
+      </c>
+      <c r="G16" s="0">
+        <v>1</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0.96270629420590126</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0.96270629420590126</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0.98099883517763542</v>
       </c>
     </row>
     <row r="17">
@@ -4005,16 +5071,28 @@
         <v>6</v>
       </c>
       <c r="C17" s="0">
-        <v>0.9013703843504689</v>
+        <v>11250</v>
       </c>
       <c r="D17" s="0">
-        <v>0.66666666666666663</v>
+        <v>250</v>
       </c>
       <c r="E17" s="0">
-        <v>0.90411432025212635</v>
+        <v>28524</v>
       </c>
       <c r="F17" s="0">
-        <v>0.6106476190346507</v>
+        <v>142</v>
+      </c>
+      <c r="G17" s="0">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="H17" s="0">
+        <v>0.9875351123595506</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0.99024050191704427</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0.9828761139262624</v>
       </c>
     </row>
     <row r="18">
@@ -4025,16 +5103,28 @@
         <v>4</v>
       </c>
       <c r="C18" s="0">
-        <v>0.022145395296459654</v>
+        <v>200</v>
       </c>
       <c r="D18" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0">
-        <v>0.022145395296459654</v>
+        <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>0.042728373918483165</v>
+        <v>20574</v>
+      </c>
+      <c r="G18" s="0">
+        <v>1</v>
+      </c>
+      <c r="H18" s="0">
+        <v>0.00962741888899586</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0.00962741888899586</v>
+      </c>
+      <c r="J18" s="0">
+        <v>0.019071231047964148</v>
       </c>
     </row>
   </sheetData>

--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -10,6 +10,7 @@
     <sheet name="By_Wrist" sheetId="3" r:id="rId5"/>
     <sheet name="By_Activity" sheetId="4" r:id="rId6"/>
     <sheet name="By_Subject" sheetId="5" r:id="rId7"/>
+    <sheet name="Data_Quality" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="5766" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12930" uniqueCount="59">
   <si>
     <t>Subject</t>
   </si>
@@ -183,6 +184,18 @@
   <si>
     <t>sum_FN</t>
   </si>
+  <si>
+    <t>TotalSec</t>
+  </si>
+  <si>
+    <t>ValidSec</t>
+  </si>
+  <si>
+    <t>RemovedSec</t>
+  </si>
+  <si>
+    <t>RemovedPct</t>
+  </si>
 </sst>
 </file>
 
@@ -233,10 +246,10 @@
     <col min="1" max="1" width="9.33203125" customWidth="true"/>
     <col min="2" max="2" width="9.88671875" customWidth="true"/>
     <col min="3" max="3" width="5.33203125" customWidth="true"/>
-    <col min="4" max="4" width="14.5546875" customWidth="true"/>
-    <col min="5" max="5" width="13.5546875" customWidth="true"/>
+    <col min="4" max="4" width="12.5546875" customWidth="true"/>
+    <col min="5" max="5" width="12.5546875" customWidth="true"/>
     <col min="6" max="6" width="12.5546875" customWidth="true"/>
-    <col min="7" max="7" width="14.5546875" customWidth="true"/>
+    <col min="7" max="7" width="12.5546875" customWidth="true"/>
     <col min="8" max="8" width="6" customWidth="true"/>
     <col min="9" max="9" width="7" customWidth="true"/>
     <col min="10" max="10" width="6" customWidth="true"/>
@@ -289,28 +302,28 @@
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>0.84680275357128643</v>
+        <v>0.83684838838042186</v>
       </c>
       <c r="E2" s="0">
-        <v>0.85048543689320399</v>
+        <v>0.83794466403162049</v>
       </c>
       <c r="F2" s="0">
-        <v>0.80811808118081185</v>
+        <v>0.80916030534351147</v>
       </c>
       <c r="G2" s="0">
-        <v>0.89754098360655743</v>
+        <v>0.86885245901639341</v>
       </c>
       <c r="H2" s="0">
-        <v>10950</v>
+        <v>10600</v>
       </c>
       <c r="I2" s="0">
-        <v>10331</v>
+        <v>10430</v>
       </c>
       <c r="J2" s="0">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="K2" s="0">
-        <v>1250</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="3">
@@ -324,7 +337,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>0.85277147745811943</v>
+        <v>0.85276561878233192</v>
       </c>
       <c r="E3" s="0">
         <v>0.85603112840466933</v>
@@ -339,7 +352,7 @@
         <v>11000</v>
       </c>
       <c r="I3" s="0">
-        <v>10431</v>
+        <v>10430</v>
       </c>
       <c r="J3" s="0">
         <v>2500</v>
@@ -359,28 +372,28 @@
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>0.97999753563067316</v>
+        <v>0.97528248587570621</v>
       </c>
       <c r="E4" s="0">
-        <v>0.98172402146583104</v>
+        <v>0.97664486854397448</v>
       </c>
       <c r="F4" s="0">
-        <v>0.97855361596009971</v>
+        <v>0.98017680150013398</v>
       </c>
       <c r="G4" s="0">
-        <v>0.98491503727316076</v>
+        <v>0.97313829787234041</v>
       </c>
       <c r="H4" s="0">
-        <v>39240</v>
+        <v>36590</v>
       </c>
       <c r="I4" s="0">
-        <v>32340</v>
+        <v>32460</v>
       </c>
       <c r="J4" s="0">
-        <v>860</v>
+        <v>740</v>
       </c>
       <c r="K4" s="0">
-        <v>601</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="5">
@@ -394,19 +407,19 @@
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>0.97877374525774741</v>
+        <v>0.97508169934640521</v>
       </c>
       <c r="E5" s="0">
-        <v>0.98083275008902149</v>
+        <v>0.97739903668025196</v>
       </c>
       <c r="F5" s="0">
-        <v>0.97177615571776155</v>
+        <v>0.97151976430149767</v>
       </c>
       <c r="G5" s="0">
-        <v>0.99005974071044345</v>
+        <v>0.98334990059642147</v>
       </c>
       <c r="H5" s="0">
-        <v>39940</v>
+        <v>39570</v>
       </c>
       <c r="I5" s="0">
         <v>32040</v>
@@ -415,7 +428,7 @@
         <v>1160</v>
       </c>
       <c r="K5" s="0">
-        <v>401</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6">
@@ -429,28 +442,28 @@
         <v>8</v>
       </c>
       <c r="D6" s="0">
-        <v>0.96480277557108352</v>
+        <v>0.95087001023541451</v>
       </c>
       <c r="E6" s="0">
-        <v>0.95157368784992524</v>
+        <v>0.87368421052631584</v>
       </c>
       <c r="F6" s="0">
-        <v>0.91939655172413792</v>
+        <v>0.88770053475935828</v>
       </c>
       <c r="G6" s="0">
-        <v>0.98608478572419211</v>
+        <v>0.86010362694300513</v>
       </c>
       <c r="H6" s="0">
-        <v>21330</v>
+        <v>8300</v>
       </c>
       <c r="I6" s="0">
-        <v>38180</v>
+        <v>38150</v>
       </c>
       <c r="J6" s="0">
-        <v>1870</v>
+        <v>1050</v>
       </c>
       <c r="K6" s="0">
-        <v>301</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="7">
@@ -464,28 +477,28 @@
         <v>9</v>
       </c>
       <c r="D7" s="0">
-        <v>0.95921417274850918</v>
+        <v>0.95156273144719306</v>
       </c>
       <c r="E7" s="0">
-        <v>0.95161040436556443</v>
+        <v>0.93895837222325929</v>
       </c>
       <c r="F7" s="0">
-        <v>0.9306397306397306</v>
+        <v>0.94584430236931172</v>
       </c>
       <c r="G7" s="0">
-        <v>0.97354795533795924</v>
+        <v>0.9321719792438844</v>
       </c>
       <c r="H7" s="0">
-        <v>27640</v>
+        <v>25150</v>
       </c>
       <c r="I7" s="0">
-        <v>38470</v>
+        <v>39090</v>
       </c>
       <c r="J7" s="0">
-        <v>2060</v>
+        <v>1440</v>
       </c>
       <c r="K7" s="0">
-        <v>751</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="8">
@@ -499,28 +512,28 @@
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <v>0.94915694385190408</v>
+        <v>0.9518318765110656</v>
       </c>
       <c r="E8" s="0">
-        <v>0.94537773260795921</v>
+        <v>0.94823106136318203</v>
       </c>
       <c r="F8" s="0">
-        <v>0.94501992031872506</v>
+        <v>0.95070140280561122</v>
       </c>
       <c r="G8" s="0">
-        <v>0.94573581595630163</v>
+        <v>0.94577352472089316</v>
       </c>
       <c r="H8" s="0">
         <v>23720</v>
       </c>
       <c r="I8" s="0">
-        <v>27450</v>
+        <v>27460</v>
       </c>
       <c r="J8" s="0">
-        <v>1380</v>
+        <v>1230</v>
       </c>
       <c r="K8" s="0">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="9">
@@ -534,28 +547,28 @@
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <v>0.93524649121189207</v>
+        <v>0.93144863266814482</v>
       </c>
       <c r="E9" s="0">
-        <v>0.93079182353984746</v>
+        <v>0.92657827033445472</v>
       </c>
       <c r="F9" s="0">
-        <v>0.92046783625730999</v>
+        <v>0.91984282907662085</v>
       </c>
       <c r="G9" s="0">
-        <v>0.94135002591603201</v>
+        <v>0.93341307814992025</v>
       </c>
       <c r="H9" s="0">
-        <v>23610</v>
+        <v>23410</v>
       </c>
       <c r="I9" s="0">
-        <v>27100</v>
+        <v>27000</v>
       </c>
       <c r="J9" s="0">
         <v>2040</v>
       </c>
       <c r="K9" s="0">
-        <v>1471</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="10">
@@ -569,28 +582,28 @@
         <v>8</v>
       </c>
       <c r="D10" s="0">
-        <v>0.78419748439509429</v>
+        <v>0.80334595959595956</v>
       </c>
       <c r="E10" s="0">
-        <v>0.77604166666666663</v>
+        <v>0.78744455817127257</v>
       </c>
       <c r="F10" s="0">
-        <v>0.66406685236768803</v>
+        <v>0.68936678614097968</v>
       </c>
       <c r="G10" s="0">
-        <v>0.93343774471417384</v>
+        <v>0.91805887032617339</v>
       </c>
       <c r="H10" s="0">
-        <v>11920</v>
+        <v>11540</v>
       </c>
       <c r="I10" s="0">
-        <v>13081</v>
+        <v>13910</v>
       </c>
       <c r="J10" s="0">
-        <v>6030</v>
+        <v>5200</v>
       </c>
       <c r="K10" s="0">
-        <v>850</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="11">
@@ -604,28 +617,28 @@
         <v>9</v>
       </c>
       <c r="D11" s="0">
-        <v>0.86713045658236976</v>
+        <v>0.84330930742713883</v>
       </c>
       <c r="E11" s="0">
-        <v>0.85771812080536913</v>
+        <v>0.82078853046594979</v>
       </c>
       <c r="F11" s="0">
-        <v>0.75176470588235289</v>
+        <v>0.75827814569536423</v>
       </c>
       <c r="G11" s="0">
-        <v>0.99843749999999998</v>
+        <v>0.89453125</v>
       </c>
       <c r="H11" s="0">
-        <v>12780</v>
+        <v>11450</v>
       </c>
       <c r="I11" s="0">
-        <v>14891</v>
+        <v>15460</v>
       </c>
       <c r="J11" s="0">
-        <v>4220</v>
+        <v>3650</v>
       </c>
       <c r="K11" s="0">
-        <v>20</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="12">
@@ -639,28 +652,28 @@
         <v>8</v>
       </c>
       <c r="D12" s="0">
-        <v>0.87785290052668929</v>
+        <v>0.86413248024087319</v>
       </c>
       <c r="E12" s="0">
-        <v>0.87408548324990376</v>
+        <v>0.8591494342567304</v>
       </c>
       <c r="F12" s="0">
-        <v>0.84074074074074079</v>
+        <v>0.82410179640718562</v>
       </c>
       <c r="G12" s="0">
-        <v>0.91018444266238974</v>
+        <v>0.89731051344743273</v>
       </c>
       <c r="H12" s="0">
-        <v>11350</v>
+        <v>11010</v>
       </c>
       <c r="I12" s="0">
-        <v>12151</v>
+        <v>11950</v>
       </c>
       <c r="J12" s="0">
-        <v>2150</v>
+        <v>2350</v>
       </c>
       <c r="K12" s="0">
-        <v>1120</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="13">
@@ -674,28 +687,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <v>0.90227891537055682</v>
+        <v>0.88913942127019918</v>
       </c>
       <c r="E13" s="0">
-        <v>0.89829192546583847</v>
+        <v>0.88353730754046578</v>
       </c>
       <c r="F13" s="0">
-        <v>0.8732075471698113</v>
+        <v>0.85944700460829493</v>
       </c>
       <c r="G13" s="0">
-        <v>0.92486011191047157</v>
+        <v>0.90901705930138099</v>
       </c>
       <c r="H13" s="0">
-        <v>11570</v>
+        <v>11190</v>
       </c>
       <c r="I13" s="0">
-        <v>12621</v>
+        <v>12470</v>
       </c>
       <c r="J13" s="0">
-        <v>1680</v>
+        <v>1830</v>
       </c>
       <c r="K13" s="0">
-        <v>940</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="14">
@@ -709,13 +722,13 @@
         <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>0.78789485645026891</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="E14" s="0">
-        <v>0.73076923076923073</v>
+        <v>0.7342995169082126</v>
       </c>
       <c r="F14" s="0">
-        <v>0.60799999999999998</v>
+        <v>0.61290322580645162</v>
       </c>
       <c r="G14" s="0">
         <v>0.91566265060240959</v>
@@ -724,10 +737,10 @@
         <v>3800</v>
       </c>
       <c r="I14" s="0">
-        <v>6601</v>
+        <v>6650</v>
       </c>
       <c r="J14" s="0">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="K14" s="0">
         <v>350</v>
@@ -744,28 +757,28 @@
         <v>9</v>
       </c>
       <c r="D15" s="0">
-        <v>0.89773502007423678</v>
+        <v>0.90151515151515149</v>
       </c>
       <c r="E15" s="0">
-        <v>0.8540540540540541</v>
+        <v>0.86021505376344087</v>
       </c>
       <c r="F15" s="0">
-        <v>0.77450980392156865</v>
+        <v>0.77669902912621358</v>
       </c>
       <c r="G15" s="0">
-        <v>0.95180722891566261</v>
+        <v>0.96385542168674698</v>
       </c>
       <c r="H15" s="0">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="I15" s="0">
-        <v>7901</v>
+        <v>7900</v>
       </c>
       <c r="J15" s="0">
         <v>1150</v>
       </c>
       <c r="K15" s="0">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -779,13 +792,13 @@
         <v>8</v>
       </c>
       <c r="D16" s="0">
-        <v>0.6580397048123896</v>
+        <v>0.67728237791932056</v>
       </c>
       <c r="E16" s="0">
-        <v>0.58089171974522291</v>
+        <v>0.59999999999999998</v>
       </c>
       <c r="F16" s="0">
-        <v>0.61621621621621625</v>
+        <v>0.66086956521739126</v>
       </c>
       <c r="G16" s="0">
         <v>0.54939759036144575</v>
@@ -794,10 +807,10 @@
         <v>2280</v>
       </c>
       <c r="I16" s="0">
-        <v>4051</v>
+        <v>4100</v>
       </c>
       <c r="J16" s="0">
-        <v>1420</v>
+        <v>1170</v>
       </c>
       <c r="K16" s="0">
         <v>1870</v>
@@ -814,13 +827,13 @@
         <v>9</v>
       </c>
       <c r="D17" s="0">
-        <v>0.75868037878016492</v>
+        <v>0.76646090534979427</v>
       </c>
       <c r="E17" s="0">
-        <v>0.74652406417112305</v>
+        <v>0.75459459459459466</v>
       </c>
       <c r="F17" s="0">
-        <v>0.6711538461538461</v>
+        <v>0.68431372549019609</v>
       </c>
       <c r="G17" s="0">
         <v>0.84096385542168672</v>
@@ -829,10 +842,10 @@
         <v>3490</v>
       </c>
       <c r="I17" s="0">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="J17" s="0">
-        <v>1710</v>
+        <v>1610</v>
       </c>
       <c r="K17" s="0">
         <v>660</v>
@@ -849,28 +862,28 @@
         <v>8</v>
       </c>
       <c r="D18" s="0">
-        <v>0.82039091389329111</v>
+        <v>0.86677240285487711</v>
       </c>
       <c r="E18" s="0">
-        <v>0.75156576200417524</v>
+        <v>0.79361179361179368</v>
       </c>
       <c r="F18" s="0">
-        <v>0.62068965517241381</v>
+        <v>0.6857749469214437</v>
       </c>
       <c r="G18" s="0">
-        <v>0.95238095238095233</v>
+        <v>0.94169096209912539</v>
       </c>
       <c r="H18" s="0">
-        <v>3600</v>
+        <v>3230</v>
       </c>
       <c r="I18" s="0">
-        <v>7271</v>
+        <v>7700</v>
       </c>
       <c r="J18" s="0">
-        <v>2200</v>
+        <v>1480</v>
       </c>
       <c r="K18" s="0">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
@@ -884,28 +897,28 @@
         <v>9</v>
       </c>
       <c r="D19" s="0">
-        <v>0.89617848464766958</v>
+        <v>0.88353115727002962</v>
       </c>
       <c r="E19" s="0">
-        <v>0.84723726977248115</v>
+        <v>0.82690187431091511</v>
       </c>
       <c r="F19" s="0">
-        <v>0.75922330097087376</v>
+        <v>0.73673870333988212</v>
       </c>
       <c r="G19" s="0">
-        <v>0.95833333333333337</v>
+        <v>0.94221105527638194</v>
       </c>
       <c r="H19" s="0">
-        <v>3910</v>
+        <v>3750</v>
       </c>
       <c r="I19" s="0">
-        <v>8261</v>
+        <v>8160</v>
       </c>
       <c r="J19" s="0">
-        <v>1240</v>
+        <v>1340</v>
       </c>
       <c r="K19" s="0">
-        <v>170</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20">
@@ -919,13 +932,13 @@
         <v>8</v>
       </c>
       <c r="D20" s="0">
-        <v>0.74314283093294198</v>
+        <v>0.76146788990825687</v>
       </c>
       <c r="E20" s="0">
-        <v>0.73831775700934565</v>
+        <v>0.75238095238095237</v>
       </c>
       <c r="F20" s="0">
-        <v>0.60305343511450382</v>
+        <v>0.62204724409448819</v>
       </c>
       <c r="G20" s="0">
         <v>0.95180722891566261</v>
@@ -934,10 +947,10 @@
         <v>3950</v>
       </c>
       <c r="I20" s="0">
-        <v>4151</v>
+        <v>4350</v>
       </c>
       <c r="J20" s="0">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="K20" s="0">
         <v>200</v>
@@ -954,28 +967,28 @@
         <v>9</v>
       </c>
       <c r="D21" s="0">
-        <v>0.89821578254101309</v>
+        <v>0.90322580645161288</v>
       </c>
       <c r="E21" s="0">
-        <v>0.8804500703234881</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="F21" s="0">
-        <v>0.81298701298701304</v>
+        <v>0.84269662921348309</v>
       </c>
       <c r="G21" s="0">
-        <v>0.96012269938650308</v>
+        <v>0.91463414634146345</v>
       </c>
       <c r="H21" s="0">
-        <v>3130</v>
+        <v>1500</v>
       </c>
       <c r="I21" s="0">
-        <v>4371</v>
+        <v>2420</v>
       </c>
       <c r="J21" s="0">
-        <v>720</v>
+        <v>280</v>
       </c>
       <c r="K21" s="0">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
@@ -989,7 +1002,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="0">
-        <v>0.92698422434598393</v>
+        <v>0.94956710980744663</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1004,10 +1017,10 @@
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>392931</v>
+        <v>401420</v>
       </c>
       <c r="J22" s="0">
-        <v>30950</v>
+        <v>21320</v>
       </c>
       <c r="K22" s="0">
         <v>0</v>
@@ -1024,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="0">
-        <v>0.97760178808462284</v>
+        <v>0.97876957916588037</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1039,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>414641</v>
+        <v>414920</v>
       </c>
       <c r="J23" s="0">
-        <v>9500</v>
+        <v>9000</v>
       </c>
       <c r="K23" s="0">
         <v>0</v>
@@ -1059,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="0">
-        <v>0.9655774279339886</v>
+        <v>0.96239267315397825</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1074,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>338011</v>
+        <v>336260</v>
       </c>
       <c r="J24" s="0">
-        <v>12050</v>
+        <v>13140</v>
       </c>
       <c r="K24" s="0">
         <v>0</v>
@@ -1094,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="0">
-        <v>0.97174101064421936</v>
+        <v>0.97059075464694633</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1109,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>340431</v>
+        <v>339930</v>
       </c>
       <c r="J25" s="0">
-        <v>9900</v>
+        <v>10300</v>
       </c>
       <c r="K25" s="0">
         <v>0</v>
@@ -1129,19 +1142,19 @@
         <v>8</v>
       </c>
       <c r="D26" s="0">
-        <v>0.9891120993712621</v>
+        <v>0.99688473520249221</v>
       </c>
       <c r="E26" s="0">
-        <v>0.99452625086731938</v>
+        <v>0.99843993759750382</v>
       </c>
       <c r="F26" s="0">
         <v>1</v>
       </c>
       <c r="G26" s="0">
-        <v>0.9891120993712621</v>
+        <v>0.99688473520249221</v>
       </c>
       <c r="H26" s="0">
-        <v>6450</v>
+        <v>6400</v>
       </c>
       <c r="I26" s="0">
         <v>0</v>
@@ -1150,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1164,19 +1177,19 @@
         <v>9</v>
       </c>
       <c r="D27" s="0">
-        <v>0.98587175904362678</v>
+        <v>0.97068403908794787</v>
       </c>
       <c r="E27" s="0">
-        <v>0.99288562270346337</v>
+        <v>0.98512396694214877</v>
       </c>
       <c r="F27" s="0">
         <v>1</v>
       </c>
       <c r="G27" s="0">
-        <v>0.98587175904362678</v>
+        <v>0.97068403908794787</v>
       </c>
       <c r="H27" s="0">
-        <v>6350</v>
+        <v>5960</v>
       </c>
       <c r="I27" s="0">
         <v>0</v>
@@ -1185,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>91</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
@@ -1199,19 +1212,19 @@
         <v>8</v>
       </c>
       <c r="D28" s="0">
-        <v>0.99326875718272867</v>
+        <v>0.99332220367278801</v>
       </c>
       <c r="E28" s="0">
-        <v>0.99662301293138955</v>
+        <v>0.99664991624790622</v>
       </c>
       <c r="F28" s="0">
         <v>1</v>
       </c>
       <c r="G28" s="0">
-        <v>0.99326875718272867</v>
+        <v>0.99332220367278801</v>
       </c>
       <c r="H28" s="0">
-        <v>6050</v>
+        <v>5950</v>
       </c>
       <c r="I28" s="0">
         <v>0</v>
@@ -1220,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -1234,19 +1247,19 @@
         <v>9</v>
       </c>
       <c r="D29" s="0">
-        <v>0.99157164105106599</v>
+        <v>0.99658119658119659</v>
       </c>
       <c r="E29" s="0">
-        <v>0.99576798605924821</v>
+        <v>0.99828767123287676</v>
       </c>
       <c r="F29" s="0">
         <v>1</v>
       </c>
       <c r="G29" s="0">
-        <v>0.99157164105106599</v>
+        <v>0.99658119658119659</v>
       </c>
       <c r="H29" s="0">
-        <v>6000</v>
+        <v>5830</v>
       </c>
       <c r="I29" s="0">
         <v>0</v>
@@ -1255,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1269,19 +1282,19 @@
         <v>8</v>
       </c>
       <c r="D30" s="0">
-        <v>0.98667982239763197</v>
+        <v>0.99498327759197325</v>
       </c>
       <c r="E30" s="0">
-        <v>0.99329525701514776</v>
+        <v>0.99748533109807203</v>
       </c>
       <c r="F30" s="0">
         <v>1</v>
       </c>
       <c r="G30" s="0">
-        <v>0.98667982239763197</v>
+        <v>0.99498327759197325</v>
       </c>
       <c r="H30" s="0">
-        <v>6000</v>
+        <v>5950</v>
       </c>
       <c r="I30" s="0">
         <v>0</v>
@@ -1290,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -1304,19 +1317,19 @@
         <v>9</v>
       </c>
       <c r="D31" s="0">
-        <v>0.90647998563992105</v>
+        <v>0.86622807017543857</v>
       </c>
       <c r="E31" s="0">
-        <v>0.95094623858393745</v>
+        <v>0.9283196239717979</v>
       </c>
       <c r="F31" s="0">
         <v>1</v>
       </c>
       <c r="G31" s="0">
-        <v>0.90647998563992105</v>
+        <v>0.86622807017543857</v>
       </c>
       <c r="H31" s="0">
-        <v>5050</v>
+        <v>3950</v>
       </c>
       <c r="I31" s="0">
         <v>0</v>
@@ -1325,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>521</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32">
@@ -1339,19 +1352,19 @@
         <v>8</v>
       </c>
       <c r="D32" s="0">
-        <v>0.97944958538637183</v>
+        <v>0.98540145985401462</v>
       </c>
       <c r="E32" s="0">
-        <v>0.98961811668993993</v>
+        <v>0.99264705882352944</v>
       </c>
       <c r="F32" s="0">
         <v>1</v>
       </c>
       <c r="G32" s="0">
-        <v>0.97944958538637183</v>
+        <v>0.98540145985401462</v>
       </c>
       <c r="H32" s="0">
-        <v>8150</v>
+        <v>8100</v>
       </c>
       <c r="I32" s="0">
         <v>0</v>
@@ -1360,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="0">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
@@ -1374,16 +1387,16 @@
         <v>9</v>
       </c>
       <c r="D33" s="0">
-        <v>0.85121688046996768</v>
+        <v>0.86165048543689315</v>
       </c>
       <c r="E33" s="0">
-        <v>0.91962955767113541</v>
+        <v>0.9256844850065189</v>
       </c>
       <c r="F33" s="0">
         <v>1</v>
       </c>
       <c r="G33" s="0">
-        <v>0.85121688046996768</v>
+        <v>0.86165048543689315</v>
       </c>
       <c r="H33" s="0">
         <v>7100</v>
@@ -1395,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="0">
-        <v>1241</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="34">
@@ -1409,19 +1422,19 @@
         <v>8</v>
       </c>
       <c r="D34" s="0">
-        <v>0.9302701828183142</v>
+        <v>0.92927631578947367</v>
       </c>
       <c r="E34" s="0">
-        <v>0.96387561813762468</v>
+        <v>0.96334185848252341</v>
       </c>
       <c r="F34" s="0">
         <v>1</v>
       </c>
       <c r="G34" s="0">
-        <v>0.9302701828183142</v>
+        <v>0.92927631578947367</v>
       </c>
       <c r="H34" s="0">
-        <v>5750</v>
+        <v>5650</v>
       </c>
       <c r="I34" s="0">
         <v>0</v>
@@ -1430,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35">
@@ -1444,19 +1457,19 @@
         <v>9</v>
       </c>
       <c r="D35" s="0">
-        <v>0.99348275313940548</v>
+        <v>0.99353796445880449</v>
       </c>
       <c r="E35" s="0">
-        <v>0.99673072322781275</v>
+        <v>0.99675850891410045</v>
       </c>
       <c r="F35" s="0">
         <v>1</v>
       </c>
       <c r="G35" s="0">
-        <v>0.99348275313940548</v>
+        <v>0.99353796445880449</v>
       </c>
       <c r="H35" s="0">
-        <v>6250</v>
+        <v>6150</v>
       </c>
       <c r="I35" s="0">
         <v>0</v>
@@ -1465,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -1479,19 +1492,19 @@
         <v>8</v>
       </c>
       <c r="D36" s="0">
-        <v>0.94547338427664807</v>
+        <v>0.94398907103825136</v>
       </c>
       <c r="E36" s="0">
-        <v>0.9719725717329073</v>
+        <v>0.97118763176387912</v>
       </c>
       <c r="F36" s="0">
         <v>1</v>
       </c>
       <c r="G36" s="0">
-        <v>0.94547338427664807</v>
+        <v>0.94398907103825136</v>
       </c>
       <c r="H36" s="0">
-        <v>7300</v>
+        <v>6910</v>
       </c>
       <c r="I36" s="0">
         <v>0</v>
@@ -1500,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="0">
-        <v>421</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37">
@@ -1514,19 +1527,19 @@
         <v>9</v>
       </c>
       <c r="D37" s="0">
-        <v>0.98064350724266125</v>
+        <v>0.95628415300546443</v>
       </c>
       <c r="E37" s="0">
-        <v>0.99022716976247493</v>
+        <v>0.97765363128491622</v>
       </c>
       <c r="F37" s="0">
         <v>1</v>
       </c>
       <c r="G37" s="0">
-        <v>0.98064350724266125</v>
+        <v>0.95628415300546443</v>
       </c>
       <c r="H37" s="0">
-        <v>7650</v>
+        <v>7000</v>
       </c>
       <c r="I37" s="0">
         <v>0</v>
@@ -1535,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="0">
-        <v>151</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38">
@@ -1549,7 +1562,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="0">
-        <v>0.27484010449509055</v>
+        <v>0.26177536231884058</v>
       </c>
       <c r="E38" s="0">
         <v>0</v>
@@ -1564,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="0">
-        <v>3051</v>
+        <v>2890</v>
       </c>
       <c r="J38" s="0">
-        <v>8050</v>
+        <v>8150</v>
       </c>
       <c r="K38" s="0">
         <v>0</v>
@@ -1584,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="0">
-        <v>0.75227456985857133</v>
+        <v>0.74568574023614898</v>
       </c>
       <c r="E39" s="0">
         <v>0</v>
@@ -1599,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="0">
-        <v>8351</v>
+        <v>8210</v>
       </c>
       <c r="J39" s="0">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="K39" s="0">
         <v>0</v>
@@ -1619,19 +1632,19 @@
         <v>8</v>
       </c>
       <c r="D40" s="0">
-        <v>0.99985716326239105</v>
+        <v>0.99414348462664714</v>
       </c>
       <c r="E40" s="0">
-        <v>0.9999285765302478</v>
+        <v>0.99706314243759186</v>
       </c>
       <c r="F40" s="0">
         <v>1</v>
       </c>
       <c r="G40" s="0">
-        <v>0.99985716326239105</v>
+        <v>0.99414348462664714</v>
       </c>
       <c r="H40" s="0">
-        <v>7000</v>
+        <v>6790</v>
       </c>
       <c r="I40" s="0">
         <v>0</v>
@@ -1640,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="0">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -1654,19 +1667,19 @@
         <v>9</v>
       </c>
       <c r="D41" s="0">
-        <v>0.99400672416313407</v>
+        <v>0.99554896142433236</v>
       </c>
       <c r="E41" s="0">
-        <v>0.99699435525254743</v>
+        <v>0.99776951672862446</v>
       </c>
       <c r="F41" s="0">
         <v>1</v>
       </c>
       <c r="G41" s="0">
-        <v>0.99400672416313407</v>
+        <v>0.99554896142433236</v>
       </c>
       <c r="H41" s="0">
-        <v>6800</v>
+        <v>6710</v>
       </c>
       <c r="I41" s="0">
         <v>0</v>
@@ -1675,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="0">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
@@ -1689,19 +1702,19 @@
         <v>8</v>
       </c>
       <c r="D42" s="0">
-        <v>0.99074436188241433</v>
+        <v>0.99735799207397624</v>
       </c>
       <c r="E42" s="0">
-        <v>0.99535066465850308</v>
+        <v>0.99867724867724861</v>
       </c>
       <c r="F42" s="0">
         <v>1</v>
       </c>
       <c r="G42" s="0">
-        <v>0.99074436188241433</v>
+        <v>0.99735799207397624</v>
       </c>
       <c r="H42" s="0">
-        <v>7600</v>
+        <v>7550</v>
       </c>
       <c r="I42" s="0">
         <v>0</v>
@@ -1710,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="0">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1724,19 +1737,19 @@
         <v>9</v>
       </c>
       <c r="D43" s="0">
-        <v>0.99850563782094826</v>
+        <v>0.99432624113475176</v>
       </c>
       <c r="E43" s="0">
-        <v>0.99925226021344571</v>
+        <v>0.99715504978662872</v>
       </c>
       <c r="F43" s="0">
         <v>1</v>
       </c>
       <c r="G43" s="0">
-        <v>0.99850563782094826</v>
+        <v>0.99432624113475176</v>
       </c>
       <c r="H43" s="0">
-        <v>7350</v>
+        <v>7010</v>
       </c>
       <c r="I43" s="0">
         <v>0</v>
@@ -1745,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="0">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -1759,19 +1772,19 @@
         <v>8</v>
       </c>
       <c r="D44" s="0">
-        <v>0.99510345916916754</v>
+        <v>0.9584120982986768</v>
       </c>
       <c r="E44" s="0">
-        <v>0.99754572084553883</v>
+        <v>0.97876447876447881</v>
       </c>
       <c r="F44" s="0">
         <v>1</v>
       </c>
       <c r="G44" s="0">
-        <v>0.99510345916916754</v>
+        <v>0.9584120982986768</v>
       </c>
       <c r="H44" s="0">
-        <v>6300</v>
+        <v>5070</v>
       </c>
       <c r="I44" s="0">
         <v>0</v>
@@ -1780,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="0">
-        <v>31</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45">
@@ -1794,19 +1807,19 @@
         <v>9</v>
       </c>
       <c r="D45" s="0">
-        <v>0.99546186502708245</v>
+        <v>1</v>
       </c>
       <c r="E45" s="0">
-        <v>0.9977257721370405</v>
+        <v>1</v>
       </c>
       <c r="F45" s="0">
         <v>1</v>
       </c>
       <c r="G45" s="0">
-        <v>0.99546186502708245</v>
+        <v>1</v>
       </c>
       <c r="H45" s="0">
-        <v>6800</v>
+        <v>6750</v>
       </c>
       <c r="I45" s="0">
         <v>0</v>
@@ -1815,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="0">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1829,19 +1842,19 @@
         <v>8</v>
       </c>
       <c r="D46" s="0">
-        <v>0.98076678130174499</v>
+        <v>0.98888888888888893</v>
       </c>
       <c r="E46" s="0">
-        <v>0.99029001350395462</v>
+        <v>0.99441340782122911</v>
       </c>
       <c r="F46" s="0">
         <v>1</v>
       </c>
       <c r="G46" s="0">
-        <v>0.98076678130174499</v>
+        <v>0.98888888888888893</v>
       </c>
       <c r="H46" s="0">
-        <v>7700</v>
+        <v>7120</v>
       </c>
       <c r="I46" s="0">
         <v>0</v>
@@ -1850,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="0">
-        <v>151</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47">
@@ -1864,19 +1877,19 @@
         <v>9</v>
       </c>
       <c r="D47" s="0">
-        <v>0.99596406717875274</v>
+        <v>0.99604221635883905</v>
       </c>
       <c r="E47" s="0">
-        <v>0.99797795316678628</v>
+        <v>0.99801718440185072</v>
       </c>
       <c r="F47" s="0">
         <v>1</v>
       </c>
       <c r="G47" s="0">
-        <v>0.99596406717875274</v>
+        <v>0.99604221635883905</v>
       </c>
       <c r="H47" s="0">
-        <v>7650</v>
+        <v>7550</v>
       </c>
       <c r="I47" s="0">
         <v>0</v>
@@ -1885,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -1899,19 +1912,19 @@
         <v>8</v>
       </c>
       <c r="D48" s="0">
-        <v>0.45681779003620065</v>
+        <v>0.45535714285714285</v>
       </c>
       <c r="E48" s="0">
-        <v>0.62714471660158555</v>
+        <v>0.62576687116564422</v>
       </c>
       <c r="F48" s="0">
         <v>1</v>
       </c>
       <c r="G48" s="0">
-        <v>0.45681779003620065</v>
+        <v>0.45535714285714285</v>
       </c>
       <c r="H48" s="0">
-        <v>2650</v>
+        <v>2550</v>
       </c>
       <c r="I48" s="0">
         <v>0</v>
@@ -1920,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="0">
-        <v>3151</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="49">
@@ -1934,19 +1947,19 @@
         <v>9</v>
       </c>
       <c r="D49" s="0">
-        <v>0.69815549043268399</v>
+        <v>0.69821428571428568</v>
       </c>
       <c r="E49" s="0">
-        <v>0.82225154806618606</v>
+        <v>0.82229232386961093</v>
       </c>
       <c r="F49" s="0">
         <v>1</v>
       </c>
       <c r="G49" s="0">
-        <v>0.69815549043268399</v>
+        <v>0.69821428571428568</v>
       </c>
       <c r="H49" s="0">
-        <v>4050</v>
+        <v>3910</v>
       </c>
       <c r="I49" s="0">
         <v>0</v>
@@ -1955,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="0">
-        <v>1751</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="50">
@@ -1969,19 +1982,19 @@
         <v>8</v>
       </c>
       <c r="D50" s="0">
-        <v>0.27047192687931354</v>
+        <v>0.40393013100436681</v>
       </c>
       <c r="E50" s="0">
-        <v>0.4257818235207752</v>
+        <v>0.57542768273716949</v>
       </c>
       <c r="F50" s="0">
         <v>1</v>
       </c>
       <c r="G50" s="0">
-        <v>0.27047192687931354</v>
+        <v>0.40393013100436681</v>
       </c>
       <c r="H50" s="0">
-        <v>1450</v>
+        <v>1850</v>
       </c>
       <c r="I50" s="0">
         <v>0</v>
@@ -1990,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="0">
-        <v>3911</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="51">
@@ -2004,19 +2017,19 @@
         <v>9</v>
       </c>
       <c r="D51" s="0">
-        <v>0.19262520638414971</v>
+        <v>0.32755298651252407</v>
       </c>
       <c r="E51" s="0">
-        <v>0.32302722658052607</v>
+        <v>0.49346879535558785</v>
       </c>
       <c r="F51" s="0">
         <v>1</v>
       </c>
       <c r="G51" s="0">
-        <v>0.19262520638414971</v>
+        <v>0.32755298651252407</v>
       </c>
       <c r="H51" s="0">
-        <v>1050</v>
+        <v>1700</v>
       </c>
       <c r="I51" s="0">
         <v>0</v>
@@ -2025,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="0">
-        <v>4401</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="52">
@@ -2039,19 +2052,19 @@
         <v>8</v>
       </c>
       <c r="D52" s="0">
-        <v>0.62385626351688572</v>
+        <v>0.70567986230636837</v>
       </c>
       <c r="E52" s="0">
-        <v>0.7683638971416864</v>
+        <v>0.82744702320887986</v>
       </c>
       <c r="F52" s="0">
         <v>1</v>
       </c>
       <c r="G52" s="0">
-        <v>0.62385626351688572</v>
+        <v>0.70567986230636837</v>
       </c>
       <c r="H52" s="0">
-        <v>3750</v>
+        <v>4100</v>
       </c>
       <c r="I52" s="0">
         <v>0</v>
@@ -2060,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="0">
-        <v>2261</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="53">
@@ -2074,19 +2087,19 @@
         <v>9</v>
       </c>
       <c r="D53" s="0">
-        <v>0.41179377367814196</v>
+        <v>0.2776831345826235</v>
       </c>
       <c r="E53" s="0">
-        <v>0.58336250145840629</v>
+        <v>0.4346666666666667</v>
       </c>
       <c r="F53" s="0">
         <v>1</v>
       </c>
       <c r="G53" s="0">
-        <v>0.41179377367814196</v>
+        <v>0.2776831345826235</v>
       </c>
       <c r="H53" s="0">
-        <v>2500</v>
+        <v>1630</v>
       </c>
       <c r="I53" s="0">
         <v>0</v>
@@ -2095,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="0">
-        <v>3571</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="54">
@@ -2109,19 +2122,19 @@
         <v>8</v>
       </c>
       <c r="D54" s="0">
-        <v>0.29744770677413163</v>
+        <v>0.3592814371257485</v>
       </c>
       <c r="E54" s="0">
-        <v>0.45851205442981802</v>
+        <v>0.52863436123348018</v>
       </c>
       <c r="F54" s="0">
         <v>1</v>
       </c>
       <c r="G54" s="0">
-        <v>0.29744770677413163</v>
+        <v>0.3592814371257485</v>
       </c>
       <c r="H54" s="0">
-        <v>1550</v>
+        <v>1800</v>
       </c>
       <c r="I54" s="0">
         <v>0</v>
@@ -2130,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="0">
-        <v>3661</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="55">
@@ -2144,19 +2157,19 @@
         <v>9</v>
       </c>
       <c r="D55" s="0">
-        <v>0.46657779470577032</v>
+        <v>0.47524752475247523</v>
       </c>
       <c r="E55" s="0">
-        <v>0.63628100246721209</v>
+        <v>0.64429530201342278</v>
       </c>
       <c r="F55" s="0">
         <v>1</v>
       </c>
       <c r="G55" s="0">
-        <v>0.46657779470577032</v>
+        <v>0.47524752475247523</v>
       </c>
       <c r="H55" s="0">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="I55" s="0">
         <v>0</v>
@@ -2165,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="0">
-        <v>2801</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="56">
@@ -2179,19 +2192,19 @@
         <v>8</v>
       </c>
       <c r="D56" s="0">
-        <v>0.79647872563403899</v>
+        <v>0.85081585081585076</v>
       </c>
       <c r="E56" s="0">
-        <v>0.88671100221677746</v>
+        <v>0.91939546599496214</v>
       </c>
       <c r="F56" s="0">
         <v>1</v>
       </c>
       <c r="G56" s="0">
-        <v>0.79647872563403899</v>
+        <v>0.85081585081585076</v>
       </c>
       <c r="H56" s="0">
-        <v>3800</v>
+        <v>3650</v>
       </c>
       <c r="I56" s="0">
         <v>0</v>
@@ -2200,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="0">
-        <v>971</v>
+        <v>640</v>
       </c>
     </row>
     <row r="57">
@@ -2214,19 +2227,19 @@
         <v>9</v>
       </c>
       <c r="D57" s="0">
-        <v>0.88641517212945786</v>
+        <v>0.88336933045356369</v>
       </c>
       <c r="E57" s="0">
-        <v>0.93978800131133211</v>
+        <v>0.93807339449541283</v>
       </c>
       <c r="F57" s="0">
         <v>1</v>
       </c>
       <c r="G57" s="0">
-        <v>0.88641517212945786</v>
+        <v>0.88336933045356369</v>
       </c>
       <c r="H57" s="0">
-        <v>4300</v>
+        <v>4090</v>
       </c>
       <c r="I57" s="0">
         <v>0</v>
@@ -2235,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="0">
-        <v>551</v>
+        <v>540</v>
       </c>
     </row>
     <row r="58">
@@ -2249,19 +2262,19 @@
         <v>8</v>
       </c>
       <c r="D58" s="0">
-        <v>0.25188916876574308</v>
+        <v>0.4536290322580645</v>
       </c>
       <c r="E58" s="0">
-        <v>0.4024144869215292</v>
+        <v>0.62413314840499301</v>
       </c>
       <c r="F58" s="0">
         <v>1</v>
       </c>
       <c r="G58" s="0">
-        <v>0.25188916876574308</v>
+        <v>0.4536290322580645</v>
       </c>
       <c r="H58" s="0">
-        <v>1300</v>
+        <v>2250</v>
       </c>
       <c r="I58" s="0">
         <v>0</v>
@@ -2270,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="0">
-        <v>3861</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="59">
@@ -2284,19 +2297,19 @@
         <v>9</v>
       </c>
       <c r="D59" s="0">
-        <v>0.43298563274945878</v>
+        <v>0.43659043659043661</v>
       </c>
       <c r="E59" s="0">
-        <v>0.60431259442384289</v>
+        <v>0.60781476121562961</v>
       </c>
       <c r="F59" s="0">
         <v>1</v>
       </c>
       <c r="G59" s="0">
-        <v>0.43298563274945878</v>
+        <v>0.43659043659043661</v>
       </c>
       <c r="H59" s="0">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="I59" s="0">
         <v>0</v>
@@ -2305,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="0">
-        <v>2881</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="60">
@@ -2319,19 +2332,19 @@
         <v>8</v>
       </c>
       <c r="D60" s="0">
-        <v>0.99396259755558825</v>
+        <v>0.99551569506726456</v>
       </c>
       <c r="E60" s="0">
-        <v>0.99697215862934785</v>
+        <v>0.99775280898876406</v>
       </c>
       <c r="F60" s="0">
         <v>1</v>
       </c>
       <c r="G60" s="0">
-        <v>0.99396259755558825</v>
+        <v>0.99551569506726456</v>
       </c>
       <c r="H60" s="0">
-        <v>6750</v>
+        <v>6660</v>
       </c>
       <c r="I60" s="0">
         <v>0</v>
@@ -2340,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="0">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
@@ -2354,19 +2367,19 @@
         <v>9</v>
       </c>
       <c r="D61" s="0">
-        <v>0.99413531683593193</v>
+        <v>0.98113207547169812</v>
       </c>
       <c r="E61" s="0">
-        <v>0.9970590345025464</v>
+        <v>0.99047619047619051</v>
       </c>
       <c r="F61" s="0">
         <v>1</v>
       </c>
       <c r="G61" s="0">
-        <v>0.99413531683593193</v>
+        <v>0.98113207547169812</v>
       </c>
       <c r="H61" s="0">
-        <v>6950</v>
+        <v>6760</v>
       </c>
       <c r="I61" s="0">
         <v>0</v>
@@ -2375,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="0">
-        <v>41</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62">
@@ -2389,19 +2402,19 @@
         <v>8</v>
       </c>
       <c r="D62" s="0">
-        <v>0.99746100834240115</v>
+        <v>0.99755201958384332</v>
       </c>
       <c r="E62" s="0">
-        <v>0.99872889050299618</v>
+        <v>0.99877450980392157</v>
       </c>
       <c r="F62" s="0">
         <v>1</v>
       </c>
       <c r="G62" s="0">
-        <v>0.99746100834240115</v>
+        <v>0.99755201958384332</v>
       </c>
       <c r="H62" s="0">
-        <v>8250</v>
+        <v>8150</v>
       </c>
       <c r="I62" s="0">
         <v>0</v>
@@ -2410,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
@@ -2424,19 +2437,19 @@
         <v>9</v>
       </c>
       <c r="D63" s="0">
-        <v>0.91008372770294865</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E63" s="0">
-        <v>0.95292548122736798</v>
+        <v>0.95238095238095233</v>
       </c>
       <c r="F63" s="0">
         <v>1</v>
       </c>
       <c r="G63" s="0">
-        <v>0.91008372770294865</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="H63" s="0">
-        <v>7500</v>
+        <v>7400</v>
       </c>
       <c r="I63" s="0">
         <v>0</v>
@@ -2445,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="0">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="64">
@@ -2459,19 +2472,19 @@
         <v>8</v>
       </c>
       <c r="D64" s="0">
-        <v>0.98725668673855205</v>
+        <v>0.99420289855072463</v>
       </c>
       <c r="E64" s="0">
-        <v>0.99358748502572047</v>
+        <v>0.99709302325581406</v>
       </c>
       <c r="F64" s="0">
         <v>1</v>
       </c>
       <c r="G64" s="0">
-        <v>0.98725668673855205</v>
+        <v>0.99420289855072463</v>
       </c>
       <c r="H64" s="0">
-        <v>7050</v>
+        <v>6860</v>
       </c>
       <c r="I64" s="0">
         <v>0</v>
@@ -2480,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="0">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -2494,19 +2507,19 @@
         <v>9</v>
       </c>
       <c r="D65" s="0">
-        <v>0.99009900990099009</v>
+        <v>0.99717114568599718</v>
       </c>
       <c r="E65" s="0">
-        <v>0.99502487562189057</v>
+        <v>0.99858356940509907</v>
       </c>
       <c r="F65" s="0">
         <v>1</v>
       </c>
       <c r="G65" s="0">
-        <v>0.99009900990099009</v>
+        <v>0.99717114568599718</v>
       </c>
       <c r="H65" s="0">
-        <v>7100</v>
+        <v>7050</v>
       </c>
       <c r="I65" s="0">
         <v>0</v>
@@ -2515,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="0">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -2529,19 +2542,19 @@
         <v>8</v>
       </c>
       <c r="D66" s="0">
-        <v>0.98154691794267768</v>
+        <v>0.98143236074270557</v>
       </c>
       <c r="E66" s="0">
-        <v>0.99068753715078262</v>
+        <v>0.99062918340026773</v>
       </c>
       <c r="F66" s="0">
         <v>1</v>
       </c>
       <c r="G66" s="0">
-        <v>0.98154691794267768</v>
+        <v>0.98143236074270557</v>
       </c>
       <c r="H66" s="0">
-        <v>7500</v>
+        <v>7400</v>
       </c>
       <c r="I66" s="0">
         <v>0</v>
@@ -2550,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="0">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67">
@@ -2564,19 +2577,19 @@
         <v>9</v>
       </c>
       <c r="D67" s="0">
-        <v>0.99466909374593682</v>
+        <v>0.99160839160839165</v>
       </c>
       <c r="E67" s="0">
-        <v>0.99732742324489931</v>
+        <v>0.9957865168539326</v>
       </c>
       <c r="F67" s="0">
         <v>1</v>
       </c>
       <c r="G67" s="0">
-        <v>0.99466909374593682</v>
+        <v>0.99160839160839165</v>
       </c>
       <c r="H67" s="0">
-        <v>7650</v>
+        <v>7090</v>
       </c>
       <c r="I67" s="0">
         <v>0</v>
@@ -2585,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="0">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68">
@@ -2599,19 +2612,19 @@
         <v>8</v>
       </c>
       <c r="D68" s="0">
-        <v>0.95546835011090259</v>
+        <v>0.90104166666666663</v>
       </c>
       <c r="E68" s="0">
-        <v>0.97722711805252593</v>
+        <v>0.94794520547945205</v>
       </c>
       <c r="F68" s="0">
         <v>1</v>
       </c>
       <c r="G68" s="0">
-        <v>0.95546835011090259</v>
+        <v>0.90104166666666663</v>
       </c>
       <c r="H68" s="0">
-        <v>5600</v>
+        <v>5190</v>
       </c>
       <c r="I68" s="0">
         <v>0</v>
@@ -2620,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="0">
-        <v>261</v>
+        <v>570</v>
       </c>
     </row>
     <row r="69">
@@ -2634,19 +2647,19 @@
         <v>9</v>
       </c>
       <c r="D69" s="0">
-        <v>0.99444543988532519</v>
+        <v>0.98035363457760316</v>
       </c>
       <c r="E69" s="0">
-        <v>0.99721498517653395</v>
+        <v>0.99007936507936511</v>
       </c>
       <c r="F69" s="0">
         <v>1</v>
       </c>
       <c r="G69" s="0">
-        <v>0.99444543988532519</v>
+        <v>0.98035363457760316</v>
       </c>
       <c r="H69" s="0">
-        <v>5550</v>
+        <v>4990</v>
       </c>
       <c r="I69" s="0">
         <v>0</v>
@@ -2655,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="0">
-        <v>31</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70">
@@ -2669,19 +2682,19 @@
         <v>8</v>
       </c>
       <c r="D70" s="0">
-        <v>0.98818058515791518</v>
+        <v>1</v>
       </c>
       <c r="E70" s="0">
-        <v>0.99405516031575869</v>
+        <v>1</v>
       </c>
       <c r="F70" s="0">
         <v>1</v>
       </c>
       <c r="G70" s="0">
-        <v>0.98818058515791518</v>
+        <v>1</v>
       </c>
       <c r="H70" s="0">
-        <v>5100</v>
+        <v>5060</v>
       </c>
       <c r="I70" s="0">
         <v>0</v>
@@ -2690,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="0">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2704,19 +2717,19 @@
         <v>9</v>
       </c>
       <c r="D71" s="0">
-        <v>0.98405825624876997</v>
+        <v>0.99164926931106467</v>
       </c>
       <c r="E71" s="0">
-        <v>0.99196508282908447</v>
+        <v>0.99580712788259951</v>
       </c>
       <c r="F71" s="0">
         <v>1</v>
       </c>
       <c r="G71" s="0">
-        <v>0.98405825624876997</v>
+        <v>0.99164926931106467</v>
       </c>
       <c r="H71" s="0">
-        <v>5000</v>
+        <v>4750</v>
       </c>
       <c r="I71" s="0">
         <v>0</v>
@@ -2725,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="0">
-        <v>81</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -2739,19 +2752,19 @@
         <v>8</v>
       </c>
       <c r="D72" s="0">
-        <v>0.99818511796733211</v>
+        <v>0.99832214765100669</v>
       </c>
       <c r="E72" s="0">
-        <v>0.99909173478655766</v>
+        <v>0.99916036943744746</v>
       </c>
       <c r="F72" s="0">
         <v>1</v>
       </c>
       <c r="G72" s="0">
-        <v>0.99818511796733211</v>
+        <v>0.99832214765100669</v>
       </c>
       <c r="H72" s="0">
-        <v>6050</v>
+        <v>5950</v>
       </c>
       <c r="I72" s="0">
         <v>0</v>
@@ -2760,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -2774,19 +2787,19 @@
         <v>9</v>
       </c>
       <c r="D73" s="0">
-        <v>0.99315640126856952</v>
+        <v>0.98242530755711777</v>
       </c>
       <c r="E73" s="0">
-        <v>0.99656645172096148</v>
+        <v>0.99113475177304966</v>
       </c>
       <c r="F73" s="0">
         <v>1</v>
       </c>
       <c r="G73" s="0">
-        <v>0.99315640126856952</v>
+        <v>0.98242530755711777</v>
       </c>
       <c r="H73" s="0">
-        <v>5950</v>
+        <v>5590</v>
       </c>
       <c r="I73" s="0">
         <v>0</v>
@@ -2795,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="0">
-        <v>41</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -2809,19 +2822,19 @@
         <v>8</v>
       </c>
       <c r="D74" s="0">
-        <v>0.98296199213630409</v>
+        <v>0.99427480916030531</v>
       </c>
       <c r="E74" s="0">
-        <v>0.99140779907468601</v>
+        <v>0.99712918660287075</v>
       </c>
       <c r="F74" s="0">
         <v>1</v>
       </c>
       <c r="G74" s="0">
-        <v>0.98296199213630409</v>
+        <v>0.99427480916030531</v>
       </c>
       <c r="H74" s="0">
-        <v>5250</v>
+        <v>5210</v>
       </c>
       <c r="I74" s="0">
         <v>0</v>
@@ -2830,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="0">
-        <v>91</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75">
@@ -2844,19 +2857,19 @@
         <v>9</v>
       </c>
       <c r="D75" s="0">
-        <v>0.98494703586693921</v>
+        <v>0.97104247104247099</v>
       </c>
       <c r="E75" s="0">
-        <v>0.99241644040820143</v>
+        <v>0.98530852105778644</v>
       </c>
       <c r="F75" s="0">
         <v>1</v>
       </c>
       <c r="G75" s="0">
-        <v>0.98494703586693921</v>
+        <v>0.97104247104247099</v>
       </c>
       <c r="H75" s="0">
-        <v>5300</v>
+        <v>5030</v>
       </c>
       <c r="I75" s="0">
         <v>0</v>
@@ -2865,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="0">
-        <v>81</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76">
@@ -2879,19 +2892,19 @@
         <v>8</v>
       </c>
       <c r="D76" s="0">
-        <v>0.77205320287417822</v>
+        <v>0.42701863354037267</v>
       </c>
       <c r="E76" s="0">
-        <v>0.87136571477870761</v>
+        <v>0.59847660500544064</v>
       </c>
       <c r="F76" s="0">
         <v>1</v>
       </c>
       <c r="G76" s="0">
-        <v>0.77205320287417822</v>
+        <v>0.42701863354037267</v>
       </c>
       <c r="H76" s="0">
-        <v>5050</v>
+        <v>2750</v>
       </c>
       <c r="I76" s="0">
         <v>0</v>
@@ -2900,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="0">
-        <v>1491</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="77">
@@ -2914,19 +2927,19 @@
         <v>9</v>
       </c>
       <c r="D77" s="0">
-        <v>0.99070263679317172</v>
+        <v>0.99845201238390091</v>
       </c>
       <c r="E77" s="0">
-        <v>0.9953296072276242</v>
+        <v>0.99922540666150272</v>
       </c>
       <c r="F77" s="0">
         <v>1</v>
       </c>
       <c r="G77" s="0">
-        <v>0.99070263679317172</v>
+        <v>0.99845201238390091</v>
       </c>
       <c r="H77" s="0">
-        <v>6500</v>
+        <v>6450</v>
       </c>
       <c r="I77" s="0">
         <v>0</v>
@@ -2935,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="0">
-        <v>61</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -2949,19 +2962,19 @@
         <v>8</v>
       </c>
       <c r="D78" s="0">
-        <v>0.99412989964021969</v>
+        <v>0.97490347490347495</v>
       </c>
       <c r="E78" s="0">
-        <v>0.99705630994207584</v>
+        <v>0.98729227761485827</v>
       </c>
       <c r="F78" s="0">
         <v>1</v>
       </c>
       <c r="G78" s="0">
-        <v>0.99412989964021969</v>
+        <v>0.97490347490347495</v>
       </c>
       <c r="H78" s="0">
-        <v>5250</v>
+        <v>5050</v>
       </c>
       <c r="I78" s="0">
         <v>0</v>
@@ -2970,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="0">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79">
@@ -2984,19 +2997,19 @@
         <v>9</v>
       </c>
       <c r="D79" s="0">
-        <v>0.96489615879433932</v>
+        <v>0.97378277153558057</v>
       </c>
       <c r="E79" s="0">
-        <v>0.98213450565896543</v>
+        <v>0.98671726755218214</v>
       </c>
       <c r="F79" s="0">
         <v>1</v>
       </c>
       <c r="G79" s="0">
-        <v>0.96489615879433932</v>
+        <v>0.97378277153558057</v>
       </c>
       <c r="H79" s="0">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="I79" s="0">
         <v>0</v>
@@ -3005,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="0">
-        <v>191</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80">
@@ -3019,19 +3032,19 @@
         <v>8</v>
       </c>
       <c r="D80" s="0">
-        <v>0.98787606645711723</v>
+        <v>0.99544072948328266</v>
       </c>
       <c r="E80" s="0">
-        <v>0.99390106166704317</v>
+        <v>0.99771515613099782</v>
       </c>
       <c r="F80" s="0">
         <v>1</v>
       </c>
       <c r="G80" s="0">
-        <v>0.98787606645711723</v>
+        <v>0.99544072948328266</v>
       </c>
       <c r="H80" s="0">
-        <v>6600</v>
+        <v>6550</v>
       </c>
       <c r="I80" s="0">
         <v>0</v>
@@ -3040,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="0">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81">
@@ -3054,19 +3067,19 @@
         <v>9</v>
       </c>
       <c r="D81" s="0">
-        <v>0.99238919564244144</v>
+        <v>1</v>
       </c>
       <c r="E81" s="0">
-        <v>0.99618006141862026</v>
+        <v>1</v>
       </c>
       <c r="F81" s="0">
         <v>1</v>
       </c>
       <c r="G81" s="0">
-        <v>0.99238919564244144</v>
+        <v>1</v>
       </c>
       <c r="H81" s="0">
-        <v>6650</v>
+        <v>6600</v>
       </c>
       <c r="I81" s="0">
         <v>0</v>
@@ -3075,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="0">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3089,19 +3102,19 @@
         <v>8</v>
       </c>
       <c r="D82" s="0">
-        <v>0.99434409779237365</v>
+        <v>0.99442379182156138</v>
       </c>
       <c r="E82" s="0">
-        <v>0.99716402890860856</v>
+        <v>0.99720410065237652</v>
       </c>
       <c r="F82" s="0">
         <v>1</v>
       </c>
       <c r="G82" s="0">
-        <v>0.99434409779237365</v>
+        <v>0.99442379182156138</v>
       </c>
       <c r="H82" s="0">
-        <v>5450</v>
+        <v>5350</v>
       </c>
       <c r="I82" s="0">
         <v>0</v>
@@ -3110,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
@@ -3124,19 +3137,19 @@
         <v>9</v>
       </c>
       <c r="D83" s="0">
-        <v>0.99429202725096666</v>
+        <v>0.99624765478424016</v>
       </c>
       <c r="E83" s="0">
-        <v>0.99713784507432379</v>
+        <v>0.99812030075187974</v>
       </c>
       <c r="F83" s="0">
         <v>1</v>
       </c>
       <c r="G83" s="0">
-        <v>0.99429202725096666</v>
+        <v>0.99624765478424016</v>
       </c>
       <c r="H83" s="0">
-        <v>5400</v>
+        <v>5310</v>
       </c>
       <c r="I83" s="0">
         <v>0</v>
@@ -3145,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="0">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
@@ -3159,19 +3172,19 @@
         <v>8</v>
       </c>
       <c r="D84" s="0">
-        <v>0.010264832683227263</v>
+        <v>0</v>
       </c>
       <c r="E84" s="0">
-        <v>0.020321072952651897</v>
+        <v>0</v>
       </c>
       <c r="F84" s="0">
         <v>1</v>
       </c>
       <c r="G84" s="0">
-        <v>0.010264832683227263</v>
+        <v>0</v>
       </c>
       <c r="H84" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I84" s="0">
         <v>0</v>
@@ -3180,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="0">
-        <v>4821</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="85">
@@ -3194,19 +3207,19 @@
         <v>9</v>
       </c>
       <c r="D85" s="0">
-        <v>0.0098212531919072872</v>
+        <v>0</v>
       </c>
       <c r="E85" s="0">
-        <v>0.019451468585878234</v>
+        <v>0</v>
       </c>
       <c r="F85" s="0">
         <v>1</v>
       </c>
       <c r="G85" s="0">
-        <v>0.0098212531919072872</v>
+        <v>0</v>
       </c>
       <c r="H85" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I85" s="0">
         <v>0</v>
@@ -3215,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="0">
-        <v>5041</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="86">
@@ -3229,19 +3242,19 @@
         <v>8</v>
       </c>
       <c r="D86" s="0">
-        <v>0.0090073860565663844</v>
+        <v>0</v>
       </c>
       <c r="E86" s="0">
-        <v>0.017853954650955184</v>
+        <v>0</v>
       </c>
       <c r="F86" s="0">
         <v>1</v>
       </c>
       <c r="G86" s="0">
-        <v>0.0090073860565663844</v>
+        <v>0</v>
       </c>
       <c r="H86" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I86" s="0">
         <v>0</v>
@@ -3250,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="0">
-        <v>5501</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="87">
@@ -3264,19 +3277,19 @@
         <v>9</v>
       </c>
       <c r="D87" s="0">
-        <v>0.0095038965976050188</v>
+        <v>0</v>
       </c>
       <c r="E87" s="0">
-        <v>0.018828845791752966</v>
+        <v>0</v>
       </c>
       <c r="F87" s="0">
         <v>1</v>
       </c>
       <c r="G87" s="0">
-        <v>0.0095038965976050188</v>
+        <v>0</v>
       </c>
       <c r="H87" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I87" s="0">
         <v>0</v>
@@ -3285,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="0">
-        <v>5211</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="88">
@@ -3314,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="0">
-        <v>6721</v>
+        <v>6520</v>
       </c>
       <c r="J88" s="0">
         <v>0</v>
@@ -3349,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="0">
-        <v>6501</v>
+        <v>6400</v>
       </c>
       <c r="J89" s="0">
         <v>0</v>
@@ -3384,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="0">
-        <v>8991</v>
+        <v>8890</v>
       </c>
       <c r="J90" s="0">
         <v>0</v>
@@ -3404,7 +3417,7 @@
         <v>9</v>
       </c>
       <c r="D91" s="0">
-        <v>0.98353638459005599</v>
+        <v>0.97234513274336287</v>
       </c>
       <c r="E91" s="0">
         <v>0</v>
@@ -3419,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="I91" s="0">
-        <v>8961</v>
+        <v>8790</v>
       </c>
       <c r="J91" s="0">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="K91" s="0">
         <v>0</v>
@@ -3439,19 +3452,19 @@
         <v>8</v>
       </c>
       <c r="D92" s="0">
-        <v>0.99680413940039569</v>
+        <v>0.84175084175084181</v>
       </c>
       <c r="E92" s="0">
-        <v>0.99839951223229939</v>
+        <v>0.9140767824497259</v>
       </c>
       <c r="F92" s="0">
         <v>1</v>
       </c>
       <c r="G92" s="0">
-        <v>0.99680413940039569</v>
+        <v>0.84175084175084181</v>
       </c>
       <c r="H92" s="0">
-        <v>6550</v>
+        <v>5000</v>
       </c>
       <c r="I92" s="0">
         <v>0</v>
@@ -3460,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="0">
-        <v>21</v>
+        <v>940</v>
       </c>
     </row>
     <row r="93">
@@ -3474,19 +3487,19 @@
         <v>9</v>
       </c>
       <c r="D93" s="0">
-        <v>0.99373184528359582</v>
+        <v>0.96779661016949148</v>
       </c>
       <c r="E93" s="0">
-        <v>0.99685606931983739</v>
+        <v>0.98363479758828598</v>
       </c>
       <c r="F93" s="0">
         <v>1</v>
       </c>
       <c r="G93" s="0">
-        <v>0.99373184528359582</v>
+        <v>0.96779661016949148</v>
       </c>
       <c r="H93" s="0">
-        <v>6500</v>
+        <v>5710</v>
       </c>
       <c r="I93" s="0">
         <v>0</v>
@@ -3495,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="0">
-        <v>41</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94">
@@ -3509,19 +3522,19 @@
         <v>8</v>
       </c>
       <c r="D94" s="0">
-        <v>0.99810703837549475</v>
+        <v>0.99440298507462688</v>
       </c>
       <c r="E94" s="0">
-        <v>0.99905262251313409</v>
+        <v>0.99719363891487378</v>
       </c>
       <c r="F94" s="0">
         <v>1</v>
       </c>
       <c r="G94" s="0">
-        <v>0.99810703837549475</v>
+        <v>0.99440298507462688</v>
       </c>
       <c r="H94" s="0">
-        <v>5800</v>
+        <v>5330</v>
       </c>
       <c r="I94" s="0">
         <v>0</v>
@@ -3530,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="0">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
@@ -3544,19 +3557,19 @@
         <v>9</v>
       </c>
       <c r="D95" s="0">
-        <v>0.97652750403153554</v>
+        <v>0.98496240601503759</v>
       </c>
       <c r="E95" s="0">
-        <v>0.98812437675641374</v>
+        <v>0.99242424242424243</v>
       </c>
       <c r="F95" s="0">
         <v>1</v>
       </c>
       <c r="G95" s="0">
-        <v>0.97652750403153554</v>
+        <v>0.98496240601503759</v>
       </c>
       <c r="H95" s="0">
-        <v>5450</v>
+        <v>5240</v>
       </c>
       <c r="I95" s="0">
         <v>0</v>
@@ -3565,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="0">
-        <v>131</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96">
@@ -3579,7 +3592,7 @@
         <v>8</v>
       </c>
       <c r="D96" s="0">
-        <v>0.85608241175579458</v>
+        <v>0.87692307692307692</v>
       </c>
       <c r="E96" s="0">
         <v>0</v>
@@ -3594,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="0">
-        <v>5651</v>
+        <v>5700</v>
       </c>
       <c r="J96" s="0">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="K96" s="0">
         <v>0</v>
@@ -3614,7 +3627,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="0">
-        <v>0.84735154938177382</v>
+        <v>0.8527131782945736</v>
       </c>
       <c r="E97" s="0">
         <v>0</v>
@@ -3629,10 +3642,10 @@
         <v>0</v>
       </c>
       <c r="I97" s="0">
-        <v>5551</v>
+        <v>5500</v>
       </c>
       <c r="J97" s="0">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="K97" s="0">
         <v>0</v>
@@ -3664,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="0">
-        <v>5351</v>
+        <v>5250</v>
       </c>
       <c r="J98" s="0">
         <v>0</v>
@@ -3684,7 +3697,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="0">
-        <v>0.98120654012403685</v>
+        <v>0.98985801217038538</v>
       </c>
       <c r="E99" s="0">
         <v>0</v>
@@ -3699,10 +3712,10 @@
         <v>0</v>
       </c>
       <c r="I99" s="0">
-        <v>5221</v>
+        <v>4880</v>
       </c>
       <c r="J99" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K99" s="0">
         <v>0</v>
@@ -3719,19 +3732,19 @@
         <v>8</v>
       </c>
       <c r="D100" s="0">
-        <v>0.98117210289047996</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="E100" s="0">
-        <v>0.99049658680230213</v>
+        <v>0.99022801302931596</v>
       </c>
       <c r="F100" s="0">
         <v>1</v>
       </c>
       <c r="G100" s="0">
-        <v>0.98117210289047996</v>
+        <v>0.98064516129032253</v>
       </c>
       <c r="H100" s="0">
-        <v>3700</v>
+        <v>3040</v>
       </c>
       <c r="I100" s="0">
         <v>0</v>
@@ -3740,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="0">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
@@ -3754,19 +3767,19 @@
         <v>9</v>
       </c>
       <c r="D101" s="0">
-        <v>0.99275870123802845</v>
+        <v>0.99282296650717705</v>
       </c>
       <c r="E101" s="0">
-        <v>0.99636619388113945</v>
+        <v>0.99639855942376954</v>
       </c>
       <c r="F101" s="0">
         <v>1</v>
       </c>
       <c r="G101" s="0">
-        <v>0.99275870123802845</v>
+        <v>0.99282296650717705</v>
       </c>
       <c r="H101" s="0">
-        <v>4250</v>
+        <v>4150</v>
       </c>
       <c r="I101" s="0">
         <v>0</v>
@@ -3775,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
@@ -3789,19 +3802,19 @@
         <v>8</v>
       </c>
       <c r="D102" s="0">
-        <v>0.98155859607376561</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="E102" s="0">
-        <v>0.99069348543980784</v>
+        <v>0.98611111111111116</v>
       </c>
       <c r="F102" s="0">
         <v>1</v>
       </c>
       <c r="G102" s="0">
-        <v>0.98155859607376561</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="H102" s="0">
-        <v>1650</v>
+        <v>1420</v>
       </c>
       <c r="I102" s="0">
         <v>0</v>
@@ -3810,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="0">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -3824,19 +3837,19 @@
         <v>9</v>
       </c>
       <c r="D103" s="0">
-        <v>0.99942889777270127</v>
+        <v>0.94160583941605835</v>
       </c>
       <c r="E103" s="0">
-        <v>0.99971436732362184</v>
+        <v>0.96992481203007508</v>
       </c>
       <c r="F103" s="0">
         <v>1</v>
       </c>
       <c r="G103" s="0">
-        <v>0.99942889777270127</v>
+        <v>0.94160583941605835</v>
       </c>
       <c r="H103" s="0">
-        <v>1750</v>
+        <v>1290</v>
       </c>
       <c r="I103" s="0">
         <v>0</v>
@@ -3845,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="0">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3909,28 +3922,28 @@
         <v>51</v>
       </c>
       <c r="C2" s="0">
-        <v>317420</v>
+        <v>302960</v>
       </c>
       <c r="D2" s="0">
-        <v>41880</v>
+        <v>40350</v>
       </c>
       <c r="E2" s="0">
-        <v>949704</v>
+        <v>947560</v>
       </c>
       <c r="F2" s="0">
-        <v>36027</v>
+        <v>38070</v>
       </c>
       <c r="G2" s="0">
-        <v>0.88344002226551632</v>
+        <v>0.88246774052605514</v>
       </c>
       <c r="H2" s="0">
-        <v>0.89806958327556885</v>
+        <v>0.88836759229393314</v>
       </c>
       <c r="I2" s="0">
-        <v>0.94207791493281567</v>
+        <v>0.94099056390807712</v>
       </c>
       <c r="J2" s="0">
-        <v>0.89069473459726944</v>
+        <v>0.88540783820907731</v>
       </c>
     </row>
     <row r="3">
@@ -3941,28 +3954,28 @@
         <v>51</v>
       </c>
       <c r="C3" s="0">
-        <v>306640</v>
+        <v>281680</v>
       </c>
       <c r="D3" s="0">
-        <v>75560</v>
+        <v>63930</v>
       </c>
       <c r="E3" s="0">
-        <v>916314</v>
+        <v>924090</v>
       </c>
       <c r="F3" s="0">
-        <v>40177</v>
+        <v>41300</v>
       </c>
       <c r="G3" s="0">
-        <v>0.80230245944531664</v>
+        <v>0.81502271346315214</v>
       </c>
       <c r="H3" s="0">
-        <v>0.88415504430290326</v>
+        <v>0.87212830515821416</v>
       </c>
       <c r="I3" s="0">
-        <v>0.9135446492132987</v>
+        <v>0.91973302822273073</v>
       </c>
       <c r="J3" s="0">
-        <v>0.84124238529417006</v>
+        <v>0.84260907282490016</v>
       </c>
     </row>
   </sheetData>
@@ -4029,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>62400</v>
+        <v>53760</v>
       </c>
       <c r="E2" s="0">
-        <v>1486014</v>
+        <v>1492530</v>
       </c>
       <c r="F2" s="0">
         <v>0</v>
@@ -4044,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>0.95970070020033404</v>
+        <v>0.96523291232563102</v>
       </c>
       <c r="J2" s="0">
         <v>0</v>
@@ -4061,10 +4074,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E3" s="0">
-        <v>31174</v>
+        <v>30600</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
@@ -4076,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="0">
-        <v>0.99521133954795049</v>
+        <v>0.99189627228525123</v>
       </c>
       <c r="J3" s="0">
         <v>0</v>
@@ -4090,7 +4103,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="0">
-        <v>102400</v>
+        <v>96230</v>
       </c>
       <c r="D4" s="0">
         <v>0</v>
@@ -4099,19 +4112,19 @@
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>3516</v>
+        <v>4600</v>
       </c>
       <c r="G4" s="0">
         <v>1</v>
       </c>
       <c r="H4" s="0">
-        <v>0.96680388232184</v>
+        <v>0.95437865714569081</v>
       </c>
       <c r="I4" s="0">
-        <v>0.96680388232184</v>
+        <v>0.95437865714569081</v>
       </c>
       <c r="J4" s="0">
-        <v>0.98312179573340497</v>
+        <v>0.97665685577996542</v>
       </c>
     </row>
     <row r="5">
@@ -4125,10 +4138,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="0">
-        <v>2050</v>
+        <v>1800</v>
       </c>
       <c r="E5" s="0">
-        <v>21774</v>
+        <v>21330</v>
       </c>
       <c r="F5" s="0">
         <v>0</v>
@@ -4140,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>0.91395231699126933</v>
+        <v>0.9221789883268483</v>
       </c>
       <c r="J5" s="0">
         <v>0</v>
@@ -4157,10 +4170,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>10800</v>
+        <v>10950</v>
       </c>
       <c r="E6" s="0">
-        <v>11402</v>
+        <v>11100</v>
       </c>
       <c r="F6" s="0">
         <v>0</v>
@@ -4172,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>0.51355733717683094</v>
+        <v>0.50340136054421769</v>
       </c>
       <c r="J6" s="0">
         <v>0</v>
@@ -4186,7 +4199,7 @@
         <v>52</v>
       </c>
       <c r="C7" s="0">
-        <v>248500</v>
+        <v>238880</v>
       </c>
       <c r="D7" s="0">
         <v>0</v>
@@ -4195,19 +4208,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>58662</v>
+        <v>55520</v>
       </c>
       <c r="G7" s="0">
         <v>1</v>
       </c>
       <c r="H7" s="0">
-        <v>0.80901934484083315</v>
+        <v>0.81141304347826082</v>
       </c>
       <c r="I7" s="0">
-        <v>0.80901934484083315</v>
+        <v>0.81141304347826082</v>
       </c>
       <c r="J7" s="0">
-        <v>0.89442862747497576</v>
+        <v>0.89588958895889581</v>
       </c>
     </row>
     <row r="8">
@@ -4218,28 +4231,28 @@
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>48970</v>
+        <v>33450</v>
       </c>
       <c r="D8" s="0">
-        <v>3930</v>
+        <v>2490</v>
       </c>
       <c r="E8" s="0">
-        <v>76650</v>
+        <v>77240</v>
       </c>
       <c r="F8" s="0">
-        <v>1052</v>
+        <v>3180</v>
       </c>
       <c r="G8" s="0">
-        <v>0.92570888468809076</v>
+        <v>0.93071786310517535</v>
       </c>
       <c r="H8" s="0">
-        <v>0.97896925352844744</v>
+        <v>0.91318591318591313</v>
       </c>
       <c r="I8" s="0">
-        <v>0.96185357038942743</v>
+        <v>0.95127191474733586</v>
       </c>
       <c r="J8" s="0">
-        <v>0.95159441130176248</v>
+        <v>0.92186854071930557</v>
       </c>
     </row>
     <row r="9">
@@ -4250,28 +4263,28 @@
         <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>21950</v>
+        <v>21600</v>
       </c>
       <c r="D9" s="0">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="E9" s="0">
-        <v>20762</v>
+        <v>20860</v>
       </c>
       <c r="F9" s="0">
-        <v>2450</v>
+        <v>2800</v>
       </c>
       <c r="G9" s="0">
-        <v>0.81146025878003691</v>
+        <v>0.81203007518796988</v>
       </c>
       <c r="H9" s="0">
-        <v>0.89959016393442626</v>
+        <v>0.88524590163934425</v>
       </c>
       <c r="I9" s="0">
-        <v>0.84978711551470298</v>
+        <v>0.84480700358137684</v>
       </c>
       <c r="J9" s="0">
-        <v>0.85325558794946554</v>
+        <v>0.84705882352941175</v>
       </c>
     </row>
     <row r="10">
@@ -4282,28 +4295,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="0">
-        <v>79180</v>
+        <v>76160</v>
       </c>
       <c r="D10" s="0">
-        <v>2020</v>
+        <v>1900</v>
       </c>
       <c r="E10" s="0">
-        <v>64380</v>
+        <v>64500</v>
       </c>
       <c r="F10" s="0">
-        <v>1002</v>
+        <v>1680</v>
       </c>
       <c r="G10" s="0">
-        <v>0.97512315270935956</v>
+        <v>0.97565974891109408</v>
       </c>
       <c r="H10" s="0">
-        <v>0.98750342969743832</v>
+        <v>0.97841726618705038</v>
       </c>
       <c r="I10" s="0">
-        <v>0.97938355323300263</v>
+        <v>0.97518025513033835</v>
       </c>
       <c r="J10" s="0">
-        <v>0.9812742437198696</v>
+        <v>0.97703656189865307</v>
       </c>
     </row>
     <row r="11">
@@ -4314,28 +4327,28 @@
         <v>2</v>
       </c>
       <c r="C11" s="0">
-        <v>47330</v>
+        <v>47130</v>
       </c>
       <c r="D11" s="0">
-        <v>3420</v>
+        <v>3270</v>
       </c>
       <c r="E11" s="0">
-        <v>54550</v>
+        <v>54460</v>
       </c>
       <c r="F11" s="0">
-        <v>2832</v>
+        <v>3030</v>
       </c>
       <c r="G11" s="0">
-        <v>0.93261083743842366</v>
+        <v>0.93511904761904763</v>
       </c>
       <c r="H11" s="0">
-        <v>0.94354292093616687</v>
+        <v>0.93959330143540665</v>
       </c>
       <c r="I11" s="0">
-        <v>0.94218177782710022</v>
+        <v>0.94160719251089076</v>
       </c>
       <c r="J11" s="0">
-        <v>0.93804502933248768</v>
+        <v>0.93735083532219554</v>
       </c>
     </row>
     <row r="12">
@@ -4346,28 +4359,28 @@
         <v>2</v>
       </c>
       <c r="C12" s="0">
-        <v>24700</v>
+        <v>22990</v>
       </c>
       <c r="D12" s="0">
-        <v>10250</v>
+        <v>8850</v>
       </c>
       <c r="E12" s="0">
-        <v>27972</v>
+        <v>29370</v>
       </c>
       <c r="F12" s="0">
-        <v>870</v>
+        <v>2380</v>
       </c>
       <c r="G12" s="0">
-        <v>0.70672389127324753</v>
+        <v>0.72204773869346739</v>
       </c>
       <c r="H12" s="0">
-        <v>0.96597575283535397</v>
+        <v>0.90618841150965712</v>
       </c>
       <c r="I12" s="0">
-        <v>0.82568347128166542</v>
+        <v>0.82339990564554177</v>
       </c>
       <c r="J12" s="0">
-        <v>0.81625908790482482</v>
+        <v>0.80370564586610749</v>
       </c>
     </row>
     <row r="13">
@@ -4378,28 +4391,28 @@
         <v>2</v>
       </c>
       <c r="C13" s="0">
-        <v>22920</v>
+        <v>22200</v>
       </c>
       <c r="D13" s="0">
-        <v>3830</v>
+        <v>4180</v>
       </c>
       <c r="E13" s="0">
-        <v>24772</v>
+        <v>24420</v>
       </c>
       <c r="F13" s="0">
-        <v>2060</v>
+        <v>2380</v>
       </c>
       <c r="G13" s="0">
-        <v>0.856822429906542</v>
+        <v>0.84154662623199394</v>
       </c>
       <c r="H13" s="0">
-        <v>0.91753402722177746</v>
+        <v>0.90317331163547598</v>
       </c>
       <c r="I13" s="0">
-        <v>0.89007502519502824</v>
+        <v>0.87664535539676569</v>
       </c>
       <c r="J13" s="0">
-        <v>0.88613957084863704</v>
+        <v>0.87127158555729989</v>
       </c>
     </row>
     <row r="14">
@@ -4410,28 +4423,28 @@
         <v>2</v>
       </c>
       <c r="C14" s="0">
-        <v>7750</v>
+        <v>7800</v>
       </c>
       <c r="D14" s="0">
-        <v>3600</v>
+        <v>3550</v>
       </c>
       <c r="E14" s="0">
-        <v>14502</v>
+        <v>14550</v>
       </c>
       <c r="F14" s="0">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G14" s="0">
-        <v>0.68281938325991187</v>
+        <v>0.68722466960352424</v>
       </c>
       <c r="H14" s="0">
-        <v>0.9337349397590361</v>
+        <v>0.93975903614457834</v>
       </c>
       <c r="I14" s="0">
-        <v>0.84281493826225284</v>
+        <v>0.84659090909090906</v>
       </c>
       <c r="J14" s="0">
-        <v>0.78880407124681939</v>
+        <v>0.79389312977099225</v>
       </c>
     </row>
     <row r="15">
@@ -4445,25 +4458,25 @@
         <v>5770</v>
       </c>
       <c r="D15" s="0">
-        <v>3130</v>
+        <v>2780</v>
       </c>
       <c r="E15" s="0">
-        <v>8012</v>
+        <v>8060</v>
       </c>
       <c r="F15" s="0">
         <v>2530</v>
       </c>
       <c r="G15" s="0">
-        <v>0.64831460674157304</v>
+        <v>0.67485380116959059</v>
       </c>
       <c r="H15" s="0">
         <v>0.69518072289156629</v>
       </c>
       <c r="I15" s="0">
-        <v>0.70887768748071189</v>
+        <v>0.72257053291536055</v>
       </c>
       <c r="J15" s="0">
-        <v>0.67093023255813955</v>
+        <v>0.68486646884272995</v>
       </c>
     </row>
     <row r="16">
@@ -4474,28 +4487,28 @@
         <v>2</v>
       </c>
       <c r="C16" s="0">
-        <v>7510</v>
+        <v>6980</v>
       </c>
       <c r="D16" s="0">
-        <v>3440</v>
+        <v>2820</v>
       </c>
       <c r="E16" s="0">
-        <v>15532</v>
+        <v>15860</v>
       </c>
       <c r="F16" s="0">
-        <v>350</v>
+        <v>430</v>
       </c>
       <c r="G16" s="0">
-        <v>0.68584474885844748</v>
+        <v>0.71224489795918366</v>
       </c>
       <c r="H16" s="0">
-        <v>0.95547073791348602</v>
+        <v>0.94197031039136303</v>
       </c>
       <c r="I16" s="0">
-        <v>0.85875074537865237</v>
+        <v>0.87543119969336913</v>
       </c>
       <c r="J16" s="0">
-        <v>0.79851143009037751</v>
+        <v>0.81115630447414289</v>
       </c>
     </row>
     <row r="17">
@@ -4506,28 +4519,28 @@
         <v>2</v>
       </c>
       <c r="C17" s="0">
-        <v>7080</v>
+        <v>5450</v>
       </c>
       <c r="D17" s="0">
-        <v>3320</v>
+        <v>2680</v>
       </c>
       <c r="E17" s="0">
-        <v>8522</v>
+        <v>6770</v>
       </c>
       <c r="F17" s="0">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G17" s="0">
-        <v>0.68076923076923079</v>
+        <v>0.67035670356703569</v>
       </c>
       <c r="H17" s="0">
-        <v>0.95546558704453444</v>
+        <v>0.94127806563039729</v>
       </c>
       <c r="I17" s="0">
-        <v>0.81040930812383127</v>
+        <v>0.80183727034120733</v>
       </c>
       <c r="J17" s="0">
-        <v>0.7950589556428973</v>
+        <v>0.78304597701149425</v>
       </c>
     </row>
   </sheetData>
@@ -4591,28 +4604,28 @@
         <v>20</v>
       </c>
       <c r="C2" s="0">
-        <v>161420</v>
+        <v>151080</v>
       </c>
       <c r="D2" s="0">
-        <v>66530</v>
+        <v>53320</v>
       </c>
       <c r="E2" s="0">
-        <v>969164</v>
+        <v>977820</v>
       </c>
       <c r="F2" s="0">
-        <v>5166</v>
+        <v>8850</v>
       </c>
       <c r="G2" s="0">
-        <v>0.70813774950647068</v>
+        <v>0.73913894324853224</v>
       </c>
       <c r="H2" s="0">
-        <v>0.96898899067148503</v>
+        <v>0.94466329018945794</v>
       </c>
       <c r="I2" s="0">
-        <v>0.94036663672355858</v>
+        <v>0.94780323574600989</v>
       </c>
       <c r="J2" s="0">
-        <v>0.81827767301336263</v>
+        <v>0.82935799961573287</v>
       </c>
     </row>
     <row r="3">
@@ -4623,28 +4636,28 @@
         <v>16</v>
       </c>
       <c r="C3" s="0">
-        <v>136140</v>
+        <v>119060</v>
       </c>
       <c r="D3" s="0">
         <v>50660</v>
       </c>
       <c r="E3" s="0">
-        <v>868330</v>
+        <v>866020</v>
       </c>
       <c r="F3" s="0">
-        <v>9056</v>
+        <v>11740</v>
       </c>
       <c r="G3" s="0">
-        <v>0.7288008565310492</v>
+        <v>0.70150836672165917</v>
       </c>
       <c r="H3" s="0">
-        <v>0.93762913578886475</v>
+        <v>0.91024464831804286</v>
       </c>
       <c r="I3" s="0">
-        <v>0.94388574929570579</v>
+        <v>0.94042845686791154</v>
       </c>
       <c r="J3" s="0">
-        <v>0.82013036301642195</v>
+        <v>0.79235990949021684</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4668,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="0">
-        <v>28750</v>
+        <v>28060</v>
       </c>
       <c r="D4" s="0">
         <v>0</v>
@@ -4664,19 +4677,19 @@
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G4" s="0">
         <v>1</v>
       </c>
       <c r="H4" s="0">
-        <v>0.99570547897762696</v>
+        <v>0.99538843561546653</v>
       </c>
       <c r="I4" s="0">
-        <v>0.99570547897762696</v>
+        <v>0.99538843561546653</v>
       </c>
       <c r="J4" s="0">
-        <v>0.99784811883937252</v>
+        <v>0.99768888888888896</v>
       </c>
     </row>
     <row r="5">
@@ -4687,7 +4700,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="0">
-        <v>28450</v>
+        <v>26490</v>
       </c>
       <c r="D5" s="0">
         <v>0</v>
@@ -4696,19 +4709,19 @@
         <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>244</v>
+        <v>330</v>
       </c>
       <c r="G5" s="0">
         <v>1</v>
       </c>
       <c r="H5" s="0">
-        <v>0.99149648010036939</v>
+        <v>0.98769574944071592</v>
       </c>
       <c r="I5" s="0">
-        <v>0.99149648010036939</v>
+        <v>0.98769574944071592</v>
       </c>
       <c r="J5" s="0">
-        <v>0.995730085398292</v>
+        <v>0.99380979178390549</v>
       </c>
     </row>
     <row r="6">
@@ -4719,7 +4732,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="0">
-        <v>9200</v>
+        <v>10010</v>
       </c>
       <c r="D6" s="0">
         <v>0</v>
@@ -4728,19 +4741,19 @@
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>13214</v>
+        <v>10960</v>
       </c>
       <c r="G6" s="0">
         <v>1</v>
       </c>
       <c r="H6" s="0">
-        <v>0.41045774962077275</v>
+        <v>0.47734859322842155</v>
       </c>
       <c r="I6" s="0">
-        <v>0.41045774962077275</v>
+        <v>0.47734859322842155</v>
       </c>
       <c r="J6" s="0">
-        <v>0.58202062377427732</v>
+        <v>0.64622336991607487</v>
       </c>
     </row>
     <row r="7">
@@ -4751,7 +4764,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="0">
-        <v>10250</v>
+        <v>9930</v>
       </c>
       <c r="D7" s="0">
         <v>0</v>
@@ -4760,19 +4773,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>12294</v>
+        <v>11810</v>
       </c>
       <c r="G7" s="0">
         <v>1</v>
       </c>
       <c r="H7" s="0">
-        <v>0.45466643009226404</v>
+        <v>0.45676172953081878</v>
       </c>
       <c r="I7" s="0">
-        <v>0.45466643009226404</v>
+        <v>0.45676172953081878</v>
       </c>
       <c r="J7" s="0">
-        <v>0.62511435018600969</v>
+        <v>0.62709188506473001</v>
       </c>
     </row>
     <row r="8">
@@ -4783,7 +4796,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="0">
-        <v>11600</v>
+        <v>12090</v>
       </c>
       <c r="D8" s="0">
         <v>0</v>
@@ -4792,19 +4805,19 @@
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>8264</v>
+        <v>6600</v>
       </c>
       <c r="G8" s="0">
         <v>1</v>
       </c>
       <c r="H8" s="0">
-        <v>0.58397100281917036</v>
+        <v>0.6468699839486356</v>
       </c>
       <c r="I8" s="0">
-        <v>0.58397100281917036</v>
+        <v>0.6468699839486356</v>
       </c>
       <c r="J8" s="0">
-        <v>0.73735062293414699</v>
+        <v>0.78557504873294348</v>
       </c>
     </row>
     <row r="9">
@@ -4815,7 +4828,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="0">
-        <v>29450</v>
+        <v>28970</v>
       </c>
       <c r="D9" s="0">
         <v>0</v>
@@ -4824,19 +4837,19 @@
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>844</v>
+        <v>920</v>
       </c>
       <c r="G9" s="0">
         <v>1</v>
       </c>
       <c r="H9" s="0">
-        <v>0.97213969762989372</v>
+        <v>0.96922047507527598</v>
       </c>
       <c r="I9" s="0">
-        <v>0.97213969762989372</v>
+        <v>0.96922047507527598</v>
       </c>
       <c r="J9" s="0">
-        <v>0.98587305838243167</v>
+        <v>0.98436969079170911</v>
       </c>
     </row>
     <row r="10">
@@ -4847,7 +4860,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="0">
-        <v>29300</v>
+        <v>28400</v>
       </c>
       <c r="D10" s="0">
         <v>0</v>
@@ -4856,19 +4869,19 @@
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>344</v>
+        <v>260</v>
       </c>
       <c r="G10" s="0">
         <v>1</v>
       </c>
       <c r="H10" s="0">
-        <v>0.98839562812036164</v>
+        <v>0.99092812281926035</v>
       </c>
       <c r="I10" s="0">
-        <v>0.98839562812036164</v>
+        <v>0.99092812281926035</v>
       </c>
       <c r="J10" s="0">
-        <v>0.99416395222584153</v>
+        <v>0.99544339291973361</v>
       </c>
     </row>
     <row r="11">
@@ -4879,7 +4892,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="0">
-        <v>21250</v>
+        <v>19990</v>
       </c>
       <c r="D11" s="0">
         <v>0</v>
@@ -4888,19 +4901,19 @@
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>434</v>
+        <v>710</v>
       </c>
       <c r="G11" s="0">
         <v>1</v>
       </c>
       <c r="H11" s="0">
-        <v>0.97998524257517061</v>
+        <v>0.96570048309178746</v>
       </c>
       <c r="I11" s="0">
-        <v>0.97998524257517061</v>
+        <v>0.96570048309178746</v>
       </c>
       <c r="J11" s="0">
-        <v>0.98989146131271244</v>
+        <v>0.98255099533054802</v>
       </c>
     </row>
     <row r="12">
@@ -4911,7 +4924,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="0">
-        <v>22550</v>
+        <v>21780</v>
       </c>
       <c r="D12" s="0">
         <v>0</v>
@@ -4920,19 +4933,19 @@
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="G12" s="0">
         <v>1</v>
       </c>
       <c r="H12" s="0">
-        <v>0.99016422235883028</v>
+        <v>0.98685999093792476</v>
       </c>
       <c r="I12" s="0">
-        <v>0.99016422235883028</v>
+        <v>0.98685999093792476</v>
       </c>
       <c r="J12" s="0">
-        <v>0.99505780601888627</v>
+        <v>0.99338654503990875</v>
       </c>
     </row>
     <row r="13">
@@ -4943,7 +4956,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="0">
-        <v>22050</v>
+        <v>19450</v>
       </c>
       <c r="D13" s="0">
         <v>0</v>
@@ -4952,19 +4965,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>1774</v>
+        <v>3970</v>
       </c>
       <c r="G13" s="0">
         <v>1</v>
       </c>
       <c r="H13" s="0">
-        <v>0.92553727333781066</v>
+        <v>0.83048676345004269</v>
       </c>
       <c r="I13" s="0">
-        <v>0.92553727333781066</v>
+        <v>0.83048676345004269</v>
       </c>
       <c r="J13" s="0">
-        <v>0.96132885730479145</v>
+        <v>0.90739444833216698</v>
       </c>
     </row>
     <row r="14">
@@ -4975,7 +4988,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="0">
-        <v>48950</v>
+        <v>47950</v>
       </c>
       <c r="D14" s="0">
         <v>0</v>
@@ -4984,19 +4997,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>448</v>
+        <v>340</v>
       </c>
       <c r="G14" s="0">
         <v>1</v>
       </c>
       <c r="H14" s="0">
-        <v>0.9909308069152597</v>
+        <v>0.99295920480430733</v>
       </c>
       <c r="I14" s="0">
-        <v>0.9909308069152597</v>
+        <v>0.99295920480430733</v>
       </c>
       <c r="J14" s="0">
-        <v>0.99544474722414289</v>
+        <v>0.99646716541978397</v>
       </c>
     </row>
     <row r="15">
@@ -5007,7 +5020,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="0">
-        <v>26300</v>
+        <v>25100</v>
       </c>
       <c r="D15" s="0">
         <v>0</v>
@@ -5016,19 +5029,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>2014</v>
+        <v>1900</v>
       </c>
       <c r="G15" s="0">
         <v>1</v>
       </c>
       <c r="H15" s="0">
-        <v>0.9288691106872925</v>
+        <v>0.92962962962962958</v>
       </c>
       <c r="I15" s="0">
-        <v>0.9288691106872925</v>
+        <v>0.92962962962962958</v>
       </c>
       <c r="J15" s="0">
-        <v>0.96312300875233459</v>
+        <v>0.96353166986564298</v>
       </c>
     </row>
     <row r="16">
@@ -5039,7 +5052,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="0">
-        <v>26950</v>
+        <v>25710</v>
       </c>
       <c r="D16" s="0">
         <v>0</v>
@@ -5048,19 +5061,19 @@
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <v>1044</v>
+        <v>1200</v>
       </c>
       <c r="G16" s="0">
         <v>1</v>
       </c>
       <c r="H16" s="0">
-        <v>0.96270629420590126</v>
+        <v>0.95540691192865101</v>
       </c>
       <c r="I16" s="0">
-        <v>0.96270629420590126</v>
+        <v>0.95540691192865101</v>
       </c>
       <c r="J16" s="0">
-        <v>0.98099883517763542</v>
+        <v>0.97719498289623719</v>
       </c>
     </row>
     <row r="17">
@@ -5071,28 +5084,28 @@
         <v>6</v>
       </c>
       <c r="C17" s="0">
-        <v>11250</v>
+        <v>10570</v>
       </c>
       <c r="D17" s="0">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E17" s="0">
-        <v>28524</v>
+        <v>27810</v>
       </c>
       <c r="F17" s="0">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="G17" s="0">
-        <v>0.97826086956521741</v>
+        <v>0.97240110395584178</v>
       </c>
       <c r="H17" s="0">
-        <v>0.9875351123595506</v>
+        <v>0.98970037453183524</v>
       </c>
       <c r="I17" s="0">
-        <v>0.99024050191704427</v>
+        <v>0.98943026553235369</v>
       </c>
       <c r="J17" s="0">
-        <v>0.9828761139262624</v>
+        <v>0.98097447795823656</v>
       </c>
     </row>
     <row r="18">
@@ -5103,7 +5116,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="0">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D18" s="0">
         <v>0</v>
@@ -5112,19 +5125,2406 @@
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>20574</v>
+        <v>19250</v>
       </c>
       <c r="G18" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="0">
-        <v>0.00962741888899586</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0">
-        <v>0.00962741888899586</v>
+        <v>0</v>
       </c>
       <c r="J18" s="0">
-        <v>0.019071231047964148</v>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G103"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" customWidth="true"/>
+    <col min="2" max="2" width="9.88671875" customWidth="true"/>
+    <col min="3" max="3" width="5.33203125" customWidth="true"/>
+    <col min="4" max="4" width="8" customWidth="true"/>
+    <col min="5" max="5" width="7.77734375" customWidth="true"/>
+    <col min="6" max="6" width="11.44140625" customWidth="true"/>
+    <col min="7" max="7" width="12.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="0">
+        <v>504.57999999999998</v>
+      </c>
+      <c r="E2" s="0">
+        <v>502.60000000000002</v>
+      </c>
+      <c r="F2" s="0">
+        <v>1.9799999999999613</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.39240556502436907</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="0">
+        <v>504.57999999999998</v>
+      </c>
+      <c r="E3" s="0">
+        <v>502.60000000000002</v>
+      </c>
+      <c r="F3" s="0">
+        <v>1.9799999999999613</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.39240556502436907</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="0">
+        <v>1474.98</v>
+      </c>
+      <c r="E4" s="0">
+        <v>1416</v>
+      </c>
+      <c r="F4" s="0">
+        <v>58.980000000000018</v>
+      </c>
+      <c r="G4" s="0">
+        <v>3.998698287434407</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1474.98</v>
+      </c>
+      <c r="E5" s="0">
+        <v>1468.8</v>
+      </c>
+      <c r="F5" s="0">
+        <v>6.1800000000000637</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.41898873205060838</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1505.78</v>
+      </c>
+      <c r="E6" s="0">
+        <v>977</v>
+      </c>
+      <c r="F6" s="0">
+        <v>528.77999999999997</v>
+      </c>
+      <c r="G6" s="0">
+        <v>35.116683712096055</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="0">
+        <v>1505.78</v>
+      </c>
+      <c r="E7" s="0">
+        <v>1350.2</v>
+      </c>
+      <c r="F7" s="0">
+        <v>155.57999999999993</v>
+      </c>
+      <c r="G7" s="0">
+        <v>10.332186640810738</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="0">
+        <v>1086.5799999999999</v>
+      </c>
+      <c r="E8" s="0">
+        <v>1075.4000000000001</v>
+      </c>
+      <c r="F8" s="0">
+        <v>11.179999999999836</v>
+      </c>
+      <c r="G8" s="0">
+        <v>1.0289164166467115</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="0">
+        <v>1086.5799999999999</v>
+      </c>
+      <c r="E9" s="0">
+        <v>1082.4000000000001</v>
+      </c>
+      <c r="F9" s="0">
+        <v>4.1799999999998363</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.38469325774446766</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="0">
+        <v>640.17999999999995</v>
+      </c>
+      <c r="E10" s="0">
+        <v>633.60000000000002</v>
+      </c>
+      <c r="F10" s="0">
+        <v>6.5799999999999272</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1.0278359211471662</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="0">
+        <v>640.17999999999995</v>
+      </c>
+      <c r="E11" s="0">
+        <v>638.20000000000005</v>
+      </c>
+      <c r="F11" s="0">
+        <v>1.9799999999999045</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.30928801274640016</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="0">
+        <v>540.98000000000002</v>
+      </c>
+      <c r="E12" s="0">
+        <v>531.39999999999998</v>
+      </c>
+      <c r="F12" s="0">
+        <v>9.5800000000000409</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1.7708602905837629</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="0">
+        <v>540.98000000000002</v>
+      </c>
+      <c r="E13" s="0">
+        <v>532.20000000000005</v>
+      </c>
+      <c r="F13" s="0">
+        <v>8.7799999999999727</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1.6229805168398042</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="0">
+        <v>265.98000000000002</v>
+      </c>
+      <c r="E14" s="0">
+        <v>264</v>
+      </c>
+      <c r="F14" s="0">
+        <v>1.9800000000000182</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0.74441687344913832</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="0">
+        <v>265.98000000000002</v>
+      </c>
+      <c r="E15" s="0">
+        <v>264</v>
+      </c>
+      <c r="F15" s="0">
+        <v>1.9800000000000182</v>
+      </c>
+      <c r="G15" s="0">
+        <v>0.74441687344913832</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="0">
+        <v>199.97999999999999</v>
+      </c>
+      <c r="E16" s="0">
+        <v>188.40000000000001</v>
+      </c>
+      <c r="F16" s="0">
+        <v>11.579999999999984</v>
+      </c>
+      <c r="G16" s="0">
+        <v>5.7905790579057825</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="0">
+        <v>199.97999999999999</v>
+      </c>
+      <c r="E17" s="0">
+        <v>194.40000000000001</v>
+      </c>
+      <c r="F17" s="0">
+        <v>5.5799999999999841</v>
+      </c>
+      <c r="G17" s="0">
+        <v>2.7902790279027823</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="0">
+        <v>274.98000000000002</v>
+      </c>
+      <c r="E18" s="0">
+        <v>252.19999999999999</v>
+      </c>
+      <c r="F18" s="0">
+        <v>22.78000000000003</v>
+      </c>
+      <c r="G18" s="0">
+        <v>8.284238853734827</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="0">
+        <v>274.98000000000002</v>
+      </c>
+      <c r="E19" s="0">
+        <v>269.60000000000002</v>
+      </c>
+      <c r="F19" s="0">
+        <v>5.3799999999999955</v>
+      </c>
+      <c r="G19" s="0">
+        <v>1.9565059277038312</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="0">
+        <v>219.97999999999999</v>
+      </c>
+      <c r="E20" s="0">
+        <v>218</v>
+      </c>
+      <c r="F20" s="0">
+        <v>1.9799999999999898</v>
+      </c>
+      <c r="G20" s="0">
+        <v>0.90008182562050632</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="0">
+        <v>217.97999999999999</v>
+      </c>
+      <c r="E21" s="0">
+        <v>86.799999999999997</v>
+      </c>
+      <c r="F21" s="0">
+        <v>131.18000000000001</v>
+      </c>
+      <c r="G21" s="0">
+        <v>60.179833012202955</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="0">
+        <v>8495.7800000000007</v>
+      </c>
+      <c r="E22" s="0">
+        <v>8454.7999999999993</v>
+      </c>
+      <c r="F22" s="0">
+        <v>40.980000000001382</v>
+      </c>
+      <c r="G22" s="0">
+        <v>0.48235712318352619</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="0">
+        <v>8495.7800000000007</v>
+      </c>
+      <c r="E23" s="0">
+        <v>8478.3999999999996</v>
+      </c>
+      <c r="F23" s="0">
+        <v>17.380000000001019</v>
+      </c>
+      <c r="G23" s="0">
+        <v>0.20457215229209111</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="0">
+        <v>7015.9799999999996</v>
+      </c>
+      <c r="E24" s="0">
+        <v>6988</v>
+      </c>
+      <c r="F24" s="0">
+        <v>27.979999999999563</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0.39880387344319063</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="0">
+        <v>7015.9799999999996</v>
+      </c>
+      <c r="E25" s="0">
+        <v>7004.6000000000004</v>
+      </c>
+      <c r="F25" s="0">
+        <v>11.3799999999992</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0.16220114652549181</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="0">
+        <v>142.18000000000001</v>
+      </c>
+      <c r="E26" s="0">
+        <v>128.40000000000001</v>
+      </c>
+      <c r="F26" s="0">
+        <v>13.780000000000001</v>
+      </c>
+      <c r="G26" s="0">
+        <v>9.6919397946265295</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="0">
+        <v>142.18000000000001</v>
+      </c>
+      <c r="E27" s="0">
+        <v>122.8</v>
+      </c>
+      <c r="F27" s="0">
+        <v>19.38000000000001</v>
+      </c>
+      <c r="G27" s="0">
+        <v>13.630609087072731</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="0">
+        <v>132.38</v>
+      </c>
+      <c r="E28" s="0">
+        <v>119.8</v>
+      </c>
+      <c r="F28" s="0">
+        <v>12.579999999999998</v>
+      </c>
+      <c r="G28" s="0">
+        <v>9.5029460643601738</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="0">
+        <v>132.38</v>
+      </c>
+      <c r="E29" s="0">
+        <v>117</v>
+      </c>
+      <c r="F29" s="0">
+        <v>15.379999999999995</v>
+      </c>
+      <c r="G29" s="0">
+        <v>11.618069194742406</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="0">
+        <v>132.58000000000001</v>
+      </c>
+      <c r="E30" s="0">
+        <v>119.59999999999999</v>
+      </c>
+      <c r="F30" s="0">
+        <v>12.980000000000018</v>
+      </c>
+      <c r="G30" s="0">
+        <v>9.7903152813395806</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="0">
+        <v>132.58000000000001</v>
+      </c>
+      <c r="E31" s="0">
+        <v>91.200000000000003</v>
+      </c>
+      <c r="F31" s="0">
+        <v>41.38000000000001</v>
+      </c>
+      <c r="G31" s="0">
+        <v>31.211344094131849</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="0">
+        <v>186.58000000000001</v>
+      </c>
+      <c r="E32" s="0">
+        <v>164.40000000000001</v>
+      </c>
+      <c r="F32" s="0">
+        <v>22.180000000000007</v>
+      </c>
+      <c r="G32" s="0">
+        <v>11.887662128845539</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="0">
+        <v>186.58000000000001</v>
+      </c>
+      <c r="E33" s="0">
+        <v>164.80000000000001</v>
+      </c>
+      <c r="F33" s="0">
+        <v>21.780000000000001</v>
+      </c>
+      <c r="G33" s="0">
+        <v>11.673276878550755</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="0">
+        <v>142.78</v>
+      </c>
+      <c r="E34" s="0">
+        <v>121.59999999999999</v>
+      </c>
+      <c r="F34" s="0">
+        <v>21.180000000000007</v>
+      </c>
+      <c r="G34" s="0">
+        <v>14.834010365597429</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="0">
+        <v>142.78</v>
+      </c>
+      <c r="E35" s="0">
+        <v>123.8</v>
+      </c>
+      <c r="F35" s="0">
+        <v>18.980000000000004</v>
+      </c>
+      <c r="G35" s="0">
+        <v>13.293178316290801</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="0">
+        <v>179.78</v>
+      </c>
+      <c r="E36" s="0">
+        <v>146.40000000000001</v>
+      </c>
+      <c r="F36" s="0">
+        <v>33.379999999999995</v>
+      </c>
+      <c r="G36" s="0">
+        <v>18.567137612637666</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="0">
+        <v>179.78</v>
+      </c>
+      <c r="E37" s="0">
+        <v>146.40000000000001</v>
+      </c>
+      <c r="F37" s="0">
+        <v>33.379999999999995</v>
+      </c>
+      <c r="G37" s="0">
+        <v>18.567137612637666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="0">
+        <v>237.97999999999999</v>
+      </c>
+      <c r="E38" s="0">
+        <v>220.80000000000001</v>
+      </c>
+      <c r="F38" s="0">
+        <v>17.179999999999978</v>
+      </c>
+      <c r="G38" s="0">
+        <v>7.2190940415160849</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="0">
+        <v>237.97999999999999</v>
+      </c>
+      <c r="E39" s="0">
+        <v>220.19999999999999</v>
+      </c>
+      <c r="F39" s="0">
+        <v>17.780000000000001</v>
+      </c>
+      <c r="G39" s="0">
+        <v>7.471216068577192</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="0">
+        <v>153.38</v>
+      </c>
+      <c r="E40" s="0">
+        <v>136.59999999999999</v>
+      </c>
+      <c r="F40" s="0">
+        <v>16.780000000000001</v>
+      </c>
+      <c r="G40" s="0">
+        <v>10.940148650410745</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="0">
+        <v>153.38</v>
+      </c>
+      <c r="E41" s="0">
+        <v>134.80000000000001</v>
+      </c>
+      <c r="F41" s="0">
+        <v>18.579999999999984</v>
+      </c>
+      <c r="G41" s="0">
+        <v>12.113704524709862</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="0">
+        <v>165.18000000000001</v>
+      </c>
+      <c r="E42" s="0">
+        <v>151.40000000000001</v>
+      </c>
+      <c r="F42" s="0">
+        <v>13.780000000000001</v>
+      </c>
+      <c r="G42" s="0">
+        <v>8.342414335876013</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="0">
+        <v>165.18000000000001</v>
+      </c>
+      <c r="E43" s="0">
+        <v>141</v>
+      </c>
+      <c r="F43" s="0">
+        <v>24.180000000000007</v>
+      </c>
+      <c r="G43" s="0">
+        <v>14.638576098801312</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="0">
+        <v>160.58000000000001</v>
+      </c>
+      <c r="E44" s="0">
+        <v>105.8</v>
+      </c>
+      <c r="F44" s="0">
+        <v>54.780000000000015</v>
+      </c>
+      <c r="G44" s="0">
+        <v>34.113837339643801</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="0">
+        <v>160.58000000000001</v>
+      </c>
+      <c r="E45" s="0">
+        <v>135</v>
+      </c>
+      <c r="F45" s="0">
+        <v>25.580000000000013</v>
+      </c>
+      <c r="G45" s="0">
+        <v>15.929754639432065</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="0">
+        <v>170.18000000000001</v>
+      </c>
+      <c r="E46" s="0">
+        <v>144</v>
+      </c>
+      <c r="F46" s="0">
+        <v>26.180000000000007</v>
+      </c>
+      <c r="G46" s="0">
+        <v>15.383711364437659</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="0">
+        <v>170.18000000000001</v>
+      </c>
+      <c r="E47" s="0">
+        <v>151.59999999999999</v>
+      </c>
+      <c r="F47" s="0">
+        <v>18.580000000000013</v>
+      </c>
+      <c r="G47" s="0">
+        <v>10.91785168644965</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="0">
+        <v>123.98</v>
+      </c>
+      <c r="E48" s="0">
+        <v>112</v>
+      </c>
+      <c r="F48" s="0">
+        <v>11.980000000000004</v>
+      </c>
+      <c r="G48" s="0">
+        <v>9.6628488465881635</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="0">
+        <v>123.98</v>
+      </c>
+      <c r="E49" s="0">
+        <v>112</v>
+      </c>
+      <c r="F49" s="0">
+        <v>11.980000000000004</v>
+      </c>
+      <c r="G49" s="0">
+        <v>9.6628488465881635</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="0">
+        <v>123.38</v>
+      </c>
+      <c r="E50" s="0">
+        <v>91.599999999999994</v>
+      </c>
+      <c r="F50" s="0">
+        <v>31.780000000000001</v>
+      </c>
+      <c r="G50" s="0">
+        <v>25.757821364888962</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="0">
+        <v>123.38</v>
+      </c>
+      <c r="E51" s="0">
+        <v>103.8</v>
+      </c>
+      <c r="F51" s="0">
+        <v>19.579999999999998</v>
+      </c>
+      <c r="G51" s="0">
+        <v>15.86967093532177</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="0">
+        <v>130.38</v>
+      </c>
+      <c r="E52" s="0">
+        <v>116.2</v>
+      </c>
+      <c r="F52" s="0">
+        <v>14.179999999999993</v>
+      </c>
+      <c r="G52" s="0">
+        <v>10.875901211842303</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="0">
+        <v>130.38</v>
+      </c>
+      <c r="E53" s="0">
+        <v>117.40000000000001</v>
+      </c>
+      <c r="F53" s="0">
+        <v>12.97999999999999</v>
+      </c>
+      <c r="G53" s="0">
+        <v>9.9555146494861102</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="0">
+        <v>116.78</v>
+      </c>
+      <c r="E54" s="0">
+        <v>100.2</v>
+      </c>
+      <c r="F54" s="0">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="G54" s="0">
+        <v>14.197636581606437</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="0">
+        <v>116.78</v>
+      </c>
+      <c r="E55" s="0">
+        <v>101</v>
+      </c>
+      <c r="F55" s="0">
+        <v>15.780000000000001</v>
+      </c>
+      <c r="G55" s="0">
+        <v>13.512587771878746</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="0">
+        <v>118.78</v>
+      </c>
+      <c r="E56" s="0">
+        <v>85.799999999999997</v>
+      </c>
+      <c r="F56" s="0">
+        <v>32.980000000000004</v>
+      </c>
+      <c r="G56" s="0">
+        <v>27.765617107257118</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="0">
+        <v>118.78</v>
+      </c>
+      <c r="E57" s="0">
+        <v>92.599999999999994</v>
+      </c>
+      <c r="F57" s="0">
+        <v>26.180000000000007</v>
+      </c>
+      <c r="G57" s="0">
+        <v>22.040747600606171</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="0">
+        <v>117.78</v>
+      </c>
+      <c r="E58" s="0">
+        <v>99.200000000000003</v>
+      </c>
+      <c r="F58" s="0">
+        <v>18.579999999999998</v>
+      </c>
+      <c r="G58" s="0">
+        <v>15.775174053319747</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="0">
+        <v>117.78</v>
+      </c>
+      <c r="E59" s="0">
+        <v>96.200000000000003</v>
+      </c>
+      <c r="F59" s="0">
+        <v>21.579999999999998</v>
+      </c>
+      <c r="G59" s="0">
+        <v>18.322295805739515</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="0">
+        <v>170.38</v>
+      </c>
+      <c r="E60" s="0">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="F60" s="0">
+        <v>36.579999999999984</v>
+      </c>
+      <c r="G60" s="0">
+        <v>21.469656062918173</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="0">
+        <v>170.38</v>
+      </c>
+      <c r="E61" s="0">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="F61" s="0">
+        <v>32.579999999999984</v>
+      </c>
+      <c r="G61" s="0">
+        <v>19.121962671675067</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="0">
+        <v>175.38</v>
+      </c>
+      <c r="E62" s="0">
+        <v>163.40000000000001</v>
+      </c>
+      <c r="F62" s="0">
+        <v>11.97999999999999</v>
+      </c>
+      <c r="G62" s="0">
+        <v>6.8308815144258128</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="0">
+        <v>175.38</v>
+      </c>
+      <c r="E63" s="0">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="F63" s="0">
+        <v>12.579999999999984</v>
+      </c>
+      <c r="G63" s="0">
+        <v>7.1729957805907087</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="0">
+        <v>157.78</v>
+      </c>
+      <c r="E64" s="0">
+        <v>138</v>
+      </c>
+      <c r="F64" s="0">
+        <v>19.780000000000001</v>
+      </c>
+      <c r="G64" s="0">
+        <v>12.536443148688047</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="0">
+        <v>157.78</v>
+      </c>
+      <c r="E65" s="0">
+        <v>141.40000000000001</v>
+      </c>
+      <c r="F65" s="0">
+        <v>16.379999999999995</v>
+      </c>
+      <c r="G65" s="0">
+        <v>10.38154392191659</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="0">
+        <v>180.58000000000001</v>
+      </c>
+      <c r="E66" s="0">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="F66" s="0">
+        <v>29.780000000000001</v>
+      </c>
+      <c r="G66" s="0">
+        <v>16.49130579244656</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="0">
+        <v>180.58000000000001</v>
+      </c>
+      <c r="E67" s="0">
+        <v>143</v>
+      </c>
+      <c r="F67" s="0">
+        <v>37.580000000000013</v>
+      </c>
+      <c r="G67" s="0">
+        <v>20.810721010078641</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="0">
+        <v>128.78</v>
+      </c>
+      <c r="E68" s="0">
+        <v>115.2</v>
+      </c>
+      <c r="F68" s="0">
+        <v>13.579999999999998</v>
+      </c>
+      <c r="G68" s="0">
+        <v>10.545115701195837</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="0">
+        <v>128.78</v>
+      </c>
+      <c r="E69" s="0">
+        <v>101.8</v>
+      </c>
+      <c r="F69" s="0">
+        <v>26.980000000000004</v>
+      </c>
+      <c r="G69" s="0">
+        <v>20.950458145674798</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="0">
+        <v>120.78</v>
+      </c>
+      <c r="E70" s="0">
+        <v>101.2</v>
+      </c>
+      <c r="F70" s="0">
+        <v>19.579999999999998</v>
+      </c>
+      <c r="G70" s="0">
+        <v>16.211293260473585</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="0">
+        <v>120.78</v>
+      </c>
+      <c r="E71" s="0">
+        <v>95.799999999999997</v>
+      </c>
+      <c r="F71" s="0">
+        <v>24.980000000000004</v>
+      </c>
+      <c r="G71" s="0">
+        <v>20.682232157641998</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="0">
+        <v>136.58000000000001</v>
+      </c>
+      <c r="E72" s="0">
+        <v>119.2</v>
+      </c>
+      <c r="F72" s="0">
+        <v>17.38000000000001</v>
+      </c>
+      <c r="G72" s="0">
+        <v>12.725142773466105</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="0">
+        <v>136.58000000000001</v>
+      </c>
+      <c r="E73" s="0">
+        <v>113.8</v>
+      </c>
+      <c r="F73" s="0">
+        <v>22.780000000000015</v>
+      </c>
+      <c r="G73" s="0">
+        <v>16.678869527017142</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="0">
+        <v>122.38</v>
+      </c>
+      <c r="E74" s="0">
+        <v>104.8</v>
+      </c>
+      <c r="F74" s="0">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="G74" s="0">
+        <v>14.365092335348912</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="0">
+        <v>122.38</v>
+      </c>
+      <c r="E75" s="0">
+        <v>103.59999999999999</v>
+      </c>
+      <c r="F75" s="0">
+        <v>18.780000000000001</v>
+      </c>
+      <c r="G75" s="0">
+        <v>15.345644713188429</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="0">
+        <v>144.78</v>
+      </c>
+      <c r="E76" s="0">
+        <v>128.80000000000001</v>
+      </c>
+      <c r="F76" s="0">
+        <v>15.97999999999999</v>
+      </c>
+      <c r="G76" s="0">
+        <v>11.037436109959932</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="0">
+        <v>144.78</v>
+      </c>
+      <c r="E77" s="0">
+        <v>129.19999999999999</v>
+      </c>
+      <c r="F77" s="0">
+        <v>15.580000000000013</v>
+      </c>
+      <c r="G77" s="0">
+        <v>10.761154855643055</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="0">
+        <v>122.58</v>
+      </c>
+      <c r="E78" s="0">
+        <v>103.59999999999999</v>
+      </c>
+      <c r="F78" s="0">
+        <v>18.980000000000004</v>
+      </c>
+      <c r="G78" s="0">
+        <v>15.483765704030025</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="0">
+        <v>122.58</v>
+      </c>
+      <c r="E79" s="0">
+        <v>106.8</v>
+      </c>
+      <c r="F79" s="0">
+        <v>15.780000000000001</v>
+      </c>
+      <c r="G79" s="0">
+        <v>12.873225648556046</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="0">
+        <v>142.97999999999999</v>
+      </c>
+      <c r="E80" s="0">
+        <v>131.59999999999999</v>
+      </c>
+      <c r="F80" s="0">
+        <v>11.379999999999995</v>
+      </c>
+      <c r="G80" s="0">
+        <v>7.9591551265911287</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="0">
+        <v>142.97999999999999</v>
+      </c>
+      <c r="E81" s="0">
+        <v>132</v>
+      </c>
+      <c r="F81" s="0">
+        <v>10.97999999999999</v>
+      </c>
+      <c r="G81" s="0">
+        <v>7.679395719681068</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="0">
+        <v>119.18000000000001</v>
+      </c>
+      <c r="E82" s="0">
+        <v>107.59999999999999</v>
+      </c>
+      <c r="F82" s="0">
+        <v>11.580000000000013</v>
+      </c>
+      <c r="G82" s="0">
+        <v>9.7163953683504047</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="0">
+        <v>119.18000000000001</v>
+      </c>
+      <c r="E83" s="0">
+        <v>106.59999999999999</v>
+      </c>
+      <c r="F83" s="0">
+        <v>12.580000000000013</v>
+      </c>
+      <c r="G83" s="0">
+        <v>10.555462325893616</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="0">
+        <v>124.78</v>
+      </c>
+      <c r="E84" s="0">
+        <v>89.400000000000006</v>
+      </c>
+      <c r="F84" s="0">
+        <v>35.379999999999995</v>
+      </c>
+      <c r="G84" s="0">
+        <v>28.353902869049524</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C85" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="0">
+        <v>124.78</v>
+      </c>
+      <c r="E85" s="0">
+        <v>92.400000000000006</v>
+      </c>
+      <c r="F85" s="0">
+        <v>32.379999999999995</v>
+      </c>
+      <c r="G85" s="0">
+        <v>25.949671421702192</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="0">
+        <v>127.38</v>
+      </c>
+      <c r="E86" s="0">
+        <v>107</v>
+      </c>
+      <c r="F86" s="0">
+        <v>20.379999999999995</v>
+      </c>
+      <c r="G86" s="0">
+        <v>15.999371957921177</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="0">
+        <v>127.38</v>
+      </c>
+      <c r="E87" s="0">
+        <v>96.200000000000003</v>
+      </c>
+      <c r="F87" s="0">
+        <v>31.179999999999993</v>
+      </c>
+      <c r="G87" s="0">
+        <v>24.477940021981468</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="0">
+        <v>143.38</v>
+      </c>
+      <c r="E88" s="0">
+        <v>130.40000000000001</v>
+      </c>
+      <c r="F88" s="0">
+        <v>12.97999999999999</v>
+      </c>
+      <c r="G88" s="0">
+        <v>9.052866508578596</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="0">
+        <v>143.38</v>
+      </c>
+      <c r="E89" s="0">
+        <v>128</v>
+      </c>
+      <c r="F89" s="0">
+        <v>15.379999999999995</v>
+      </c>
+      <c r="G89" s="0">
+        <v>10.726740131120097</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="0">
+        <v>188.18000000000001</v>
+      </c>
+      <c r="E90" s="0">
+        <v>177.80000000000001</v>
+      </c>
+      <c r="F90" s="0">
+        <v>10.379999999999995</v>
+      </c>
+      <c r="G90" s="0">
+        <v>5.5159953236263126</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="0">
+        <v>188.18000000000001</v>
+      </c>
+      <c r="E91" s="0">
+        <v>180.80000000000001</v>
+      </c>
+      <c r="F91" s="0">
+        <v>7.3799999999999955</v>
+      </c>
+      <c r="G91" s="0">
+        <v>3.9217770220002102</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="0">
+        <v>147.58000000000001</v>
+      </c>
+      <c r="E92" s="0">
+        <v>118.8</v>
+      </c>
+      <c r="F92" s="0">
+        <v>28.780000000000015</v>
+      </c>
+      <c r="G92" s="0">
+        <v>19.501287437322137</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C93" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="0">
+        <v>147.58000000000001</v>
+      </c>
+      <c r="E93" s="0">
+        <v>118</v>
+      </c>
+      <c r="F93" s="0">
+        <v>29.580000000000013</v>
+      </c>
+      <c r="G93" s="0">
+        <v>20.043366309798085</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="0">
+        <v>189.97999999999999</v>
+      </c>
+      <c r="E94" s="0">
+        <v>107.2</v>
+      </c>
+      <c r="F94" s="0">
+        <v>82.779999999999987</v>
+      </c>
+      <c r="G94" s="0">
+        <v>43.573007685019469</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="0">
+        <v>189.97999999999999</v>
+      </c>
+      <c r="E95" s="0">
+        <v>106.40000000000001</v>
+      </c>
+      <c r="F95" s="0">
+        <v>83.579999999999984</v>
+      </c>
+      <c r="G95" s="0">
+        <v>43.994104642593953</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="0">
+        <v>140.97999999999999</v>
+      </c>
+      <c r="E96" s="0">
+        <v>130</v>
+      </c>
+      <c r="F96" s="0">
+        <v>10.97999999999999</v>
+      </c>
+      <c r="G96" s="0">
+        <v>7.7883387714569388</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="0">
+        <v>140.97999999999999</v>
+      </c>
+      <c r="E97" s="0">
+        <v>129</v>
+      </c>
+      <c r="F97" s="0">
+        <v>11.97999999999999</v>
+      </c>
+      <c r="G97" s="0">
+        <v>8.4976592424457316</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="0">
+        <v>119.58</v>
+      </c>
+      <c r="E98" s="0">
+        <v>105</v>
+      </c>
+      <c r="F98" s="0">
+        <v>14.579999999999998</v>
+      </c>
+      <c r="G98" s="0">
+        <v>12.192674360260911</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="0">
+        <v>119.58</v>
+      </c>
+      <c r="E99" s="0">
+        <v>98.599999999999994</v>
+      </c>
+      <c r="F99" s="0">
+        <v>20.980000000000004</v>
+      </c>
+      <c r="G99" s="0">
+        <v>17.544739923064061</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="0">
+        <v>94.379999999999995</v>
+      </c>
+      <c r="E100" s="0">
+        <v>62</v>
+      </c>
+      <c r="F100" s="0">
+        <v>32.379999999999995</v>
+      </c>
+      <c r="G100" s="0">
+        <v>34.308116126297939</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="0">
+        <v>94.379999999999995</v>
+      </c>
+      <c r="E101" s="0">
+        <v>83.599999999999994</v>
+      </c>
+      <c r="F101" s="0">
+        <v>10.780000000000001</v>
+      </c>
+      <c r="G101" s="0">
+        <v>11.421911421911423</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="0">
+        <v>118.58</v>
+      </c>
+      <c r="E102" s="0">
+        <v>29.199999999999999</v>
+      </c>
+      <c r="F102" s="0">
+        <v>89.379999999999995</v>
+      </c>
+      <c r="G102" s="0">
+        <v>75.375274076572779</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="0">
+        <v>118.58</v>
+      </c>
+      <c r="E103" s="0">
+        <v>27.399999999999999</v>
+      </c>
+      <c r="F103" s="0">
+        <v>91.180000000000007</v>
+      </c>
+      <c r="G103" s="0">
+        <v>76.893236633496372</v>
       </c>
     </row>
   </sheetData>

--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12930" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="13625" uniqueCount="59">
   <si>
     <t>Subject</t>
   </si>
@@ -305,25 +305,25 @@
         <v>0.83684838838042186</v>
       </c>
       <c r="E2" s="0">
-        <v>0.83794466403162049</v>
+        <v>0.8423076923076922</v>
       </c>
       <c r="F2" s="0">
-        <v>0.80916030534351147</v>
+        <v>0.79347826086956519</v>
       </c>
       <c r="G2" s="0">
-        <v>0.86885245901639341</v>
+        <v>0.89754098360655743</v>
       </c>
       <c r="H2" s="0">
-        <v>10600</v>
+        <v>10950</v>
       </c>
       <c r="I2" s="0">
-        <v>10430</v>
+        <v>10080</v>
       </c>
       <c r="J2" s="0">
-        <v>2500</v>
+        <v>2850</v>
       </c>
       <c r="K2" s="0">
-        <v>1600</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="3">
@@ -337,28 +337,28 @@
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>0.85276561878233192</v>
+        <v>0.84480700358137684</v>
       </c>
       <c r="E3" s="0">
-        <v>0.85603112840466933</v>
+        <v>0.84999999999999998</v>
       </c>
       <c r="F3" s="0">
-        <v>0.81481481481481477</v>
+        <v>0.80072463768115942</v>
       </c>
       <c r="G3" s="0">
-        <v>0.90163934426229508</v>
+        <v>0.90573770491803274</v>
       </c>
       <c r="H3" s="0">
-        <v>11000</v>
+        <v>11050</v>
       </c>
       <c r="I3" s="0">
-        <v>10430</v>
+        <v>10180</v>
       </c>
       <c r="J3" s="0">
-        <v>2500</v>
+        <v>2750</v>
       </c>
       <c r="K3" s="0">
-        <v>1200</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="4">
@@ -372,28 +372,28 @@
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>0.97528248587570621</v>
+        <v>0.97598870056497178</v>
       </c>
       <c r="E4" s="0">
-        <v>0.97664486854397448</v>
+        <v>0.97735748534896105</v>
       </c>
       <c r="F4" s="0">
-        <v>0.98017680150013398</v>
+        <v>0.97892209178228384</v>
       </c>
       <c r="G4" s="0">
-        <v>0.97313829787234041</v>
+        <v>0.97579787234042559</v>
       </c>
       <c r="H4" s="0">
-        <v>36590</v>
+        <v>36690</v>
       </c>
       <c r="I4" s="0">
-        <v>32460</v>
+        <v>32410</v>
       </c>
       <c r="J4" s="0">
-        <v>740</v>
+        <v>790</v>
       </c>
       <c r="K4" s="0">
-        <v>1010</v>
+        <v>910</v>
       </c>
     </row>
     <row r="5">
@@ -407,19 +407,19 @@
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>0.97508169934640521</v>
+        <v>0.97780501089324623</v>
       </c>
       <c r="E5" s="0">
-        <v>0.97739903668025196</v>
+        <v>0.97991868917087588</v>
       </c>
       <c r="F5" s="0">
-        <v>0.97151976430149767</v>
+        <v>0.97165892988028346</v>
       </c>
       <c r="G5" s="0">
-        <v>0.98334990059642147</v>
+        <v>0.98832007952286283</v>
       </c>
       <c r="H5" s="0">
-        <v>39570</v>
+        <v>39770</v>
       </c>
       <c r="I5" s="0">
         <v>32040</v>
@@ -428,7 +428,7 @@
         <v>1160</v>
       </c>
       <c r="K5" s="0">
-        <v>670</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6">
@@ -442,28 +442,28 @@
         <v>8</v>
       </c>
       <c r="D6" s="0">
-        <v>0.95087001023541451</v>
+        <v>0.95005117707267139</v>
       </c>
       <c r="E6" s="0">
-        <v>0.87368421052631584</v>
+        <v>0.87651821862348178</v>
       </c>
       <c r="F6" s="0">
-        <v>0.88770053475935828</v>
+        <v>0.85657764589515328</v>
       </c>
       <c r="G6" s="0">
-        <v>0.86010362694300513</v>
+        <v>0.89740932642487048</v>
       </c>
       <c r="H6" s="0">
-        <v>8300</v>
+        <v>8660</v>
       </c>
       <c r="I6" s="0">
-        <v>38150</v>
+        <v>37750</v>
       </c>
       <c r="J6" s="0">
-        <v>1050</v>
+        <v>1450</v>
       </c>
       <c r="K6" s="0">
-        <v>1350</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7">
@@ -477,28 +477,28 @@
         <v>9</v>
       </c>
       <c r="D7" s="0">
-        <v>0.95156273144719306</v>
+        <v>0.95970967264109019</v>
       </c>
       <c r="E7" s="0">
-        <v>0.93895837222325929</v>
+        <v>0.95056343147946187</v>
       </c>
       <c r="F7" s="0">
-        <v>0.94584430236931172</v>
+        <v>0.93259629101283881</v>
       </c>
       <c r="G7" s="0">
-        <v>0.9321719792438844</v>
+        <v>0.96923647146034098</v>
       </c>
       <c r="H7" s="0">
-        <v>25150</v>
+        <v>26150</v>
       </c>
       <c r="I7" s="0">
-        <v>39090</v>
+        <v>38640</v>
       </c>
       <c r="J7" s="0">
-        <v>1440</v>
+        <v>1890</v>
       </c>
       <c r="K7" s="0">
-        <v>1830</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8">
@@ -512,28 +512,28 @@
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <v>0.9518318765110656</v>
+        <v>0.95462153617258694</v>
       </c>
       <c r="E8" s="0">
-        <v>0.94823106136318203</v>
+        <v>0.95166402535657679</v>
       </c>
       <c r="F8" s="0">
-        <v>0.95070140280561122</v>
+        <v>0.94566929133858268</v>
       </c>
       <c r="G8" s="0">
-        <v>0.94577352472089316</v>
+        <v>0.95773524720893144</v>
       </c>
       <c r="H8" s="0">
-        <v>23720</v>
+        <v>24020</v>
       </c>
       <c r="I8" s="0">
-        <v>27460</v>
+        <v>27310</v>
       </c>
       <c r="J8" s="0">
-        <v>1230</v>
+        <v>1380</v>
       </c>
       <c r="K8" s="0">
-        <v>1360</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="9">
@@ -547,28 +547,28 @@
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <v>0.93144863266814482</v>
+        <v>0.93237250554323725</v>
       </c>
       <c r="E9" s="0">
-        <v>0.92657827033445472</v>
+        <v>0.92834768989819905</v>
       </c>
       <c r="F9" s="0">
-        <v>0.91984282907662085</v>
+        <v>0.91192307692307695</v>
       </c>
       <c r="G9" s="0">
-        <v>0.93341307814992025</v>
+        <v>0.94537480063795853</v>
       </c>
       <c r="H9" s="0">
-        <v>23410</v>
+        <v>23710</v>
       </c>
       <c r="I9" s="0">
-        <v>27000</v>
+        <v>26750</v>
       </c>
       <c r="J9" s="0">
-        <v>2040</v>
+        <v>2290</v>
       </c>
       <c r="K9" s="0">
-        <v>1670</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="10">
@@ -582,28 +582,28 @@
         <v>8</v>
       </c>
       <c r="D10" s="0">
-        <v>0.80334595959595956</v>
+        <v>0.79071969696969702</v>
       </c>
       <c r="E10" s="0">
-        <v>0.78744455817127257</v>
+        <v>0.78126031012867048</v>
       </c>
       <c r="F10" s="0">
-        <v>0.68936678614097968</v>
+        <v>0.66741826381059755</v>
       </c>
       <c r="G10" s="0">
-        <v>0.91805887032617339</v>
+        <v>0.9419252187748608</v>
       </c>
       <c r="H10" s="0">
-        <v>11540</v>
+        <v>11840</v>
       </c>
       <c r="I10" s="0">
-        <v>13910</v>
+        <v>13210</v>
       </c>
       <c r="J10" s="0">
-        <v>5200</v>
+        <v>5900</v>
       </c>
       <c r="K10" s="0">
-        <v>1030</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11">
@@ -617,28 +617,28 @@
         <v>9</v>
       </c>
       <c r="D11" s="0">
-        <v>0.84330930742713883</v>
+        <v>0.86869319962394231</v>
       </c>
       <c r="E11" s="0">
-        <v>0.82078853046594979</v>
+        <v>0.85915966386554621</v>
       </c>
       <c r="F11" s="0">
-        <v>0.75827814569536423</v>
+        <v>0.75398230088495577</v>
       </c>
       <c r="G11" s="0">
-        <v>0.89453125</v>
+        <v>0.99843749999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>11450</v>
+        <v>12780</v>
       </c>
       <c r="I11" s="0">
-        <v>15460</v>
+        <v>14940</v>
       </c>
       <c r="J11" s="0">
-        <v>3650</v>
+        <v>4170</v>
       </c>
       <c r="K11" s="0">
-        <v>1350</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -652,28 +652,28 @@
         <v>8</v>
       </c>
       <c r="D12" s="0">
-        <v>0.86413248024087319</v>
+        <v>0.87542340986074518</v>
       </c>
       <c r="E12" s="0">
-        <v>0.8591494342567304</v>
+        <v>0.87085446742099104</v>
       </c>
       <c r="F12" s="0">
-        <v>0.82410179640718562</v>
+        <v>0.83532934131736525</v>
       </c>
       <c r="G12" s="0">
-        <v>0.89731051344743273</v>
+        <v>0.90953545232273836</v>
       </c>
       <c r="H12" s="0">
-        <v>11010</v>
+        <v>11160</v>
       </c>
       <c r="I12" s="0">
-        <v>11950</v>
+        <v>12100</v>
       </c>
       <c r="J12" s="0">
-        <v>2350</v>
+        <v>2200</v>
       </c>
       <c r="K12" s="0">
-        <v>1260</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="13">
@@ -687,28 +687,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <v>0.88913942127019918</v>
+        <v>0.91356632844795194</v>
       </c>
       <c r="E13" s="0">
-        <v>0.88353730754046578</v>
+        <v>0.91008600469116496</v>
       </c>
       <c r="F13" s="0">
-        <v>0.85944700460829493</v>
+        <v>0.87716654107008285</v>
       </c>
       <c r="G13" s="0">
-        <v>0.90901705930138099</v>
+        <v>0.94557270511779046</v>
       </c>
       <c r="H13" s="0">
-        <v>11190</v>
+        <v>11640</v>
       </c>
       <c r="I13" s="0">
-        <v>12470</v>
+        <v>12670</v>
       </c>
       <c r="J13" s="0">
-        <v>1830</v>
+        <v>1630</v>
       </c>
       <c r="K13" s="0">
-        <v>1120</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14">
@@ -722,13 +722,13 @@
         <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>0.79166666666666663</v>
+        <v>0.78409090909090906</v>
       </c>
       <c r="E14" s="0">
-        <v>0.7342995169082126</v>
+        <v>0.72727272727272718</v>
       </c>
       <c r="F14" s="0">
-        <v>0.61290322580645162</v>
+        <v>0.60317460317460314</v>
       </c>
       <c r="G14" s="0">
         <v>0.91566265060240959</v>
@@ -737,10 +737,10 @@
         <v>3800</v>
       </c>
       <c r="I14" s="0">
-        <v>6650</v>
+        <v>6550</v>
       </c>
       <c r="J14" s="0">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="K14" s="0">
         <v>350</v>
@@ -757,28 +757,28 @@
         <v>9</v>
       </c>
       <c r="D15" s="0">
-        <v>0.90151515151515149</v>
+        <v>0.89015151515151514</v>
       </c>
       <c r="E15" s="0">
-        <v>0.86021505376344087</v>
+        <v>0.84491978609625673</v>
       </c>
       <c r="F15" s="0">
-        <v>0.77669902912621358</v>
+        <v>0.75961538461538458</v>
       </c>
       <c r="G15" s="0">
-        <v>0.96385542168674698</v>
+        <v>0.95180722891566261</v>
       </c>
       <c r="H15" s="0">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="I15" s="0">
-        <v>7900</v>
+        <v>7800</v>
       </c>
       <c r="J15" s="0">
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="K15" s="0">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
@@ -792,28 +792,28 @@
         <v>8</v>
       </c>
       <c r="D16" s="0">
-        <v>0.67728237791932056</v>
+        <v>0.64543524416135878</v>
       </c>
       <c r="E16" s="0">
-        <v>0.59999999999999998</v>
+        <v>0.58249999999999991</v>
       </c>
       <c r="F16" s="0">
-        <v>0.66086956521739126</v>
+        <v>0.60519480519480517</v>
       </c>
       <c r="G16" s="0">
-        <v>0.54939759036144575</v>
+        <v>0.56144578313253013</v>
       </c>
       <c r="H16" s="0">
-        <v>2280</v>
+        <v>2330</v>
       </c>
       <c r="I16" s="0">
-        <v>4100</v>
+        <v>3750</v>
       </c>
       <c r="J16" s="0">
-        <v>1170</v>
+        <v>1520</v>
       </c>
       <c r="K16" s="0">
-        <v>1870</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="17">
@@ -827,28 +827,28 @@
         <v>9</v>
       </c>
       <c r="D17" s="0">
-        <v>0.76646090534979427</v>
+        <v>0.76028806584362141</v>
       </c>
       <c r="E17" s="0">
-        <v>0.75459459459459466</v>
+        <v>0.75343915343915335</v>
       </c>
       <c r="F17" s="0">
-        <v>0.68431372549019609</v>
+        <v>0.67169811320754713</v>
       </c>
       <c r="G17" s="0">
-        <v>0.84096385542168672</v>
+        <v>0.85783132530120487</v>
       </c>
       <c r="H17" s="0">
-        <v>3490</v>
+        <v>3560</v>
       </c>
       <c r="I17" s="0">
-        <v>3960</v>
+        <v>3830</v>
       </c>
       <c r="J17" s="0">
-        <v>1610</v>
+        <v>1740</v>
       </c>
       <c r="K17" s="0">
-        <v>660</v>
+        <v>590</v>
       </c>
     </row>
     <row r="18">
@@ -862,13 +862,13 @@
         <v>8</v>
       </c>
       <c r="D18" s="0">
-        <v>0.86677240285487711</v>
+        <v>0.80333068992862811</v>
       </c>
       <c r="E18" s="0">
-        <v>0.79361179361179368</v>
+        <v>0.72259507829977632</v>
       </c>
       <c r="F18" s="0">
-        <v>0.6857749469214437</v>
+        <v>0.58620689655172409</v>
       </c>
       <c r="G18" s="0">
         <v>0.94169096209912539</v>
@@ -877,10 +877,10 @@
         <v>3230</v>
       </c>
       <c r="I18" s="0">
-        <v>7700</v>
+        <v>6900</v>
       </c>
       <c r="J18" s="0">
-        <v>1480</v>
+        <v>2280</v>
       </c>
       <c r="K18" s="0">
         <v>200</v>
@@ -897,19 +897,19 @@
         <v>9</v>
       </c>
       <c r="D19" s="0">
-        <v>0.88353115727002962</v>
+        <v>0.88724035608308605</v>
       </c>
       <c r="E19" s="0">
-        <v>0.82690187431091511</v>
+        <v>0.83333333333333348</v>
       </c>
       <c r="F19" s="0">
-        <v>0.73673870333988212</v>
+        <v>0.73929961089494167</v>
       </c>
       <c r="G19" s="0">
-        <v>0.94221105527638194</v>
+        <v>0.95477386934673369</v>
       </c>
       <c r="H19" s="0">
-        <v>3750</v>
+        <v>3800</v>
       </c>
       <c r="I19" s="0">
         <v>8160</v>
@@ -918,7 +918,7 @@
         <v>1340</v>
       </c>
       <c r="K19" s="0">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20">
@@ -932,13 +932,13 @@
         <v>8</v>
       </c>
       <c r="D20" s="0">
-        <v>0.76146788990825687</v>
+        <v>0.74311926605504586</v>
       </c>
       <c r="E20" s="0">
-        <v>0.75238095238095237</v>
+        <v>0.73831775700934565</v>
       </c>
       <c r="F20" s="0">
-        <v>0.62204724409448819</v>
+        <v>0.60305343511450382</v>
       </c>
       <c r="G20" s="0">
         <v>0.95180722891566261</v>
@@ -947,10 +947,10 @@
         <v>3950</v>
       </c>
       <c r="I20" s="0">
-        <v>4350</v>
+        <v>4150</v>
       </c>
       <c r="J20" s="0">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="K20" s="0">
         <v>200</v>
@@ -967,13 +967,13 @@
         <v>9</v>
       </c>
       <c r="D21" s="0">
-        <v>0.90322580645161288</v>
+        <v>0.91474654377880182</v>
       </c>
       <c r="E21" s="0">
-        <v>0.8771929824561403</v>
+        <v>0.89020771513353114</v>
       </c>
       <c r="F21" s="0">
-        <v>0.84269662921348309</v>
+        <v>0.86705202312138729</v>
       </c>
       <c r="G21" s="0">
         <v>0.91463414634146345</v>
@@ -982,10 +982,10 @@
         <v>1500</v>
       </c>
       <c r="I21" s="0">
-        <v>2420</v>
+        <v>2470</v>
       </c>
       <c r="J21" s="0">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="K21" s="0">
         <v>140</v>
@@ -1002,7 +1002,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="0">
-        <v>0.94956710980744663</v>
+        <v>0.92555708000189241</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1017,10 +1017,10 @@
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>401420</v>
+        <v>391270</v>
       </c>
       <c r="J22" s="0">
-        <v>21320</v>
+        <v>31470</v>
       </c>
       <c r="K22" s="0">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="0">
-        <v>0.97876957916588037</v>
+        <v>0.97688243064729197</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>414920</v>
+        <v>414120</v>
       </c>
       <c r="J23" s="0">
-        <v>9000</v>
+        <v>9800</v>
       </c>
       <c r="K23" s="0">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="0">
-        <v>0.96239267315397825</v>
+        <v>0.96210646823125356</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1087,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>336260</v>
+        <v>336160</v>
       </c>
       <c r="J24" s="0">
-        <v>13140</v>
+        <v>13240</v>
       </c>
       <c r="K24" s="0">
         <v>0</v>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="0">
-        <v>0.97059075464694633</v>
+        <v>0.96973417468520684</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>339930</v>
+        <v>339630</v>
       </c>
       <c r="J25" s="0">
-        <v>10300</v>
+        <v>10600</v>
       </c>
       <c r="K25" s="0">
         <v>0</v>
@@ -1177,19 +1177,19 @@
         <v>9</v>
       </c>
       <c r="D27" s="0">
-        <v>0.97068403908794787</v>
+        <v>0.98697068403908794</v>
       </c>
       <c r="E27" s="0">
-        <v>0.98512396694214877</v>
+        <v>0.99344262295081964</v>
       </c>
       <c r="F27" s="0">
         <v>1</v>
       </c>
       <c r="G27" s="0">
-        <v>0.97068403908794787</v>
+        <v>0.98697068403908794</v>
       </c>
       <c r="H27" s="0">
-        <v>5960</v>
+        <v>6060</v>
       </c>
       <c r="I27" s="0">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
@@ -1317,19 +1317,19 @@
         <v>9</v>
       </c>
       <c r="D31" s="0">
-        <v>0.86622807017543857</v>
+        <v>0.89912280701754388</v>
       </c>
       <c r="E31" s="0">
-        <v>0.9283196239717979</v>
+        <v>0.94688221709006926</v>
       </c>
       <c r="F31" s="0">
         <v>1</v>
       </c>
       <c r="G31" s="0">
-        <v>0.86622807017543857</v>
+        <v>0.89912280701754388</v>
       </c>
       <c r="H31" s="0">
-        <v>3950</v>
+        <v>4100</v>
       </c>
       <c r="I31" s="0">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>610</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32">
@@ -1422,19 +1422,19 @@
         <v>8</v>
       </c>
       <c r="D34" s="0">
-        <v>0.92927631578947367</v>
+        <v>0.97861842105263153</v>
       </c>
       <c r="E34" s="0">
-        <v>0.96334185848252341</v>
+        <v>0.98919368246051542</v>
       </c>
       <c r="F34" s="0">
         <v>1</v>
       </c>
       <c r="G34" s="0">
-        <v>0.92927631578947367</v>
+        <v>0.97861842105263153</v>
       </c>
       <c r="H34" s="0">
-        <v>5650</v>
+        <v>5950</v>
       </c>
       <c r="I34" s="0">
         <v>0</v>
@@ -1443,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>430</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35">
@@ -1492,19 +1492,19 @@
         <v>8</v>
       </c>
       <c r="D36" s="0">
-        <v>0.94398907103825136</v>
+        <v>0.95765027322404372</v>
       </c>
       <c r="E36" s="0">
-        <v>0.97118763176387912</v>
+        <v>0.97836706210746682</v>
       </c>
       <c r="F36" s="0">
         <v>1</v>
       </c>
       <c r="G36" s="0">
-        <v>0.94398907103825136</v>
+        <v>0.95765027322404372</v>
       </c>
       <c r="H36" s="0">
-        <v>6910</v>
+        <v>7010</v>
       </c>
       <c r="I36" s="0">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="0">
-        <v>410</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37">
@@ -1562,7 +1562,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="0">
-        <v>0.26177536231884058</v>
+        <v>0.23460144927536231</v>
       </c>
       <c r="E38" s="0">
         <v>0</v>
@@ -1577,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="0">
-        <v>2890</v>
+        <v>2590</v>
       </c>
       <c r="J38" s="0">
-        <v>8150</v>
+        <v>8450</v>
       </c>
       <c r="K38" s="0">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="0">
-        <v>0.74568574023614898</v>
+        <v>0.72752043596730243</v>
       </c>
       <c r="E39" s="0">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="0">
-        <v>8210</v>
+        <v>8010</v>
       </c>
       <c r="J39" s="0">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="K39" s="0">
         <v>0</v>
@@ -1912,19 +1912,19 @@
         <v>8</v>
       </c>
       <c r="D48" s="0">
-        <v>0.45535714285714285</v>
+        <v>0.4375</v>
       </c>
       <c r="E48" s="0">
-        <v>0.62576687116564422</v>
+        <v>0.60869565217391308</v>
       </c>
       <c r="F48" s="0">
         <v>1</v>
       </c>
       <c r="G48" s="0">
-        <v>0.45535714285714285</v>
+        <v>0.4375</v>
       </c>
       <c r="H48" s="0">
-        <v>2550</v>
+        <v>2450</v>
       </c>
       <c r="I48" s="0">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="0">
-        <v>3050</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="49">
@@ -1947,19 +1947,19 @@
         <v>9</v>
       </c>
       <c r="D49" s="0">
-        <v>0.69821428571428568</v>
+        <v>0.71607142857142858</v>
       </c>
       <c r="E49" s="0">
-        <v>0.82229232386961093</v>
+        <v>0.83454734651404794</v>
       </c>
       <c r="F49" s="0">
         <v>1</v>
       </c>
       <c r="G49" s="0">
-        <v>0.69821428571428568</v>
+        <v>0.71607142857142858</v>
       </c>
       <c r="H49" s="0">
-        <v>3910</v>
+        <v>4010</v>
       </c>
       <c r="I49" s="0">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="0">
-        <v>1690</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="50">
@@ -1982,19 +1982,19 @@
         <v>8</v>
       </c>
       <c r="D50" s="0">
-        <v>0.40393013100436681</v>
+        <v>0.41484716157205243</v>
       </c>
       <c r="E50" s="0">
-        <v>0.57542768273716949</v>
+        <v>0.5864197530864198</v>
       </c>
       <c r="F50" s="0">
         <v>1</v>
       </c>
       <c r="G50" s="0">
-        <v>0.40393013100436681</v>
+        <v>0.41484716157205243</v>
       </c>
       <c r="H50" s="0">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="I50" s="0">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="0">
-        <v>2730</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="51">
@@ -2017,19 +2017,19 @@
         <v>9</v>
       </c>
       <c r="D51" s="0">
-        <v>0.32755298651252407</v>
+        <v>0.23121387283236994</v>
       </c>
       <c r="E51" s="0">
-        <v>0.49346879535558785</v>
+        <v>0.37558685446009393</v>
       </c>
       <c r="F51" s="0">
         <v>1</v>
       </c>
       <c r="G51" s="0">
-        <v>0.32755298651252407</v>
+        <v>0.23121387283236994</v>
       </c>
       <c r="H51" s="0">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="I51" s="0">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="0">
-        <v>3490</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="52">
@@ -2052,19 +2052,19 @@
         <v>8</v>
       </c>
       <c r="D52" s="0">
-        <v>0.70567986230636837</v>
+        <v>0.68846815834767638</v>
       </c>
       <c r="E52" s="0">
-        <v>0.82744702320887986</v>
+        <v>0.8154943934760448</v>
       </c>
       <c r="F52" s="0">
         <v>1</v>
       </c>
       <c r="G52" s="0">
-        <v>0.70567986230636837</v>
+        <v>0.68846815834767638</v>
       </c>
       <c r="H52" s="0">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="I52" s="0">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="0">
-        <v>1710</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="53">
@@ -2087,19 +2087,19 @@
         <v>9</v>
       </c>
       <c r="D53" s="0">
-        <v>0.2776831345826235</v>
+        <v>0.17546848381601363</v>
       </c>
       <c r="E53" s="0">
-        <v>0.4346666666666667</v>
+        <v>0.29855072463768118</v>
       </c>
       <c r="F53" s="0">
         <v>1</v>
       </c>
       <c r="G53" s="0">
-        <v>0.2776831345826235</v>
+        <v>0.17546848381601363</v>
       </c>
       <c r="H53" s="0">
-        <v>1630</v>
+        <v>1030</v>
       </c>
       <c r="I53" s="0">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="0">
-        <v>4240</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="54">
@@ -2122,19 +2122,19 @@
         <v>8</v>
       </c>
       <c r="D54" s="0">
-        <v>0.3592814371257485</v>
+        <v>0.34930139720558884</v>
       </c>
       <c r="E54" s="0">
-        <v>0.52863436123348018</v>
+        <v>0.51775147928994081</v>
       </c>
       <c r="F54" s="0">
         <v>1</v>
       </c>
       <c r="G54" s="0">
-        <v>0.3592814371257485</v>
+        <v>0.34930139720558884</v>
       </c>
       <c r="H54" s="0">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="I54" s="0">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="0">
-        <v>3210</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="55">
@@ -2157,19 +2157,19 @@
         <v>9</v>
       </c>
       <c r="D55" s="0">
-        <v>0.47524752475247523</v>
+        <v>0.51485148514851486</v>
       </c>
       <c r="E55" s="0">
-        <v>0.64429530201342278</v>
+        <v>0.6797385620915033</v>
       </c>
       <c r="F55" s="0">
         <v>1</v>
       </c>
       <c r="G55" s="0">
-        <v>0.47524752475247523</v>
+        <v>0.51485148514851486</v>
       </c>
       <c r="H55" s="0">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="I55" s="0">
         <v>0</v>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="0">
-        <v>2650</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="56">
@@ -2192,19 +2192,19 @@
         <v>8</v>
       </c>
       <c r="D56" s="0">
-        <v>0.85081585081585076</v>
+        <v>0.78088578088578087</v>
       </c>
       <c r="E56" s="0">
-        <v>0.91939546599496214</v>
+        <v>0.87696335078534027</v>
       </c>
       <c r="F56" s="0">
         <v>1</v>
       </c>
       <c r="G56" s="0">
-        <v>0.85081585081585076</v>
+        <v>0.78088578088578087</v>
       </c>
       <c r="H56" s="0">
-        <v>3650</v>
+        <v>3350</v>
       </c>
       <c r="I56" s="0">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="0">
-        <v>640</v>
+        <v>940</v>
       </c>
     </row>
     <row r="57">
@@ -2262,19 +2262,19 @@
         <v>8</v>
       </c>
       <c r="D58" s="0">
-        <v>0.4536290322580645</v>
+        <v>0.33266129032258063</v>
       </c>
       <c r="E58" s="0">
-        <v>0.62413314840499301</v>
+        <v>0.49924357034795769</v>
       </c>
       <c r="F58" s="0">
         <v>1</v>
       </c>
       <c r="G58" s="0">
-        <v>0.4536290322580645</v>
+        <v>0.33266129032258063</v>
       </c>
       <c r="H58" s="0">
-        <v>2250</v>
+        <v>1650</v>
       </c>
       <c r="I58" s="0">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="0">
-        <v>2710</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="59">
@@ -2297,19 +2297,19 @@
         <v>9</v>
       </c>
       <c r="D59" s="0">
-        <v>0.43659043659043661</v>
+        <v>0.45738045738045741</v>
       </c>
       <c r="E59" s="0">
-        <v>0.60781476121562961</v>
+        <v>0.62767475035663345</v>
       </c>
       <c r="F59" s="0">
         <v>1</v>
       </c>
       <c r="G59" s="0">
-        <v>0.43659043659043661</v>
+        <v>0.45738045738045741</v>
       </c>
       <c r="H59" s="0">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I59" s="0">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="0">
-        <v>2710</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="60">
@@ -2437,19 +2437,19 @@
         <v>9</v>
       </c>
       <c r="D63" s="0">
-        <v>0.90909090909090906</v>
+        <v>0.93366093366093361</v>
       </c>
       <c r="E63" s="0">
-        <v>0.95238095238095233</v>
+        <v>0.96569250317662003</v>
       </c>
       <c r="F63" s="0">
         <v>1</v>
       </c>
       <c r="G63" s="0">
-        <v>0.90909090909090906</v>
+        <v>0.93366093366093361</v>
       </c>
       <c r="H63" s="0">
-        <v>7400</v>
+        <v>7600</v>
       </c>
       <c r="I63" s="0">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="0">
-        <v>740</v>
+        <v>540</v>
       </c>
     </row>
     <row r="64">
@@ -2542,19 +2542,19 @@
         <v>8</v>
       </c>
       <c r="D66" s="0">
-        <v>0.98143236074270557</v>
+        <v>0.99469496021220161</v>
       </c>
       <c r="E66" s="0">
-        <v>0.99062918340026773</v>
+        <v>0.99734042553191482</v>
       </c>
       <c r="F66" s="0">
         <v>1</v>
       </c>
       <c r="G66" s="0">
-        <v>0.98143236074270557</v>
+        <v>0.99469496021220161</v>
       </c>
       <c r="H66" s="0">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="I66" s="0">
         <v>0</v>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="0">
-        <v>140</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67">
@@ -2612,19 +2612,19 @@
         <v>8</v>
       </c>
       <c r="D68" s="0">
-        <v>0.90104166666666663</v>
+        <v>0.71006944444444442</v>
       </c>
       <c r="E68" s="0">
-        <v>0.94794520547945205</v>
+        <v>0.8304568527918782</v>
       </c>
       <c r="F68" s="0">
         <v>1</v>
       </c>
       <c r="G68" s="0">
-        <v>0.90104166666666663</v>
+        <v>0.71006944444444442</v>
       </c>
       <c r="H68" s="0">
-        <v>5190</v>
+        <v>4090</v>
       </c>
       <c r="I68" s="0">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="0">
-        <v>570</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="69">
@@ -2647,19 +2647,19 @@
         <v>9</v>
       </c>
       <c r="D69" s="0">
-        <v>0.98035363457760316</v>
+        <v>0.92337917485265231</v>
       </c>
       <c r="E69" s="0">
-        <v>0.99007936507936511</v>
+        <v>0.96016343207354449</v>
       </c>
       <c r="F69" s="0">
         <v>1</v>
       </c>
       <c r="G69" s="0">
-        <v>0.98035363457760316</v>
+        <v>0.92337917485265231</v>
       </c>
       <c r="H69" s="0">
-        <v>4990</v>
+        <v>4700</v>
       </c>
       <c r="I69" s="0">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="0">
-        <v>100</v>
+        <v>390</v>
       </c>
     </row>
     <row r="70">
@@ -2857,19 +2857,19 @@
         <v>9</v>
       </c>
       <c r="D75" s="0">
-        <v>0.97104247104247099</v>
+        <v>0.82625482625482627</v>
       </c>
       <c r="E75" s="0">
-        <v>0.98530852105778644</v>
+        <v>0.90486257928118385</v>
       </c>
       <c r="F75" s="0">
         <v>1</v>
       </c>
       <c r="G75" s="0">
-        <v>0.97104247104247099</v>
+        <v>0.82625482625482627</v>
       </c>
       <c r="H75" s="0">
-        <v>5030</v>
+        <v>4280</v>
       </c>
       <c r="I75" s="0">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="0">
-        <v>150</v>
+        <v>900</v>
       </c>
     </row>
     <row r="76">
@@ -2892,19 +2892,19 @@
         <v>8</v>
       </c>
       <c r="D76" s="0">
-        <v>0.42701863354037267</v>
+        <v>0.069875776397515521</v>
       </c>
       <c r="E76" s="0">
-        <v>0.59847660500544064</v>
+        <v>0.13062409288824381</v>
       </c>
       <c r="F76" s="0">
         <v>1</v>
       </c>
       <c r="G76" s="0">
-        <v>0.42701863354037267</v>
+        <v>0.069875776397515521</v>
       </c>
       <c r="H76" s="0">
-        <v>2750</v>
+        <v>450</v>
       </c>
       <c r="I76" s="0">
         <v>0</v>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="0">
-        <v>3690</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="77">
@@ -2962,19 +2962,19 @@
         <v>8</v>
       </c>
       <c r="D78" s="0">
-        <v>0.97490347490347495</v>
+        <v>0.86872586872586877</v>
       </c>
       <c r="E78" s="0">
-        <v>0.98729227761485827</v>
+        <v>0.92975206611570249</v>
       </c>
       <c r="F78" s="0">
         <v>1</v>
       </c>
       <c r="G78" s="0">
-        <v>0.97490347490347495</v>
+        <v>0.86872586872586877</v>
       </c>
       <c r="H78" s="0">
-        <v>5050</v>
+        <v>4500</v>
       </c>
       <c r="I78" s="0">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="0">
-        <v>130</v>
+        <v>680</v>
       </c>
     </row>
     <row r="79">
@@ -2997,19 +2997,19 @@
         <v>9</v>
       </c>
       <c r="D79" s="0">
-        <v>0.97378277153558057</v>
+        <v>0.91760299625468167</v>
       </c>
       <c r="E79" s="0">
-        <v>0.98671726755218214</v>
+        <v>0.95703125</v>
       </c>
       <c r="F79" s="0">
         <v>1</v>
       </c>
       <c r="G79" s="0">
-        <v>0.97378277153558057</v>
+        <v>0.91760299625468167</v>
       </c>
       <c r="H79" s="0">
-        <v>5200</v>
+        <v>4900</v>
       </c>
       <c r="I79" s="0">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="0">
-        <v>140</v>
+        <v>440</v>
       </c>
     </row>
     <row r="80">
@@ -3452,19 +3452,19 @@
         <v>8</v>
       </c>
       <c r="D92" s="0">
-        <v>0.84175084175084181</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="E92" s="0">
-        <v>0.9140767824497259</v>
+        <v>0.99236641221374045</v>
       </c>
       <c r="F92" s="0">
         <v>1</v>
       </c>
       <c r="G92" s="0">
-        <v>0.84175084175084181</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="H92" s="0">
-        <v>5000</v>
+        <v>5850</v>
       </c>
       <c r="I92" s="0">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="0">
-        <v>940</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93">
@@ -3487,19 +3487,19 @@
         <v>9</v>
       </c>
       <c r="D93" s="0">
-        <v>0.96779661016949148</v>
+        <v>0.98474576271186443</v>
       </c>
       <c r="E93" s="0">
-        <v>0.98363479758828598</v>
+        <v>0.99231426131511524</v>
       </c>
       <c r="F93" s="0">
         <v>1</v>
       </c>
       <c r="G93" s="0">
-        <v>0.96779661016949148</v>
+        <v>0.98474576271186443</v>
       </c>
       <c r="H93" s="0">
-        <v>5710</v>
+        <v>5810</v>
       </c>
       <c r="I93" s="0">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="0">
-        <v>190</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94">
@@ -3592,7 +3592,7 @@
         <v>8</v>
       </c>
       <c r="D96" s="0">
-        <v>0.87692307692307692</v>
+        <v>0.83846153846153848</v>
       </c>
       <c r="E96" s="0">
         <v>0</v>
@@ -3607,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="0">
-        <v>5700</v>
+        <v>5450</v>
       </c>
       <c r="J96" s="0">
-        <v>800</v>
+        <v>1050</v>
       </c>
       <c r="K96" s="0">
         <v>0</v>
@@ -3627,7 +3627,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="0">
-        <v>0.8527131782945736</v>
+        <v>0.86046511627906974</v>
       </c>
       <c r="E97" s="0">
         <v>0</v>
@@ -3642,10 +3642,10 @@
         <v>0</v>
       </c>
       <c r="I97" s="0">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="J97" s="0">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="K97" s="0">
         <v>0</v>
@@ -3662,13 +3662,13 @@
         <v>8</v>
       </c>
       <c r="D98" s="0">
-        <v>1</v>
+        <v>0.99047619047619051</v>
       </c>
       <c r="E98" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="0">
         <v>1</v>
@@ -3677,10 +3677,10 @@
         <v>0</v>
       </c>
       <c r="I98" s="0">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="J98" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K98" s="0">
         <v>0</v>
@@ -3697,13 +3697,13 @@
         <v>9</v>
       </c>
       <c r="D99" s="0">
-        <v>0.98985801217038538</v>
+        <v>1</v>
       </c>
       <c r="E99" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="0">
         <v>1</v>
@@ -3712,10 +3712,10 @@
         <v>0</v>
       </c>
       <c r="I99" s="0">
-        <v>4880</v>
+        <v>4930</v>
       </c>
       <c r="J99" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K99" s="0">
         <v>0</v>
@@ -3922,28 +3922,28 @@
         <v>51</v>
       </c>
       <c r="C2" s="0">
-        <v>302960</v>
+        <v>304870</v>
       </c>
       <c r="D2" s="0">
-        <v>40350</v>
+        <v>43000</v>
       </c>
       <c r="E2" s="0">
-        <v>947560</v>
+        <v>944910</v>
       </c>
       <c r="F2" s="0">
-        <v>38070</v>
+        <v>36160</v>
       </c>
       <c r="G2" s="0">
-        <v>0.88246774052605514</v>
+        <v>0.87639060568603211</v>
       </c>
       <c r="H2" s="0">
-        <v>0.88836759229393314</v>
+        <v>0.89396827258598954</v>
       </c>
       <c r="I2" s="0">
-        <v>0.94099056390807712</v>
+        <v>0.94043372913750811</v>
       </c>
       <c r="J2" s="0">
-        <v>0.88540783820907731</v>
+        <v>0.88509217593264633</v>
       </c>
     </row>
     <row r="3">
@@ -3954,28 +3954,28 @@
         <v>51</v>
       </c>
       <c r="C3" s="0">
-        <v>281680</v>
+        <v>279590</v>
       </c>
       <c r="D3" s="0">
-        <v>63930</v>
+        <v>77730</v>
       </c>
       <c r="E3" s="0">
-        <v>924090</v>
+        <v>910290</v>
       </c>
       <c r="F3" s="0">
-        <v>41300</v>
+        <v>43390</v>
       </c>
       <c r="G3" s="0">
-        <v>0.81502271346315214</v>
+        <v>0.78246389790663828</v>
       </c>
       <c r="H3" s="0">
-        <v>0.87212830515821416</v>
+        <v>0.86565731624249176</v>
       </c>
       <c r="I3" s="0">
-        <v>0.91973302822273073</v>
+        <v>0.90761250953470629</v>
       </c>
       <c r="J3" s="0">
-        <v>0.84260907282490016</v>
+        <v>0.82196089960311625</v>
       </c>
     </row>
   </sheetData>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>53760</v>
+        <v>65110</v>
       </c>
       <c r="E2" s="0">
-        <v>1492530</v>
+        <v>1481180</v>
       </c>
       <c r="F2" s="0">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>0.96523291232563102</v>
+        <v>0.95789276267711754</v>
       </c>
       <c r="J2" s="0">
         <v>0</v>
@@ -4103,7 +4103,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="0">
-        <v>96230</v>
+        <v>97830</v>
       </c>
       <c r="D4" s="0">
         <v>0</v>
@@ -4112,19 +4112,19 @@
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>4600</v>
+        <v>3000</v>
       </c>
       <c r="G4" s="0">
         <v>1</v>
       </c>
       <c r="H4" s="0">
-        <v>0.95437865714569081</v>
+        <v>0.97024695031240704</v>
       </c>
       <c r="I4" s="0">
-        <v>0.95437865714569081</v>
+        <v>0.97024695031240704</v>
       </c>
       <c r="J4" s="0">
-        <v>0.97665685577996542</v>
+        <v>0.98489882210812452</v>
       </c>
     </row>
     <row r="5">
@@ -4138,10 +4138,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="0">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="E5" s="0">
-        <v>21330</v>
+        <v>21130</v>
       </c>
       <c r="F5" s="0">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>0.9221789883268483</v>
+        <v>0.91353220925205358</v>
       </c>
       <c r="J5" s="0">
         <v>0</v>
@@ -4170,10 +4170,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>10950</v>
+        <v>11450</v>
       </c>
       <c r="E6" s="0">
-        <v>11100</v>
+        <v>10600</v>
       </c>
       <c r="F6" s="0">
         <v>0</v>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>0.50340136054421769</v>
+        <v>0.48072562358276644</v>
       </c>
       <c r="J6" s="0">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         <v>52</v>
       </c>
       <c r="C7" s="0">
-        <v>238880</v>
+        <v>232090</v>
       </c>
       <c r="D7" s="0">
         <v>0</v>
@@ -4208,19 +4208,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>55520</v>
+        <v>62310</v>
       </c>
       <c r="G7" s="0">
         <v>1</v>
       </c>
       <c r="H7" s="0">
-        <v>0.81141304347826082</v>
+        <v>0.78834918478260874</v>
       </c>
       <c r="I7" s="0">
-        <v>0.81141304347826082</v>
+        <v>0.78834918478260874</v>
       </c>
       <c r="J7" s="0">
-        <v>0.89588958895889581</v>
+        <v>0.88165017379247468</v>
       </c>
     </row>
     <row r="8">
@@ -4231,28 +4231,28 @@
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>33450</v>
+        <v>34810</v>
       </c>
       <c r="D8" s="0">
-        <v>2490</v>
+        <v>3340</v>
       </c>
       <c r="E8" s="0">
-        <v>77240</v>
+        <v>76390</v>
       </c>
       <c r="F8" s="0">
-        <v>3180</v>
+        <v>1820</v>
       </c>
       <c r="G8" s="0">
-        <v>0.93071786310517535</v>
+        <v>0.91245085190039321</v>
       </c>
       <c r="H8" s="0">
-        <v>0.91318591318591313</v>
+        <v>0.95031395031395027</v>
       </c>
       <c r="I8" s="0">
-        <v>0.95127191474733586</v>
+        <v>0.95565486421450674</v>
       </c>
       <c r="J8" s="0">
-        <v>0.92186854071930557</v>
+        <v>0.93099759293928863</v>
       </c>
     </row>
     <row r="9">
@@ -4263,28 +4263,28 @@
         <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>21600</v>
+        <v>22000</v>
       </c>
       <c r="D9" s="0">
-        <v>5000</v>
+        <v>5600</v>
       </c>
       <c r="E9" s="0">
-        <v>20860</v>
+        <v>20260</v>
       </c>
       <c r="F9" s="0">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="G9" s="0">
-        <v>0.81203007518796988</v>
+        <v>0.79710144927536231</v>
       </c>
       <c r="H9" s="0">
-        <v>0.88524590163934425</v>
+        <v>0.90163934426229508</v>
       </c>
       <c r="I9" s="0">
-        <v>0.84480700358137684</v>
+        <v>0.84082769598089935</v>
       </c>
       <c r="J9" s="0">
-        <v>0.84705882352941175</v>
+        <v>0.84615384615384615</v>
       </c>
     </row>
     <row r="10">
@@ -4295,28 +4295,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="0">
-        <v>76160</v>
+        <v>76460</v>
       </c>
       <c r="D10" s="0">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="E10" s="0">
-        <v>64500</v>
+        <v>64450</v>
       </c>
       <c r="F10" s="0">
-        <v>1680</v>
+        <v>1380</v>
       </c>
       <c r="G10" s="0">
-        <v>0.97565974891109408</v>
+        <v>0.97513072312205074</v>
       </c>
       <c r="H10" s="0">
-        <v>0.97841726618705038</v>
+        <v>0.98227132579650567</v>
       </c>
       <c r="I10" s="0">
-        <v>0.97518025513033835</v>
+        <v>0.97691347753743762</v>
       </c>
       <c r="J10" s="0">
-        <v>0.97703656189865307</v>
+        <v>0.978688</v>
       </c>
     </row>
     <row r="11">
@@ -4327,28 +4327,28 @@
         <v>2</v>
       </c>
       <c r="C11" s="0">
-        <v>47130</v>
+        <v>47730</v>
       </c>
       <c r="D11" s="0">
-        <v>3270</v>
+        <v>3670</v>
       </c>
       <c r="E11" s="0">
-        <v>54460</v>
+        <v>54060</v>
       </c>
       <c r="F11" s="0">
-        <v>3030</v>
+        <v>2430</v>
       </c>
       <c r="G11" s="0">
-        <v>0.93511904761904763</v>
+        <v>0.9285992217898833</v>
       </c>
       <c r="H11" s="0">
-        <v>0.93959330143540665</v>
+        <v>0.95155502392344493</v>
       </c>
       <c r="I11" s="0">
-        <v>0.94160719251089076</v>
+        <v>0.9434609324311799</v>
       </c>
       <c r="J11" s="0">
-        <v>0.93735083532219554</v>
+        <v>0.93993698306419848</v>
       </c>
     </row>
     <row r="12">
@@ -4359,28 +4359,28 @@
         <v>2</v>
       </c>
       <c r="C12" s="0">
-        <v>22990</v>
+        <v>24620</v>
       </c>
       <c r="D12" s="0">
-        <v>8850</v>
+        <v>10070</v>
       </c>
       <c r="E12" s="0">
-        <v>29370</v>
+        <v>28150</v>
       </c>
       <c r="F12" s="0">
-        <v>2380</v>
+        <v>750</v>
       </c>
       <c r="G12" s="0">
-        <v>0.72204773869346739</v>
+        <v>0.70971461516287115</v>
       </c>
       <c r="H12" s="0">
-        <v>0.90618841150965712</v>
+        <v>0.97043752463539612</v>
       </c>
       <c r="I12" s="0">
-        <v>0.82339990564554177</v>
+        <v>0.82984746029249878</v>
       </c>
       <c r="J12" s="0">
-        <v>0.80370564586610749</v>
+        <v>0.81984681984681984</v>
       </c>
     </row>
     <row r="13">
@@ -4391,28 +4391,28 @@
         <v>2</v>
       </c>
       <c r="C13" s="0">
-        <v>22200</v>
+        <v>22800</v>
       </c>
       <c r="D13" s="0">
-        <v>4180</v>
+        <v>3830</v>
       </c>
       <c r="E13" s="0">
-        <v>24420</v>
+        <v>24770</v>
       </c>
       <c r="F13" s="0">
-        <v>2380</v>
+        <v>1780</v>
       </c>
       <c r="G13" s="0">
-        <v>0.84154662623199394</v>
+        <v>0.8561772437101014</v>
       </c>
       <c r="H13" s="0">
-        <v>0.90317331163547598</v>
+        <v>0.92758340113913751</v>
       </c>
       <c r="I13" s="0">
-        <v>0.87664535539676569</v>
+        <v>0.89450921399022187</v>
       </c>
       <c r="J13" s="0">
-        <v>0.87127158555729989</v>
+        <v>0.89045108377270066</v>
       </c>
     </row>
     <row r="14">
@@ -4423,28 +4423,28 @@
         <v>2</v>
       </c>
       <c r="C14" s="0">
-        <v>7800</v>
+        <v>7750</v>
       </c>
       <c r="D14" s="0">
-        <v>3550</v>
+        <v>3750</v>
       </c>
       <c r="E14" s="0">
-        <v>14550</v>
+        <v>14350</v>
       </c>
       <c r="F14" s="0">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G14" s="0">
-        <v>0.68722466960352424</v>
+        <v>0.67391304347826086</v>
       </c>
       <c r="H14" s="0">
-        <v>0.93975903614457834</v>
+        <v>0.9337349397590361</v>
       </c>
       <c r="I14" s="0">
-        <v>0.84659090909090906</v>
+        <v>0.83712121212121215</v>
       </c>
       <c r="J14" s="0">
-        <v>0.79389312977099225</v>
+        <v>0.78282828282828276</v>
       </c>
     </row>
     <row r="15">
@@ -4455,28 +4455,28 @@
         <v>2</v>
       </c>
       <c r="C15" s="0">
-        <v>5770</v>
+        <v>5890</v>
       </c>
       <c r="D15" s="0">
-        <v>2780</v>
+        <v>3260</v>
       </c>
       <c r="E15" s="0">
-        <v>8060</v>
+        <v>7580</v>
       </c>
       <c r="F15" s="0">
-        <v>2530</v>
+        <v>2410</v>
       </c>
       <c r="G15" s="0">
-        <v>0.67485380116959059</v>
+        <v>0.64371584699453555</v>
       </c>
       <c r="H15" s="0">
-        <v>0.69518072289156629</v>
+        <v>0.7096385542168675</v>
       </c>
       <c r="I15" s="0">
-        <v>0.72257053291536055</v>
+        <v>0.70376175548589337</v>
       </c>
       <c r="J15" s="0">
-        <v>0.68486646884272995</v>
+        <v>0.67507163323782227</v>
       </c>
     </row>
     <row r="16">
@@ -4487,28 +4487,28 @@
         <v>2</v>
       </c>
       <c r="C16" s="0">
-        <v>6980</v>
+        <v>7030</v>
       </c>
       <c r="D16" s="0">
-        <v>2820</v>
+        <v>3620</v>
       </c>
       <c r="E16" s="0">
-        <v>15860</v>
+        <v>15060</v>
       </c>
       <c r="F16" s="0">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="G16" s="0">
-        <v>0.71224489795918366</v>
+        <v>0.66009389671361507</v>
       </c>
       <c r="H16" s="0">
-        <v>0.94197031039136303</v>
+        <v>0.94871794871794868</v>
       </c>
       <c r="I16" s="0">
-        <v>0.87543119969336913</v>
+        <v>0.84668455346876192</v>
       </c>
       <c r="J16" s="0">
-        <v>0.81115630447414289</v>
+        <v>0.77851605758582509</v>
       </c>
     </row>
     <row r="17">
@@ -4522,25 +4522,25 @@
         <v>5450</v>
       </c>
       <c r="D17" s="0">
-        <v>2680</v>
+        <v>2830</v>
       </c>
       <c r="E17" s="0">
-        <v>6770</v>
+        <v>6620</v>
       </c>
       <c r="F17" s="0">
         <v>340</v>
       </c>
       <c r="G17" s="0">
-        <v>0.67035670356703569</v>
+        <v>0.65821256038647347</v>
       </c>
       <c r="H17" s="0">
         <v>0.94127806563039729</v>
       </c>
       <c r="I17" s="0">
-        <v>0.80183727034120733</v>
+        <v>0.79199475065616798</v>
       </c>
       <c r="J17" s="0">
-        <v>0.78304597701149425</v>
+        <v>0.77469793887704341</v>
       </c>
     </row>
   </sheetData>
@@ -4604,28 +4604,28 @@
         <v>20</v>
       </c>
       <c r="C2" s="0">
-        <v>151080</v>
+        <v>154410</v>
       </c>
       <c r="D2" s="0">
-        <v>53320</v>
+        <v>67290</v>
       </c>
       <c r="E2" s="0">
-        <v>977820</v>
+        <v>963850</v>
       </c>
       <c r="F2" s="0">
-        <v>8850</v>
+        <v>5520</v>
       </c>
       <c r="G2" s="0">
-        <v>0.73913894324853224</v>
+        <v>0.69648173207036534</v>
       </c>
       <c r="H2" s="0">
-        <v>0.94466329018945794</v>
+        <v>0.96548489964359407</v>
       </c>
       <c r="I2" s="0">
-        <v>0.94780323574600989</v>
+        <v>0.93887009159831081</v>
       </c>
       <c r="J2" s="0">
-        <v>0.82935799961573287</v>
+        <v>0.80921311217671565</v>
       </c>
     </row>
     <row r="3">
@@ -4636,28 +4636,28 @@
         <v>16</v>
       </c>
       <c r="C3" s="0">
-        <v>119060</v>
+        <v>121690</v>
       </c>
       <c r="D3" s="0">
-        <v>50660</v>
+        <v>53140</v>
       </c>
       <c r="E3" s="0">
-        <v>866020</v>
+        <v>863540</v>
       </c>
       <c r="F3" s="0">
-        <v>11740</v>
+        <v>9110</v>
       </c>
       <c r="G3" s="0">
-        <v>0.70150836672165917</v>
+        <v>0.69604758908654119</v>
       </c>
       <c r="H3" s="0">
-        <v>0.91024464831804286</v>
+        <v>0.93035168195718654</v>
       </c>
       <c r="I3" s="0">
-        <v>0.94042845686791154</v>
+        <v>0.94057165769274831</v>
       </c>
       <c r="J3" s="0">
-        <v>0.79235990949021684</v>
+        <v>0.79632235055459222</v>
       </c>
     </row>
     <row r="4">
@@ -4732,7 +4732,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="0">
-        <v>10010</v>
+        <v>9560</v>
       </c>
       <c r="D6" s="0">
         <v>0</v>
@@ -4741,19 +4741,19 @@
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>10960</v>
+        <v>11410</v>
       </c>
       <c r="G6" s="0">
         <v>1</v>
       </c>
       <c r="H6" s="0">
-        <v>0.47734859322842155</v>
+        <v>0.4558893657606104</v>
       </c>
       <c r="I6" s="0">
-        <v>0.47734859322842155</v>
+        <v>0.4558893657606104</v>
       </c>
       <c r="J6" s="0">
-        <v>0.64622336991607487</v>
+        <v>0.62626924336717982</v>
       </c>
     </row>
     <row r="7">
@@ -4764,7 +4764,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="0">
-        <v>9930</v>
+        <v>9380</v>
       </c>
       <c r="D7" s="0">
         <v>0</v>
@@ -4773,19 +4773,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>11810</v>
+        <v>12360</v>
       </c>
       <c r="G7" s="0">
         <v>1</v>
       </c>
       <c r="H7" s="0">
-        <v>0.45676172953081878</v>
+        <v>0.43146274149034036</v>
       </c>
       <c r="I7" s="0">
-        <v>0.45676172953081878</v>
+        <v>0.43146274149034036</v>
       </c>
       <c r="J7" s="0">
-        <v>0.62709188506473001</v>
+        <v>0.60282776349614386</v>
       </c>
     </row>
     <row r="8">
@@ -4796,7 +4796,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="0">
-        <v>12090</v>
+        <v>11290</v>
       </c>
       <c r="D8" s="0">
         <v>0</v>
@@ -4805,19 +4805,19 @@
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>6600</v>
+        <v>7400</v>
       </c>
       <c r="G8" s="0">
         <v>1</v>
       </c>
       <c r="H8" s="0">
-        <v>0.6468699839486356</v>
+        <v>0.60406634563937933</v>
       </c>
       <c r="I8" s="0">
-        <v>0.6468699839486356</v>
+        <v>0.60406634563937933</v>
       </c>
       <c r="J8" s="0">
-        <v>0.78557504873294348</v>
+        <v>0.75316877918612402</v>
       </c>
     </row>
     <row r="9">
@@ -4828,7 +4828,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="0">
-        <v>28970</v>
+        <v>29170</v>
       </c>
       <c r="D9" s="0">
         <v>0</v>
@@ -4837,19 +4837,19 @@
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>920</v>
+        <v>720</v>
       </c>
       <c r="G9" s="0">
         <v>1</v>
       </c>
       <c r="H9" s="0">
-        <v>0.96922047507527598</v>
+        <v>0.97591167614586816</v>
       </c>
       <c r="I9" s="0">
-        <v>0.96922047507527598</v>
+        <v>0.97591167614586816</v>
       </c>
       <c r="J9" s="0">
-        <v>0.98436969079170911</v>
+        <v>0.98780900778868941</v>
       </c>
     </row>
     <row r="10">
@@ -4860,7 +4860,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="0">
-        <v>28400</v>
+        <v>28500</v>
       </c>
       <c r="D10" s="0">
         <v>0</v>
@@ -4869,19 +4869,19 @@
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="G10" s="0">
         <v>1</v>
       </c>
       <c r="H10" s="0">
-        <v>0.99092812281926035</v>
+        <v>0.994417306350314</v>
       </c>
       <c r="I10" s="0">
-        <v>0.99092812281926035</v>
+        <v>0.994417306350314</v>
       </c>
       <c r="J10" s="0">
-        <v>0.99544339291973361</v>
+        <v>0.99720083974807561</v>
       </c>
     </row>
     <row r="11">
@@ -4892,7 +4892,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="0">
-        <v>19990</v>
+        <v>18600</v>
       </c>
       <c r="D11" s="0">
         <v>0</v>
@@ -4901,19 +4901,19 @@
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>710</v>
+        <v>2100</v>
       </c>
       <c r="G11" s="0">
         <v>1</v>
       </c>
       <c r="H11" s="0">
-        <v>0.96570048309178746</v>
+        <v>0.89855072463768115</v>
       </c>
       <c r="I11" s="0">
-        <v>0.96570048309178746</v>
+        <v>0.89855072463768115</v>
       </c>
       <c r="J11" s="0">
-        <v>0.98255099533054802</v>
+        <v>0.94656488549618323</v>
       </c>
     </row>
     <row r="12">
@@ -4924,7 +4924,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="0">
-        <v>21780</v>
+        <v>21030</v>
       </c>
       <c r="D12" s="0">
         <v>0</v>
@@ -4933,19 +4933,19 @@
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>290</v>
+        <v>1040</v>
       </c>
       <c r="G12" s="0">
         <v>1</v>
       </c>
       <c r="H12" s="0">
-        <v>0.98685999093792476</v>
+        <v>0.95287720888083371</v>
       </c>
       <c r="I12" s="0">
-        <v>0.98685999093792476</v>
+        <v>0.95287720888083371</v>
       </c>
       <c r="J12" s="0">
-        <v>0.99338654503990875</v>
+        <v>0.97587006960556844</v>
       </c>
     </row>
     <row r="13">
@@ -4956,7 +4956,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="0">
-        <v>19450</v>
+        <v>16300</v>
       </c>
       <c r="D13" s="0">
         <v>0</v>
@@ -4965,19 +4965,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>3970</v>
+        <v>7120</v>
       </c>
       <c r="G13" s="0">
         <v>1</v>
       </c>
       <c r="H13" s="0">
-        <v>0.83048676345004269</v>
+        <v>0.69598633646456021</v>
       </c>
       <c r="I13" s="0">
-        <v>0.83048676345004269</v>
+        <v>0.69598633646456021</v>
       </c>
       <c r="J13" s="0">
-        <v>0.90739444833216698</v>
+        <v>0.82074521651560928</v>
       </c>
     </row>
     <row r="14">
@@ -4988,7 +4988,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="0">
-        <v>47950</v>
+        <v>48050</v>
       </c>
       <c r="D14" s="0">
         <v>0</v>
@@ -4997,19 +4997,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="G14" s="0">
         <v>1</v>
       </c>
       <c r="H14" s="0">
-        <v>0.99295920480430733</v>
+        <v>0.99503002692068754</v>
       </c>
       <c r="I14" s="0">
-        <v>0.99295920480430733</v>
+        <v>0.99503002692068754</v>
       </c>
       <c r="J14" s="0">
-        <v>0.99646716541978397</v>
+        <v>0.99750882291882914</v>
       </c>
     </row>
     <row r="15">
@@ -5020,7 +5020,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="0">
-        <v>25100</v>
+        <v>25250</v>
       </c>
       <c r="D15" s="0">
         <v>0</v>
@@ -5029,19 +5029,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>1900</v>
+        <v>1750</v>
       </c>
       <c r="G15" s="0">
         <v>1</v>
       </c>
       <c r="H15" s="0">
-        <v>0.92962962962962958</v>
+        <v>0.93518518518518523</v>
       </c>
       <c r="I15" s="0">
-        <v>0.92962962962962958</v>
+        <v>0.93518518518518523</v>
       </c>
       <c r="J15" s="0">
-        <v>0.96353166986564298</v>
+        <v>0.96650717703349287</v>
       </c>
     </row>
     <row r="16">
@@ -5052,7 +5052,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="0">
-        <v>25710</v>
+        <v>26110</v>
       </c>
       <c r="D16" s="0">
         <v>0</v>
@@ -5061,19 +5061,19 @@
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="G16" s="0">
         <v>1</v>
       </c>
       <c r="H16" s="0">
-        <v>0.95540691192865101</v>
+        <v>0.97027127461910068</v>
       </c>
       <c r="I16" s="0">
-        <v>0.95540691192865101</v>
+        <v>0.97027127461910068</v>
       </c>
       <c r="J16" s="0">
-        <v>0.97719498289623719</v>
+        <v>0.98491135420595999</v>
       </c>
     </row>
     <row r="17">

--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="13625" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15572" uniqueCount="66">
   <si>
     <t>Subject</t>
   </si>
@@ -196,6 +196,27 @@
   <si>
     <t>RemovedPct</t>
   </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Overnight</t>
+  </si>
+  <si>
+    <t>TotalRawRows</t>
+  </si>
+  <si>
+    <t>FaultyRowsRemoved</t>
+  </si>
+  <si>
+    <t>PctFaultyRows</t>
+  </si>
+  <si>
+    <t>TotalCleanedSec</t>
+  </si>
+  <si>
+    <t>EvaluableSec</t>
+  </si>
 </sst>
 </file>
 
@@ -240,7 +261,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="true"/>
@@ -251,7 +272,7 @@
     <col min="6" max="6" width="12.5546875" customWidth="true"/>
     <col min="7" max="7" width="12.5546875" customWidth="true"/>
     <col min="8" max="8" width="6" customWidth="true"/>
-    <col min="9" max="9" width="7" customWidth="true"/>
+    <col min="9" max="9" width="8" customWidth="true"/>
     <col min="10" max="10" width="6" customWidth="true"/>
     <col min="11" max="11" width="5" customWidth="true"/>
   </cols>
@@ -3859,6 +3880,76 @@
       </c>
       <c r="K103" s="0">
         <v>80</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="0">
+        <v>0.9835828953602398</v>
+      </c>
+      <c r="E104" s="0">
+        <v>0</v>
+      </c>
+      <c r="F104" s="0">
+        <v>0</v>
+      </c>
+      <c r="G104" s="0">
+        <v>1</v>
+      </c>
+      <c r="H104" s="0">
+        <v>0</v>
+      </c>
+      <c r="I104" s="0">
+        <v>1785380</v>
+      </c>
+      <c r="J104" s="0">
+        <v>29800</v>
+      </c>
+      <c r="K104" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="0">
+        <v>0.98421887565685828</v>
+      </c>
+      <c r="E105" s="0">
+        <v>0</v>
+      </c>
+      <c r="F105" s="0">
+        <v>0</v>
+      </c>
+      <c r="G105" s="0">
+        <v>1</v>
+      </c>
+      <c r="H105" s="0">
+        <v>0</v>
+      </c>
+      <c r="I105" s="0">
+        <v>1786810</v>
+      </c>
+      <c r="J105" s="0">
+        <v>28650</v>
+      </c>
+      <c r="K105" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3874,7 +3965,7 @@
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="7.33203125" customWidth="true"/>
     <col min="4" max="4" width="7.21875" customWidth="true"/>
-    <col min="5" max="5" width="7.6640625" customWidth="true"/>
+    <col min="5" max="5" width="8" customWidth="true"/>
     <col min="6" max="6" width="7.5546875" customWidth="true"/>
     <col min="7" max="7" width="12.5546875" customWidth="true"/>
     <col min="8" max="8" width="12.5546875" customWidth="true"/>
@@ -3919,31 +4010,31 @@
         <v>9</v>
       </c>
       <c r="B2" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="0">
         <v>304870</v>
       </c>
       <c r="D2" s="0">
-        <v>43000</v>
+        <v>71650</v>
       </c>
       <c r="E2" s="0">
-        <v>944910</v>
+        <v>2731720</v>
       </c>
       <c r="F2" s="0">
         <v>36160</v>
       </c>
       <c r="G2" s="0">
-        <v>0.87639060568603211</v>
+        <v>0.80970466376288108</v>
       </c>
       <c r="H2" s="0">
         <v>0.89396827258598954</v>
       </c>
       <c r="I2" s="0">
-        <v>0.94043372913750811</v>
+        <v>0.96571364966289275</v>
       </c>
       <c r="J2" s="0">
-        <v>0.88509217593264633</v>
+        <v>0.84975263047871241</v>
       </c>
     </row>
     <row r="3">
@@ -3951,31 +4042,31 @@
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="0">
         <v>279590</v>
       </c>
       <c r="D3" s="0">
-        <v>77730</v>
+        <v>107530</v>
       </c>
       <c r="E3" s="0">
-        <v>910290</v>
+        <v>2695670</v>
       </c>
       <c r="F3" s="0">
         <v>43390</v>
       </c>
       <c r="G3" s="0">
-        <v>0.78246389790663828</v>
+        <v>0.72223083281669764</v>
       </c>
       <c r="H3" s="0">
         <v>0.86565731624249176</v>
       </c>
       <c r="I3" s="0">
-        <v>0.90761250953470629</v>
+        <v>0.95172382908213859</v>
       </c>
       <c r="J3" s="0">
-        <v>0.82196089960311625</v>
+        <v>0.78746655400647791</v>
       </c>
     </row>
   </sheetData>
@@ -3984,7 +4075,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="true"/>
@@ -4097,83 +4188,83 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B4" s="0">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>97830</v>
+        <v>0</v>
       </c>
       <c r="D4" s="0">
-        <v>0</v>
+        <v>58450</v>
       </c>
       <c r="E4" s="0">
-        <v>0</v>
+        <v>3572190</v>
       </c>
       <c r="F4" s="0">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="0">
-        <v>0.97024695031240704</v>
+        <v>0</v>
       </c>
       <c r="I4" s="0">
-        <v>0.97024695031240704</v>
+        <v>0.983900910032391</v>
       </c>
       <c r="J4" s="0">
-        <v>0.98489882210812452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B5" s="0">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C5" s="0">
-        <v>0</v>
+        <v>97830</v>
       </c>
       <c r="D5" s="0">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>21130</v>
+        <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G5" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="0">
-        <v>0</v>
+        <v>0.97024695031240704</v>
       </c>
       <c r="I5" s="0">
-        <v>0.91353220925205358</v>
+        <v>0.97024695031240704</v>
       </c>
       <c r="J5" s="0">
-        <v>0</v>
+        <v>0.98489882210812452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B6" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="0">
         <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>11450</v>
+        <v>2000</v>
       </c>
       <c r="E6" s="0">
-        <v>10600</v>
+        <v>21130</v>
       </c>
       <c r="F6" s="0">
         <v>0</v>
@@ -4185,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>0.48072562358276644</v>
+        <v>0.91353220925205358</v>
       </c>
       <c r="J6" s="0">
         <v>0</v>
@@ -4193,353 +4284,385 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="0">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C7" s="0">
-        <v>232090</v>
+        <v>0</v>
       </c>
       <c r="D7" s="0">
-        <v>0</v>
+        <v>11450</v>
       </c>
       <c r="E7" s="0">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="F7" s="0">
-        <v>62310</v>
+        <v>0</v>
       </c>
       <c r="G7" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0">
-        <v>0.78834918478260874</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0">
-        <v>0.78834918478260874</v>
+        <v>0.48072562358276644</v>
       </c>
       <c r="J7" s="0">
-        <v>0.88165017379247468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B8" s="0">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="C8" s="0">
-        <v>34810</v>
+        <v>232090</v>
       </c>
       <c r="D8" s="0">
-        <v>3340</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>76390</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>1820</v>
+        <v>62310</v>
       </c>
       <c r="G8" s="0">
-        <v>0.91245085190039321</v>
+        <v>1</v>
       </c>
       <c r="H8" s="0">
-        <v>0.95031395031395027</v>
+        <v>0.78834918478260874</v>
       </c>
       <c r="I8" s="0">
-        <v>0.95565486421450674</v>
+        <v>0.78834918478260874</v>
       </c>
       <c r="J8" s="0">
-        <v>0.93099759293928863</v>
+        <v>0.88165017379247468</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>22000</v>
+        <v>34810</v>
       </c>
       <c r="D9" s="0">
-        <v>5600</v>
+        <v>3340</v>
       </c>
       <c r="E9" s="0">
-        <v>20260</v>
+        <v>76390</v>
       </c>
       <c r="F9" s="0">
-        <v>2400</v>
+        <v>1820</v>
       </c>
       <c r="G9" s="0">
-        <v>0.79710144927536231</v>
+        <v>0.91245085190039321</v>
       </c>
       <c r="H9" s="0">
-        <v>0.90163934426229508</v>
+        <v>0.95031395031395027</v>
       </c>
       <c r="I9" s="0">
-        <v>0.84082769598089935</v>
+        <v>0.95565486421450674</v>
       </c>
       <c r="J9" s="0">
-        <v>0.84615384615384615</v>
+        <v>0.93099759293928863</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="0">
         <v>2</v>
       </c>
       <c r="C10" s="0">
-        <v>76460</v>
+        <v>22000</v>
       </c>
       <c r="D10" s="0">
-        <v>1950</v>
+        <v>5600</v>
       </c>
       <c r="E10" s="0">
-        <v>64450</v>
+        <v>20260</v>
       </c>
       <c r="F10" s="0">
-        <v>1380</v>
+        <v>2400</v>
       </c>
       <c r="G10" s="0">
-        <v>0.97513072312205074</v>
+        <v>0.79710144927536231</v>
       </c>
       <c r="H10" s="0">
-        <v>0.98227132579650567</v>
+        <v>0.90163934426229508</v>
       </c>
       <c r="I10" s="0">
-        <v>0.97691347753743762</v>
+        <v>0.84082769598089935</v>
       </c>
       <c r="J10" s="0">
-        <v>0.978688</v>
+        <v>0.84615384615384615</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="B11" s="0">
         <v>2</v>
       </c>
       <c r="C11" s="0">
-        <v>47730</v>
+        <v>76460</v>
       </c>
       <c r="D11" s="0">
-        <v>3670</v>
+        <v>1950</v>
       </c>
       <c r="E11" s="0">
-        <v>54060</v>
+        <v>64450</v>
       </c>
       <c r="F11" s="0">
-        <v>2430</v>
+        <v>1380</v>
       </c>
       <c r="G11" s="0">
-        <v>0.9285992217898833</v>
+        <v>0.97513072312205074</v>
       </c>
       <c r="H11" s="0">
-        <v>0.95155502392344493</v>
+        <v>0.98227132579650567</v>
       </c>
       <c r="I11" s="0">
-        <v>0.9434609324311799</v>
+        <v>0.97691347753743762</v>
       </c>
       <c r="J11" s="0">
-        <v>0.93993698306419848</v>
+        <v>0.978688</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="0">
         <v>2</v>
       </c>
       <c r="C12" s="0">
-        <v>24620</v>
+        <v>47730</v>
       </c>
       <c r="D12" s="0">
-        <v>10070</v>
+        <v>3670</v>
       </c>
       <c r="E12" s="0">
-        <v>28150</v>
+        <v>54060</v>
       </c>
       <c r="F12" s="0">
-        <v>750</v>
+        <v>2430</v>
       </c>
       <c r="G12" s="0">
-        <v>0.70971461516287115</v>
+        <v>0.9285992217898833</v>
       </c>
       <c r="H12" s="0">
-        <v>0.97043752463539612</v>
+        <v>0.95155502392344493</v>
       </c>
       <c r="I12" s="0">
-        <v>0.82984746029249878</v>
+        <v>0.9434609324311799</v>
       </c>
       <c r="J12" s="0">
-        <v>0.81984681984681984</v>
+        <v>0.93993698306419848</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B13" s="0">
         <v>2</v>
       </c>
       <c r="C13" s="0">
-        <v>22800</v>
+        <v>24620</v>
       </c>
       <c r="D13" s="0">
-        <v>3830</v>
+        <v>10070</v>
       </c>
       <c r="E13" s="0">
-        <v>24770</v>
+        <v>28150</v>
       </c>
       <c r="F13" s="0">
-        <v>1780</v>
+        <v>750</v>
       </c>
       <c r="G13" s="0">
-        <v>0.8561772437101014</v>
+        <v>0.70971461516287115</v>
       </c>
       <c r="H13" s="0">
-        <v>0.92758340113913751</v>
+        <v>0.97043752463539612</v>
       </c>
       <c r="I13" s="0">
-        <v>0.89450921399022187</v>
+        <v>0.82984746029249878</v>
       </c>
       <c r="J13" s="0">
-        <v>0.89045108377270066</v>
+        <v>0.81984681984681984</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="0">
         <v>2</v>
       </c>
       <c r="C14" s="0">
-        <v>7750</v>
+        <v>22800</v>
       </c>
       <c r="D14" s="0">
-        <v>3750</v>
+        <v>3830</v>
       </c>
       <c r="E14" s="0">
-        <v>14350</v>
+        <v>24770</v>
       </c>
       <c r="F14" s="0">
-        <v>550</v>
+        <v>1780</v>
       </c>
       <c r="G14" s="0">
-        <v>0.67391304347826086</v>
+        <v>0.8561772437101014</v>
       </c>
       <c r="H14" s="0">
-        <v>0.9337349397590361</v>
+        <v>0.92758340113913751</v>
       </c>
       <c r="I14" s="0">
-        <v>0.83712121212121215</v>
+        <v>0.89450921399022187</v>
       </c>
       <c r="J14" s="0">
-        <v>0.78282828282828276</v>
+        <v>0.89045108377270066</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
       </c>
       <c r="C15" s="0">
-        <v>5890</v>
+        <v>7750</v>
       </c>
       <c r="D15" s="0">
-        <v>3260</v>
+        <v>3750</v>
       </c>
       <c r="E15" s="0">
-        <v>7580</v>
+        <v>14350</v>
       </c>
       <c r="F15" s="0">
-        <v>2410</v>
+        <v>550</v>
       </c>
       <c r="G15" s="0">
-        <v>0.64371584699453555</v>
+        <v>0.67391304347826086</v>
       </c>
       <c r="H15" s="0">
-        <v>0.7096385542168675</v>
+        <v>0.9337349397590361</v>
       </c>
       <c r="I15" s="0">
-        <v>0.70376175548589337</v>
+        <v>0.83712121212121215</v>
       </c>
       <c r="J15" s="0">
-        <v>0.67507163323782227</v>
+        <v>0.78282828282828276</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="0">
         <v>2</v>
       </c>
       <c r="C16" s="0">
-        <v>7030</v>
+        <v>5890</v>
       </c>
       <c r="D16" s="0">
-        <v>3620</v>
+        <v>3260</v>
       </c>
       <c r="E16" s="0">
-        <v>15060</v>
+        <v>7580</v>
       </c>
       <c r="F16" s="0">
-        <v>380</v>
+        <v>2410</v>
       </c>
       <c r="G16" s="0">
-        <v>0.66009389671361507</v>
+        <v>0.64371584699453555</v>
       </c>
       <c r="H16" s="0">
-        <v>0.94871794871794868</v>
+        <v>0.7096385542168675</v>
       </c>
       <c r="I16" s="0">
-        <v>0.84668455346876192</v>
+        <v>0.70376175548589337</v>
       </c>
       <c r="J16" s="0">
-        <v>0.77851605758582509</v>
+        <v>0.67507163323782227</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="0">
         <v>2</v>
       </c>
       <c r="C17" s="0">
+        <v>7030</v>
+      </c>
+      <c r="D17" s="0">
+        <v>3620</v>
+      </c>
+      <c r="E17" s="0">
+        <v>15060</v>
+      </c>
+      <c r="F17" s="0">
+        <v>380</v>
+      </c>
+      <c r="G17" s="0">
+        <v>0.66009389671361507</v>
+      </c>
+      <c r="H17" s="0">
+        <v>0.94871794871794868</v>
+      </c>
+      <c r="I17" s="0">
+        <v>0.84668455346876192</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0.77851605758582509</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="0">
+        <v>2</v>
+      </c>
+      <c r="C18" s="0">
         <v>5450</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D18" s="0">
         <v>2830</v>
       </c>
-      <c r="E17" s="0">
+      <c r="E18" s="0">
         <v>6620</v>
       </c>
-      <c r="F17" s="0">
+      <c r="F18" s="0">
         <v>340</v>
       </c>
-      <c r="G17" s="0">
+      <c r="G18" s="0">
         <v>0.65821256038647347</v>
       </c>
-      <c r="H17" s="0">
+      <c r="H18" s="0">
         <v>0.94127806563039729</v>
       </c>
-      <c r="I17" s="0">
+      <c r="I18" s="0">
         <v>0.79199475065616798</v>
       </c>
-      <c r="J17" s="0">
+      <c r="J18" s="0">
         <v>0.77469793887704341</v>
       </c>
     </row>
@@ -4549,14 +4672,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="7.33203125" customWidth="true"/>
     <col min="4" max="4" width="7.21875" customWidth="true"/>
-    <col min="5" max="5" width="7.6640625" customWidth="true"/>
+    <col min="5" max="5" width="8" customWidth="true"/>
     <col min="6" max="6" width="7.5546875" customWidth="true"/>
     <col min="7" max="7" width="12.5546875" customWidth="true"/>
     <col min="8" max="8" width="12.5546875" customWidth="true"/>
@@ -5110,33 +5233,65 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="0">
+        <v>2</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0</v>
+      </c>
+      <c r="D18" s="0">
+        <v>58450</v>
+      </c>
+      <c r="E18" s="0">
+        <v>3572190</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" s="0">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0">
+        <v>0.983900910032391</v>
+      </c>
+      <c r="J18" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="0">
+      <c r="B19" s="0">
         <v>4</v>
       </c>
-      <c r="C18" s="0">
-        <v>0</v>
-      </c>
-      <c r="D18" s="0">
-        <v>0</v>
-      </c>
-      <c r="E18" s="0">
-        <v>0</v>
-      </c>
-      <c r="F18" s="0">
+      <c r="C19" s="0">
+        <v>0</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0">
         <v>19250</v>
       </c>
-      <c r="G18" s="0">
-        <v>0</v>
-      </c>
-      <c r="H18" s="0">
-        <v>0</v>
-      </c>
-      <c r="I18" s="0">
-        <v>0</v>
-      </c>
-      <c r="J18" s="0">
+      <c r="G19" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0">
+        <v>0</v>
+      </c>
+      <c r="I19" s="0">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0">
         <v>0</v>
       </c>
     </row>
@@ -5146,16 +5301,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="true"/>
     <col min="2" max="2" width="9.88671875" customWidth="true"/>
     <col min="3" max="3" width="5.33203125" customWidth="true"/>
-    <col min="4" max="4" width="8" customWidth="true"/>
-    <col min="5" max="5" width="7.77734375" customWidth="true"/>
-    <col min="6" max="6" width="11.44140625" customWidth="true"/>
-    <col min="7" max="7" width="12.5546875" customWidth="true"/>
+    <col min="4" max="4" width="13.21875" customWidth="true"/>
+    <col min="5" max="5" width="18" customWidth="true"/>
+    <col min="6" max="6" width="13.5546875" customWidth="true"/>
+    <col min="7" max="7" width="14.5546875" customWidth="true"/>
+    <col min="8" max="8" width="11.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5169,16 +5325,19 @@
         <v>7</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>58</v>
+        <v>64</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2">
@@ -5192,16 +5351,19 @@
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>504.57999999999998</v>
+        <v>25230</v>
       </c>
       <c r="E2" s="0">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0">
+        <v>504.60000000000002</v>
+      </c>
+      <c r="H2" s="0">
         <v>502.60000000000002</v>
-      </c>
-      <c r="F2" s="0">
-        <v>1.9799999999999613</v>
-      </c>
-      <c r="G2" s="0">
-        <v>0.39240556502436907</v>
       </c>
     </row>
     <row r="3">
@@ -5215,16 +5377,19 @@
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>504.57999999999998</v>
+        <v>25230</v>
       </c>
       <c r="E3" s="0">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0">
+        <v>504.60000000000002</v>
+      </c>
+      <c r="H3" s="0">
         <v>502.60000000000002</v>
-      </c>
-      <c r="F3" s="0">
-        <v>1.9799999999999613</v>
-      </c>
-      <c r="G3" s="0">
-        <v>0.39240556502436907</v>
       </c>
     </row>
     <row r="4">
@@ -5238,16 +5403,19 @@
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>1474.98</v>
+        <v>73750</v>
       </c>
       <c r="E4" s="0">
+        <v>640</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0.8677966101694915</v>
+      </c>
+      <c r="G4" s="0">
+        <v>1462.2</v>
+      </c>
+      <c r="H4" s="0">
         <v>1416</v>
-      </c>
-      <c r="F4" s="0">
-        <v>58.980000000000018</v>
-      </c>
-      <c r="G4" s="0">
-        <v>3.998698287434407</v>
       </c>
     </row>
     <row r="5">
@@ -5261,16 +5429,19 @@
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>1474.98</v>
+        <v>73750</v>
       </c>
       <c r="E5" s="0">
+        <v>110</v>
+      </c>
+      <c r="F5" s="0">
+        <v>0.14915254237288136</v>
+      </c>
+      <c r="G5" s="0">
+        <v>1472.8</v>
+      </c>
+      <c r="H5" s="0">
         <v>1468.8</v>
-      </c>
-      <c r="F5" s="0">
-        <v>6.1800000000000637</v>
-      </c>
-      <c r="G5" s="0">
-        <v>0.41898873205060838</v>
       </c>
     </row>
     <row r="6">
@@ -5284,16 +5455,19 @@
         <v>8</v>
       </c>
       <c r="D6" s="0">
-        <v>1505.78</v>
+        <v>69690</v>
       </c>
       <c r="E6" s="0">
+        <v>8090</v>
+      </c>
+      <c r="F6" s="0">
+        <v>11.608552159563782</v>
+      </c>
+      <c r="G6" s="0">
+        <v>1232</v>
+      </c>
+      <c r="H6" s="0">
         <v>977</v>
-      </c>
-      <c r="F6" s="0">
-        <v>528.77999999999997</v>
-      </c>
-      <c r="G6" s="0">
-        <v>35.116683712096055</v>
       </c>
     </row>
     <row r="7">
@@ -5307,16 +5481,19 @@
         <v>9</v>
       </c>
       <c r="D7" s="0">
-        <v>1505.78</v>
+        <v>69690</v>
       </c>
       <c r="E7" s="0">
+        <v>700</v>
+      </c>
+      <c r="F7" s="0">
+        <v>1.0044482709140479</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1379.8</v>
+      </c>
+      <c r="H7" s="0">
         <v>1350.2</v>
-      </c>
-      <c r="F7" s="0">
-        <v>155.57999999999993</v>
-      </c>
-      <c r="G7" s="0">
-        <v>10.332186640810738</v>
       </c>
     </row>
     <row r="8">
@@ -5330,16 +5507,19 @@
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <v>1086.5799999999999</v>
+        <v>54330</v>
       </c>
       <c r="E8" s="0">
+        <v>320</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0.58899318976624337</v>
+      </c>
+      <c r="G8" s="0">
+        <v>1080.2</v>
+      </c>
+      <c r="H8" s="0">
         <v>1075.4000000000001</v>
-      </c>
-      <c r="F8" s="0">
-        <v>11.179999999999836</v>
-      </c>
-      <c r="G8" s="0">
-        <v>1.0289164166467115</v>
       </c>
     </row>
     <row r="9">
@@ -5353,16 +5533,19 @@
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <v>1086.5799999999999</v>
+        <v>54330</v>
       </c>
       <c r="E9" s="0">
+        <v>10</v>
+      </c>
+      <c r="F9" s="0">
+        <v>0.018406037180195105</v>
+      </c>
+      <c r="G9" s="0">
+        <v>1086.4000000000001</v>
+      </c>
+      <c r="H9" s="0">
         <v>1082.4000000000001</v>
-      </c>
-      <c r="F9" s="0">
-        <v>4.1799999999998363</v>
-      </c>
-      <c r="G9" s="0">
-        <v>0.38469325774446766</v>
       </c>
     </row>
     <row r="10">
@@ -5376,16 +5559,19 @@
         <v>8</v>
       </c>
       <c r="D10" s="0">
-        <v>640.17999999999995</v>
+        <v>32010</v>
       </c>
       <c r="E10" s="0">
+        <v>30</v>
+      </c>
+      <c r="F10" s="0">
+        <v>0.093720712277413312</v>
+      </c>
+      <c r="G10" s="0">
+        <v>639.60000000000002</v>
+      </c>
+      <c r="H10" s="0">
         <v>633.60000000000002</v>
-      </c>
-      <c r="F10" s="0">
-        <v>6.5799999999999272</v>
-      </c>
-      <c r="G10" s="0">
-        <v>1.0278359211471662</v>
       </c>
     </row>
     <row r="11">
@@ -5399,16 +5585,19 @@
         <v>9</v>
       </c>
       <c r="D11" s="0">
-        <v>640.17999999999995</v>
+        <v>32010</v>
       </c>
       <c r="E11" s="0">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0">
+        <v>640.20000000000005</v>
+      </c>
+      <c r="H11" s="0">
         <v>638.20000000000005</v>
-      </c>
-      <c r="F11" s="0">
-        <v>1.9799999999999045</v>
-      </c>
-      <c r="G11" s="0">
-        <v>0.30928801274640016</v>
       </c>
     </row>
     <row r="12">
@@ -5422,16 +5611,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="0">
-        <v>540.98000000000002</v>
+        <v>27050</v>
       </c>
       <c r="E12" s="0">
+        <v>180</v>
+      </c>
+      <c r="F12" s="0">
+        <v>0.6654343807763401</v>
+      </c>
+      <c r="G12" s="0">
+        <v>537.39999999999998</v>
+      </c>
+      <c r="H12" s="0">
         <v>531.39999999999998</v>
-      </c>
-      <c r="F12" s="0">
-        <v>9.5800000000000409</v>
-      </c>
-      <c r="G12" s="0">
-        <v>1.7708602905837629</v>
       </c>
     </row>
     <row r="13">
@@ -5445,16 +5637,19 @@
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <v>540.98000000000002</v>
+        <v>27050</v>
       </c>
       <c r="E13" s="0">
+        <v>140</v>
+      </c>
+      <c r="F13" s="0">
+        <v>0.51756007393715342</v>
+      </c>
+      <c r="G13" s="0">
+        <v>538.20000000000005</v>
+      </c>
+      <c r="H13" s="0">
         <v>532.20000000000005</v>
-      </c>
-      <c r="F13" s="0">
-        <v>8.7799999999999727</v>
-      </c>
-      <c r="G13" s="0">
-        <v>1.6229805168398042</v>
       </c>
     </row>
     <row r="14">
@@ -5468,16 +5663,19 @@
         <v>8</v>
       </c>
       <c r="D14" s="0">
-        <v>265.98000000000002</v>
+        <v>13300</v>
       </c>
       <c r="E14" s="0">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>266</v>
+      </c>
+      <c r="H14" s="0">
         <v>264</v>
-      </c>
-      <c r="F14" s="0">
-        <v>1.9800000000000182</v>
-      </c>
-      <c r="G14" s="0">
-        <v>0.74441687344913832</v>
       </c>
     </row>
     <row r="15">
@@ -5491,16 +5689,19 @@
         <v>9</v>
       </c>
       <c r="D15" s="0">
-        <v>265.98000000000002</v>
+        <v>13300</v>
       </c>
       <c r="E15" s="0">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0">
+        <v>266</v>
+      </c>
+      <c r="H15" s="0">
         <v>264</v>
-      </c>
-      <c r="F15" s="0">
-        <v>1.9800000000000182</v>
-      </c>
-      <c r="G15" s="0">
-        <v>0.74441687344913832</v>
       </c>
     </row>
     <row r="16">
@@ -5514,16 +5715,19 @@
         <v>8</v>
       </c>
       <c r="D16" s="0">
-        <v>199.97999999999999</v>
+        <v>10000</v>
       </c>
       <c r="E16" s="0">
+        <v>280</v>
+      </c>
+      <c r="F16" s="0">
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="G16" s="0">
+        <v>194.40000000000001</v>
+      </c>
+      <c r="H16" s="0">
         <v>188.40000000000001</v>
-      </c>
-      <c r="F16" s="0">
-        <v>11.579999999999984</v>
-      </c>
-      <c r="G16" s="0">
-        <v>5.7905790579057825</v>
       </c>
     </row>
     <row r="17">
@@ -5537,16 +5741,19 @@
         <v>9</v>
       </c>
       <c r="D17" s="0">
-        <v>199.97999999999999</v>
+        <v>10000</v>
       </c>
       <c r="E17" s="0">
+        <v>80</v>
+      </c>
+      <c r="F17" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="G17" s="0">
+        <v>198.40000000000001</v>
+      </c>
+      <c r="H17" s="0">
         <v>194.40000000000001</v>
-      </c>
-      <c r="F17" s="0">
-        <v>5.5799999999999841</v>
-      </c>
-      <c r="G17" s="0">
-        <v>2.7902790279027823</v>
       </c>
     </row>
     <row r="18">
@@ -5560,16 +5767,19 @@
         <v>8</v>
       </c>
       <c r="D18" s="0">
-        <v>274.98000000000002</v>
+        <v>13750</v>
       </c>
       <c r="E18" s="0">
+        <v>410</v>
+      </c>
+      <c r="F18" s="0">
+        <v>2.9818181818181815</v>
+      </c>
+      <c r="G18" s="0">
+        <v>266.80000000000001</v>
+      </c>
+      <c r="H18" s="0">
         <v>252.19999999999999</v>
-      </c>
-      <c r="F18" s="0">
-        <v>22.78000000000003</v>
-      </c>
-      <c r="G18" s="0">
-        <v>8.284238853734827</v>
       </c>
     </row>
     <row r="19">
@@ -5583,16 +5793,19 @@
         <v>9</v>
       </c>
       <c r="D19" s="0">
-        <v>274.98000000000002</v>
+        <v>13750</v>
       </c>
       <c r="E19" s="0">
+        <v>70</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0.50909090909090915</v>
+      </c>
+      <c r="G19" s="0">
+        <v>273.60000000000002</v>
+      </c>
+      <c r="H19" s="0">
         <v>269.60000000000002</v>
-      </c>
-      <c r="F19" s="0">
-        <v>5.3799999999999955</v>
-      </c>
-      <c r="G19" s="0">
-        <v>1.9565059277038312</v>
       </c>
     </row>
     <row r="20">
@@ -5606,16 +5819,19 @@
         <v>8</v>
       </c>
       <c r="D20" s="0">
-        <v>219.97999999999999</v>
+        <v>11000</v>
       </c>
       <c r="E20" s="0">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0">
+        <v>220</v>
+      </c>
+      <c r="H20" s="0">
         <v>218</v>
-      </c>
-      <c r="F20" s="0">
-        <v>1.9799999999999898</v>
-      </c>
-      <c r="G20" s="0">
-        <v>0.90008182562050632</v>
       </c>
     </row>
     <row r="21">
@@ -5629,16 +5845,19 @@
         <v>9</v>
       </c>
       <c r="D21" s="0">
-        <v>217.97999999999999</v>
+        <v>10990</v>
       </c>
       <c r="E21" s="0">
+        <v>2750</v>
+      </c>
+      <c r="F21" s="0">
+        <v>25.022747952684259</v>
+      </c>
+      <c r="G21" s="0">
+        <v>164.80000000000001</v>
+      </c>
+      <c r="H21" s="0">
         <v>86.799999999999997</v>
-      </c>
-      <c r="F21" s="0">
-        <v>131.18000000000001</v>
-      </c>
-      <c r="G21" s="0">
-        <v>60.179833012202955</v>
       </c>
     </row>
     <row r="22">
@@ -5652,16 +5871,19 @@
         <v>8</v>
       </c>
       <c r="D22" s="0">
-        <v>8495.7800000000007</v>
+        <v>424290</v>
       </c>
       <c r="E22" s="0">
+        <v>380</v>
+      </c>
+      <c r="F22" s="0">
+        <v>0.089561384901836003</v>
+      </c>
+      <c r="G22" s="0">
+        <v>8478.2000000000007</v>
+      </c>
+      <c r="H22" s="0">
         <v>8454.7999999999993</v>
-      </c>
-      <c r="F22" s="0">
-        <v>40.980000000001382</v>
-      </c>
-      <c r="G22" s="0">
-        <v>0.48235712318352619</v>
       </c>
     </row>
     <row r="23">
@@ -5675,16 +5897,19 @@
         <v>9</v>
       </c>
       <c r="D23" s="0">
-        <v>8495.7800000000007</v>
+        <v>424290</v>
       </c>
       <c r="E23" s="0">
+        <v>100</v>
+      </c>
+      <c r="F23" s="0">
+        <v>0.02356878550048316</v>
+      </c>
+      <c r="G23" s="0">
+        <v>8483.7999999999993</v>
+      </c>
+      <c r="H23" s="0">
         <v>8478.3999999999996</v>
-      </c>
-      <c r="F23" s="0">
-        <v>17.380000000001019</v>
-      </c>
-      <c r="G23" s="0">
-        <v>0.20457215229209111</v>
       </c>
     </row>
     <row r="24">
@@ -5698,16 +5923,19 @@
         <v>8</v>
       </c>
       <c r="D24" s="0">
-        <v>7015.9799999999996</v>
+        <v>350500</v>
       </c>
       <c r="E24" s="0">
+        <v>410</v>
+      </c>
+      <c r="F24" s="0">
+        <v>0.11697574893009986</v>
+      </c>
+      <c r="G24" s="0">
+        <v>7001.8000000000002</v>
+      </c>
+      <c r="H24" s="0">
         <v>6988</v>
-      </c>
-      <c r="F24" s="0">
-        <v>27.979999999999563</v>
-      </c>
-      <c r="G24" s="0">
-        <v>0.39880387344319063</v>
       </c>
     </row>
     <row r="25">
@@ -5721,16 +5949,19 @@
         <v>9</v>
       </c>
       <c r="D25" s="0">
-        <v>7015.9799999999996</v>
+        <v>350500</v>
       </c>
       <c r="E25" s="0">
+        <v>120</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0.034236804564907276</v>
+      </c>
+      <c r="G25" s="0">
+        <v>7007.6000000000004</v>
+      </c>
+      <c r="H25" s="0">
         <v>7004.6000000000004</v>
-      </c>
-      <c r="F25" s="0">
-        <v>11.3799999999992</v>
-      </c>
-      <c r="G25" s="0">
-        <v>0.16220114652549181</v>
       </c>
     </row>
     <row r="26">
@@ -5744,16 +5975,19 @@
         <v>8</v>
       </c>
       <c r="D26" s="0">
-        <v>142.18000000000001</v>
+        <v>6710</v>
       </c>
       <c r="E26" s="0">
+        <v>140</v>
+      </c>
+      <c r="F26" s="0">
+        <v>2.0864381520119228</v>
+      </c>
+      <c r="G26" s="0">
+        <v>131.40000000000001</v>
+      </c>
+      <c r="H26" s="0">
         <v>128.40000000000001</v>
-      </c>
-      <c r="F26" s="0">
-        <v>13.780000000000001</v>
-      </c>
-      <c r="G26" s="0">
-        <v>9.6919397946265295</v>
       </c>
     </row>
     <row r="27">
@@ -5767,16 +6001,19 @@
         <v>9</v>
       </c>
       <c r="D27" s="0">
-        <v>142.18000000000001</v>
+        <v>6710</v>
       </c>
       <c r="E27" s="0">
+        <v>220</v>
+      </c>
+      <c r="F27" s="0">
+        <v>3.278688524590164</v>
+      </c>
+      <c r="G27" s="0">
+        <v>129.80000000000001</v>
+      </c>
+      <c r="H27" s="0">
         <v>122.8</v>
-      </c>
-      <c r="F27" s="0">
-        <v>19.38000000000001</v>
-      </c>
-      <c r="G27" s="0">
-        <v>13.630609087072731</v>
       </c>
     </row>
     <row r="28">
@@ -5790,16 +6027,19 @@
         <v>8</v>
       </c>
       <c r="D28" s="0">
-        <v>132.38</v>
+        <v>6220</v>
       </c>
       <c r="E28" s="0">
+        <v>80</v>
+      </c>
+      <c r="F28" s="0">
+        <v>1.2861736334405145</v>
+      </c>
+      <c r="G28" s="0">
+        <v>122.8</v>
+      </c>
+      <c r="H28" s="0">
         <v>119.8</v>
-      </c>
-      <c r="F28" s="0">
-        <v>12.579999999999998</v>
-      </c>
-      <c r="G28" s="0">
-        <v>9.5029460643601738</v>
       </c>
     </row>
     <row r="29">
@@ -5813,16 +6053,19 @@
         <v>9</v>
       </c>
       <c r="D29" s="0">
-        <v>132.38</v>
+        <v>6220</v>
       </c>
       <c r="E29" s="0">
+        <v>120</v>
+      </c>
+      <c r="F29" s="0">
+        <v>1.929260450160772</v>
+      </c>
+      <c r="G29" s="0">
+        <v>122</v>
+      </c>
+      <c r="H29" s="0">
         <v>117</v>
-      </c>
-      <c r="F29" s="0">
-        <v>15.379999999999995</v>
-      </c>
-      <c r="G29" s="0">
-        <v>11.618069194742406</v>
       </c>
     </row>
     <row r="30">
@@ -5836,16 +6079,19 @@
         <v>8</v>
       </c>
       <c r="D30" s="0">
-        <v>132.58000000000001</v>
+        <v>6230</v>
       </c>
       <c r="E30" s="0">
+        <v>100</v>
+      </c>
+      <c r="F30" s="0">
+        <v>1.6051364365971106</v>
+      </c>
+      <c r="G30" s="0">
+        <v>122.59999999999999</v>
+      </c>
+      <c r="H30" s="0">
         <v>119.59999999999999</v>
-      </c>
-      <c r="F30" s="0">
-        <v>12.980000000000018</v>
-      </c>
-      <c r="G30" s="0">
-        <v>9.7903152813395806</v>
       </c>
     </row>
     <row r="31">
@@ -5859,16 +6105,19 @@
         <v>9</v>
       </c>
       <c r="D31" s="0">
-        <v>132.58000000000001</v>
+        <v>6230</v>
       </c>
       <c r="E31" s="0">
+        <v>630</v>
+      </c>
+      <c r="F31" s="0">
+        <v>10.112359550561797</v>
+      </c>
+      <c r="G31" s="0">
+        <v>112</v>
+      </c>
+      <c r="H31" s="0">
         <v>91.200000000000003</v>
-      </c>
-      <c r="F31" s="0">
-        <v>41.38000000000001</v>
-      </c>
-      <c r="G31" s="0">
-        <v>31.211344094131849</v>
       </c>
     </row>
     <row r="32">
@@ -5882,16 +6131,19 @@
         <v>8</v>
       </c>
       <c r="D32" s="0">
-        <v>186.58000000000001</v>
+        <v>8530</v>
       </c>
       <c r="E32" s="0">
+        <v>160</v>
+      </c>
+      <c r="F32" s="0">
+        <v>1.8757327080890971</v>
+      </c>
+      <c r="G32" s="0">
+        <v>167.40000000000001</v>
+      </c>
+      <c r="H32" s="0">
         <v>164.40000000000001</v>
-      </c>
-      <c r="F32" s="0">
-        <v>22.180000000000007</v>
-      </c>
-      <c r="G32" s="0">
-        <v>11.887662128845539</v>
       </c>
     </row>
     <row r="33">
@@ -5905,16 +6157,19 @@
         <v>9</v>
       </c>
       <c r="D33" s="0">
-        <v>186.58000000000001</v>
+        <v>8530</v>
       </c>
       <c r="E33" s="0">
+        <v>140</v>
+      </c>
+      <c r="F33" s="0">
+        <v>1.6412661195779603</v>
+      </c>
+      <c r="G33" s="0">
+        <v>167.80000000000001</v>
+      </c>
+      <c r="H33" s="0">
         <v>164.80000000000001</v>
-      </c>
-      <c r="F33" s="0">
-        <v>21.780000000000001</v>
-      </c>
-      <c r="G33" s="0">
-        <v>11.673276878550755</v>
       </c>
     </row>
     <row r="34">
@@ -5928,16 +6183,19 @@
         <v>8</v>
       </c>
       <c r="D34" s="0">
-        <v>142.78</v>
+        <v>6440</v>
       </c>
       <c r="E34" s="0">
+        <v>210</v>
+      </c>
+      <c r="F34" s="0">
+        <v>3.2608695652173911</v>
+      </c>
+      <c r="G34" s="0">
+        <v>124.59999999999999</v>
+      </c>
+      <c r="H34" s="0">
         <v>121.59999999999999</v>
-      </c>
-      <c r="F34" s="0">
-        <v>21.180000000000007</v>
-      </c>
-      <c r="G34" s="0">
-        <v>14.834010365597429</v>
       </c>
     </row>
     <row r="35">
@@ -5951,16 +6209,19 @@
         <v>9</v>
       </c>
       <c r="D35" s="0">
-        <v>142.78</v>
+        <v>6440</v>
       </c>
       <c r="E35" s="0">
+        <v>100</v>
+      </c>
+      <c r="F35" s="0">
+        <v>1.5527950310559007</v>
+      </c>
+      <c r="G35" s="0">
+        <v>126.8</v>
+      </c>
+      <c r="H35" s="0">
         <v>123.8</v>
-      </c>
-      <c r="F35" s="0">
-        <v>18.980000000000004</v>
-      </c>
-      <c r="G35" s="0">
-        <v>13.293178316290801</v>
       </c>
     </row>
     <row r="36">
@@ -5974,16 +6235,19 @@
         <v>8</v>
       </c>
       <c r="D36" s="0">
-        <v>179.78</v>
+        <v>7990</v>
       </c>
       <c r="E36" s="0">
+        <v>170</v>
+      </c>
+      <c r="F36" s="0">
+        <v>2.1276595744680851</v>
+      </c>
+      <c r="G36" s="0">
+        <v>156.40000000000001</v>
+      </c>
+      <c r="H36" s="0">
         <v>146.40000000000001</v>
-      </c>
-      <c r="F36" s="0">
-        <v>33.379999999999995</v>
-      </c>
-      <c r="G36" s="0">
-        <v>18.567137612637666</v>
       </c>
     </row>
     <row r="37">
@@ -5997,16 +6261,19 @@
         <v>9</v>
       </c>
       <c r="D37" s="0">
-        <v>179.78</v>
+        <v>7990</v>
       </c>
       <c r="E37" s="0">
+        <v>160</v>
+      </c>
+      <c r="F37" s="0">
+        <v>2.002503128911139</v>
+      </c>
+      <c r="G37" s="0">
+        <v>156.59999999999999</v>
+      </c>
+      <c r="H37" s="0">
         <v>146.40000000000001</v>
-      </c>
-      <c r="F37" s="0">
-        <v>33.379999999999995</v>
-      </c>
-      <c r="G37" s="0">
-        <v>18.567137612637666</v>
       </c>
     </row>
     <row r="38">
@@ -6020,16 +6287,19 @@
         <v>8</v>
       </c>
       <c r="D38" s="0">
-        <v>237.97999999999999</v>
+        <v>11200</v>
       </c>
       <c r="E38" s="0">
+        <v>10</v>
+      </c>
+      <c r="F38" s="0">
+        <v>0.089285714285714288</v>
+      </c>
+      <c r="G38" s="0">
+        <v>223.80000000000001</v>
+      </c>
+      <c r="H38" s="0">
         <v>220.80000000000001</v>
-      </c>
-      <c r="F38" s="0">
-        <v>17.179999999999978</v>
-      </c>
-      <c r="G38" s="0">
-        <v>7.2190940415160849</v>
       </c>
     </row>
     <row r="39">
@@ -6043,16 +6313,19 @@
         <v>9</v>
       </c>
       <c r="D39" s="0">
-        <v>237.97999999999999</v>
+        <v>11200</v>
       </c>
       <c r="E39" s="0">
+        <v>50</v>
+      </c>
+      <c r="F39" s="0">
+        <v>0.4464285714285714</v>
+      </c>
+      <c r="G39" s="0">
+        <v>223</v>
+      </c>
+      <c r="H39" s="0">
         <v>220.19999999999999</v>
-      </c>
-      <c r="F39" s="0">
-        <v>17.780000000000001</v>
-      </c>
-      <c r="G39" s="0">
-        <v>7.471216068577192</v>
       </c>
     </row>
     <row r="40">
@@ -6066,16 +6339,19 @@
         <v>8</v>
       </c>
       <c r="D40" s="0">
-        <v>153.38</v>
+        <v>7270</v>
       </c>
       <c r="E40" s="0">
+        <v>230</v>
+      </c>
+      <c r="F40" s="0">
+        <v>3.1636863823933976</v>
+      </c>
+      <c r="G40" s="0">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="H40" s="0">
         <v>136.59999999999999</v>
-      </c>
-      <c r="F40" s="0">
-        <v>16.780000000000001</v>
-      </c>
-      <c r="G40" s="0">
-        <v>10.940148650410745</v>
       </c>
     </row>
     <row r="41">
@@ -6089,16 +6365,19 @@
         <v>9</v>
       </c>
       <c r="D41" s="0">
-        <v>153.38</v>
+        <v>7270</v>
       </c>
       <c r="E41" s="0">
+        <v>390</v>
+      </c>
+      <c r="F41" s="0">
+        <v>5.3645116918844566</v>
+      </c>
+      <c r="G41" s="0">
+        <v>137.59999999999999</v>
+      </c>
+      <c r="H41" s="0">
         <v>134.80000000000001</v>
-      </c>
-      <c r="F41" s="0">
-        <v>18.579999999999984</v>
-      </c>
-      <c r="G41" s="0">
-        <v>12.113704524709862</v>
       </c>
     </row>
     <row r="42">
@@ -6112,16 +6391,19 @@
         <v>8</v>
       </c>
       <c r="D42" s="0">
-        <v>165.18000000000001</v>
+        <v>7960</v>
       </c>
       <c r="E42" s="0">
+        <v>240</v>
+      </c>
+      <c r="F42" s="0">
+        <v>3.0150753768844218</v>
+      </c>
+      <c r="G42" s="0">
+        <v>154.40000000000001</v>
+      </c>
+      <c r="H42" s="0">
         <v>151.40000000000001</v>
-      </c>
-      <c r="F42" s="0">
-        <v>13.780000000000001</v>
-      </c>
-      <c r="G42" s="0">
-        <v>8.342414335876013</v>
       </c>
     </row>
     <row r="43">
@@ -6135,16 +6417,19 @@
         <v>9</v>
       </c>
       <c r="D43" s="0">
-        <v>165.18000000000001</v>
+        <v>7960</v>
       </c>
       <c r="E43" s="0">
+        <v>550</v>
+      </c>
+      <c r="F43" s="0">
+        <v>6.9095477386934672</v>
+      </c>
+      <c r="G43" s="0">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="H43" s="0">
         <v>141</v>
-      </c>
-      <c r="F43" s="0">
-        <v>24.180000000000007</v>
-      </c>
-      <c r="G43" s="0">
-        <v>14.638576098801312</v>
       </c>
     </row>
     <row r="44">
@@ -6158,16 +6443,19 @@
         <v>8</v>
       </c>
       <c r="D44" s="0">
-        <v>160.58000000000001</v>
+        <v>6930</v>
       </c>
       <c r="E44" s="0">
+        <v>540</v>
+      </c>
+      <c r="F44" s="0">
+        <v>7.7922077922077921</v>
+      </c>
+      <c r="G44" s="0">
+        <v>127.8</v>
+      </c>
+      <c r="H44" s="0">
         <v>105.8</v>
-      </c>
-      <c r="F44" s="0">
-        <v>54.780000000000015</v>
-      </c>
-      <c r="G44" s="0">
-        <v>34.113837339643801</v>
       </c>
     </row>
     <row r="45">
@@ -6181,16 +6469,19 @@
         <v>9</v>
       </c>
       <c r="D45" s="0">
-        <v>160.58000000000001</v>
+        <v>6930</v>
       </c>
       <c r="E45" s="0">
+        <v>30</v>
+      </c>
+      <c r="F45" s="0">
+        <v>0.4329004329004329</v>
+      </c>
+      <c r="G45" s="0">
+        <v>138</v>
+      </c>
+      <c r="H45" s="0">
         <v>135</v>
-      </c>
-      <c r="F45" s="0">
-        <v>25.580000000000013</v>
-      </c>
-      <c r="G45" s="0">
-        <v>15.929754639432065</v>
       </c>
     </row>
     <row r="46">
@@ -6204,16 +6495,19 @@
         <v>8</v>
       </c>
       <c r="D46" s="0">
-        <v>170.18000000000001</v>
+        <v>8210</v>
       </c>
       <c r="E46" s="0">
+        <v>350</v>
+      </c>
+      <c r="F46" s="0">
+        <v>4.2630937880633368</v>
+      </c>
+      <c r="G46" s="0">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="H46" s="0">
         <v>144</v>
-      </c>
-      <c r="F46" s="0">
-        <v>26.180000000000007</v>
-      </c>
-      <c r="G46" s="0">
-        <v>15.383711364437659</v>
       </c>
     </row>
     <row r="47">
@@ -6227,16 +6521,19 @@
         <v>9</v>
       </c>
       <c r="D47" s="0">
-        <v>170.18000000000001</v>
+        <v>8210</v>
       </c>
       <c r="E47" s="0">
+        <v>480</v>
+      </c>
+      <c r="F47" s="0">
+        <v>5.8465286236297196</v>
+      </c>
+      <c r="G47" s="0">
+        <v>154.59999999999999</v>
+      </c>
+      <c r="H47" s="0">
         <v>151.59999999999999</v>
-      </c>
-      <c r="F47" s="0">
-        <v>18.580000000000013</v>
-      </c>
-      <c r="G47" s="0">
-        <v>10.91785168644965</v>
       </c>
     </row>
     <row r="48">
@@ -6250,16 +6547,19 @@
         <v>8</v>
       </c>
       <c r="D48" s="0">
-        <v>123.98</v>
+        <v>6000</v>
       </c>
       <c r="E48" s="0">
+        <v>150</v>
+      </c>
+      <c r="F48" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="G48" s="0">
+        <v>117</v>
+      </c>
+      <c r="H48" s="0">
         <v>112</v>
-      </c>
-      <c r="F48" s="0">
-        <v>11.980000000000004</v>
-      </c>
-      <c r="G48" s="0">
-        <v>9.6628488465881635</v>
       </c>
     </row>
     <row r="49">
@@ -6273,16 +6573,19 @@
         <v>9</v>
       </c>
       <c r="D49" s="0">
-        <v>123.98</v>
+        <v>6000</v>
       </c>
       <c r="E49" s="0">
+        <v>150</v>
+      </c>
+      <c r="F49" s="0">
+        <v>2.5</v>
+      </c>
+      <c r="G49" s="0">
+        <v>117</v>
+      </c>
+      <c r="H49" s="0">
         <v>112</v>
-      </c>
-      <c r="F49" s="0">
-        <v>11.980000000000004</v>
-      </c>
-      <c r="G49" s="0">
-        <v>9.6628488465881635</v>
       </c>
     </row>
     <row r="50">
@@ -6296,16 +6599,19 @@
         <v>8</v>
       </c>
       <c r="D50" s="0">
-        <v>123.38</v>
+        <v>5870</v>
       </c>
       <c r="E50" s="0">
+        <v>540</v>
+      </c>
+      <c r="F50" s="0">
+        <v>9.1993185689948902</v>
+      </c>
+      <c r="G50" s="0">
+        <v>106.59999999999999</v>
+      </c>
+      <c r="H50" s="0">
         <v>91.599999999999994</v>
-      </c>
-      <c r="F50" s="0">
-        <v>31.780000000000001</v>
-      </c>
-      <c r="G50" s="0">
-        <v>25.757821364888962</v>
       </c>
     </row>
     <row r="51">
@@ -6319,16 +6625,19 @@
         <v>9</v>
       </c>
       <c r="D51" s="0">
-        <v>123.38</v>
+        <v>5870</v>
       </c>
       <c r="E51" s="0">
+        <v>370</v>
+      </c>
+      <c r="F51" s="0">
+        <v>6.3032367972742751</v>
+      </c>
+      <c r="G51" s="0">
+        <v>110</v>
+      </c>
+      <c r="H51" s="0">
         <v>103.8</v>
-      </c>
-      <c r="F51" s="0">
-        <v>19.579999999999998</v>
-      </c>
-      <c r="G51" s="0">
-        <v>15.86967093532177</v>
       </c>
     </row>
     <row r="52">
@@ -6342,16 +6651,19 @@
         <v>8</v>
       </c>
       <c r="D52" s="0">
-        <v>130.38</v>
+        <v>6220</v>
       </c>
       <c r="E52" s="0">
+        <v>160</v>
+      </c>
+      <c r="F52" s="0">
+        <v>2.572347266881029</v>
+      </c>
+      <c r="G52" s="0">
+        <v>121.2</v>
+      </c>
+      <c r="H52" s="0">
         <v>116.2</v>
-      </c>
-      <c r="F52" s="0">
-        <v>14.179999999999993</v>
-      </c>
-      <c r="G52" s="0">
-        <v>10.875901211842303</v>
       </c>
     </row>
     <row r="53">
@@ -6365,16 +6677,19 @@
         <v>9</v>
       </c>
       <c r="D53" s="0">
-        <v>130.38</v>
+        <v>6220</v>
       </c>
       <c r="E53" s="0">
+        <v>90</v>
+      </c>
+      <c r="F53" s="0">
+        <v>1.4469453376205788</v>
+      </c>
+      <c r="G53" s="0">
+        <v>122.59999999999999</v>
+      </c>
+      <c r="H53" s="0">
         <v>117.40000000000001</v>
-      </c>
-      <c r="F53" s="0">
-        <v>12.97999999999999</v>
-      </c>
-      <c r="G53" s="0">
-        <v>9.9555146494861102</v>
       </c>
     </row>
     <row r="54">
@@ -6388,16 +6703,19 @@
         <v>8</v>
       </c>
       <c r="D54" s="0">
-        <v>116.78</v>
+        <v>5440</v>
       </c>
       <c r="E54" s="0">
+        <v>180</v>
+      </c>
+      <c r="F54" s="0">
+        <v>3.3088235294117649</v>
+      </c>
+      <c r="G54" s="0">
+        <v>105.2</v>
+      </c>
+      <c r="H54" s="0">
         <v>100.2</v>
-      </c>
-      <c r="F54" s="0">
-        <v>16.579999999999998</v>
-      </c>
-      <c r="G54" s="0">
-        <v>14.197636581606437</v>
       </c>
     </row>
     <row r="55">
@@ -6411,16 +6729,19 @@
         <v>9</v>
       </c>
       <c r="D55" s="0">
-        <v>116.78</v>
+        <v>5440</v>
       </c>
       <c r="E55" s="0">
+        <v>140</v>
+      </c>
+      <c r="F55" s="0">
+        <v>2.5735294117647056</v>
+      </c>
+      <c r="G55" s="0">
+        <v>106</v>
+      </c>
+      <c r="H55" s="0">
         <v>101</v>
-      </c>
-      <c r="F55" s="0">
-        <v>15.780000000000001</v>
-      </c>
-      <c r="G55" s="0">
-        <v>13.512587771878746</v>
       </c>
     </row>
     <row r="56">
@@ -6434,16 +6755,19 @@
         <v>8</v>
       </c>
       <c r="D56" s="0">
-        <v>118.78</v>
+        <v>5140</v>
       </c>
       <c r="E56" s="0">
+        <v>450</v>
+      </c>
+      <c r="F56" s="0">
+        <v>8.7548638132295711</v>
+      </c>
+      <c r="G56" s="0">
+        <v>93.799999999999997</v>
+      </c>
+      <c r="H56" s="0">
         <v>85.799999999999997</v>
-      </c>
-      <c r="F56" s="0">
-        <v>32.980000000000004</v>
-      </c>
-      <c r="G56" s="0">
-        <v>27.765617107257118</v>
       </c>
     </row>
     <row r="57">
@@ -6457,16 +6781,19 @@
         <v>9</v>
       </c>
       <c r="D57" s="0">
-        <v>118.78</v>
+        <v>5140</v>
       </c>
       <c r="E57" s="0">
+        <v>240</v>
+      </c>
+      <c r="F57" s="0">
+        <v>4.6692607003891053</v>
+      </c>
+      <c r="G57" s="0">
+        <v>98</v>
+      </c>
+      <c r="H57" s="0">
         <v>92.599999999999994</v>
-      </c>
-      <c r="F57" s="0">
-        <v>26.180000000000007</v>
-      </c>
-      <c r="G57" s="0">
-        <v>22.040747600606171</v>
       </c>
     </row>
     <row r="58">
@@ -6480,16 +6807,19 @@
         <v>8</v>
       </c>
       <c r="D58" s="0">
-        <v>117.78</v>
+        <v>5390</v>
       </c>
       <c r="E58" s="0">
+        <v>180</v>
+      </c>
+      <c r="F58" s="0">
+        <v>3.339517625231911</v>
+      </c>
+      <c r="G58" s="0">
+        <v>104.2</v>
+      </c>
+      <c r="H58" s="0">
         <v>99.200000000000003</v>
-      </c>
-      <c r="F58" s="0">
-        <v>18.579999999999998</v>
-      </c>
-      <c r="G58" s="0">
-        <v>15.775174053319747</v>
       </c>
     </row>
     <row r="59">
@@ -6503,16 +6833,19 @@
         <v>9</v>
       </c>
       <c r="D59" s="0">
-        <v>117.78</v>
+        <v>5390</v>
       </c>
       <c r="E59" s="0">
+        <v>260</v>
+      </c>
+      <c r="F59" s="0">
+        <v>4.8237476808905377</v>
+      </c>
+      <c r="G59" s="0">
+        <v>102.59999999999999</v>
+      </c>
+      <c r="H59" s="0">
         <v>96.200000000000003</v>
-      </c>
-      <c r="F59" s="0">
-        <v>21.579999999999998</v>
-      </c>
-      <c r="G59" s="0">
-        <v>18.322295805739515</v>
       </c>
     </row>
     <row r="60">
@@ -6526,16 +6859,19 @@
         <v>8</v>
       </c>
       <c r="D60" s="0">
-        <v>170.38</v>
+        <v>7120</v>
       </c>
       <c r="E60" s="0">
+        <v>290</v>
+      </c>
+      <c r="F60" s="0">
+        <v>4.0730337078651688</v>
+      </c>
+      <c r="G60" s="0">
+        <v>136.59999999999999</v>
+      </c>
+      <c r="H60" s="0">
         <v>133.80000000000001</v>
-      </c>
-      <c r="F60" s="0">
-        <v>36.579999999999984</v>
-      </c>
-      <c r="G60" s="0">
-        <v>21.469656062918173</v>
       </c>
     </row>
     <row r="61">
@@ -6549,16 +6885,19 @@
         <v>9</v>
       </c>
       <c r="D61" s="0">
-        <v>170.38</v>
+        <v>7120</v>
       </c>
       <c r="E61" s="0">
+        <v>90</v>
+      </c>
+      <c r="F61" s="0">
+        <v>1.2640449438202246</v>
+      </c>
+      <c r="G61" s="0">
+        <v>140.59999999999999</v>
+      </c>
+      <c r="H61" s="0">
         <v>137.80000000000001</v>
-      </c>
-      <c r="F61" s="0">
-        <v>32.579999999999984</v>
-      </c>
-      <c r="G61" s="0">
-        <v>19.121962671675067</v>
       </c>
     </row>
     <row r="62">
@@ -6572,16 +6911,19 @@
         <v>8</v>
       </c>
       <c r="D62" s="0">
-        <v>175.38</v>
+        <v>8470</v>
       </c>
       <c r="E62" s="0">
+        <v>150</v>
+      </c>
+      <c r="F62" s="0">
+        <v>1.7709563164108619</v>
+      </c>
+      <c r="G62" s="0">
+        <v>166.40000000000001</v>
+      </c>
+      <c r="H62" s="0">
         <v>163.40000000000001</v>
-      </c>
-      <c r="F62" s="0">
-        <v>11.97999999999999</v>
-      </c>
-      <c r="G62" s="0">
-        <v>6.8308815144258128</v>
       </c>
     </row>
     <row r="63">
@@ -6595,16 +6937,19 @@
         <v>9</v>
       </c>
       <c r="D63" s="0">
-        <v>175.38</v>
+        <v>8470</v>
       </c>
       <c r="E63" s="0">
+        <v>180</v>
+      </c>
+      <c r="F63" s="0">
+        <v>2.1251475796930341</v>
+      </c>
+      <c r="G63" s="0">
+        <v>165.80000000000001</v>
+      </c>
+      <c r="H63" s="0">
         <v>162.80000000000001</v>
-      </c>
-      <c r="F63" s="0">
-        <v>12.579999999999984</v>
-      </c>
-      <c r="G63" s="0">
-        <v>7.1729957805907087</v>
       </c>
     </row>
     <row r="64">
@@ -6618,16 +6963,19 @@
         <v>8</v>
       </c>
       <c r="D64" s="0">
-        <v>157.78</v>
+        <v>7290</v>
       </c>
       <c r="E64" s="0">
+        <v>100</v>
+      </c>
+      <c r="F64" s="0">
+        <v>1.3717421124828533</v>
+      </c>
+      <c r="G64" s="0">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="H64" s="0">
         <v>138</v>
-      </c>
-      <c r="F64" s="0">
-        <v>19.780000000000001</v>
-      </c>
-      <c r="G64" s="0">
-        <v>12.536443148688047</v>
       </c>
     </row>
     <row r="65">
@@ -6641,16 +6989,19 @@
         <v>9</v>
       </c>
       <c r="D65" s="0">
-        <v>157.78</v>
+        <v>7290</v>
       </c>
       <c r="E65" s="0">
+        <v>70</v>
+      </c>
+      <c r="F65" s="0">
+        <v>0.96021947873799729</v>
+      </c>
+      <c r="G65" s="0">
+        <v>144.40000000000001</v>
+      </c>
+      <c r="H65" s="0">
         <v>141.40000000000001</v>
-      </c>
-      <c r="F65" s="0">
-        <v>16.379999999999995</v>
-      </c>
-      <c r="G65" s="0">
-        <v>10.38154392191659</v>
       </c>
     </row>
     <row r="66">
@@ -6664,16 +7015,19 @@
         <v>8</v>
       </c>
       <c r="D66" s="0">
-        <v>180.58000000000001</v>
+        <v>8030</v>
       </c>
       <c r="E66" s="0">
+        <v>340</v>
+      </c>
+      <c r="F66" s="0">
+        <v>4.2341220423412205</v>
+      </c>
+      <c r="G66" s="0">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="H66" s="0">
         <v>150.80000000000001</v>
-      </c>
-      <c r="F66" s="0">
-        <v>29.780000000000001</v>
-      </c>
-      <c r="G66" s="0">
-        <v>16.49130579244656</v>
       </c>
     </row>
     <row r="67">
@@ -6687,16 +7041,19 @@
         <v>9</v>
       </c>
       <c r="D67" s="0">
-        <v>180.58000000000001</v>
+        <v>8030</v>
       </c>
       <c r="E67" s="0">
+        <v>420</v>
+      </c>
+      <c r="F67" s="0">
+        <v>5.230386052303861</v>
+      </c>
+      <c r="G67" s="0">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="H67" s="0">
         <v>143</v>
-      </c>
-      <c r="F67" s="0">
-        <v>37.580000000000013</v>
-      </c>
-      <c r="G67" s="0">
-        <v>20.810721010078641</v>
       </c>
     </row>
     <row r="68">
@@ -6710,16 +7067,19 @@
         <v>8</v>
       </c>
       <c r="D68" s="0">
-        <v>128.78</v>
+        <v>6040</v>
       </c>
       <c r="E68" s="0">
+        <v>120</v>
+      </c>
+      <c r="F68" s="0">
+        <v>1.9867549668874174</v>
+      </c>
+      <c r="G68" s="0">
+        <v>118.40000000000001</v>
+      </c>
+      <c r="H68" s="0">
         <v>115.2</v>
-      </c>
-      <c r="F68" s="0">
-        <v>13.579999999999998</v>
-      </c>
-      <c r="G68" s="0">
-        <v>10.545115701195837</v>
       </c>
     </row>
     <row r="69">
@@ -6733,16 +7093,19 @@
         <v>9</v>
       </c>
       <c r="D69" s="0">
-        <v>128.78</v>
+        <v>6040</v>
       </c>
       <c r="E69" s="0">
+        <v>410</v>
+      </c>
+      <c r="F69" s="0">
+        <v>6.7880794701986753</v>
+      </c>
+      <c r="G69" s="0">
+        <v>112.59999999999999</v>
+      </c>
+      <c r="H69" s="0">
         <v>101.8</v>
-      </c>
-      <c r="F69" s="0">
-        <v>26.980000000000004</v>
-      </c>
-      <c r="G69" s="0">
-        <v>20.950458145674798</v>
       </c>
     </row>
     <row r="70">
@@ -6756,16 +7119,19 @@
         <v>8</v>
       </c>
       <c r="D70" s="0">
-        <v>120.78</v>
+        <v>5540</v>
       </c>
       <c r="E70" s="0">
+        <v>340</v>
+      </c>
+      <c r="F70" s="0">
+        <v>6.1371841155234659</v>
+      </c>
+      <c r="G70" s="0">
+        <v>104</v>
+      </c>
+      <c r="H70" s="0">
         <v>101.2</v>
-      </c>
-      <c r="F70" s="0">
-        <v>19.579999999999998</v>
-      </c>
-      <c r="G70" s="0">
-        <v>16.211293260473585</v>
       </c>
     </row>
     <row r="71">
@@ -6779,16 +7145,19 @@
         <v>9</v>
       </c>
       <c r="D71" s="0">
-        <v>120.78</v>
+        <v>5540</v>
       </c>
       <c r="E71" s="0">
+        <v>410</v>
+      </c>
+      <c r="F71" s="0">
+        <v>7.4007220216606493</v>
+      </c>
+      <c r="G71" s="0">
+        <v>102.59999999999999</v>
+      </c>
+      <c r="H71" s="0">
         <v>95.799999999999997</v>
-      </c>
-      <c r="F71" s="0">
-        <v>24.980000000000004</v>
-      </c>
-      <c r="G71" s="0">
-        <v>20.682232157641998</v>
       </c>
     </row>
     <row r="72">
@@ -6802,16 +7171,19 @@
         <v>8</v>
       </c>
       <c r="D72" s="0">
-        <v>136.58000000000001</v>
+        <v>6230</v>
       </c>
       <c r="E72" s="0">
+        <v>120</v>
+      </c>
+      <c r="F72" s="0">
+        <v>1.9261637239165328</v>
+      </c>
+      <c r="G72" s="0">
+        <v>122.2</v>
+      </c>
+      <c r="H72" s="0">
         <v>119.2</v>
-      </c>
-      <c r="F72" s="0">
-        <v>17.38000000000001</v>
-      </c>
-      <c r="G72" s="0">
-        <v>12.725142773466105</v>
       </c>
     </row>
     <row r="73">
@@ -6825,16 +7197,19 @@
         <v>9</v>
       </c>
       <c r="D73" s="0">
-        <v>136.58000000000001</v>
+        <v>6230</v>
       </c>
       <c r="E73" s="0">
+        <v>200</v>
+      </c>
+      <c r="F73" s="0">
+        <v>3.2102728731942212</v>
+      </c>
+      <c r="G73" s="0">
+        <v>120.59999999999999</v>
+      </c>
+      <c r="H73" s="0">
         <v>113.8</v>
-      </c>
-      <c r="F73" s="0">
-        <v>22.780000000000015</v>
-      </c>
-      <c r="G73" s="0">
-        <v>16.678869527017142</v>
       </c>
     </row>
     <row r="74">
@@ -6848,16 +7223,19 @@
         <v>8</v>
       </c>
       <c r="D74" s="0">
-        <v>122.38</v>
+        <v>5820</v>
       </c>
       <c r="E74" s="0">
+        <v>440</v>
+      </c>
+      <c r="F74" s="0">
+        <v>7.5601374570446733</v>
+      </c>
+      <c r="G74" s="0">
+        <v>107.59999999999999</v>
+      </c>
+      <c r="H74" s="0">
         <v>104.8</v>
-      </c>
-      <c r="F74" s="0">
-        <v>17.579999999999998</v>
-      </c>
-      <c r="G74" s="0">
-        <v>14.365092335348912</v>
       </c>
     </row>
     <row r="75">
@@ -6871,16 +7249,19 @@
         <v>9</v>
       </c>
       <c r="D75" s="0">
-        <v>122.38</v>
+        <v>5820</v>
       </c>
       <c r="E75" s="0">
+        <v>400</v>
+      </c>
+      <c r="F75" s="0">
+        <v>6.8728522336769764</v>
+      </c>
+      <c r="G75" s="0">
+        <v>108.40000000000001</v>
+      </c>
+      <c r="H75" s="0">
         <v>103.59999999999999</v>
-      </c>
-      <c r="F75" s="0">
-        <v>18.780000000000001</v>
-      </c>
-      <c r="G75" s="0">
-        <v>15.345644713188429</v>
       </c>
     </row>
     <row r="76">
@@ -6894,16 +7275,19 @@
         <v>8</v>
       </c>
       <c r="D76" s="0">
-        <v>144.78</v>
+        <v>6740</v>
       </c>
       <c r="E76" s="0">
+        <v>150</v>
+      </c>
+      <c r="F76" s="0">
+        <v>2.2255192878338281</v>
+      </c>
+      <c r="G76" s="0">
+        <v>131.80000000000001</v>
+      </c>
+      <c r="H76" s="0">
         <v>128.80000000000001</v>
-      </c>
-      <c r="F76" s="0">
-        <v>15.97999999999999</v>
-      </c>
-      <c r="G76" s="0">
-        <v>11.037436109959932</v>
       </c>
     </row>
     <row r="77">
@@ -6917,16 +7301,19 @@
         <v>9</v>
       </c>
       <c r="D77" s="0">
-        <v>144.78</v>
+        <v>6740</v>
       </c>
       <c r="E77" s="0">
+        <v>130</v>
+      </c>
+      <c r="F77" s="0">
+        <v>1.9287833827893175</v>
+      </c>
+      <c r="G77" s="0">
+        <v>132.19999999999999</v>
+      </c>
+      <c r="H77" s="0">
         <v>129.19999999999999</v>
-      </c>
-      <c r="F77" s="0">
-        <v>15.580000000000013</v>
-      </c>
-      <c r="G77" s="0">
-        <v>10.761154855643055</v>
       </c>
     </row>
     <row r="78">
@@ -6940,16 +7327,19 @@
         <v>8</v>
       </c>
       <c r="D78" s="0">
-        <v>122.58</v>
+        <v>5930</v>
       </c>
       <c r="E78" s="0">
+        <v>600</v>
+      </c>
+      <c r="F78" s="0">
+        <v>10.118043844856661</v>
+      </c>
+      <c r="G78" s="0">
+        <v>106.59999999999999</v>
+      </c>
+      <c r="H78" s="0">
         <v>103.59999999999999</v>
-      </c>
-      <c r="F78" s="0">
-        <v>18.980000000000004</v>
-      </c>
-      <c r="G78" s="0">
-        <v>15.483765704030025</v>
       </c>
     </row>
     <row r="79">
@@ -6963,16 +7353,19 @@
         <v>9</v>
       </c>
       <c r="D79" s="0">
-        <v>122.58</v>
+        <v>5930</v>
       </c>
       <c r="E79" s="0">
+        <v>440</v>
+      </c>
+      <c r="F79" s="0">
+        <v>7.4198988195615518</v>
+      </c>
+      <c r="G79" s="0">
+        <v>109.8</v>
+      </c>
+      <c r="H79" s="0">
         <v>106.8</v>
-      </c>
-      <c r="F79" s="0">
-        <v>15.780000000000001</v>
-      </c>
-      <c r="G79" s="0">
-        <v>12.873225648556046</v>
       </c>
     </row>
     <row r="80">
@@ -6986,16 +7379,19 @@
         <v>8</v>
       </c>
       <c r="D80" s="0">
-        <v>142.97999999999999</v>
+        <v>6850</v>
       </c>
       <c r="E80" s="0">
+        <v>120</v>
+      </c>
+      <c r="F80" s="0">
+        <v>1.7518248175182483</v>
+      </c>
+      <c r="G80" s="0">
+        <v>134.59999999999999</v>
+      </c>
+      <c r="H80" s="0">
         <v>131.59999999999999</v>
-      </c>
-      <c r="F80" s="0">
-        <v>11.379999999999995</v>
-      </c>
-      <c r="G80" s="0">
-        <v>7.9591551265911287</v>
       </c>
     </row>
     <row r="81">
@@ -7009,16 +7405,19 @@
         <v>9</v>
       </c>
       <c r="D81" s="0">
-        <v>142.97999999999999</v>
+        <v>6850</v>
       </c>
       <c r="E81" s="0">
+        <v>50</v>
+      </c>
+      <c r="F81" s="0">
+        <v>0.72992700729927007</v>
+      </c>
+      <c r="G81" s="0">
+        <v>136</v>
+      </c>
+      <c r="H81" s="0">
         <v>132</v>
-      </c>
-      <c r="F81" s="0">
-        <v>10.97999999999999</v>
-      </c>
-      <c r="G81" s="0">
-        <v>7.679395719681068</v>
       </c>
     </row>
     <row r="82">
@@ -7032,16 +7431,19 @@
         <v>8</v>
       </c>
       <c r="D82" s="0">
-        <v>119.18000000000001</v>
+        <v>5660</v>
       </c>
       <c r="E82" s="0">
+        <v>130</v>
+      </c>
+      <c r="F82" s="0">
+        <v>2.2968197879858656</v>
+      </c>
+      <c r="G82" s="0">
+        <v>110.59999999999999</v>
+      </c>
+      <c r="H82" s="0">
         <v>107.59999999999999</v>
-      </c>
-      <c r="F82" s="0">
-        <v>11.580000000000013</v>
-      </c>
-      <c r="G82" s="0">
-        <v>9.7163953683504047</v>
       </c>
     </row>
     <row r="83">
@@ -7055,16 +7457,19 @@
         <v>9</v>
       </c>
       <c r="D83" s="0">
-        <v>119.18000000000001</v>
+        <v>5660</v>
       </c>
       <c r="E83" s="0">
+        <v>190</v>
+      </c>
+      <c r="F83" s="0">
+        <v>3.3568904593639579</v>
+      </c>
+      <c r="G83" s="0">
+        <v>109.40000000000001</v>
+      </c>
+      <c r="H83" s="0">
         <v>106.59999999999999</v>
-      </c>
-      <c r="F83" s="0">
-        <v>12.580000000000013</v>
-      </c>
-      <c r="G83" s="0">
-        <v>10.555462325893616</v>
       </c>
     </row>
     <row r="84">
@@ -7078,16 +7483,19 @@
         <v>8</v>
       </c>
       <c r="D84" s="0">
-        <v>124.78</v>
+        <v>5640</v>
       </c>
       <c r="E84" s="0">
+        <v>760</v>
+      </c>
+      <c r="F84" s="0">
+        <v>13.475177304964539</v>
+      </c>
+      <c r="G84" s="0">
+        <v>97.599999999999994</v>
+      </c>
+      <c r="H84" s="0">
         <v>89.400000000000006</v>
-      </c>
-      <c r="F84" s="0">
-        <v>35.379999999999995</v>
-      </c>
-      <c r="G84" s="0">
-        <v>28.353902869049524</v>
       </c>
     </row>
     <row r="85">
@@ -7101,16 +7509,19 @@
         <v>9</v>
       </c>
       <c r="D85" s="0">
-        <v>124.78</v>
+        <v>5640</v>
       </c>
       <c r="E85" s="0">
+        <v>570</v>
+      </c>
+      <c r="F85" s="0">
+        <v>10.106382978723403</v>
+      </c>
+      <c r="G85" s="0">
+        <v>101.40000000000001</v>
+      </c>
+      <c r="H85" s="0">
         <v>92.400000000000006</v>
-      </c>
-      <c r="F85" s="0">
-        <v>32.379999999999995</v>
-      </c>
-      <c r="G85" s="0">
-        <v>25.949671421702192</v>
       </c>
     </row>
     <row r="86">
@@ -7124,16 +7535,19 @@
         <v>8</v>
       </c>
       <c r="D86" s="0">
-        <v>127.38</v>
+        <v>5770</v>
       </c>
       <c r="E86" s="0">
+        <v>170</v>
+      </c>
+      <c r="F86" s="0">
+        <v>2.9462738301559792</v>
+      </c>
+      <c r="G86" s="0">
+        <v>112</v>
+      </c>
+      <c r="H86" s="0">
         <v>107</v>
-      </c>
-      <c r="F86" s="0">
-        <v>20.379999999999995</v>
-      </c>
-      <c r="G86" s="0">
-        <v>15.999371957921177</v>
       </c>
     </row>
     <row r="87">
@@ -7147,16 +7561,19 @@
         <v>9</v>
       </c>
       <c r="D87" s="0">
-        <v>127.38</v>
+        <v>5770</v>
       </c>
       <c r="E87" s="0">
+        <v>470</v>
+      </c>
+      <c r="F87" s="0">
+        <v>8.1455805892547666</v>
+      </c>
+      <c r="G87" s="0">
+        <v>106</v>
+      </c>
+      <c r="H87" s="0">
         <v>96.200000000000003</v>
-      </c>
-      <c r="F87" s="0">
-        <v>31.179999999999993</v>
-      </c>
-      <c r="G87" s="0">
-        <v>24.477940021981468</v>
       </c>
     </row>
     <row r="88">
@@ -7170,16 +7587,19 @@
         <v>8</v>
       </c>
       <c r="D88" s="0">
-        <v>143.38</v>
+        <v>6870</v>
       </c>
       <c r="E88" s="0">
+        <v>100</v>
+      </c>
+      <c r="F88" s="0">
+        <v>1.4556040756914119</v>
+      </c>
+      <c r="G88" s="0">
+        <v>135.40000000000001</v>
+      </c>
+      <c r="H88" s="0">
         <v>130.40000000000001</v>
-      </c>
-      <c r="F88" s="0">
-        <v>12.97999999999999</v>
-      </c>
-      <c r="G88" s="0">
-        <v>9.052866508578596</v>
       </c>
     </row>
     <row r="89">
@@ -7193,16 +7613,19 @@
         <v>9</v>
       </c>
       <c r="D89" s="0">
-        <v>143.38</v>
+        <v>6870</v>
       </c>
       <c r="E89" s="0">
+        <v>320</v>
+      </c>
+      <c r="F89" s="0">
+        <v>4.6579330422125187</v>
+      </c>
+      <c r="G89" s="0">
+        <v>131</v>
+      </c>
+      <c r="H89" s="0">
         <v>128</v>
-      </c>
-      <c r="F89" s="0">
-        <v>15.379999999999995</v>
-      </c>
-      <c r="G89" s="0">
-        <v>10.726740131120097</v>
       </c>
     </row>
     <row r="90">
@@ -7216,16 +7639,19 @@
         <v>8</v>
       </c>
       <c r="D90" s="0">
-        <v>188.18000000000001</v>
+        <v>9210</v>
       </c>
       <c r="E90" s="0">
+        <v>170</v>
+      </c>
+      <c r="F90" s="0">
+        <v>1.8458197611292075</v>
+      </c>
+      <c r="G90" s="0">
+        <v>180.80000000000001</v>
+      </c>
+      <c r="H90" s="0">
         <v>177.80000000000001</v>
-      </c>
-      <c r="F90" s="0">
-        <v>10.379999999999995</v>
-      </c>
-      <c r="G90" s="0">
-        <v>5.5159953236263126</v>
       </c>
     </row>
     <row r="91">
@@ -7239,16 +7665,19 @@
         <v>9</v>
       </c>
       <c r="D91" s="0">
-        <v>188.18000000000001</v>
+        <v>9210</v>
       </c>
       <c r="E91" s="0">
+        <v>20</v>
+      </c>
+      <c r="F91" s="0">
+        <v>0.21715526601520088</v>
+      </c>
+      <c r="G91" s="0">
+        <v>183.80000000000001</v>
+      </c>
+      <c r="H91" s="0">
         <v>180.80000000000001</v>
-      </c>
-      <c r="F91" s="0">
-        <v>7.3799999999999955</v>
-      </c>
-      <c r="G91" s="0">
-        <v>3.9217770220002102</v>
       </c>
     </row>
     <row r="92">
@@ -7262,16 +7691,19 @@
         <v>8</v>
       </c>
       <c r="D92" s="0">
-        <v>147.58000000000001</v>
+        <v>6980</v>
       </c>
       <c r="E92" s="0">
+        <v>370</v>
+      </c>
+      <c r="F92" s="0">
+        <v>5.3008595988538678</v>
+      </c>
+      <c r="G92" s="0">
+        <v>132.19999999999999</v>
+      </c>
+      <c r="H92" s="0">
         <v>118.8</v>
-      </c>
-      <c r="F92" s="0">
-        <v>28.780000000000015</v>
-      </c>
-      <c r="G92" s="0">
-        <v>19.501287437322137</v>
       </c>
     </row>
     <row r="93">
@@ -7285,16 +7717,19 @@
         <v>9</v>
       </c>
       <c r="D93" s="0">
-        <v>147.58000000000001</v>
+        <v>6980</v>
       </c>
       <c r="E93" s="0">
+        <v>420</v>
+      </c>
+      <c r="F93" s="0">
+        <v>6.0171919770773634</v>
+      </c>
+      <c r="G93" s="0">
+        <v>131.19999999999999</v>
+      </c>
+      <c r="H93" s="0">
         <v>118</v>
-      </c>
-      <c r="F93" s="0">
-        <v>29.580000000000013</v>
-      </c>
-      <c r="G93" s="0">
-        <v>20.043366309798085</v>
       </c>
     </row>
     <row r="94">
@@ -7308,16 +7743,19 @@
         <v>8</v>
       </c>
       <c r="D94" s="0">
-        <v>189.97999999999999</v>
+        <v>7820</v>
       </c>
       <c r="E94" s="0">
+        <v>2000</v>
+      </c>
+      <c r="F94" s="0">
+        <v>25.575447570332482</v>
+      </c>
+      <c r="G94" s="0">
+        <v>116.40000000000001</v>
+      </c>
+      <c r="H94" s="0">
         <v>107.2</v>
-      </c>
-      <c r="F94" s="0">
-        <v>82.779999999999987</v>
-      </c>
-      <c r="G94" s="0">
-        <v>43.573007685019469</v>
       </c>
     </row>
     <row r="95">
@@ -7331,16 +7769,19 @@
         <v>9</v>
       </c>
       <c r="D95" s="0">
-        <v>189.97999999999999</v>
+        <v>7820</v>
       </c>
       <c r="E95" s="0">
+        <v>2230</v>
+      </c>
+      <c r="F95" s="0">
+        <v>28.516624040920718</v>
+      </c>
+      <c r="G95" s="0">
+        <v>111.8</v>
+      </c>
+      <c r="H95" s="0">
         <v>106.40000000000001</v>
-      </c>
-      <c r="F95" s="0">
-        <v>83.579999999999984</v>
-      </c>
-      <c r="G95" s="0">
-        <v>43.994104642593953</v>
       </c>
     </row>
     <row r="96">
@@ -7354,16 +7795,19 @@
         <v>8</v>
       </c>
       <c r="D96" s="0">
-        <v>140.97999999999999</v>
+        <v>6750</v>
       </c>
       <c r="E96" s="0">
+        <v>110</v>
+      </c>
+      <c r="F96" s="0">
+        <v>1.6296296296296295</v>
+      </c>
+      <c r="G96" s="0">
+        <v>132.80000000000001</v>
+      </c>
+      <c r="H96" s="0">
         <v>130</v>
-      </c>
-      <c r="F96" s="0">
-        <v>10.97999999999999</v>
-      </c>
-      <c r="G96" s="0">
-        <v>7.7883387714569388</v>
       </c>
     </row>
     <row r="97">
@@ -7377,16 +7821,19 @@
         <v>9</v>
       </c>
       <c r="D97" s="0">
-        <v>140.97999999999999</v>
+        <v>6750</v>
       </c>
       <c r="E97" s="0">
+        <v>160</v>
+      </c>
+      <c r="F97" s="0">
+        <v>2.3703703703703702</v>
+      </c>
+      <c r="G97" s="0">
+        <v>131.80000000000001</v>
+      </c>
+      <c r="H97" s="0">
         <v>129</v>
-      </c>
-      <c r="F97" s="0">
-        <v>11.97999999999999</v>
-      </c>
-      <c r="G97" s="0">
-        <v>8.4976592424457316</v>
       </c>
     </row>
     <row r="98">
@@ -7400,16 +7847,19 @@
         <v>8</v>
       </c>
       <c r="D98" s="0">
-        <v>119.58</v>
+        <v>5480</v>
       </c>
       <c r="E98" s="0">
+        <v>80</v>
+      </c>
+      <c r="F98" s="0">
+        <v>1.4598540145985401</v>
+      </c>
+      <c r="G98" s="0">
+        <v>108</v>
+      </c>
+      <c r="H98" s="0">
         <v>105</v>
-      </c>
-      <c r="F98" s="0">
-        <v>14.579999999999998</v>
-      </c>
-      <c r="G98" s="0">
-        <v>12.192674360260911</v>
       </c>
     </row>
     <row r="99">
@@ -7423,16 +7873,19 @@
         <v>9</v>
       </c>
       <c r="D99" s="0">
-        <v>119.58</v>
+        <v>5480</v>
       </c>
       <c r="E99" s="0">
+        <v>200</v>
+      </c>
+      <c r="F99" s="0">
+        <v>3.6496350364963499</v>
+      </c>
+      <c r="G99" s="0">
+        <v>105.59999999999999</v>
+      </c>
+      <c r="H99" s="0">
         <v>98.599999999999994</v>
-      </c>
-      <c r="F99" s="0">
-        <v>20.980000000000004</v>
-      </c>
-      <c r="G99" s="0">
-        <v>17.544739923064061</v>
       </c>
     </row>
     <row r="100">
@@ -7446,16 +7899,19 @@
         <v>8</v>
       </c>
       <c r="D100" s="0">
-        <v>94.379999999999995</v>
+        <v>4420</v>
       </c>
       <c r="E100" s="0">
+        <v>610</v>
+      </c>
+      <c r="F100" s="0">
+        <v>13.800904977375566</v>
+      </c>
+      <c r="G100" s="0">
+        <v>76.200000000000003</v>
+      </c>
+      <c r="H100" s="0">
         <v>62</v>
-      </c>
-      <c r="F100" s="0">
-        <v>32.379999999999995</v>
-      </c>
-      <c r="G100" s="0">
-        <v>34.308116126297939</v>
       </c>
     </row>
     <row r="101">
@@ -7469,16 +7925,19 @@
         <v>9</v>
       </c>
       <c r="D101" s="0">
-        <v>94.379999999999995</v>
+        <v>4420</v>
       </c>
       <c r="E101" s="0">
+        <v>90</v>
+      </c>
+      <c r="F101" s="0">
+        <v>2.0361990950226243</v>
+      </c>
+      <c r="G101" s="0">
+        <v>86.599999999999994</v>
+      </c>
+      <c r="H101" s="0">
         <v>83.599999999999994</v>
-      </c>
-      <c r="F101" s="0">
-        <v>10.780000000000001</v>
-      </c>
-      <c r="G101" s="0">
-        <v>11.421911421911423</v>
       </c>
     </row>
     <row r="102">
@@ -7492,16 +7951,19 @@
         <v>8</v>
       </c>
       <c r="D102" s="0">
-        <v>118.58</v>
+        <v>5730</v>
       </c>
       <c r="E102" s="0">
+        <v>4010</v>
+      </c>
+      <c r="F102" s="0">
+        <v>69.982547993019196</v>
+      </c>
+      <c r="G102" s="0">
+        <v>34.399999999999999</v>
+      </c>
+      <c r="H102" s="0">
         <v>29.199999999999999</v>
-      </c>
-      <c r="F102" s="0">
-        <v>89.379999999999995</v>
-      </c>
-      <c r="G102" s="0">
-        <v>75.375274076572779</v>
       </c>
     </row>
     <row r="103">
@@ -7515,16 +7977,71 @@
         <v>9</v>
       </c>
       <c r="D103" s="0">
-        <v>118.58</v>
+        <v>5730</v>
       </c>
       <c r="E103" s="0">
+        <v>3940</v>
+      </c>
+      <c r="F103" s="0">
+        <v>68.760907504363004</v>
+      </c>
+      <c r="G103" s="0">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="H103" s="0">
         <v>27.399999999999999</v>
       </c>
-      <c r="F103" s="0">
-        <v>91.180000000000007</v>
-      </c>
-      <c r="G103" s="0">
-        <v>76.893236633496372</v>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="0">
+        <v>1816140</v>
+      </c>
+      <c r="E104" s="0">
+        <v>450</v>
+      </c>
+      <c r="F104" s="0">
+        <v>0.024777825498034291</v>
+      </c>
+      <c r="G104" s="0">
+        <v>36313.800000000003</v>
+      </c>
+      <c r="H104" s="0">
+        <v>36303.599999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="0">
+        <v>1816140</v>
+      </c>
+      <c r="E105" s="0">
+        <v>320</v>
+      </c>
+      <c r="F105" s="0">
+        <v>0.017619787020824385</v>
+      </c>
+      <c r="G105" s="0">
+        <v>36316.400000000001</v>
+      </c>
+      <c r="H105" s="0">
+        <v>36309.199999999997</v>
       </c>
     </row>
   </sheetData>

--- a/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
+++ b/mstraczkiewicz/MStraPlots_RT/Detailed_MStra_RT_Results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15572" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15728" uniqueCount="67">
   <si>
     <t>Subject</t>
   </si>
@@ -217,6 +217,9 @@
   <si>
     <t>EvaluableSec</t>
   </si>
+  <si>
+    <t>Hub</t>
+  </si>
 </sst>
 </file>
 
@@ -264,17 +267,17 @@
   <dimension ref="A1:K105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="true"/>
-    <col min="2" max="2" width="9.88671875" customWidth="true"/>
+    <col min="1" max="1" width="6.88671875" customWidth="true"/>
+    <col min="2" max="2" width="8.88671875" customWidth="true"/>
     <col min="3" max="3" width="5.33203125" customWidth="true"/>
     <col min="4" max="4" width="12.5546875" customWidth="true"/>
-    <col min="5" max="5" width="12.5546875" customWidth="true"/>
-    <col min="6" max="6" width="12.5546875" customWidth="true"/>
-    <col min="7" max="7" width="12.5546875" customWidth="true"/>
-    <col min="8" max="8" width="6" customWidth="true"/>
+    <col min="5" max="5" width="2.88671875" customWidth="true"/>
+    <col min="6" max="6" width="8.33203125" customWidth="true"/>
+    <col min="7" max="7" width="5.88671875" customWidth="true"/>
+    <col min="8" max="8" width="3" customWidth="true"/>
     <col min="9" max="9" width="8" customWidth="true"/>
     <col min="10" max="10" width="6" customWidth="true"/>
-    <col min="11" max="11" width="5" customWidth="true"/>
+    <col min="11" max="11" width="3.21875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -314,142 +317,142 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>0.83684838838042186</v>
+        <v>0.3602540834845735</v>
       </c>
       <c r="E2" s="0">
-        <v>0.8423076923076922</v>
+        <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>0.79347826086956519</v>
+        <v>0</v>
       </c>
       <c r="G2" s="0">
-        <v>0.89754098360655743</v>
+        <v>1</v>
       </c>
       <c r="H2" s="0">
-        <v>10950</v>
+        <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>10080</v>
+        <v>7940</v>
       </c>
       <c r="J2" s="0">
-        <v>2850</v>
+        <v>14100</v>
       </c>
       <c r="K2" s="0">
-        <v>1250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>0.84480700358137684</v>
+        <v>0.3693101830126701</v>
       </c>
       <c r="E3" s="0">
-        <v>0.84999999999999998</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>0.80072463768115942</v>
+        <v>0</v>
       </c>
       <c r="G3" s="0">
-        <v>0.90573770491803274</v>
+        <v>1</v>
       </c>
       <c r="H3" s="0">
-        <v>11050</v>
+        <v>0</v>
       </c>
       <c r="I3" s="0">
-        <v>10180</v>
+        <v>7870</v>
       </c>
       <c r="J3" s="0">
-        <v>2750</v>
+        <v>13440</v>
       </c>
       <c r="K3" s="0">
-        <v>1150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>0.97598870056497178</v>
+        <v>0.98328781304376556</v>
       </c>
       <c r="E4" s="0">
-        <v>0.97735748534896105</v>
+        <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>0.97892209178228384</v>
+        <v>0</v>
       </c>
       <c r="G4" s="0">
-        <v>0.97579787234042559</v>
+        <v>1</v>
       </c>
       <c r="H4" s="0">
-        <v>36690</v>
+        <v>0</v>
       </c>
       <c r="I4" s="0">
-        <v>32410</v>
+        <v>1785690</v>
       </c>
       <c r="J4" s="0">
-        <v>790</v>
+        <v>30350</v>
       </c>
       <c r="K4" s="0">
-        <v>910</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>0.97780501089324623</v>
+        <v>0.98421887565685828</v>
       </c>
       <c r="E5" s="0">
-        <v>0.97991868917087588</v>
+        <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>0.97165892988028346</v>
+        <v>0</v>
       </c>
       <c r="G5" s="0">
-        <v>0.98832007952286283</v>
+        <v>1</v>
       </c>
       <c r="H5" s="0">
-        <v>39770</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>32040</v>
+        <v>1786810</v>
       </c>
       <c r="J5" s="0">
-        <v>1160</v>
+        <v>28650</v>
       </c>
       <c r="K5" s="0">
-        <v>470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3967,10 +3970,10 @@
     <col min="4" max="4" width="7.21875" customWidth="true"/>
     <col min="5" max="5" width="8" customWidth="true"/>
     <col min="6" max="6" width="7.5546875" customWidth="true"/>
-    <col min="7" max="7" width="12.5546875" customWidth="true"/>
-    <col min="8" max="8" width="12.5546875" customWidth="true"/>
+    <col min="7" max="7" width="8.33203125" customWidth="true"/>
+    <col min="8" max="8" width="5.88671875" customWidth="true"/>
     <col min="9" max="9" width="12.5546875" customWidth="true"/>
-    <col min="10" max="10" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="2.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4010,31 +4013,31 @@
         <v>9</v>
       </c>
       <c r="B2" s="0">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C2" s="0">
-        <v>304870</v>
+        <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>71650</v>
+        <v>42090</v>
       </c>
       <c r="E2" s="0">
-        <v>2731720</v>
+        <v>1794680</v>
       </c>
       <c r="F2" s="0">
-        <v>36160</v>
+        <v>0</v>
       </c>
       <c r="G2" s="0">
-        <v>0.80970466376288108</v>
+        <v>0</v>
       </c>
       <c r="H2" s="0">
-        <v>0.89396827258598954</v>
+        <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>0.96571364966289275</v>
+        <v>0.97708477381490333</v>
       </c>
       <c r="J2" s="0">
-        <v>0.84975263047871241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4042,31 +4045,31 @@
         <v>8</v>
       </c>
       <c r="B3" s="0">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C3" s="0">
-        <v>279590</v>
+        <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>107530</v>
+        <v>44450</v>
       </c>
       <c r="E3" s="0">
-        <v>2695670</v>
+        <v>1793630</v>
       </c>
       <c r="F3" s="0">
-        <v>43390</v>
+        <v>0</v>
       </c>
       <c r="G3" s="0">
-        <v>0.72223083281669764</v>
+        <v>0</v>
       </c>
       <c r="H3" s="0">
-        <v>0.86565731624249176</v>
+        <v>0</v>
       </c>
       <c r="I3" s="0">
-        <v>0.95172382908213859</v>
+        <v>0.9758171570334262</v>
       </c>
       <c r="J3" s="0">
-        <v>0.78746655400647791</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4078,16 +4081,16 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" customWidth="true"/>
+    <col min="1" max="1" width="7" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="7.33203125" customWidth="true"/>
     <col min="4" max="4" width="7.21875" customWidth="true"/>
-    <col min="5" max="5" width="8" customWidth="true"/>
+    <col min="5" max="5" width="7.6640625" customWidth="true"/>
     <col min="6" max="6" width="7.5546875" customWidth="true"/>
-    <col min="7" max="7" width="12.5546875" customWidth="true"/>
-    <col min="8" max="8" width="12.5546875" customWidth="true"/>
+    <col min="7" max="7" width="8.33203125" customWidth="true"/>
+    <col min="8" max="8" width="5.88671875" customWidth="true"/>
     <col min="9" max="9" width="12.5546875" customWidth="true"/>
-    <col min="10" max="10" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="2.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4124,19 +4127,19 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B2" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="0">
         <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>65110</v>
+        <v>27540</v>
       </c>
       <c r="E2" s="0">
-        <v>1481180</v>
+        <v>15810</v>
       </c>
       <c r="F2" s="0">
         <v>0</v>
@@ -4148,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>0.95789276267711754</v>
+        <v>0.36470588235294116</v>
       </c>
       <c r="J2" s="0">
         <v>0</v>
@@ -4156,19 +4159,19 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B3" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="0">
         <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>250</v>
+        <v>59000</v>
       </c>
       <c r="E3" s="0">
-        <v>30600</v>
+        <v>3572500</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
@@ -4180,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="0">
-        <v>0.99189627228525123</v>
+        <v>0.98375326999862311</v>
       </c>
       <c r="J3" s="0">
         <v>0</v>
@@ -4675,16 +4678,16 @@
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="true"/>
+    <col min="1" max="1" width="6.88671875" customWidth="true"/>
     <col min="2" max="2" width="10.88671875" customWidth="true"/>
     <col min="3" max="3" width="7.33203125" customWidth="true"/>
     <col min="4" max="4" width="7.21875" customWidth="true"/>
-    <col min="5" max="5" width="8" customWidth="true"/>
+    <col min="5" max="5" width="7.6640625" customWidth="true"/>
     <col min="6" max="6" width="7.5546875" customWidth="true"/>
-    <col min="7" max="7" width="12.5546875" customWidth="true"/>
-    <col min="8" max="8" width="12.5546875" customWidth="true"/>
-    <col min="9" max="9" width="12.5546875" customWidth="true"/>
-    <col min="10" max="10" width="12.5546875" customWidth="true"/>
+    <col min="7" max="7" width="8.33203125" customWidth="true"/>
+    <col min="8" max="8" width="5.88671875" customWidth="true"/>
+    <col min="9" max="9" width="8.33203125" customWidth="true"/>
+    <col min="10" max="10" width="2.88671875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4721,34 +4724,34 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B2" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C2" s="0">
-        <v>154410</v>
+        <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>67290</v>
+        <v>86540</v>
       </c>
       <c r="E2" s="0">
-        <v>963850</v>
+        <v>3588310</v>
       </c>
       <c r="F2" s="0">
-        <v>5520</v>
+        <v>0</v>
       </c>
       <c r="G2" s="0">
-        <v>0.69648173207036534</v>
+        <v>0</v>
       </c>
       <c r="H2" s="0">
-        <v>0.96548489964359407</v>
+        <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>0.93887009159831081</v>
+        <v>0.97645073948596539</v>
       </c>
       <c r="J2" s="0">
-        <v>0.80921311217671565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5304,12 +5307,12 @@
   <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="true"/>
-    <col min="2" max="2" width="9.88671875" customWidth="true"/>
+    <col min="1" max="1" width="6.88671875" customWidth="true"/>
+    <col min="2" max="2" width="8.88671875" customWidth="true"/>
     <col min="3" max="3" width="5.33203125" customWidth="true"/>
     <col min="4" max="4" width="13.21875" customWidth="true"/>
     <col min="5" max="5" width="18" customWidth="true"/>
-    <col min="6" max="6" width="13.5546875" customWidth="true"/>
+    <col min="6" max="6" width="12.88671875" customWidth="true"/>
     <col min="7" max="7" width="14.5546875" customWidth="true"/>
     <col min="8" max="8" width="11.5546875" customWidth="true"/>
   </cols>
@@ -5342,16 +5345,16 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="0">
-        <v>25230</v>
+        <v>22150</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -5360,88 +5363,88 @@
         <v>0</v>
       </c>
       <c r="G2" s="0">
-        <v>504.60000000000002</v>
+        <v>443</v>
       </c>
       <c r="H2" s="0">
-        <v>502.60000000000002</v>
+        <v>440.80000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="0">
-        <v>25230</v>
+        <v>22150</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>1.3092550790067718</v>
       </c>
       <c r="G3" s="0">
-        <v>504.60000000000002</v>
+        <v>437.19999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>502.60000000000002</v>
+        <v>426.19999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="0">
-        <v>73750</v>
+        <v>1816140</v>
       </c>
       <c r="E4" s="0">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>0.8677966101694915</v>
+        <v>0</v>
       </c>
       <c r="G4" s="0">
-        <v>1462.2</v>
+        <v>36322.800000000003</v>
       </c>
       <c r="H4" s="0">
-        <v>1416</v>
+        <v>36320.800000000003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="0">
-        <v>73750</v>
+        <v>1816140</v>
       </c>
       <c r="E5" s="0">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="F5" s="0">
-        <v>0.14915254237288136</v>
+        <v>0.017619787020824385</v>
       </c>
       <c r="G5" s="0">
-        <v>1472.8</v>
+        <v>36316.400000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>1468.8</v>
+        <v>36309.199999999997</v>
       </c>
     </row>
     <row r="6">
